--- a/data/rka.xlsx
+++ b/data/rka.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x15 xr xr6 xr10">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\76193\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A842523A-B681-4FB6-8DE4-C6B259D66125}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:40009_{B926CE83-FEB6-4418-BD8D-37ADC92BA2FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456"/>
   </bookViews>
   <sheets>
-    <sheet name="20260907 SAP ZFM01" sheetId="1" r:id="rId1"/>
+    <sheet name="20260911 SAP ZFM01" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
   <extLst>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1079" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1093" uniqueCount="131">
   <si>
     <t>Funds Center/Commitment Item</t>
   </si>
@@ -423,7 +423,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -560,7 +560,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -740,6 +740,12 @@
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="10">
     <border>
@@ -901,8 +907,9 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1257,7 +1264,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H564"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -1301,22 +1308,22 @@
         <v>8</v>
       </c>
       <c r="B2">
-        <v>109317656175</v>
+        <v>108940456175</v>
       </c>
       <c r="C2">
-        <v>109317656175</v>
+        <v>108940456175</v>
       </c>
       <c r="D2">
-        <v>99268647251</v>
+        <v>94287482435</v>
       </c>
       <c r="E2">
-        <v>8267348916</v>
+        <v>13248513732</v>
       </c>
       <c r="F2">
         <v>107535996167</v>
       </c>
       <c r="G2">
-        <v>1781660008</v>
+        <v>1404460008</v>
       </c>
       <c r="H2" t="s">
         <v>9</v>
@@ -1463,10 +1470,10 @@
         <v>3726972261</v>
       </c>
       <c r="D8">
-        <v>3622271715</v>
+        <v>3398631820</v>
       </c>
       <c r="E8">
-        <v>77164840</v>
+        <v>300804735</v>
       </c>
       <c r="F8">
         <v>3699436555</v>
@@ -1489,10 +1496,10 @@
         <v>62772333130</v>
       </c>
       <c r="D9">
-        <v>54589308663</v>
+        <v>37626079655</v>
       </c>
       <c r="E9">
-        <v>8154071362</v>
+        <v>25117300370</v>
       </c>
       <c r="F9">
         <v>62743380025</v>
@@ -1509,22 +1516,22 @@
         <v>17</v>
       </c>
       <c r="B10">
-        <v>579317296</v>
+        <v>490324430</v>
       </c>
       <c r="C10">
-        <v>579317296</v>
+        <v>490324430</v>
       </c>
       <c r="D10">
-        <v>197598375</v>
+        <v>148038375</v>
       </c>
       <c r="E10">
-        <v>192718055</v>
+        <v>242278055</v>
       </c>
       <c r="F10">
         <v>390316430</v>
       </c>
       <c r="G10">
-        <v>189000866</v>
+        <v>100008000</v>
       </c>
       <c r="H10" t="s">
         <v>9</v>
@@ -1691,7 +1698,7 @@
         <v>24</v>
       </c>
       <c r="B17">
-        <v>1600000000</v>
+        <v>1200000000</v>
       </c>
       <c r="C17">
         <v>1200000000</v>
@@ -1708,8 +1715,8 @@
       <c r="G17">
         <v>1015199000</v>
       </c>
-      <c r="H17">
-        <v>400000000</v>
+      <c r="H17" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.3">
@@ -1717,10 +1724,10 @@
         <v>25</v>
       </c>
       <c r="B18">
-        <v>454442400</v>
+        <v>391942400</v>
       </c>
       <c r="C18">
-        <v>329442400</v>
+        <v>391942400</v>
       </c>
       <c r="D18">
         <v>0</v>
@@ -1732,10 +1739,10 @@
         <v>20986164</v>
       </c>
       <c r="G18">
-        <v>308456236</v>
-      </c>
-      <c r="H18">
-        <v>125000000</v>
+        <v>370956236</v>
+      </c>
+      <c r="H18" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.3">
@@ -1743,10 +1750,10 @@
         <v>26</v>
       </c>
       <c r="B19">
-        <v>4500000000</v>
+        <v>3894602130</v>
       </c>
       <c r="C19">
-        <v>4500000000</v>
+        <v>3894602130</v>
       </c>
       <c r="D19">
         <v>346244860</v>
@@ -1758,7 +1765,7 @@
         <v>2910182489</v>
       </c>
       <c r="G19">
-        <v>1589817511</v>
+        <v>984419641</v>
       </c>
       <c r="H19" t="s">
         <v>9</v>
@@ -1769,10 +1776,10 @@
         <v>27</v>
       </c>
       <c r="B20">
-        <v>1483013800</v>
+        <v>1000698000</v>
       </c>
       <c r="C20">
-        <v>1108013800</v>
+        <v>1000698000</v>
       </c>
       <c r="D20">
         <v>0</v>
@@ -1784,10 +1791,10 @@
         <v>406948000</v>
       </c>
       <c r="G20">
-        <v>701065800</v>
-      </c>
-      <c r="H20">
-        <v>375000000</v>
+        <v>593750000</v>
+      </c>
+      <c r="H20" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.3">
@@ -1795,25 +1802,25 @@
         <v>28</v>
       </c>
       <c r="B21">
-        <v>702885000</v>
+        <v>406635000</v>
       </c>
       <c r="C21">
-        <v>510385000</v>
+        <v>406635000</v>
       </c>
       <c r="D21">
-        <v>75773600</v>
+        <v>77481217</v>
       </c>
       <c r="E21">
-        <v>84557037</v>
+        <v>89696662</v>
       </c>
       <c r="F21">
-        <v>160330637</v>
+        <v>167177879</v>
       </c>
       <c r="G21">
-        <v>350054363</v>
-      </c>
-      <c r="H21">
-        <v>192500000</v>
+        <v>239457121</v>
+      </c>
+      <c r="H21" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.3">
@@ -1821,10 +1828,10 @@
         <v>29</v>
       </c>
       <c r="B22">
-        <v>156000000</v>
+        <v>146000000</v>
       </c>
       <c r="C22">
-        <v>156000000</v>
+        <v>146000000</v>
       </c>
       <c r="D22">
         <v>0</v>
@@ -1836,7 +1843,7 @@
         <v>103000000</v>
       </c>
       <c r="G22">
-        <v>53000000</v>
+        <v>43000000</v>
       </c>
       <c r="H22" t="s">
         <v>9</v>
@@ -1847,25 +1854,25 @@
         <v>30</v>
       </c>
       <c r="B23">
-        <v>747597314</v>
+        <v>685097314</v>
       </c>
       <c r="C23">
-        <v>622597314</v>
+        <v>685097314</v>
       </c>
       <c r="D23">
-        <v>507783920</v>
+        <v>551635520</v>
       </c>
       <c r="E23">
         <v>114645294</v>
       </c>
       <c r="F23">
-        <v>622429214</v>
+        <v>666280814</v>
       </c>
       <c r="G23">
-        <v>168100</v>
-      </c>
-      <c r="H23">
-        <v>125000000</v>
+        <v>18816500</v>
+      </c>
+      <c r="H23" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.3">
@@ -1873,7 +1880,7 @@
         <v>31</v>
       </c>
       <c r="B24">
-        <v>800000000</v>
+        <v>600000000</v>
       </c>
       <c r="C24">
         <v>600000000</v>
@@ -1890,8 +1897,8 @@
       <c r="G24">
         <v>353609968</v>
       </c>
-      <c r="H24">
-        <v>200000000</v>
+      <c r="H24" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.3">
@@ -1899,25 +1906,25 @@
         <v>32</v>
       </c>
       <c r="B25">
-        <v>2312674754</v>
+        <v>1691277133</v>
       </c>
       <c r="C25">
-        <v>1687674754</v>
+        <v>1691277133</v>
       </c>
       <c r="D25">
         <v>215556103</v>
       </c>
       <c r="E25">
-        <v>1066286941</v>
+        <v>1088880691</v>
       </c>
       <c r="F25">
-        <v>1281843044</v>
+        <v>1304436794</v>
       </c>
       <c r="G25">
-        <v>405831710</v>
-      </c>
-      <c r="H25">
-        <v>625000000</v>
+        <v>386840339</v>
+      </c>
+      <c r="H25" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.3">
@@ -1925,10 +1932,10 @@
         <v>33</v>
       </c>
       <c r="B26">
-        <v>220000000</v>
+        <v>128132588</v>
       </c>
       <c r="C26">
-        <v>220000000</v>
+        <v>128132588</v>
       </c>
       <c r="D26">
         <v>0</v>
@@ -1940,7 +1947,7 @@
         <v>28132588</v>
       </c>
       <c r="G26">
-        <v>191867412</v>
+        <v>100000000</v>
       </c>
       <c r="H26" t="s">
         <v>9</v>
@@ -1986,13 +1993,13 @@
         <v>0</v>
       </c>
       <c r="E28">
-        <v>2833990776</v>
+        <v>2834764214</v>
       </c>
       <c r="F28">
-        <v>2833990776</v>
+        <v>2834764214</v>
       </c>
       <c r="G28">
-        <v>622623428</v>
+        <v>621849990</v>
       </c>
       <c r="H28" t="s">
         <v>9</v>
@@ -2038,13 +2045,13 @@
         <v>0</v>
       </c>
       <c r="E30">
-        <v>3661908187</v>
+        <v>3669312187</v>
       </c>
       <c r="F30">
-        <v>3661908187</v>
+        <v>3669312187</v>
       </c>
       <c r="G30">
-        <v>416361848</v>
+        <v>408957848</v>
       </c>
       <c r="H30" t="s">
         <v>9</v>
@@ -2142,13 +2149,13 @@
         <v>0</v>
       </c>
       <c r="E34">
-        <v>10058200960</v>
+        <v>10062254960</v>
       </c>
       <c r="F34">
-        <v>10058200960</v>
+        <v>10062254960</v>
       </c>
       <c r="G34">
-        <v>3911865086</v>
+        <v>3907811086</v>
       </c>
       <c r="H34" t="s">
         <v>9</v>
@@ -2263,10 +2270,10 @@
         <v>46</v>
       </c>
       <c r="B39">
-        <v>752402686</v>
+        <v>274300566</v>
       </c>
       <c r="C39">
-        <v>502402686</v>
+        <v>274300566</v>
       </c>
       <c r="D39">
         <v>0</v>
@@ -2278,10 +2285,10 @@
         <v>8807378</v>
       </c>
       <c r="G39">
-        <v>493595308</v>
-      </c>
-      <c r="H39">
-        <v>250000000</v>
+        <v>265493188</v>
+      </c>
+      <c r="H39" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.3">
@@ -2289,10 +2296,10 @@
         <v>47</v>
       </c>
       <c r="B40">
-        <v>500000000</v>
+        <v>437500000</v>
       </c>
       <c r="C40">
-        <v>375000000</v>
+        <v>437500000</v>
       </c>
       <c r="D40">
         <v>0</v>
@@ -2304,10 +2311,10 @@
         <v>15794000</v>
       </c>
       <c r="G40">
-        <v>359206000</v>
-      </c>
-      <c r="H40">
-        <v>125000000</v>
+        <v>421706000</v>
+      </c>
+      <c r="H40" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.3">
@@ -2341,25 +2348,25 @@
         <v>49</v>
       </c>
       <c r="B42">
-        <v>350773419540</v>
+        <v>346934395851</v>
       </c>
       <c r="C42">
-        <v>348355919540</v>
+        <v>346934395851</v>
       </c>
       <c r="D42">
-        <v>237558913890</v>
+        <v>215386879388</v>
       </c>
       <c r="E42">
-        <v>94119402504</v>
+        <v>116376961036</v>
       </c>
       <c r="F42">
-        <v>331678316394</v>
+        <v>331763840424</v>
       </c>
       <c r="G42">
-        <v>16677603146</v>
-      </c>
-      <c r="H42">
-        <v>2417500000</v>
+        <v>15170555427</v>
+      </c>
+      <c r="H42" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.3">
@@ -2373,16 +2380,16 @@
         <v>26681487101</v>
       </c>
       <c r="D43">
-        <v>17366902401</v>
+        <v>17343493202</v>
       </c>
       <c r="E43">
         <v>9295238000</v>
       </c>
       <c r="F43">
-        <v>26662140401</v>
+        <v>26638731202</v>
       </c>
       <c r="G43">
-        <v>19346700</v>
+        <v>42755899</v>
       </c>
       <c r="H43" t="s">
         <v>9</v>
@@ -2607,16 +2614,16 @@
         <v>400000000</v>
       </c>
       <c r="D52">
-        <v>399980984</v>
+        <v>391600000</v>
       </c>
       <c r="E52">
         <v>0</v>
       </c>
       <c r="F52">
-        <v>399980984</v>
+        <v>391600000</v>
       </c>
       <c r="G52">
-        <v>19016</v>
+        <v>8400000</v>
       </c>
       <c r="H52" t="s">
         <v>9</v>
@@ -2659,16 +2666,16 @@
         <v>6000000000</v>
       </c>
       <c r="D54">
-        <v>5252888358</v>
+        <v>5229810269</v>
       </c>
       <c r="E54">
         <v>541614545</v>
       </c>
       <c r="F54">
-        <v>5794502903</v>
+        <v>5771424814</v>
       </c>
       <c r="G54">
-        <v>205497097</v>
+        <v>228575186</v>
       </c>
       <c r="H54" t="s">
         <v>9</v>
@@ -2685,16 +2692,16 @@
         <v>4260000000</v>
       </c>
       <c r="D55">
-        <v>1541830234</v>
+        <v>1178332074</v>
       </c>
       <c r="E55">
-        <v>2204642978</v>
+        <v>2608784178</v>
       </c>
       <c r="F55">
-        <v>3746473212</v>
+        <v>3787116252</v>
       </c>
       <c r="G55">
-        <v>513526788</v>
+        <v>472883748</v>
       </c>
       <c r="H55" t="s">
         <v>9</v>
@@ -2763,10 +2770,10 @@
         <v>250000000</v>
       </c>
       <c r="D58">
-        <v>75748702</v>
+        <v>0</v>
       </c>
       <c r="E58">
-        <v>73804960</v>
+        <v>149553662</v>
       </c>
       <c r="F58">
         <v>149553662</v>
@@ -2815,16 +2822,16 @@
         <v>2620000000</v>
       </c>
       <c r="D60">
-        <v>704306959</v>
+        <v>652442541</v>
       </c>
       <c r="E60">
-        <v>762786867</v>
+        <v>815038867</v>
       </c>
       <c r="F60">
-        <v>1467093826</v>
+        <v>1467481408</v>
       </c>
       <c r="G60">
-        <v>1152906174</v>
+        <v>1152518592</v>
       </c>
       <c r="H60" t="s">
         <v>9</v>
@@ -2893,16 +2900,16 @@
         <v>2500000000</v>
       </c>
       <c r="D63">
-        <v>2007946000</v>
+        <v>1948112000</v>
       </c>
       <c r="E63">
-        <v>333260100</v>
+        <v>383110100</v>
       </c>
       <c r="F63">
-        <v>2341206100</v>
+        <v>2331222100</v>
       </c>
       <c r="G63">
-        <v>158793900</v>
+        <v>168777900</v>
       </c>
       <c r="H63" t="s">
         <v>9</v>
@@ -2945,16 +2952,16 @@
         <v>180000150</v>
       </c>
       <c r="D65">
-        <v>9176000</v>
+        <v>31856000</v>
       </c>
       <c r="E65">
         <v>139677600</v>
       </c>
       <c r="F65">
-        <v>148853600</v>
+        <v>171533600</v>
       </c>
       <c r="G65">
-        <v>31146550</v>
+        <v>8466550</v>
       </c>
       <c r="H65" t="s">
         <v>9</v>
@@ -3130,13 +3137,13 @@
         <v>46676000</v>
       </c>
       <c r="E72">
-        <v>253203000</v>
+        <v>258971750</v>
       </c>
       <c r="F72">
-        <v>299879000</v>
+        <v>305647750</v>
       </c>
       <c r="G72">
-        <v>54346000</v>
+        <v>48577250</v>
       </c>
       <c r="H72">
         <v>118075000</v>
@@ -3208,13 +3215,13 @@
         <v>0</v>
       </c>
       <c r="E75">
-        <v>16580866780</v>
+        <v>16581026155</v>
       </c>
       <c r="F75">
-        <v>16580866780</v>
+        <v>16581026155</v>
       </c>
       <c r="G75">
-        <v>6350740449</v>
+        <v>6350581074</v>
       </c>
       <c r="H75" t="s">
         <v>9</v>
@@ -3257,10 +3264,10 @@
         <v>20967421530</v>
       </c>
       <c r="D77">
-        <v>62448139</v>
+        <v>9566218</v>
       </c>
       <c r="E77">
-        <v>17994131226</v>
+        <v>18047013147</v>
       </c>
       <c r="F77">
         <v>18056579365</v>
@@ -3361,10 +3368,10 @@
         <v>1937118528</v>
       </c>
       <c r="D81">
-        <v>1099501</v>
+        <v>165657</v>
       </c>
       <c r="E81">
-        <v>1889267075</v>
+        <v>1890200919</v>
       </c>
       <c r="F81">
         <v>1890366576</v>
@@ -3439,16 +3446,16 @@
         <v>110881210191</v>
       </c>
       <c r="D84">
-        <v>36852239634</v>
+        <v>36215290317</v>
       </c>
       <c r="E84">
-        <v>57297214607</v>
+        <v>57938950399</v>
       </c>
       <c r="F84">
-        <v>94149454241</v>
+        <v>94154240716</v>
       </c>
       <c r="G84">
-        <v>16731755950</v>
+        <v>16726969475</v>
       </c>
       <c r="H84">
         <v>671501500</v>
@@ -3569,16 +3576,16 @@
         <v>30639775739</v>
       </c>
       <c r="D89">
-        <v>14015063637</v>
+        <v>16314020110</v>
       </c>
       <c r="E89">
         <v>11956954821</v>
       </c>
       <c r="F89">
-        <v>25972018458</v>
+        <v>28270974931</v>
       </c>
       <c r="G89">
-        <v>4667757281</v>
+        <v>2368800808</v>
       </c>
       <c r="H89" t="s">
         <v>9</v>
@@ -3699,16 +3706,16 @@
         <v>2796520000</v>
       </c>
       <c r="D94">
-        <v>761898804</v>
+        <v>768155804</v>
       </c>
       <c r="E94">
         <v>2028357617</v>
       </c>
       <c r="F94">
-        <v>2790256421</v>
+        <v>2796513421</v>
       </c>
       <c r="G94">
-        <v>6263579</v>
+        <v>6579</v>
       </c>
       <c r="H94" t="s">
         <v>9</v>
@@ -3803,16 +3810,16 @@
         <v>289155000</v>
       </c>
       <c r="D98">
-        <v>20359000</v>
+        <v>38159000</v>
       </c>
       <c r="E98">
         <v>57100000</v>
       </c>
       <c r="F98">
-        <v>77459000</v>
+        <v>95259000</v>
       </c>
       <c r="G98">
-        <v>211696000</v>
+        <v>193896000</v>
       </c>
       <c r="H98" t="s">
         <v>9</v>
@@ -3829,16 +3836,16 @@
         <v>360000000</v>
       </c>
       <c r="D99">
-        <v>105051976</v>
+        <v>141522576</v>
       </c>
       <c r="E99">
         <v>204218000</v>
       </c>
       <c r="F99">
-        <v>309269976</v>
+        <v>345740576</v>
       </c>
       <c r="G99">
-        <v>50730024</v>
+        <v>14259424</v>
       </c>
       <c r="H99" t="s">
         <v>9</v>
@@ -3855,16 +3862,16 @@
         <v>1710494400</v>
       </c>
       <c r="D100">
-        <v>598275580</v>
+        <v>484281260</v>
       </c>
       <c r="E100">
         <v>1099212506</v>
       </c>
       <c r="F100">
-        <v>1697488086</v>
+        <v>1583493766</v>
       </c>
       <c r="G100">
-        <v>13006314</v>
+        <v>127000634</v>
       </c>
       <c r="H100" t="s">
         <v>9</v>
@@ -3907,16 +3914,16 @@
         <v>394475000</v>
       </c>
       <c r="D102">
-        <v>119148000</v>
+        <v>70510900</v>
       </c>
       <c r="E102">
         <v>45427850</v>
       </c>
       <c r="F102">
-        <v>164575850</v>
+        <v>115938750</v>
       </c>
       <c r="G102">
-        <v>229899150</v>
+        <v>278536250</v>
       </c>
       <c r="H102">
         <v>139825000</v>
@@ -3933,16 +3940,16 @@
         <v>255960000</v>
       </c>
       <c r="D103">
-        <v>65004150</v>
+        <v>60960230</v>
       </c>
       <c r="E103">
         <v>174999400</v>
       </c>
       <c r="F103">
-        <v>240003550</v>
+        <v>235959630</v>
       </c>
       <c r="G103">
-        <v>15956450</v>
+        <v>20000370</v>
       </c>
       <c r="H103">
         <v>85320000</v>
@@ -3985,16 +3992,16 @@
         <v>291600000</v>
       </c>
       <c r="D105">
-        <v>220821700</v>
+        <v>243281700</v>
       </c>
       <c r="E105">
         <v>28079000</v>
       </c>
       <c r="F105">
-        <v>248900700</v>
+        <v>271360700</v>
       </c>
       <c r="G105">
-        <v>42699300</v>
+        <v>20239300</v>
       </c>
       <c r="H105">
         <v>97200000</v>
@@ -4040,13 +4047,13 @@
         <v>0</v>
       </c>
       <c r="E107">
-        <v>291366068</v>
+        <v>292803568</v>
       </c>
       <c r="F107">
-        <v>291366068</v>
+        <v>292803568</v>
       </c>
       <c r="G107">
-        <v>3691432</v>
+        <v>2253932</v>
       </c>
       <c r="H107">
         <v>98352500</v>
@@ -4170,13 +4177,13 @@
         <v>0</v>
       </c>
       <c r="E112">
-        <v>11992041949</v>
+        <v>11992098199</v>
       </c>
       <c r="F112">
-        <v>11992041949</v>
+        <v>11992098199</v>
       </c>
       <c r="G112">
-        <v>4231602904</v>
+        <v>4231546654</v>
       </c>
       <c r="H112" t="s">
         <v>9</v>
@@ -4219,10 +4226,10 @@
         <v>14498179948</v>
       </c>
       <c r="D114">
-        <v>54284729</v>
+        <v>9868545</v>
       </c>
       <c r="E114">
-        <v>13036981539</v>
+        <v>13081397723</v>
       </c>
       <c r="F114">
         <v>13091266268</v>
@@ -4323,10 +4330,10 @@
         <v>1928660874</v>
       </c>
       <c r="D118">
-        <v>194430</v>
+        <v>0</v>
       </c>
       <c r="E118">
-        <v>1493780716</v>
+        <v>1493975146</v>
       </c>
       <c r="F118">
         <v>1493975146</v>
@@ -4401,16 +4408,16 @@
         <v>81693644736</v>
       </c>
       <c r="D121">
-        <v>18868718909</v>
+        <v>21039377028</v>
       </c>
       <c r="E121">
-        <v>50086023534</v>
+        <v>50132127898</v>
       </c>
       <c r="F121">
-        <v>68954742443</v>
+        <v>71171504926</v>
       </c>
       <c r="G121">
-        <v>12738902293</v>
+        <v>10522139810</v>
       </c>
       <c r="H121">
         <v>475697500</v>
@@ -4453,16 +4460,16 @@
         <v>1494332364</v>
       </c>
       <c r="D123">
-        <v>491000000</v>
+        <v>985946819</v>
       </c>
       <c r="E123">
         <v>127583711</v>
       </c>
       <c r="F123">
-        <v>618583711</v>
+        <v>1113530530</v>
       </c>
       <c r="G123">
-        <v>875748653</v>
+        <v>380801834</v>
       </c>
       <c r="H123" t="s">
         <v>9</v>
@@ -4531,16 +4538,16 @@
         <v>1200699000</v>
       </c>
       <c r="D126">
-        <v>668247328</v>
+        <v>662998053</v>
       </c>
       <c r="E126">
         <v>81220975</v>
       </c>
       <c r="F126">
-        <v>749468303</v>
+        <v>744219028</v>
       </c>
       <c r="G126">
-        <v>451230697</v>
+        <v>456479972</v>
       </c>
       <c r="H126" t="s">
         <v>9</v>
@@ -4557,10 +4564,10 @@
         <v>818532000</v>
       </c>
       <c r="D127">
-        <v>494768983</v>
+        <v>333965683</v>
       </c>
       <c r="E127">
-        <v>287074500</v>
+        <v>447877800</v>
       </c>
       <c r="F127">
         <v>781843483</v>
@@ -4583,16 +4590,16 @@
         <v>4824864000</v>
       </c>
       <c r="D128">
-        <v>0</v>
+        <v>1685220</v>
       </c>
       <c r="E128">
         <v>4612652831</v>
       </c>
       <c r="F128">
-        <v>4612652831</v>
+        <v>4614338051</v>
       </c>
       <c r="G128">
-        <v>212211169</v>
+        <v>210525949</v>
       </c>
       <c r="H128" t="s">
         <v>9</v>
@@ -4609,16 +4616,16 @@
         <v>1665000000</v>
       </c>
       <c r="D129">
-        <v>144401157</v>
+        <v>212643952</v>
       </c>
       <c r="E129">
         <v>713065052</v>
       </c>
       <c r="F129">
-        <v>857466209</v>
+        <v>925709004</v>
       </c>
       <c r="G129">
-        <v>807533791</v>
+        <v>739290996</v>
       </c>
       <c r="H129" t="s">
         <v>9</v>
@@ -4788,7 +4795,7 @@
         <v>705000000</v>
       </c>
       <c r="C136">
-        <v>528750000</v>
+        <v>593920000</v>
       </c>
       <c r="D136">
         <v>0</v>
@@ -4800,10 +4807,10 @@
         <v>491500000</v>
       </c>
       <c r="G136">
-        <v>37250000</v>
+        <v>102420000</v>
       </c>
       <c r="H136">
-        <v>176250000</v>
+        <v>111080000</v>
       </c>
     </row>
     <row r="137" spans="1:8" x14ac:dyDescent="0.3">
@@ -4817,16 +4824,16 @@
         <v>118875000</v>
       </c>
       <c r="D137">
-        <v>3172500</v>
+        <v>14682500</v>
       </c>
       <c r="E137">
         <v>62015400</v>
       </c>
       <c r="F137">
-        <v>65187900</v>
+        <v>76697900</v>
       </c>
       <c r="G137">
-        <v>53687100</v>
+        <v>42177100</v>
       </c>
       <c r="H137" t="s">
         <v>9</v>
@@ -4866,22 +4873,22 @@
         <v>100000000</v>
       </c>
       <c r="C139">
-        <v>75000000</v>
+        <v>100000000</v>
       </c>
       <c r="D139">
-        <v>0</v>
+        <v>7999750</v>
       </c>
       <c r="E139">
         <v>74403889</v>
       </c>
       <c r="F139">
-        <v>74403889</v>
+        <v>82403639</v>
       </c>
       <c r="G139">
-        <v>596111</v>
-      </c>
-      <c r="H139">
-        <v>25000000</v>
+        <v>17596361</v>
+      </c>
+      <c r="H139" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="140" spans="1:8" x14ac:dyDescent="0.3">
@@ -4892,22 +4899,22 @@
         <v>354600000</v>
       </c>
       <c r="C140">
-        <v>265950000</v>
+        <v>354600000</v>
       </c>
       <c r="D140">
-        <v>11555000</v>
+        <v>4357100</v>
       </c>
       <c r="E140">
-        <v>209966600</v>
+        <v>220966600</v>
       </c>
       <c r="F140">
-        <v>221521600</v>
+        <v>225323700</v>
       </c>
       <c r="G140">
-        <v>44428400</v>
-      </c>
-      <c r="H140">
-        <v>88650000</v>
+        <v>129276300</v>
+      </c>
+      <c r="H140" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="141" spans="1:8" x14ac:dyDescent="0.3">
@@ -4944,7 +4951,7 @@
         <v>271400000</v>
       </c>
       <c r="C142">
-        <v>203550000</v>
+        <v>271400000</v>
       </c>
       <c r="D142">
         <v>2380000</v>
@@ -4956,10 +4963,10 @@
         <v>179583982</v>
       </c>
       <c r="G142">
-        <v>23966018</v>
-      </c>
-      <c r="H142">
-        <v>67850000</v>
+        <v>91816018</v>
+      </c>
+      <c r="H142" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="143" spans="1:8" x14ac:dyDescent="0.3">
@@ -4970,22 +4977,22 @@
         <v>213320000</v>
       </c>
       <c r="C143">
-        <v>159990000</v>
+        <v>213320000</v>
       </c>
       <c r="D143">
         <v>0</v>
       </c>
       <c r="E143">
-        <v>152110750</v>
+        <v>152660750</v>
       </c>
       <c r="F143">
-        <v>152110750</v>
+        <v>152660750</v>
       </c>
       <c r="G143">
-        <v>7879250</v>
-      </c>
-      <c r="H143">
-        <v>53330000</v>
+        <v>60659250</v>
+      </c>
+      <c r="H143" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="144" spans="1:8" x14ac:dyDescent="0.3">
@@ -5054,13 +5061,13 @@
         <v>0</v>
       </c>
       <c r="E146">
-        <v>7120196100</v>
+        <v>7120218600</v>
       </c>
       <c r="F146">
-        <v>7120196100</v>
+        <v>7120218600</v>
       </c>
       <c r="G146">
-        <v>2828897983</v>
+        <v>2828875483</v>
       </c>
       <c r="H146" t="s">
         <v>9</v>
@@ -5106,13 +5113,13 @@
         <v>0</v>
       </c>
       <c r="E148">
-        <v>8371186419</v>
+        <v>8399118521</v>
       </c>
       <c r="F148">
-        <v>8371186419</v>
+        <v>8399118521</v>
       </c>
       <c r="G148">
-        <v>1398663472</v>
+        <v>1370731370</v>
       </c>
       <c r="H148" t="s">
         <v>9</v>
@@ -5210,13 +5217,13 @@
         <v>0</v>
       </c>
       <c r="E152">
-        <v>1071715901</v>
+        <v>1073128014</v>
       </c>
       <c r="F152">
-        <v>1071715901</v>
+        <v>1073128014</v>
       </c>
       <c r="G152">
-        <v>258601638</v>
+        <v>257189525</v>
       </c>
       <c r="H152" t="s">
         <v>9</v>
@@ -5282,22 +5289,22 @@
         <v>52584136175</v>
       </c>
       <c r="C155">
-        <v>52173056175</v>
+        <v>52473056175</v>
       </c>
       <c r="D155">
-        <v>9723132060</v>
+        <v>10134266169</v>
       </c>
       <c r="E155">
-        <v>32526968870</v>
+        <v>32728688885</v>
       </c>
       <c r="F155">
-        <v>42250100930</v>
+        <v>42862955054</v>
       </c>
       <c r="G155">
-        <v>9922955245</v>
+        <v>9610101121</v>
       </c>
       <c r="H155">
-        <v>411080000</v>
+        <v>111080000</v>
       </c>
     </row>
     <row r="156" spans="1:8" x14ac:dyDescent="0.3">
@@ -5597,16 +5604,16 @@
         <v>500000000</v>
       </c>
       <c r="D167">
-        <v>54664725</v>
+        <v>0</v>
       </c>
       <c r="E167">
         <v>185788488</v>
       </c>
       <c r="F167">
-        <v>240453213</v>
+        <v>185788488</v>
       </c>
       <c r="G167">
-        <v>259546787</v>
+        <v>314211512</v>
       </c>
       <c r="H167" t="s">
         <v>9</v>
@@ -5649,10 +5656,10 @@
         <v>867942000</v>
       </c>
       <c r="D169">
-        <v>642565410</v>
+        <v>235899000</v>
       </c>
       <c r="E169">
-        <v>0</v>
+        <v>406666410</v>
       </c>
       <c r="F169">
         <v>642565410</v>
@@ -5675,10 +5682,10 @@
         <v>187500000</v>
       </c>
       <c r="D170">
+        <v>0</v>
+      </c>
+      <c r="E170">
         <v>142100000</v>
-      </c>
-      <c r="E170">
-        <v>0</v>
       </c>
       <c r="F170">
         <v>142100000</v>
@@ -5805,16 +5812,16 @@
         <v>595150000</v>
       </c>
       <c r="D175">
-        <v>73181400</v>
+        <v>70019500</v>
       </c>
       <c r="E175">
         <v>451500394</v>
       </c>
       <c r="F175">
-        <v>524681794</v>
+        <v>521519894</v>
       </c>
       <c r="G175">
-        <v>70468206</v>
+        <v>73630106</v>
       </c>
       <c r="H175">
         <v>136250000</v>
@@ -5857,16 +5864,16 @@
         <v>253250000</v>
       </c>
       <c r="D177">
-        <v>49900000</v>
+        <v>104564725</v>
       </c>
       <c r="E177">
         <v>104678200</v>
       </c>
       <c r="F177">
-        <v>154578200</v>
+        <v>209242925</v>
       </c>
       <c r="G177">
-        <v>98671800</v>
+        <v>44007075</v>
       </c>
       <c r="H177">
         <v>146550000</v>
@@ -5912,13 +5919,13 @@
         <v>0</v>
       </c>
       <c r="E179">
-        <v>115634250</v>
+        <v>127765250</v>
       </c>
       <c r="F179">
-        <v>115634250</v>
+        <v>127765250</v>
       </c>
       <c r="G179">
-        <v>46667250</v>
+        <v>34536250</v>
       </c>
       <c r="H179">
         <v>54100500</v>
@@ -5964,13 +5971,13 @@
         <v>0</v>
       </c>
       <c r="E181">
-        <v>5304783338</v>
+        <v>5305580738</v>
       </c>
       <c r="F181">
-        <v>5304783338</v>
+        <v>5305580738</v>
       </c>
       <c r="G181">
-        <v>2199940040</v>
+        <v>2199142640</v>
       </c>
       <c r="H181" t="s">
         <v>9</v>
@@ -6169,16 +6176,16 @@
         <v>46375593027</v>
       </c>
       <c r="D189">
-        <v>10089378160</v>
+        <v>9537449850</v>
       </c>
       <c r="E189">
-        <v>28698856885</v>
+        <v>29260551695</v>
       </c>
       <c r="F189">
-        <v>38788235045</v>
+        <v>38798001545</v>
       </c>
       <c r="G189">
-        <v>7587357982</v>
+        <v>7577591482</v>
       </c>
       <c r="H189">
         <v>449400500</v>
@@ -6481,10 +6488,10 @@
         <v>1862650000</v>
       </c>
       <c r="D201">
-        <v>345529067</v>
+        <v>300009067</v>
       </c>
       <c r="E201">
-        <v>1370639706</v>
+        <v>1416159706</v>
       </c>
       <c r="F201">
         <v>1716168773</v>
@@ -6585,16 +6592,16 @@
         <v>4350172680</v>
       </c>
       <c r="D205">
-        <v>3109885000</v>
+        <v>2986575000</v>
       </c>
       <c r="E205">
         <v>1236281200</v>
       </c>
       <c r="F205">
-        <v>4346166200</v>
+        <v>4222856200</v>
       </c>
       <c r="G205">
-        <v>4006480</v>
+        <v>127316480</v>
       </c>
       <c r="H205" t="s">
         <v>9</v>
@@ -6611,16 +6618,16 @@
         <v>40000000</v>
       </c>
       <c r="D206">
-        <v>0</v>
+        <v>7640000</v>
       </c>
       <c r="E206">
         <v>13010000</v>
       </c>
       <c r="F206">
-        <v>13010000</v>
+        <v>20650000</v>
       </c>
       <c r="G206">
-        <v>26990000</v>
+        <v>19350000</v>
       </c>
       <c r="H206" t="s">
         <v>9</v>
@@ -6761,25 +6768,25 @@
         <v>27</v>
       </c>
       <c r="B212">
-        <v>130000000</v>
+        <v>113750000</v>
       </c>
       <c r="C212">
-        <v>97500000</v>
+        <v>113750000</v>
       </c>
       <c r="D212">
-        <v>6800000</v>
+        <v>3400000</v>
       </c>
       <c r="E212">
-        <v>71071407</v>
+        <v>74218210</v>
       </c>
       <c r="F212">
-        <v>77871407</v>
+        <v>77618210</v>
       </c>
       <c r="G212">
-        <v>19628593</v>
-      </c>
-      <c r="H212">
-        <v>32500000</v>
+        <v>36131790</v>
+      </c>
+      <c r="H212" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="213" spans="1:8" x14ac:dyDescent="0.3">
@@ -6845,16 +6852,16 @@
         <v>337500000</v>
       </c>
       <c r="D215">
-        <v>110694039</v>
+        <v>92956149</v>
       </c>
       <c r="E215">
-        <v>118245454</v>
+        <v>132840958</v>
       </c>
       <c r="F215">
-        <v>228939493</v>
+        <v>225797107</v>
       </c>
       <c r="G215">
-        <v>108560507</v>
+        <v>111702893</v>
       </c>
       <c r="H215">
         <v>112500000</v>
@@ -6871,10 +6878,10 @@
         <v>123750000</v>
       </c>
       <c r="D216">
-        <v>10000000</v>
+        <v>0</v>
       </c>
       <c r="E216">
-        <v>10900000</v>
+        <v>20900000</v>
       </c>
       <c r="F216">
         <v>20900000</v>
@@ -6891,25 +6898,25 @@
         <v>32</v>
       </c>
       <c r="B217">
-        <v>252000000</v>
+        <v>220500000</v>
       </c>
       <c r="C217">
-        <v>189000000</v>
+        <v>220500000</v>
       </c>
       <c r="D217">
         <v>0</v>
       </c>
       <c r="E217">
-        <v>169013000</v>
+        <v>170638000</v>
       </c>
       <c r="F217">
-        <v>169013000</v>
+        <v>170638000</v>
       </c>
       <c r="G217">
-        <v>19987000</v>
-      </c>
-      <c r="H217">
-        <v>63000000</v>
+        <v>49862000</v>
+      </c>
+      <c r="H217" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="218" spans="1:8" x14ac:dyDescent="0.3">
@@ -6978,13 +6985,13 @@
         <v>0</v>
       </c>
       <c r="E220">
-        <v>7090319905</v>
+        <v>7090340530</v>
       </c>
       <c r="F220">
-        <v>7090319905</v>
+        <v>7090340530</v>
       </c>
       <c r="G220">
-        <v>2732842221</v>
+        <v>2732821596</v>
       </c>
       <c r="H220" t="s">
         <v>9</v>
@@ -7027,10 +7034,10 @@
         <v>9245675372</v>
       </c>
       <c r="D222">
-        <v>29020768</v>
+        <v>0</v>
       </c>
       <c r="E222">
-        <v>8241279986</v>
+        <v>8270300754</v>
       </c>
       <c r="F222">
         <v>8270300754</v>
@@ -7131,10 +7138,10 @@
         <v>825165933</v>
       </c>
       <c r="D226">
-        <v>504035</v>
+        <v>0</v>
       </c>
       <c r="E226">
-        <v>1029675511</v>
+        <v>1030179546</v>
       </c>
       <c r="F226">
         <v>1030179546</v>
@@ -7177,25 +7184,25 @@
         <v>85</v>
       </c>
       <c r="B228">
-        <v>47914495045</v>
+        <v>47866745045</v>
       </c>
       <c r="C228">
-        <v>47499233545</v>
+        <v>47546983545</v>
       </c>
       <c r="D228">
-        <v>11457923938</v>
+        <v>11236071245</v>
       </c>
       <c r="E228">
-        <v>28822809671</v>
+        <v>28927242406</v>
       </c>
       <c r="F228">
-        <v>40280733609</v>
+        <v>40163313651</v>
       </c>
       <c r="G228">
-        <v>7218499936</v>
+        <v>7383669894</v>
       </c>
       <c r="H228">
-        <v>415261500</v>
+        <v>319761500</v>
       </c>
     </row>
     <row r="229" spans="1:8" x14ac:dyDescent="0.3">
@@ -7209,16 +7216,16 @@
         <v>12264606000</v>
       </c>
       <c r="D229">
-        <v>8206842730</v>
+        <v>8042712730</v>
       </c>
       <c r="E229">
-        <v>3238064000</v>
+        <v>3888767000</v>
       </c>
       <c r="F229">
-        <v>11444906730</v>
+        <v>11931479730</v>
       </c>
       <c r="G229">
-        <v>819699270</v>
+        <v>333126270</v>
       </c>
       <c r="H229" t="s">
         <v>9</v>
@@ -7235,10 +7242,10 @@
         <v>1126306000</v>
       </c>
       <c r="D230">
-        <v>1108174121</v>
+        <v>499624121</v>
       </c>
       <c r="E230">
-        <v>12436007</v>
+        <v>620986007</v>
       </c>
       <c r="F230">
         <v>1120610128</v>
@@ -7365,16 +7372,16 @@
         <v>1380000000</v>
       </c>
       <c r="D235">
-        <v>195458460</v>
+        <v>188118460</v>
       </c>
       <c r="E235">
         <v>1036121967</v>
       </c>
       <c r="F235">
-        <v>1231580427</v>
+        <v>1224240427</v>
       </c>
       <c r="G235">
-        <v>148419573</v>
+        <v>155759573</v>
       </c>
       <c r="H235" t="s">
         <v>9</v>
@@ -7732,13 +7739,13 @@
         <v>0</v>
       </c>
       <c r="E249">
-        <v>156115250</v>
+        <v>157565250</v>
       </c>
       <c r="F249">
-        <v>156115250</v>
+        <v>157565250</v>
       </c>
       <c r="G249">
-        <v>46168750</v>
+        <v>44718750</v>
       </c>
       <c r="H249">
         <v>67428000</v>
@@ -7784,13 +7791,13 @@
         <v>0</v>
       </c>
       <c r="E251">
-        <v>6996299227</v>
+        <v>6996336726</v>
       </c>
       <c r="F251">
-        <v>6996299227</v>
+        <v>6996336726</v>
       </c>
       <c r="G251">
-        <v>2829656943</v>
+        <v>2829619444</v>
       </c>
       <c r="H251" t="s">
         <v>9</v>
@@ -7833,10 +7840,10 @@
         <v>9512105917</v>
       </c>
       <c r="D253">
-        <v>27847073</v>
+        <v>0</v>
       </c>
       <c r="E253">
-        <v>8018348145</v>
+        <v>8046195218</v>
       </c>
       <c r="F253">
         <v>8046195218</v>
@@ -8015,16 +8022,16 @@
         <v>48914772555</v>
       </c>
       <c r="D260">
-        <v>11870059251</v>
+        <v>11062192178</v>
       </c>
       <c r="E260">
-        <v>28842124492</v>
+        <v>30130712064</v>
       </c>
       <c r="F260">
-        <v>40712183743</v>
+        <v>41192904242</v>
       </c>
       <c r="G260">
-        <v>8202588812</v>
+        <v>7721868313</v>
       </c>
       <c r="H260">
         <v>525212165</v>
@@ -8041,10 +8048,10 @@
         <v>5695069150</v>
       </c>
       <c r="D261">
-        <v>4255699600</v>
+        <v>3485289600</v>
       </c>
       <c r="E261">
-        <v>1346122000</v>
+        <v>2116532000</v>
       </c>
       <c r="F261">
         <v>5601821600</v>
@@ -8067,16 +8074,16 @@
         <v>1540000000</v>
       </c>
       <c r="D262">
-        <v>433950000</v>
+        <v>743352000</v>
       </c>
       <c r="E262">
         <v>784443706</v>
       </c>
       <c r="F262">
-        <v>1218393706</v>
+        <v>1527795706</v>
       </c>
       <c r="G262">
-        <v>321606294</v>
+        <v>12204294</v>
       </c>
       <c r="H262" t="s">
         <v>9</v>
@@ -8119,16 +8126,16 @@
         <v>150000000</v>
       </c>
       <c r="D264">
-        <v>0</v>
+        <v>137837144</v>
       </c>
       <c r="E264">
         <v>0</v>
       </c>
-      <c r="F264" t="s">
-        <v>9</v>
+      <c r="F264">
+        <v>137837144</v>
       </c>
       <c r="G264">
-        <v>150000000</v>
+        <v>12162856</v>
       </c>
       <c r="H264" t="s">
         <v>9</v>
@@ -8197,16 +8204,16 @@
         <v>491133000</v>
       </c>
       <c r="D267">
-        <v>0</v>
+        <v>388850000</v>
       </c>
       <c r="E267">
         <v>98325000</v>
       </c>
       <c r="F267">
-        <v>98325000</v>
+        <v>487175000</v>
       </c>
       <c r="G267">
-        <v>392808000</v>
+        <v>3958000</v>
       </c>
       <c r="H267" t="s">
         <v>9</v>
@@ -8223,16 +8230,16 @@
         <v>3609800000</v>
       </c>
       <c r="D268">
-        <v>1153620420</v>
+        <v>1660603451</v>
       </c>
       <c r="E268">
         <v>764581755</v>
       </c>
       <c r="F268">
-        <v>1918202175</v>
+        <v>2425185206</v>
       </c>
       <c r="G268">
-        <v>1691597825</v>
+        <v>1184614794</v>
       </c>
       <c r="H268" t="s">
         <v>9</v>
@@ -8535,16 +8542,16 @@
         <v>1242000000</v>
       </c>
       <c r="D280">
-        <v>922639865</v>
+        <v>878639865</v>
       </c>
       <c r="E280">
-        <v>47046943</v>
+        <v>90954943</v>
       </c>
       <c r="F280">
-        <v>969686808</v>
+        <v>969594808</v>
       </c>
       <c r="G280">
-        <v>272313192</v>
+        <v>272405192</v>
       </c>
       <c r="H280" t="s">
         <v>9</v>
@@ -8561,16 +8568,16 @@
         <v>150000000</v>
       </c>
       <c r="D281">
-        <v>121000000</v>
+        <v>0</v>
       </c>
       <c r="E281">
-        <v>0</v>
+        <v>120747000</v>
       </c>
       <c r="F281">
-        <v>121000000</v>
+        <v>120747000</v>
       </c>
       <c r="G281">
-        <v>29000000</v>
+        <v>29253000</v>
       </c>
       <c r="H281">
         <v>50000000</v>
@@ -8639,16 +8646,16 @@
         <v>235553350</v>
       </c>
       <c r="D284">
-        <v>7500000</v>
+        <v>107400000</v>
       </c>
       <c r="E284">
         <v>56925714</v>
       </c>
       <c r="F284">
-        <v>64425714</v>
+        <v>164325714</v>
       </c>
       <c r="G284">
-        <v>171127636</v>
+        <v>71227636</v>
       </c>
       <c r="H284">
         <v>20684450</v>
@@ -8665,16 +8672,16 @@
         <v>470406638</v>
       </c>
       <c r="D285">
-        <v>87270322</v>
+        <v>131370322</v>
       </c>
       <c r="E285">
         <v>282876433</v>
       </c>
       <c r="F285">
-        <v>370146755</v>
+        <v>414246755</v>
       </c>
       <c r="G285">
-        <v>100259883</v>
+        <v>56159883</v>
       </c>
       <c r="H285">
         <v>156802213</v>
@@ -8746,13 +8753,13 @@
         <v>0</v>
       </c>
       <c r="E288">
-        <v>212360250</v>
+        <v>212835250</v>
       </c>
       <c r="F288">
-        <v>212360250</v>
+        <v>212835250</v>
       </c>
       <c r="G288">
-        <v>136114000</v>
+        <v>135639000</v>
       </c>
       <c r="H288">
         <v>67824750</v>
@@ -8850,13 +8857,13 @@
         <v>0</v>
       </c>
       <c r="E292">
-        <v>8983834098</v>
+        <v>8983839723</v>
       </c>
       <c r="F292">
-        <v>8983834098</v>
+        <v>8983839723</v>
       </c>
       <c r="G292">
-        <v>3638784829</v>
+        <v>3638779204</v>
       </c>
       <c r="H292" t="s">
         <v>9</v>
@@ -8902,13 +8909,13 @@
         <v>0</v>
       </c>
       <c r="E294">
-        <v>10802659505</v>
+        <v>10841494695</v>
       </c>
       <c r="F294">
-        <v>10802659505</v>
+        <v>10841494695</v>
       </c>
       <c r="G294">
-        <v>2109057910</v>
+        <v>2070222720</v>
       </c>
       <c r="H294" t="s">
         <v>9</v>
@@ -9006,13 +9013,13 @@
         <v>0</v>
       </c>
       <c r="E298">
-        <v>1283180553</v>
+        <v>1283585105</v>
       </c>
       <c r="F298">
-        <v>1283180553</v>
+        <v>1283585105</v>
       </c>
       <c r="G298">
-        <v>277148284</v>
+        <v>276743732</v>
       </c>
       <c r="H298" t="s">
         <v>9</v>
@@ -9055,16 +9062,16 @@
         <v>63706784713</v>
       </c>
       <c r="D300">
-        <v>13985403855</v>
+        <v>14537066030</v>
       </c>
       <c r="E300">
-        <v>36266772843</v>
+        <v>37241558210</v>
       </c>
       <c r="F300">
-        <v>50252176698</v>
+        <v>51778624240</v>
       </c>
       <c r="G300">
-        <v>13454608015</v>
+        <v>11928160473</v>
       </c>
       <c r="H300">
         <v>531045413</v>
@@ -9081,10 +9088,10 @@
         <v>3628073000</v>
       </c>
       <c r="D301">
-        <v>1305682100</v>
+        <v>348213000</v>
       </c>
       <c r="E301">
-        <v>2322388900</v>
+        <v>3279858000</v>
       </c>
       <c r="F301">
         <v>3628071000</v>
@@ -9185,16 +9192,16 @@
         <v>298750000</v>
       </c>
       <c r="D305">
-        <v>228565327</v>
+        <v>232513230</v>
       </c>
       <c r="E305">
         <v>65826870</v>
       </c>
       <c r="F305">
-        <v>294392197</v>
+        <v>298340100</v>
       </c>
       <c r="G305">
-        <v>4357803</v>
+        <v>409900</v>
       </c>
       <c r="H305" t="s">
         <v>9</v>
@@ -9237,16 +9244,16 @@
         <v>1222108000</v>
       </c>
       <c r="D307">
-        <v>154177064</v>
+        <v>155107114</v>
       </c>
       <c r="E307">
         <v>1066657271</v>
       </c>
       <c r="F307">
-        <v>1220834335</v>
+        <v>1221764385</v>
       </c>
       <c r="G307">
-        <v>1273665</v>
+        <v>343615</v>
       </c>
       <c r="H307" t="s">
         <v>9</v>
@@ -9263,16 +9270,16 @@
         <v>534300000</v>
       </c>
       <c r="D308">
-        <v>130976265</v>
+        <v>140921415</v>
       </c>
       <c r="E308">
         <v>298405428</v>
       </c>
       <c r="F308">
-        <v>429381693</v>
+        <v>439326843</v>
       </c>
       <c r="G308">
-        <v>104918307</v>
+        <v>94973157</v>
       </c>
       <c r="H308" t="s">
         <v>9</v>
@@ -9315,16 +9322,16 @@
         <v>174000000</v>
       </c>
       <c r="D310">
-        <v>129869969</v>
+        <v>126215000</v>
       </c>
       <c r="E310">
         <v>44129340</v>
       </c>
       <c r="F310">
-        <v>173999309</v>
+        <v>170344340</v>
       </c>
       <c r="G310">
-        <v>691</v>
+        <v>3655660</v>
       </c>
       <c r="H310" t="s">
         <v>9</v>
@@ -9367,10 +9374,10 @@
         <v>1882400000</v>
       </c>
       <c r="D312">
-        <v>169090000</v>
+        <v>159330000</v>
       </c>
       <c r="E312">
-        <v>1713305000</v>
+        <v>1723065000</v>
       </c>
       <c r="F312">
         <v>1882395000</v>
@@ -9445,10 +9452,10 @@
         <v>463000000</v>
       </c>
       <c r="D315">
-        <v>388736000</v>
+        <v>353636000</v>
       </c>
       <c r="E315">
-        <v>45600000</v>
+        <v>80700000</v>
       </c>
       <c r="F315">
         <v>434336000</v>
@@ -9549,16 +9556,16 @@
         <v>64614000</v>
       </c>
       <c r="D319">
-        <v>20700400</v>
+        <v>22603358</v>
       </c>
       <c r="E319">
-        <v>24737271</v>
+        <v>26763571</v>
       </c>
       <c r="F319">
-        <v>45437671</v>
+        <v>49366929</v>
       </c>
       <c r="G319">
-        <v>19176329</v>
+        <v>15247071</v>
       </c>
       <c r="H319">
         <v>21538000</v>
@@ -9575,16 +9582,16 @@
         <v>82504500</v>
       </c>
       <c r="D320">
-        <v>8291500</v>
+        <v>12818500</v>
       </c>
       <c r="E320">
         <v>58799000</v>
       </c>
       <c r="F320">
-        <v>67090500</v>
+        <v>71617500</v>
       </c>
       <c r="G320">
-        <v>15414000</v>
+        <v>10887000</v>
       </c>
       <c r="H320">
         <v>27501500</v>
@@ -9757,10 +9764,10 @@
         <v>7015042421</v>
       </c>
       <c r="D327">
-        <v>19053817</v>
+        <v>0</v>
       </c>
       <c r="E327">
-        <v>5976157047</v>
+        <v>5995210864</v>
       </c>
       <c r="F327">
         <v>5995210864</v>
@@ -9861,10 +9868,10 @@
         <v>1449712379</v>
       </c>
       <c r="D331">
-        <v>608911</v>
+        <v>0</v>
       </c>
       <c r="E331">
-        <v>1144195047</v>
+        <v>1144803958</v>
       </c>
       <c r="F331">
         <v>1144803958</v>
@@ -9913,16 +9920,16 @@
         <v>30454436960</v>
       </c>
       <c r="D333">
-        <v>3303811758</v>
+        <v>2299418022</v>
       </c>
       <c r="E333">
-        <v>21478661365</v>
+        <v>22502679493</v>
       </c>
       <c r="F333">
-        <v>24782473123</v>
+        <v>24802097515</v>
       </c>
       <c r="G333">
-        <v>5671963837</v>
+        <v>5652339445</v>
       </c>
       <c r="H333">
         <v>260139500</v>
@@ -10017,10 +10024,10 @@
         <v>2593734264</v>
       </c>
       <c r="D337">
-        <v>1120961396</v>
+        <v>723018000</v>
       </c>
       <c r="E337">
-        <v>1472772814</v>
+        <v>1870716210</v>
       </c>
       <c r="F337">
         <v>2593734210</v>
@@ -10121,10 +10128,10 @@
         <v>1748195004</v>
       </c>
       <c r="D341">
-        <v>410290553</v>
+        <v>250654563</v>
       </c>
       <c r="E341">
-        <v>1202550785</v>
+        <v>1362186775</v>
       </c>
       <c r="F341">
         <v>1612841338</v>
@@ -10277,10 +10284,10 @@
         <v>150000000</v>
       </c>
       <c r="D347">
-        <v>143281590</v>
+        <v>100602000</v>
       </c>
       <c r="E347">
-        <v>0</v>
+        <v>42679590</v>
       </c>
       <c r="F347">
         <v>143281590</v>
@@ -10381,16 +10388,16 @@
         <v>571079775</v>
       </c>
       <c r="D351">
-        <v>241943670</v>
+        <v>262833670</v>
       </c>
       <c r="E351">
         <v>274818994</v>
       </c>
       <c r="F351">
-        <v>516762664</v>
+        <v>537652664</v>
       </c>
       <c r="G351">
-        <v>54317111</v>
+        <v>33427111</v>
       </c>
       <c r="H351">
         <v>190359925</v>
@@ -10433,16 +10440,16 @@
         <v>462375000</v>
       </c>
       <c r="D353">
-        <v>7253912</v>
+        <v>21419612</v>
       </c>
       <c r="E353">
         <v>331134371</v>
       </c>
       <c r="F353">
-        <v>338388283</v>
+        <v>352553983</v>
       </c>
       <c r="G353">
-        <v>123986717</v>
+        <v>109821017</v>
       </c>
       <c r="H353">
         <v>154125000</v>
@@ -10462,13 +10469,13 @@
         <v>0</v>
       </c>
       <c r="E354">
-        <v>167211500</v>
+        <v>169130250</v>
       </c>
       <c r="F354">
-        <v>167211500</v>
+        <v>169130250</v>
       </c>
       <c r="G354">
-        <v>93338500</v>
+        <v>91419750</v>
       </c>
       <c r="H354">
         <v>86850000</v>
@@ -10485,16 +10492,16 @@
         <v>6000000</v>
       </c>
       <c r="D355">
-        <v>467190</v>
+        <v>838020</v>
       </c>
       <c r="E355">
         <v>1500170</v>
       </c>
       <c r="F355">
-        <v>1967360</v>
+        <v>2338190</v>
       </c>
       <c r="G355">
-        <v>4032640</v>
+        <v>3661810</v>
       </c>
       <c r="H355" t="s">
         <v>9</v>
@@ -10540,13 +10547,13 @@
         <v>0</v>
       </c>
       <c r="E357">
-        <v>7461283668</v>
+        <v>7461330543</v>
       </c>
       <c r="F357">
-        <v>7461283668</v>
+        <v>7461330543</v>
       </c>
       <c r="G357">
-        <v>3253632345</v>
+        <v>3253585470</v>
       </c>
       <c r="H357" t="s">
         <v>9</v>
@@ -10589,16 +10596,16 @@
         <v>10532164202</v>
       </c>
       <c r="D359">
-        <v>0</v>
+        <v>32608180</v>
       </c>
       <c r="E359">
         <v>8834277017</v>
       </c>
       <c r="F359">
-        <v>8834277017</v>
+        <v>8866885197</v>
       </c>
       <c r="G359">
-        <v>1697887185</v>
+        <v>1665279005</v>
       </c>
       <c r="H359" t="s">
         <v>9</v>
@@ -10693,16 +10700,16 @@
         <v>1523018104</v>
       </c>
       <c r="D363">
-        <v>0</v>
+        <v>811692</v>
       </c>
       <c r="E363">
         <v>1236176601</v>
       </c>
       <c r="F363">
-        <v>1236176601</v>
+        <v>1236988293</v>
       </c>
       <c r="G363">
-        <v>286841503</v>
+        <v>286029811</v>
       </c>
       <c r="H363" t="s">
         <v>9</v>
@@ -10745,16 +10752,16 @@
         <v>57427089299</v>
       </c>
       <c r="D365">
-        <v>8890841939</v>
+        <v>8359429365</v>
       </c>
       <c r="E365">
-        <v>40908452881</v>
+        <v>41510677482</v>
       </c>
       <c r="F365">
-        <v>49799294820</v>
+        <v>49870106847</v>
       </c>
       <c r="G365">
-        <v>7627794479</v>
+        <v>7556982452</v>
       </c>
       <c r="H365">
         <v>526334925</v>
@@ -10849,16 +10856,16 @@
         <v>2467762918</v>
       </c>
       <c r="D369">
-        <v>1217556059</v>
+        <v>1755568584</v>
       </c>
       <c r="E369">
         <v>558800786</v>
       </c>
       <c r="F369">
-        <v>1776356845</v>
+        <v>2314369370</v>
       </c>
       <c r="G369">
-        <v>691406073</v>
+        <v>153393548</v>
       </c>
       <c r="H369" t="s">
         <v>9</v>
@@ -10927,16 +10934,16 @@
         <v>1714789867</v>
       </c>
       <c r="D372">
-        <v>920522269</v>
+        <v>951703341</v>
       </c>
       <c r="E372">
         <v>732962308</v>
       </c>
       <c r="F372">
-        <v>1653484577</v>
+        <v>1684665649</v>
       </c>
       <c r="G372">
-        <v>61305290</v>
+        <v>30124218</v>
       </c>
       <c r="H372" t="s">
         <v>9</v>
@@ -10979,16 +10986,16 @@
         <v>290550000</v>
       </c>
       <c r="D374">
-        <v>290377764</v>
+        <v>290264873</v>
       </c>
       <c r="E374">
         <v>0</v>
       </c>
       <c r="F374">
-        <v>290377764</v>
+        <v>290264873</v>
       </c>
       <c r="G374">
-        <v>172236</v>
+        <v>285127</v>
       </c>
       <c r="H374" t="s">
         <v>9</v>
@@ -11031,16 +11038,16 @@
         <v>470200000</v>
       </c>
       <c r="D376">
-        <v>45290400</v>
+        <v>0</v>
       </c>
       <c r="E376">
         <v>424909600</v>
       </c>
       <c r="F376">
-        <v>470200000</v>
-      </c>
-      <c r="G376" t="s">
-        <v>9</v>
+        <v>424909600</v>
+      </c>
+      <c r="G376">
+        <v>45290400</v>
       </c>
       <c r="H376" t="s">
         <v>9</v>
@@ -11057,16 +11064,16 @@
         <v>200000000</v>
       </c>
       <c r="D377">
-        <v>150079500</v>
+        <v>147528500</v>
       </c>
       <c r="E377">
         <v>49920000</v>
       </c>
       <c r="F377">
-        <v>199999500</v>
+        <v>197448500</v>
       </c>
       <c r="G377">
-        <v>500</v>
+        <v>2551500</v>
       </c>
       <c r="H377" t="s">
         <v>9</v>
@@ -11083,16 +11090,16 @@
         <v>82500000</v>
       </c>
       <c r="D378">
-        <v>77719680</v>
+        <v>0</v>
       </c>
       <c r="E378">
-        <v>0</v>
+        <v>76086680</v>
       </c>
       <c r="F378">
-        <v>77719680</v>
+        <v>76086680</v>
       </c>
       <c r="G378">
-        <v>4780320</v>
+        <v>6413320</v>
       </c>
       <c r="H378">
         <v>27500000</v>
@@ -11135,10 +11142,10 @@
         <v>411080000</v>
       </c>
       <c r="D380">
-        <v>1827440</v>
+        <v>489790</v>
       </c>
       <c r="E380">
-        <v>279958254</v>
+        <v>281295904</v>
       </c>
       <c r="F380">
         <v>281785694</v>
@@ -11187,10 +11194,10 @@
         <v>300000000</v>
       </c>
       <c r="D382">
-        <v>79412000</v>
+        <v>67912000</v>
       </c>
       <c r="E382">
-        <v>183314712</v>
+        <v>194814712</v>
       </c>
       <c r="F382">
         <v>262726712</v>
@@ -11268,13 +11275,13 @@
         <v>0</v>
       </c>
       <c r="E385">
-        <v>110610500</v>
+        <v>124406000</v>
       </c>
       <c r="F385">
-        <v>110610500</v>
+        <v>124406000</v>
       </c>
       <c r="G385">
-        <v>17414500</v>
+        <v>3619000</v>
       </c>
       <c r="H385">
         <v>42675000</v>
@@ -11372,13 +11379,13 @@
         <v>0</v>
       </c>
       <c r="E389">
-        <v>3205079550</v>
+        <v>3205993500</v>
       </c>
       <c r="F389">
-        <v>3205079550</v>
+        <v>3205993500</v>
       </c>
       <c r="G389">
-        <v>1334727368</v>
+        <v>1333813418</v>
       </c>
       <c r="H389" t="s">
         <v>9</v>
@@ -11577,16 +11584,16 @@
         <v>24628424376</v>
       </c>
       <c r="D397">
-        <v>4529784150</v>
+        <v>4960466126</v>
       </c>
       <c r="E397">
-        <v>15449970210</v>
+        <v>15553603990</v>
       </c>
       <c r="F397">
-        <v>19979754360</v>
+        <v>20514070116</v>
       </c>
       <c r="G397">
-        <v>4648670016</v>
+        <v>4114354260</v>
       </c>
       <c r="H397">
         <v>232675000</v>
@@ -12019,16 +12026,16 @@
         <v>2230000000</v>
       </c>
       <c r="D414">
-        <v>19000000</v>
+        <v>9815000</v>
       </c>
       <c r="E414">
-        <v>1017375537</v>
+        <v>1025934097</v>
       </c>
       <c r="F414">
-        <v>1036375537</v>
+        <v>1035749097</v>
       </c>
       <c r="G414">
-        <v>1193624463</v>
+        <v>1194250903</v>
       </c>
       <c r="H414" t="s">
         <v>9</v>
@@ -12045,10 +12052,10 @@
         <v>145200000</v>
       </c>
       <c r="D415">
-        <v>30647800</v>
+        <v>22211800</v>
       </c>
       <c r="E415">
-        <v>67309500</v>
+        <v>75745500</v>
       </c>
       <c r="F415">
         <v>97957300</v>
@@ -12305,16 +12312,16 @@
         <v>9379568492</v>
       </c>
       <c r="D425">
-        <v>0</v>
+        <v>26591563</v>
       </c>
       <c r="E425">
         <v>7295042089</v>
       </c>
       <c r="F425">
-        <v>7295042089</v>
+        <v>7321633652</v>
       </c>
       <c r="G425">
-        <v>2084526403</v>
+        <v>2057934840</v>
       </c>
       <c r="H425" t="s">
         <v>9</v>
@@ -12461,16 +12468,16 @@
         <v>35458361640</v>
       </c>
       <c r="D431">
-        <v>5477255293</v>
+        <v>5486225856</v>
       </c>
       <c r="E431">
-        <v>21346375474</v>
+        <v>21363370034</v>
       </c>
       <c r="F431">
-        <v>26823630767</v>
+        <v>26849595890</v>
       </c>
       <c r="G431">
-        <v>8634730873</v>
+        <v>8608765750</v>
       </c>
       <c r="H431">
         <v>472807750</v>
@@ -12480,128 +12487,241 @@
       <c r="A432" t="s">
         <v>8</v>
       </c>
-      <c r="B432">
+      <c r="B432" s="1">
         <v>873740000</v>
       </c>
-      <c r="C432">
+      <c r="C432" s="1">
         <v>873740000</v>
       </c>
-      <c r="D432">
+      <c r="D432" s="1">
         <v>255557500</v>
       </c>
-      <c r="E432">
+      <c r="E432" s="1">
         <v>589750552</v>
       </c>
-      <c r="F432">
+      <c r="F432" s="1">
         <v>845308052</v>
       </c>
-      <c r="G432">
+      <c r="G432" s="1">
         <v>28431948</v>
       </c>
-      <c r="H432">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="433" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="H432" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="433" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A433" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="434" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B433" s="1"/>
+      <c r="C433" s="1"/>
+      <c r="D433" s="1"/>
+      <c r="E433" s="1"/>
+      <c r="F433" s="1"/>
+      <c r="G433" s="1"/>
+      <c r="H433" s="1"/>
+    </row>
+    <row r="434" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A434" t="s">
         <v>93</v>
       </c>
-    </row>
-    <row r="435" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B434" s="1"/>
+      <c r="C434" s="1"/>
+      <c r="D434" s="1"/>
+      <c r="E434" s="1"/>
+      <c r="F434" s="1"/>
+      <c r="G434" s="1"/>
+      <c r="H434" s="1"/>
+    </row>
+    <row r="435" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A435" t="s">
         <v>94</v>
       </c>
-    </row>
-    <row r="436" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B435" s="1"/>
+      <c r="C435" s="1"/>
+      <c r="D435" s="1"/>
+      <c r="E435" s="1"/>
+      <c r="F435" s="1"/>
+      <c r="G435" s="1"/>
+      <c r="H435" s="1"/>
+    </row>
+    <row r="436" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A436" t="s">
         <v>95</v>
       </c>
-    </row>
-    <row r="437" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B436" s="1"/>
+      <c r="C436" s="1"/>
+      <c r="D436" s="1"/>
+      <c r="E436" s="1"/>
+      <c r="F436" s="1"/>
+      <c r="G436" s="1"/>
+      <c r="H436" s="1"/>
+    </row>
+    <row r="437" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A437" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="438" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B437" s="1"/>
+      <c r="C437" s="1"/>
+      <c r="D437" s="1"/>
+      <c r="E437" s="1"/>
+      <c r="F437" s="1"/>
+      <c r="G437" s="1"/>
+      <c r="H437" s="1"/>
+    </row>
+    <row r="438" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A438" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="439" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B438" s="1"/>
+      <c r="C438" s="1"/>
+      <c r="D438" s="1"/>
+      <c r="E438" s="1"/>
+      <c r="F438" s="1"/>
+      <c r="G438" s="1"/>
+      <c r="H438" s="1"/>
+    </row>
+    <row r="439" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A439" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="440" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B439" s="1"/>
+      <c r="C439" s="1"/>
+      <c r="D439" s="1"/>
+      <c r="E439" s="1"/>
+      <c r="F439" s="1"/>
+      <c r="G439" s="1"/>
+      <c r="H439" s="1"/>
+    </row>
+    <row r="440" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A440" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="441" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B440" s="1"/>
+      <c r="C440" s="1"/>
+      <c r="D440" s="1"/>
+      <c r="E440" s="1"/>
+      <c r="F440" s="1"/>
+      <c r="G440" s="1"/>
+      <c r="H440" s="1"/>
+    </row>
+    <row r="441" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A441" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="442" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B441" s="1"/>
+      <c r="C441" s="1"/>
+      <c r="D441" s="1"/>
+      <c r="E441" s="1"/>
+      <c r="F441" s="1"/>
+      <c r="G441" s="1"/>
+      <c r="H441" s="1"/>
+    </row>
+    <row r="442" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A442" t="s">
         <v>101</v>
       </c>
-    </row>
-    <row r="443" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B442" s="1"/>
+      <c r="C442" s="1"/>
+      <c r="D442" s="1"/>
+      <c r="E442" s="1"/>
+      <c r="F442" s="1"/>
+      <c r="G442" s="1"/>
+      <c r="H442" s="1"/>
+    </row>
+    <row r="443" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A443" t="s">
         <v>102</v>
       </c>
-    </row>
-    <row r="444" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B443" s="1"/>
+      <c r="C443" s="1"/>
+      <c r="D443" s="1"/>
+      <c r="E443" s="1"/>
+      <c r="F443" s="1"/>
+      <c r="G443" s="1"/>
+      <c r="H443" s="1"/>
+    </row>
+    <row r="444" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A444" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="445" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B444" s="1"/>
+      <c r="C444" s="1"/>
+      <c r="D444" s="1"/>
+      <c r="E444" s="1"/>
+      <c r="F444" s="1"/>
+      <c r="G444" s="1"/>
+      <c r="H444" s="1"/>
+    </row>
+    <row r="445" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A445" t="s">
         <v>104</v>
       </c>
-    </row>
-    <row r="446" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B445" s="1"/>
+      <c r="C445" s="1"/>
+      <c r="D445" s="1"/>
+      <c r="E445" s="1"/>
+      <c r="F445" s="1"/>
+      <c r="G445" s="1"/>
+      <c r="H445" s="1"/>
+    </row>
+    <row r="446" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A446" t="s">
         <v>105</v>
       </c>
-    </row>
-    <row r="447" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B446" s="1"/>
+      <c r="C446" s="1"/>
+      <c r="D446" s="1"/>
+      <c r="E446" s="1"/>
+      <c r="F446" s="1"/>
+      <c r="G446" s="1"/>
+      <c r="H446" s="1"/>
+    </row>
+    <row r="447" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A447" t="s">
         <v>106</v>
       </c>
-    </row>
-    <row r="448" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B447" s="1"/>
+      <c r="C447" s="1"/>
+      <c r="D447" s="1"/>
+      <c r="E447" s="1"/>
+      <c r="F447" s="1"/>
+      <c r="G447" s="1"/>
+      <c r="H447" s="1"/>
+    </row>
+    <row r="448" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A448" t="s">
         <v>107</v>
       </c>
+      <c r="B448" s="1"/>
+      <c r="C448" s="1"/>
+      <c r="D448" s="1"/>
+      <c r="E448" s="1"/>
+      <c r="F448" s="1"/>
+      <c r="G448" s="1"/>
+      <c r="H448" s="1"/>
     </row>
     <row r="449" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A449" t="s">
         <v>55</v>
       </c>
-      <c r="B449">
+      <c r="B449" s="1">
         <v>474786000</v>
       </c>
-      <c r="C449">
+      <c r="C449" s="1">
         <v>474786000</v>
       </c>
-      <c r="D449">
+      <c r="D449" s="1">
         <v>474154600</v>
       </c>
-      <c r="F449">
+      <c r="E449" s="1"/>
+      <c r="F449" s="1">
         <v>474154600</v>
       </c>
-      <c r="G449">
+      <c r="G449" s="1">
         <v>631400</v>
       </c>
-      <c r="H449">
+      <c r="H449" s="1">
         <v>0</v>
       </c>
     </row>
@@ -12609,22 +12729,23 @@
       <c r="A450" t="s">
         <v>14</v>
       </c>
-      <c r="B450">
+      <c r="B450" s="1">
         <v>208424730</v>
       </c>
-      <c r="C450">
+      <c r="C450" s="1">
         <v>208424730</v>
       </c>
-      <c r="D450">
+      <c r="D450" s="1">
         <v>180590600</v>
       </c>
-      <c r="F450">
+      <c r="E450" s="1"/>
+      <c r="F450" s="1">
         <v>180590600</v>
       </c>
-      <c r="G450">
+      <c r="G450" s="1">
         <v>27834130</v>
       </c>
-      <c r="H450">
+      <c r="H450" s="1">
         <v>0</v>
       </c>
     </row>
@@ -12632,25 +12753,25 @@
       <c r="A451" t="s">
         <v>16</v>
       </c>
-      <c r="B451">
+      <c r="B451" s="1">
         <v>20000000</v>
       </c>
-      <c r="C451">
+      <c r="C451" s="1">
         <v>20000000</v>
       </c>
-      <c r="D451">
-        <v>0</v>
-      </c>
-      <c r="E451">
+      <c r="D451" s="1">
+        <v>0</v>
+      </c>
+      <c r="E451" s="1">
         <v>13970000</v>
       </c>
-      <c r="F451">
+      <c r="F451" s="1">
         <v>13970000</v>
       </c>
-      <c r="G451">
+      <c r="G451" s="1">
         <v>6030000</v>
       </c>
-      <c r="H451">
+      <c r="H451" s="1">
         <v>0</v>
       </c>
     </row>
@@ -12658,25 +12779,25 @@
       <c r="A452" t="s">
         <v>17</v>
       </c>
-      <c r="B452">
+      <c r="B452" s="1">
         <v>220000000</v>
       </c>
-      <c r="C452">
+      <c r="C452" s="1">
         <v>220000000</v>
       </c>
-      <c r="D452">
+      <c r="D452" s="1">
         <v>48700000</v>
       </c>
-      <c r="E452">
+      <c r="E452" s="1">
         <v>89688678</v>
       </c>
-      <c r="F452">
+      <c r="F452" s="1">
         <v>138388678</v>
       </c>
-      <c r="G452">
+      <c r="G452" s="1">
         <v>81611322</v>
       </c>
-      <c r="H452">
+      <c r="H452" s="1">
         <v>0</v>
       </c>
     </row>
@@ -12684,22 +12805,23 @@
       <c r="A453" t="s">
         <v>59</v>
       </c>
-      <c r="B453">
+      <c r="B453" s="1">
         <v>75000000</v>
       </c>
-      <c r="C453">
+      <c r="C453" s="1">
         <v>75000000</v>
       </c>
-      <c r="D453">
+      <c r="D453" s="1">
         <v>38500000</v>
       </c>
-      <c r="F453">
+      <c r="E453" s="1"/>
+      <c r="F453" s="1">
         <v>38500000</v>
       </c>
-      <c r="G453">
+      <c r="G453" s="1">
         <v>36500000</v>
       </c>
-      <c r="H453">
+      <c r="H453" s="1">
         <v>0</v>
       </c>
     </row>
@@ -12707,35 +12829,49 @@
       <c r="A454" t="s">
         <v>108</v>
       </c>
+      <c r="B454" s="1"/>
+      <c r="C454" s="1"/>
+      <c r="D454" s="1"/>
+      <c r="E454" s="1"/>
+      <c r="F454" s="1"/>
+      <c r="G454" s="1"/>
+      <c r="H454" s="1"/>
     </row>
     <row r="455" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A455" t="s">
         <v>109</v>
       </c>
+      <c r="B455" s="1"/>
+      <c r="C455" s="1"/>
+      <c r="D455" s="1"/>
+      <c r="E455" s="1"/>
+      <c r="F455" s="1"/>
+      <c r="G455" s="1"/>
+      <c r="H455" s="1"/>
     </row>
     <row r="456" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A456" t="s">
         <v>24</v>
       </c>
-      <c r="B456">
+      <c r="B456" s="1">
         <v>60000000</v>
       </c>
-      <c r="C456">
+      <c r="C456" s="1">
         <v>45000000</v>
       </c>
-      <c r="D456">
+      <c r="D456" s="1">
         <v>7388000</v>
       </c>
-      <c r="E456">
+      <c r="E456" s="1">
         <v>10120000</v>
       </c>
-      <c r="F456">
+      <c r="F456" s="1">
         <v>17508000</v>
       </c>
-      <c r="G456">
+      <c r="G456" s="1">
         <v>27492000</v>
       </c>
-      <c r="H456">
+      <c r="H456" s="1">
         <v>15000000</v>
       </c>
     </row>
@@ -12743,25 +12879,25 @@
       <c r="A457" t="s">
         <v>64</v>
       </c>
-      <c r="B457">
+      <c r="B457" s="1">
         <v>45150000</v>
       </c>
-      <c r="C457">
+      <c r="C457" s="1">
         <v>45150000</v>
       </c>
-      <c r="D457">
+      <c r="D457" s="1">
         <v>7130850</v>
       </c>
-      <c r="E457">
+      <c r="E457" s="1">
         <v>20796200</v>
       </c>
-      <c r="F457">
+      <c r="F457" s="1">
         <v>27927050</v>
       </c>
-      <c r="G457">
+      <c r="G457" s="1">
         <v>17222950</v>
       </c>
-      <c r="H457">
+      <c r="H457" s="1">
         <v>0</v>
       </c>
     </row>
@@ -12769,64 +12905,129 @@
       <c r="A458" t="s">
         <v>25</v>
       </c>
+      <c r="B458" s="1"/>
+      <c r="C458" s="1"/>
+      <c r="D458" s="1"/>
+      <c r="E458" s="1"/>
+      <c r="F458" s="1"/>
+      <c r="G458" s="1"/>
+      <c r="H458" s="1"/>
     </row>
     <row r="459" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A459" t="s">
         <v>110</v>
       </c>
+      <c r="B459" s="1"/>
+      <c r="C459" s="1"/>
+      <c r="D459" s="1"/>
+      <c r="E459" s="1"/>
+      <c r="F459" s="1"/>
+      <c r="G459" s="1"/>
+      <c r="H459" s="1"/>
     </row>
     <row r="460" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A460" t="s">
         <v>111</v>
       </c>
+      <c r="B460" s="1"/>
+      <c r="C460" s="1"/>
+      <c r="D460" s="1"/>
+      <c r="E460" s="1"/>
+      <c r="F460" s="1"/>
+      <c r="G460" s="1"/>
+      <c r="H460" s="1"/>
     </row>
     <row r="461" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A461" t="s">
         <v>112</v>
       </c>
+      <c r="B461" s="1"/>
+      <c r="C461" s="1"/>
+      <c r="D461" s="1"/>
+      <c r="E461" s="1"/>
+      <c r="F461" s="1"/>
+      <c r="G461" s="1"/>
+      <c r="H461" s="1"/>
     </row>
     <row r="462" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A462" t="s">
         <v>113</v>
       </c>
+      <c r="B462" s="1"/>
+      <c r="C462" s="1"/>
+      <c r="D462" s="1"/>
+      <c r="E462" s="1"/>
+      <c r="F462" s="1"/>
+      <c r="G462" s="1"/>
+      <c r="H462" s="1"/>
     </row>
     <row r="463" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A463" t="s">
         <v>114</v>
       </c>
+      <c r="B463" s="1"/>
+      <c r="C463" s="1"/>
+      <c r="D463" s="1"/>
+      <c r="E463" s="1"/>
+      <c r="F463" s="1"/>
+      <c r="G463" s="1"/>
+      <c r="H463" s="1"/>
     </row>
     <row r="464" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A464" t="s">
         <v>115</v>
       </c>
+      <c r="B464" s="1"/>
+      <c r="C464" s="1"/>
+      <c r="D464" s="1"/>
+      <c r="E464" s="1"/>
+      <c r="F464" s="1"/>
+      <c r="G464" s="1"/>
+      <c r="H464" s="1"/>
     </row>
     <row r="465" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A465" t="s">
         <v>116</v>
       </c>
+      <c r="B465" s="1"/>
+      <c r="C465" s="1"/>
+      <c r="D465" s="1"/>
+      <c r="E465" s="1"/>
+      <c r="F465" s="1"/>
+      <c r="G465" s="1"/>
+      <c r="H465" s="1"/>
     </row>
     <row r="466" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A466" t="s">
         <v>117</v>
       </c>
+      <c r="B466" s="1"/>
+      <c r="C466" s="1"/>
+      <c r="D466" s="1"/>
+      <c r="E466" s="1"/>
+      <c r="F466" s="1"/>
+      <c r="G466" s="1"/>
+      <c r="H466" s="1"/>
     </row>
     <row r="467" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A467" t="s">
         <v>27</v>
       </c>
-      <c r="B467">
+      <c r="B467" s="1">
         <v>6000000</v>
       </c>
-      <c r="C467">
+      <c r="C467" s="1">
         <v>4500000</v>
       </c>
-      <c r="D467">
-        <v>0</v>
-      </c>
-      <c r="G467">
+      <c r="D467" s="1">
+        <v>0</v>
+      </c>
+      <c r="E467" s="1"/>
+      <c r="F467" s="1"/>
+      <c r="G467" s="1">
         <v>4500000</v>
       </c>
-      <c r="H467">
+      <c r="H467" s="1">
         <v>1500000</v>
       </c>
     </row>
@@ -12834,25 +13035,25 @@
       <c r="A468" t="s">
         <v>28</v>
       </c>
-      <c r="B468">
+      <c r="B468" s="1">
         <v>41000000</v>
       </c>
-      <c r="C468">
+      <c r="C468" s="1">
         <v>30750000</v>
       </c>
-      <c r="D468">
+      <c r="D468" s="1">
         <v>6869550</v>
       </c>
-      <c r="E468">
+      <c r="E468" s="1">
         <v>4982700</v>
       </c>
-      <c r="F468">
+      <c r="F468" s="1">
         <v>11852250</v>
       </c>
-      <c r="G468">
+      <c r="G468" s="1">
         <v>18897750</v>
       </c>
-      <c r="H468">
+      <c r="H468" s="1">
         <v>10250000</v>
       </c>
     </row>
@@ -12860,19 +13061,21 @@
       <c r="A469" t="s">
         <v>29</v>
       </c>
-      <c r="B469">
+      <c r="B469" s="1">
         <v>12000000</v>
       </c>
-      <c r="C469">
+      <c r="C469" s="1">
         <v>3000000</v>
       </c>
-      <c r="D469">
-        <v>0</v>
-      </c>
-      <c r="G469">
+      <c r="D469" s="1">
+        <v>0</v>
+      </c>
+      <c r="E469" s="1"/>
+      <c r="F469" s="1"/>
+      <c r="G469" s="1">
         <v>3000000</v>
       </c>
-      <c r="H469">
+      <c r="H469" s="1">
         <v>9000000</v>
       </c>
     </row>
@@ -12880,25 +13083,25 @@
       <c r="A470" t="s">
         <v>30</v>
       </c>
-      <c r="B470">
+      <c r="B470" s="1">
         <v>171000000</v>
       </c>
-      <c r="C470">
+      <c r="C470" s="1">
         <v>128250000</v>
       </c>
-      <c r="D470">
+      <c r="D470" s="1">
         <v>17585000</v>
       </c>
-      <c r="E470">
+      <c r="E470" s="1">
         <v>20876000</v>
       </c>
-      <c r="F470">
+      <c r="F470" s="1">
         <v>38461000</v>
       </c>
-      <c r="G470">
+      <c r="G470" s="1">
         <v>89789000</v>
       </c>
-      <c r="H470">
+      <c r="H470" s="1">
         <v>42750000</v>
       </c>
     </row>
@@ -12906,25 +13109,25 @@
       <c r="A471" t="s">
         <v>32</v>
       </c>
-      <c r="B471">
+      <c r="B471" s="1">
         <v>130000000</v>
       </c>
-      <c r="C471">
+      <c r="C471" s="1">
         <v>97500000</v>
       </c>
-      <c r="D471">
+      <c r="D471" s="1">
         <v>23953308</v>
       </c>
-      <c r="E471">
+      <c r="E471" s="1">
         <v>59537750</v>
       </c>
-      <c r="F471">
+      <c r="F471" s="1">
         <v>83491058</v>
       </c>
-      <c r="G471">
+      <c r="G471" s="1">
         <v>14008942</v>
       </c>
-      <c r="H471">
+      <c r="H471" s="1">
         <v>32500000</v>
       </c>
     </row>
@@ -12932,25 +13135,25 @@
       <c r="A472" t="s">
         <v>84</v>
       </c>
-      <c r="B472">
+      <c r="B472" s="1">
         <v>6660000</v>
       </c>
-      <c r="C472">
+      <c r="C472" s="1">
         <v>6660000</v>
       </c>
-      <c r="D472">
+      <c r="D472" s="1">
         <v>2240000</v>
       </c>
-      <c r="E472">
+      <c r="E472" s="1">
         <v>4246644</v>
       </c>
-      <c r="F472">
+      <c r="F472" s="1">
         <v>6486644</v>
       </c>
-      <c r="G472">
+      <c r="G472" s="1">
         <v>173356</v>
       </c>
-      <c r="H472">
+      <c r="H472" s="1">
         <v>0</v>
       </c>
     </row>
@@ -12958,25 +13161,25 @@
       <c r="A473" t="s">
         <v>33</v>
       </c>
-      <c r="B473">
+      <c r="B473" s="1">
         <v>6000000</v>
       </c>
-      <c r="C473">
+      <c r="C473" s="1">
         <v>6000000</v>
       </c>
-      <c r="D473">
-        <v>0</v>
-      </c>
-      <c r="E473">
+      <c r="D473" s="1">
+        <v>0</v>
+      </c>
+      <c r="E473" s="1">
         <v>5982000</v>
       </c>
-      <c r="F473">
+      <c r="F473" s="1">
         <v>5982000</v>
       </c>
-      <c r="G473">
+      <c r="G473" s="1">
         <v>18000</v>
       </c>
-      <c r="H473">
+      <c r="H473" s="1">
         <v>0</v>
       </c>
     </row>
@@ -12984,71 +13187,169 @@
       <c r="A474" t="s">
         <v>78</v>
       </c>
+      <c r="B474" s="1"/>
+      <c r="C474" s="1"/>
+      <c r="D474" s="1"/>
+      <c r="E474" s="1"/>
+      <c r="F474" s="1"/>
+      <c r="G474" s="1"/>
+      <c r="H474" s="1"/>
     </row>
     <row r="475" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A475" t="s">
         <v>66</v>
       </c>
+      <c r="B475" s="1"/>
+      <c r="C475" s="1"/>
+      <c r="D475" s="1"/>
+      <c r="E475" s="1"/>
+      <c r="F475" s="1"/>
+      <c r="G475" s="1"/>
+      <c r="H475" s="1"/>
     </row>
     <row r="476" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A476" t="s">
         <v>34</v>
       </c>
+      <c r="B476" s="1"/>
+      <c r="C476" s="1"/>
+      <c r="D476" s="1"/>
+      <c r="E476" s="1"/>
+      <c r="F476" s="1"/>
+      <c r="G476" s="1"/>
+      <c r="H476" s="1"/>
     </row>
     <row r="477" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A477" t="s">
         <v>79</v>
       </c>
+      <c r="B477" s="1"/>
+      <c r="C477" s="1"/>
+      <c r="D477" s="1"/>
+      <c r="E477" s="1"/>
+      <c r="F477" s="1"/>
+      <c r="G477" s="1"/>
+      <c r="H477" s="1"/>
     </row>
     <row r="478" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A478" t="s">
         <v>118</v>
       </c>
+      <c r="B478" s="1"/>
+      <c r="C478" s="1"/>
+      <c r="D478" s="1"/>
+      <c r="E478" s="1"/>
+      <c r="F478" s="1"/>
+      <c r="G478" s="1"/>
+      <c r="H478" s="1"/>
     </row>
     <row r="479" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A479" t="s">
         <v>35</v>
       </c>
+      <c r="B479" s="1"/>
+      <c r="C479" s="1"/>
+      <c r="D479" s="1"/>
+      <c r="E479" s="1"/>
+      <c r="F479" s="1"/>
+      <c r="G479" s="1"/>
+      <c r="H479" s="1"/>
     </row>
     <row r="480" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A480" t="s">
         <v>36</v>
       </c>
+      <c r="B480" s="1"/>
+      <c r="C480" s="1"/>
+      <c r="D480" s="1"/>
+      <c r="E480" s="1"/>
+      <c r="F480" s="1"/>
+      <c r="G480" s="1"/>
+      <c r="H480" s="1"/>
     </row>
     <row r="481" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A481" t="s">
         <v>37</v>
       </c>
+      <c r="B481" s="1"/>
+      <c r="C481" s="1"/>
+      <c r="D481" s="1"/>
+      <c r="E481" s="1"/>
+      <c r="F481" s="1"/>
+      <c r="G481" s="1"/>
+      <c r="H481" s="1"/>
     </row>
     <row r="482" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A482" t="s">
         <v>38</v>
       </c>
+      <c r="B482" s="1"/>
+      <c r="C482" s="1"/>
+      <c r="D482" s="1"/>
+      <c r="E482" s="1"/>
+      <c r="F482" s="1"/>
+      <c r="G482" s="1"/>
+      <c r="H482" s="1"/>
     </row>
     <row r="483" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A483" t="s">
         <v>39</v>
       </c>
+      <c r="B483" s="1"/>
+      <c r="C483" s="1"/>
+      <c r="D483" s="1"/>
+      <c r="E483" s="1"/>
+      <c r="F483" s="1"/>
+      <c r="G483" s="1"/>
+      <c r="H483" s="1"/>
     </row>
     <row r="484" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A484" t="s">
         <v>41</v>
       </c>
+      <c r="B484" s="1"/>
+      <c r="C484" s="1"/>
+      <c r="D484" s="1"/>
+      <c r="E484" s="1"/>
+      <c r="F484" s="1"/>
+      <c r="G484" s="1"/>
+      <c r="H484" s="1"/>
     </row>
     <row r="485" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A485" t="s">
         <v>42</v>
       </c>
+      <c r="B485" s="1"/>
+      <c r="C485" s="1"/>
+      <c r="D485" s="1"/>
+      <c r="E485" s="1"/>
+      <c r="F485" s="1"/>
+      <c r="G485" s="1"/>
+      <c r="H485" s="1"/>
     </row>
     <row r="486" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A486" t="s">
         <v>48</v>
       </c>
+      <c r="B486" s="1"/>
+      <c r="C486" s="1"/>
+      <c r="D486" s="1"/>
+      <c r="E486" s="1"/>
+      <c r="F486" s="1"/>
+      <c r="G486" s="1"/>
+      <c r="H486" s="1"/>
     </row>
     <row r="487" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A487" t="s">
         <v>119</v>
       </c>
+      <c r="B487" s="1"/>
+      <c r="C487" s="1"/>
+      <c r="D487" s="1"/>
+      <c r="E487" s="1"/>
+      <c r="F487" s="1"/>
+      <c r="G487" s="1"/>
+      <c r="H487" s="1"/>
     </row>
     <row r="488" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A488" t="s">
@@ -13243,16 +13544,16 @@
         <v>2312795000</v>
       </c>
       <c r="D495">
-        <v>1294531850</v>
+        <v>1255550010</v>
       </c>
       <c r="E495">
-        <v>605293954</v>
+        <v>654993954</v>
       </c>
       <c r="F495">
-        <v>1899825804</v>
+        <v>1910543964</v>
       </c>
       <c r="G495">
-        <v>412969196</v>
+        <v>402251036</v>
       </c>
       <c r="H495" t="s">
         <v>9</v>
@@ -13269,16 +13570,16 @@
         <v>6189486656</v>
       </c>
       <c r="D496">
-        <v>3087140272</v>
+        <v>3109048832</v>
       </c>
       <c r="E496">
         <v>1331606604</v>
       </c>
       <c r="F496">
-        <v>4418746876</v>
+        <v>4440655436</v>
       </c>
       <c r="G496">
-        <v>1770739780</v>
+        <v>1748831220</v>
       </c>
       <c r="H496" t="s">
         <v>9</v>
@@ -13477,16 +13778,16 @@
         <v>7401091133</v>
       </c>
       <c r="D504">
-        <v>4673665116</v>
+        <v>4572970263</v>
       </c>
       <c r="E504">
         <v>2607739789</v>
       </c>
       <c r="F504">
-        <v>7281404905</v>
+        <v>7180710052</v>
       </c>
       <c r="G504">
-        <v>119686228</v>
+        <v>220381081</v>
       </c>
       <c r="H504" t="s">
         <v>9</v>
@@ -13529,10 +13830,10 @@
         <v>266250000</v>
       </c>
       <c r="D506">
-        <v>6838800</v>
+        <v>0</v>
       </c>
       <c r="E506">
-        <v>190238200</v>
+        <v>197077000</v>
       </c>
       <c r="F506">
         <v>197077000</v>
@@ -13763,10 +14064,10 @@
         <v>516433500</v>
       </c>
       <c r="D515">
-        <v>21491715</v>
+        <v>7568076</v>
       </c>
       <c r="E515">
-        <v>360346580</v>
+        <v>374270219</v>
       </c>
       <c r="F515">
         <v>381838295</v>
@@ -13789,16 +14090,16 @@
         <v>36180000</v>
       </c>
       <c r="D516">
-        <v>2747000</v>
+        <v>3015406</v>
       </c>
       <c r="E516">
         <v>10574568</v>
       </c>
       <c r="F516">
-        <v>13321568</v>
+        <v>13589974</v>
       </c>
       <c r="G516">
-        <v>22858432</v>
+        <v>22590026</v>
       </c>
       <c r="H516" t="s">
         <v>9</v>
@@ -13815,16 +14116,16 @@
         <v>61741000</v>
       </c>
       <c r="D517">
-        <v>0</v>
+        <v>20788000</v>
       </c>
       <c r="E517">
         <v>40855444</v>
       </c>
       <c r="F517">
-        <v>40855444</v>
+        <v>61643444</v>
       </c>
       <c r="G517">
-        <v>20885556</v>
+        <v>97556</v>
       </c>
       <c r="H517" t="s">
         <v>9</v>
@@ -13893,16 +14194,16 @@
         <v>0</v>
       </c>
       <c r="D520">
-        <v>0</v>
+        <v>25388</v>
       </c>
       <c r="E520">
         <v>748141</v>
       </c>
       <c r="F520">
-        <v>748141</v>
+        <v>773529</v>
       </c>
       <c r="G520">
-        <v>-748141</v>
+        <v>-773529</v>
       </c>
       <c r="H520" t="s">
         <v>9</v>
@@ -13919,16 +14220,16 @@
         <v>0</v>
       </c>
       <c r="D521">
-        <v>0</v>
+        <v>1800000</v>
       </c>
       <c r="E521">
         <v>115182625</v>
       </c>
       <c r="F521">
-        <v>115182625</v>
+        <v>116982625</v>
       </c>
       <c r="G521">
-        <v>-115182625</v>
+        <v>-116982625</v>
       </c>
       <c r="H521" t="s">
         <v>9</v>
@@ -13945,16 +14246,16 @@
         <v>12164281897</v>
       </c>
       <c r="D522">
-        <v>0</v>
+        <v>1068968</v>
       </c>
       <c r="E522">
         <v>8956957415</v>
       </c>
       <c r="F522">
-        <v>8956957415</v>
+        <v>8958026383</v>
       </c>
       <c r="G522">
-        <v>3207324482</v>
+        <v>3206255514</v>
       </c>
       <c r="H522" t="s">
         <v>9</v>
@@ -13997,16 +14298,16 @@
         <v>10801404197</v>
       </c>
       <c r="D524">
-        <v>0</v>
+        <v>79545016</v>
       </c>
       <c r="E524">
         <v>9796841081</v>
       </c>
       <c r="F524">
-        <v>9796841081</v>
+        <v>9876386097</v>
       </c>
       <c r="G524">
-        <v>1004563116</v>
+        <v>925018100</v>
       </c>
       <c r="H524" t="s">
         <v>9</v>
@@ -14179,16 +14480,16 @@
         <v>64019485320</v>
       </c>
       <c r="D531">
-        <v>14431488399</v>
+        <v>14396453605</v>
       </c>
       <c r="E531">
-        <v>40616310114</v>
+        <v>40686772553</v>
       </c>
       <c r="F531">
-        <v>55047798513</v>
+        <v>55083226158</v>
       </c>
       <c r="G531">
-        <v>8971686807</v>
+        <v>8936259162</v>
       </c>
       <c r="H531">
         <v>850782250</v>
@@ -14205,10 +14506,10 @@
         <v>5572131338</v>
       </c>
       <c r="D532">
-        <v>1782973068</v>
+        <v>1641723068</v>
       </c>
       <c r="E532">
-        <v>3781033270</v>
+        <v>3922283270</v>
       </c>
       <c r="F532">
         <v>5564006338</v>
@@ -14283,10 +14584,10 @@
         <v>2166235262</v>
       </c>
       <c r="D535">
-        <v>1729853601</v>
+        <v>1284417699</v>
       </c>
       <c r="E535">
-        <v>436381661</v>
+        <v>881817563</v>
       </c>
       <c r="F535">
         <v>2166235262</v>
@@ -14361,10 +14662,10 @@
         <v>11576266001</v>
       </c>
       <c r="D538">
-        <v>11246822851</v>
+        <v>7366219160</v>
       </c>
       <c r="E538">
-        <v>259825808</v>
+        <v>4140429499</v>
       </c>
       <c r="F538">
         <v>11506648659</v>
@@ -14387,16 +14688,16 @@
         <v>2103744312</v>
       </c>
       <c r="D539">
-        <v>1356681115</v>
+        <v>1036023487</v>
       </c>
       <c r="E539">
-        <v>330635136</v>
+        <v>699348736</v>
       </c>
       <c r="F539">
-        <v>1687316251</v>
+        <v>1735372223</v>
       </c>
       <c r="G539">
-        <v>416428061</v>
+        <v>368372089</v>
       </c>
       <c r="H539" t="s">
         <v>9</v>
@@ -14491,10 +14792,10 @@
         <v>1710735389</v>
       </c>
       <c r="D543">
-        <v>384000000</v>
+        <v>0</v>
       </c>
       <c r="E543">
-        <v>1326735389</v>
+        <v>1710735389</v>
       </c>
       <c r="F543">
         <v>1710735389</v>
@@ -14595,16 +14896,16 @@
         <v>1539315000</v>
       </c>
       <c r="D547">
-        <v>6343694</v>
+        <v>6712544</v>
       </c>
       <c r="E547">
         <v>933071899</v>
       </c>
       <c r="F547">
-        <v>939415593</v>
+        <v>939784443</v>
       </c>
       <c r="G547">
-        <v>599899407</v>
+        <v>599530557</v>
       </c>
       <c r="H547" t="s">
         <v>9</v>
@@ -14647,16 +14948,16 @@
         <v>532875000</v>
       </c>
       <c r="D549">
-        <v>51119621</v>
+        <v>52322721</v>
       </c>
       <c r="E549">
         <v>167536270</v>
       </c>
       <c r="F549">
-        <v>218655891</v>
+        <v>219858991</v>
       </c>
       <c r="G549">
-        <v>314219109</v>
+        <v>313016009</v>
       </c>
       <c r="H549">
         <v>177625000</v>
@@ -14728,13 +15029,13 @@
         <v>7225381</v>
       </c>
       <c r="E552">
-        <v>251095601</v>
+        <v>253789351</v>
       </c>
       <c r="F552">
-        <v>258320982</v>
+        <v>261014732</v>
       </c>
       <c r="G552">
-        <v>78481518</v>
+        <v>75787768</v>
       </c>
       <c r="H552">
         <v>112267500</v>
@@ -14806,13 +15107,13 @@
         <v>0</v>
       </c>
       <c r="E555">
-        <v>7784065393</v>
+        <v>7784118830</v>
       </c>
       <c r="F555">
-        <v>7784065393</v>
+        <v>7784118830</v>
       </c>
       <c r="G555">
-        <v>2904851473</v>
+        <v>2904798036</v>
       </c>
       <c r="H555" t="s">
         <v>9</v>
@@ -15011,16 +15312,16 @@
         <v>57848682223</v>
       </c>
       <c r="D563">
-        <v>19245745658</v>
+        <v>14075370387</v>
       </c>
       <c r="E563">
-        <v>31864701745</v>
+        <v>37087452125</v>
       </c>
       <c r="F563">
-        <v>51110447403</v>
+        <v>51162822512</v>
       </c>
       <c r="G563">
-        <v>6738234820</v>
+        <v>6685859711</v>
       </c>
       <c r="H563">
         <v>720558750</v>
@@ -15031,25 +15332,25 @@
         <v>130</v>
       </c>
       <c r="B564">
-        <v>1118540641744</v>
+        <v>1114653868055</v>
       </c>
       <c r="C564">
-        <v>1109231301920</v>
+        <v>1108157528231</v>
       </c>
       <c r="D564">
-        <v>414927051289</v>
+        <v>387069966949</v>
       </c>
       <c r="E564">
-        <v>552152652380</v>
+        <v>585636774332</v>
       </c>
       <c r="F564">
-        <v>967079703669</v>
+        <v>972706741281</v>
       </c>
       <c r="G564">
-        <v>142151598251</v>
+        <v>135450786950</v>
       </c>
       <c r="H564">
-        <v>9309339824</v>
+        <v>6496339824</v>
       </c>
     </row>
   </sheetData>

--- a/data/rka.xlsx
+++ b/data/rka.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\76193\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:40009_{B926CE83-FEB6-4418-BD8D-37ADC92BA2FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:40009_{6590ACE8-AF52-4EA6-B5EC-0C5CF4291360}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456"/>
   </bookViews>
   <sheets>
-    <sheet name="20260911 SAP ZFM01" sheetId="1" r:id="rId1"/>
+    <sheet name="20260914 SAP ZFM01" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
   <extLst>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1093" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1094" uniqueCount="131">
   <si>
     <t>Funds Center/Commitment Item</t>
   </si>
@@ -1314,16 +1314,16 @@
         <v>108940456175</v>
       </c>
       <c r="D2">
-        <v>94287482435</v>
+        <v>80755967435</v>
       </c>
       <c r="E2">
-        <v>13248513732</v>
+        <v>27616513732</v>
       </c>
       <c r="F2">
-        <v>107535996167</v>
+        <v>108372481167</v>
       </c>
       <c r="G2">
-        <v>1404460008</v>
+        <v>567975008</v>
       </c>
       <c r="H2" t="s">
         <v>9</v>
@@ -1392,10 +1392,10 @@
         <v>31123480081</v>
       </c>
       <c r="D5">
-        <v>2894652600</v>
+        <v>232170400</v>
       </c>
       <c r="E5">
-        <v>28199383820</v>
+        <v>30861866020</v>
       </c>
       <c r="F5">
         <v>31094036420</v>
@@ -1756,16 +1756,16 @@
         <v>3894602130</v>
       </c>
       <c r="D19">
-        <v>346244860</v>
+        <v>402739408</v>
       </c>
       <c r="E19">
         <v>2563937629</v>
       </c>
       <c r="F19">
-        <v>2910182489</v>
+        <v>2966677037</v>
       </c>
       <c r="G19">
-        <v>984419641</v>
+        <v>927925093</v>
       </c>
       <c r="H19" t="s">
         <v>9</v>
@@ -1808,16 +1808,16 @@
         <v>406635000</v>
       </c>
       <c r="D21">
-        <v>77481217</v>
+        <v>78034042</v>
       </c>
       <c r="E21">
         <v>89696662</v>
       </c>
       <c r="F21">
-        <v>167177879</v>
+        <v>167730704</v>
       </c>
       <c r="G21">
-        <v>239457121</v>
+        <v>238904296</v>
       </c>
       <c r="H21" t="s">
         <v>9</v>
@@ -1915,13 +1915,13 @@
         <v>215556103</v>
       </c>
       <c r="E25">
-        <v>1088880691</v>
+        <v>1100380691</v>
       </c>
       <c r="F25">
-        <v>1304436794</v>
+        <v>1315936794</v>
       </c>
       <c r="G25">
-        <v>386840339</v>
+        <v>375340339</v>
       </c>
       <c r="H25" t="s">
         <v>9</v>
@@ -1993,13 +1993,13 @@
         <v>0</v>
       </c>
       <c r="E28">
-        <v>2834764214</v>
+        <v>2835270464</v>
       </c>
       <c r="F28">
-        <v>2834764214</v>
+        <v>2835270464</v>
       </c>
       <c r="G28">
-        <v>621849990</v>
+        <v>621343740</v>
       </c>
       <c r="H28" t="s">
         <v>9</v>
@@ -2354,16 +2354,16 @@
         <v>346934395851</v>
       </c>
       <c r="D42">
-        <v>215386879388</v>
+        <v>199249929561</v>
       </c>
       <c r="E42">
-        <v>116376961036</v>
+        <v>133419449486</v>
       </c>
       <c r="F42">
-        <v>331763840424</v>
+        <v>332669379047</v>
       </c>
       <c r="G42">
-        <v>15170555427</v>
+        <v>14265016804</v>
       </c>
       <c r="H42" t="s">
         <v>9</v>
@@ -2380,10 +2380,10 @@
         <v>26681487101</v>
       </c>
       <c r="D43">
-        <v>17343493202</v>
+        <v>16851399022</v>
       </c>
       <c r="E43">
-        <v>9295238000</v>
+        <v>9787332180</v>
       </c>
       <c r="F43">
         <v>26638731202</v>
@@ -2562,10 +2562,10 @@
         <v>2000000000</v>
       </c>
       <c r="D50">
-        <v>1883336224</v>
+        <v>1391798724</v>
       </c>
       <c r="E50">
-        <v>0</v>
+        <v>491537500</v>
       </c>
       <c r="F50">
         <v>1883336224</v>
@@ -3446,10 +3446,10 @@
         <v>110881210191</v>
       </c>
       <c r="D84">
-        <v>36215290317</v>
+        <v>35231658637</v>
       </c>
       <c r="E84">
-        <v>57938950399</v>
+        <v>58922582079</v>
       </c>
       <c r="F84">
         <v>94154240716</v>
@@ -3576,10 +3576,10 @@
         <v>30639775739</v>
       </c>
       <c r="D89">
-        <v>16314020110</v>
+        <v>16269963610</v>
       </c>
       <c r="E89">
-        <v>11956954821</v>
+        <v>12001011321</v>
       </c>
       <c r="F89">
         <v>28270974931</v>
@@ -3628,10 +3628,10 @@
         <v>88512582</v>
       </c>
       <c r="D91">
-        <v>87737900</v>
+        <v>24168400</v>
       </c>
       <c r="E91">
-        <v>0</v>
+        <v>63569500</v>
       </c>
       <c r="F91">
         <v>87737900</v>
@@ -3654,10 +3654,10 @@
         <v>1210765056</v>
       </c>
       <c r="D92">
-        <v>548419940</v>
+        <v>460919940</v>
       </c>
       <c r="E92">
-        <v>159842440</v>
+        <v>247342440</v>
       </c>
       <c r="F92">
         <v>708262380</v>
@@ -3836,10 +3836,10 @@
         <v>360000000</v>
       </c>
       <c r="D99">
-        <v>141522576</v>
+        <v>108184576</v>
       </c>
       <c r="E99">
-        <v>204218000</v>
+        <v>237556000</v>
       </c>
       <c r="F99">
         <v>345740576</v>
@@ -3914,16 +3914,16 @@
         <v>394475000</v>
       </c>
       <c r="D102">
-        <v>70510900</v>
+        <v>51550900</v>
       </c>
       <c r="E102">
         <v>45427850</v>
       </c>
       <c r="F102">
-        <v>115938750</v>
+        <v>96978750</v>
       </c>
       <c r="G102">
-        <v>278536250</v>
+        <v>297496250</v>
       </c>
       <c r="H102">
         <v>139825000</v>
@@ -3940,16 +3940,16 @@
         <v>255960000</v>
       </c>
       <c r="D103">
-        <v>60960230</v>
+        <v>43040230</v>
       </c>
       <c r="E103">
         <v>174999400</v>
       </c>
       <c r="F103">
-        <v>235959630</v>
+        <v>218039630</v>
       </c>
       <c r="G103">
-        <v>20000370</v>
+        <v>37920370</v>
       </c>
       <c r="H103">
         <v>85320000</v>
@@ -3992,16 +3992,16 @@
         <v>291600000</v>
       </c>
       <c r="D105">
-        <v>243281700</v>
+        <v>192481700</v>
       </c>
       <c r="E105">
         <v>28079000</v>
       </c>
       <c r="F105">
-        <v>271360700</v>
+        <v>220560700</v>
       </c>
       <c r="G105">
-        <v>20239300</v>
+        <v>71039300</v>
       </c>
       <c r="H105">
         <v>97200000</v>
@@ -4018,16 +4018,16 @@
         <v>15000000</v>
       </c>
       <c r="D106">
-        <v>2400000</v>
+        <v>0</v>
       </c>
       <c r="E106">
         <v>0</v>
       </c>
-      <c r="F106">
-        <v>2400000</v>
+      <c r="F106" t="s">
+        <v>9</v>
       </c>
       <c r="G106">
-        <v>12600000</v>
+        <v>15000000</v>
       </c>
       <c r="H106">
         <v>5000000</v>
@@ -4047,13 +4047,13 @@
         <v>0</v>
       </c>
       <c r="E107">
-        <v>292803568</v>
+        <v>294691068</v>
       </c>
       <c r="F107">
-        <v>292803568</v>
+        <v>294691068</v>
       </c>
       <c r="G107">
-        <v>2253932</v>
+        <v>366432</v>
       </c>
       <c r="H107">
         <v>98352500</v>
@@ -4070,16 +4070,16 @@
         <v>91080000</v>
       </c>
       <c r="D108">
-        <v>11880000</v>
+        <v>0</v>
       </c>
       <c r="E108">
         <v>38927400</v>
       </c>
       <c r="F108">
-        <v>50807400</v>
+        <v>38927400</v>
       </c>
       <c r="G108">
-        <v>40272600</v>
+        <v>52152600</v>
       </c>
       <c r="H108" t="s">
         <v>9</v>
@@ -4177,13 +4177,13 @@
         <v>0</v>
       </c>
       <c r="E112">
-        <v>11992098199</v>
+        <v>11992126324</v>
       </c>
       <c r="F112">
-        <v>11992098199</v>
+        <v>11992126324</v>
       </c>
       <c r="G112">
-        <v>4231546654</v>
+        <v>4231518529</v>
       </c>
       <c r="H112" t="s">
         <v>9</v>
@@ -4408,16 +4408,16 @@
         <v>81693644736</v>
       </c>
       <c r="D121">
-        <v>21039377028</v>
+        <v>20708953028</v>
       </c>
       <c r="E121">
-        <v>50132127898</v>
+        <v>50362507523</v>
       </c>
       <c r="F121">
-        <v>71171504926</v>
+        <v>71071460551</v>
       </c>
       <c r="G121">
-        <v>10522139810</v>
+        <v>10622184185</v>
       </c>
       <c r="H121">
         <v>475697500</v>
@@ -4590,16 +4590,16 @@
         <v>4824864000</v>
       </c>
       <c r="D128">
-        <v>1685220</v>
+        <v>11569210</v>
       </c>
       <c r="E128">
         <v>4612652831</v>
       </c>
       <c r="F128">
-        <v>4614338051</v>
+        <v>4624222041</v>
       </c>
       <c r="G128">
-        <v>210525949</v>
+        <v>200641959</v>
       </c>
       <c r="H128" t="s">
         <v>9</v>
@@ -4694,16 +4694,16 @@
         <v>2233168000</v>
       </c>
       <c r="D132">
-        <v>1437810620</v>
+        <v>1462560620</v>
       </c>
       <c r="E132">
         <v>766560444</v>
       </c>
       <c r="F132">
-        <v>2204371064</v>
+        <v>2229121064</v>
       </c>
       <c r="G132">
-        <v>28796936</v>
+        <v>4046936</v>
       </c>
       <c r="H132" t="s">
         <v>9</v>
@@ -4824,16 +4824,16 @@
         <v>118875000</v>
       </c>
       <c r="D137">
-        <v>14682500</v>
+        <v>18462500</v>
       </c>
       <c r="E137">
         <v>62015400</v>
       </c>
       <c r="F137">
-        <v>76697900</v>
+        <v>80477900</v>
       </c>
       <c r="G137">
-        <v>42177100</v>
+        <v>38397100</v>
       </c>
       <c r="H137" t="s">
         <v>9</v>
@@ -4902,16 +4902,16 @@
         <v>354600000</v>
       </c>
       <c r="D140">
-        <v>4357100</v>
+        <v>23757100</v>
       </c>
       <c r="E140">
         <v>220966600</v>
       </c>
       <c r="F140">
-        <v>225323700</v>
+        <v>244723700</v>
       </c>
       <c r="G140">
-        <v>129276300</v>
+        <v>109876300</v>
       </c>
       <c r="H140" t="s">
         <v>9</v>
@@ -5292,16 +5292,16 @@
         <v>52473056175</v>
       </c>
       <c r="D155">
-        <v>10134266169</v>
+        <v>10192080159</v>
       </c>
       <c r="E155">
         <v>32728688885</v>
       </c>
       <c r="F155">
-        <v>42862955054</v>
+        <v>42920769044</v>
       </c>
       <c r="G155">
-        <v>9610101121</v>
+        <v>9552287131</v>
       </c>
       <c r="H155">
         <v>111080000</v>
@@ -5318,10 +5318,10 @@
         <v>11383511000</v>
       </c>
       <c r="D156">
-        <v>2949251692</v>
+        <v>2695026692</v>
       </c>
       <c r="E156">
-        <v>8419849198</v>
+        <v>8674074198</v>
       </c>
       <c r="F156">
         <v>11369100890</v>
@@ -5474,16 +5474,16 @@
         <v>1702406000</v>
       </c>
       <c r="D162">
-        <v>384453009</v>
+        <v>504786557</v>
       </c>
       <c r="E162">
         <v>807533375</v>
       </c>
       <c r="F162">
-        <v>1191986384</v>
+        <v>1312319932</v>
       </c>
       <c r="G162">
-        <v>510419616</v>
+        <v>390086068</v>
       </c>
       <c r="H162" t="s">
         <v>9</v>
@@ -5500,10 +5500,10 @@
         <v>463360000</v>
       </c>
       <c r="D163">
-        <v>429930120</v>
+        <v>0</v>
       </c>
       <c r="E163">
-        <v>19958000</v>
+        <v>449888120</v>
       </c>
       <c r="F163">
         <v>449888120</v>
@@ -5604,16 +5604,16 @@
         <v>500000000</v>
       </c>
       <c r="D167">
-        <v>0</v>
+        <v>55354016</v>
       </c>
       <c r="E167">
         <v>185788488</v>
       </c>
       <c r="F167">
-        <v>185788488</v>
+        <v>241142504</v>
       </c>
       <c r="G167">
-        <v>314211512</v>
+        <v>258857496</v>
       </c>
       <c r="H167" t="s">
         <v>9</v>
@@ -5656,10 +5656,10 @@
         <v>867942000</v>
       </c>
       <c r="D169">
-        <v>235899000</v>
+        <v>0</v>
       </c>
       <c r="E169">
-        <v>406666410</v>
+        <v>642565410</v>
       </c>
       <c r="F169">
         <v>642565410</v>
@@ -5919,13 +5919,13 @@
         <v>0</v>
       </c>
       <c r="E179">
-        <v>127765250</v>
+        <v>128090250</v>
       </c>
       <c r="F179">
-        <v>127765250</v>
+        <v>128090250</v>
       </c>
       <c r="G179">
-        <v>34536250</v>
+        <v>34211250</v>
       </c>
       <c r="H179">
         <v>54100500</v>
@@ -5971,13 +5971,13 @@
         <v>0</v>
       </c>
       <c r="E181">
-        <v>5305580738</v>
+        <v>5305591988</v>
       </c>
       <c r="F181">
-        <v>5305580738</v>
+        <v>5305591988</v>
       </c>
       <c r="G181">
-        <v>2199142640</v>
+        <v>2199131390</v>
       </c>
       <c r="H181" t="s">
         <v>9</v>
@@ -6176,16 +6176,16 @@
         <v>46375593027</v>
       </c>
       <c r="D189">
-        <v>9537449850</v>
+        <v>8793083294</v>
       </c>
       <c r="E189">
-        <v>29260551695</v>
+        <v>30180942065</v>
       </c>
       <c r="F189">
-        <v>38798001545</v>
+        <v>38974025359</v>
       </c>
       <c r="G189">
-        <v>7577591482</v>
+        <v>7401567668</v>
       </c>
       <c r="H189">
         <v>449400500</v>
@@ -6332,16 +6332,16 @@
         <v>3919663677</v>
       </c>
       <c r="D195">
-        <v>2885377960</v>
+        <v>2893777960</v>
       </c>
       <c r="E195">
         <v>530323683</v>
       </c>
       <c r="F195">
-        <v>3415701643</v>
+        <v>3424101643</v>
       </c>
       <c r="G195">
-        <v>503962034</v>
+        <v>495562034</v>
       </c>
       <c r="H195" t="s">
         <v>9</v>
@@ -6410,16 +6410,16 @@
         <v>469000000</v>
       </c>
       <c r="D198">
-        <v>77690468</v>
+        <v>84376635</v>
       </c>
       <c r="E198">
         <v>64102434</v>
       </c>
       <c r="F198">
-        <v>141792902</v>
+        <v>148479069</v>
       </c>
       <c r="G198">
-        <v>327207098</v>
+        <v>320520931</v>
       </c>
       <c r="H198" t="s">
         <v>9</v>
@@ -6488,16 +6488,16 @@
         <v>1862650000</v>
       </c>
       <c r="D201">
-        <v>300009067</v>
+        <v>310005157</v>
       </c>
       <c r="E201">
         <v>1416159706</v>
       </c>
       <c r="F201">
-        <v>1716168773</v>
+        <v>1726164863</v>
       </c>
       <c r="G201">
-        <v>146481227</v>
+        <v>136485137</v>
       </c>
       <c r="H201" t="s">
         <v>9</v>
@@ -6514,16 +6514,16 @@
         <v>281000000</v>
       </c>
       <c r="D202">
-        <v>0</v>
+        <v>35987168</v>
       </c>
       <c r="E202">
         <v>54403548</v>
       </c>
       <c r="F202">
-        <v>54403548</v>
+        <v>90390716</v>
       </c>
       <c r="G202">
-        <v>226596452</v>
+        <v>190609284</v>
       </c>
       <c r="H202" t="s">
         <v>9</v>
@@ -6592,16 +6592,16 @@
         <v>4350172680</v>
       </c>
       <c r="D205">
-        <v>2986575000</v>
+        <v>3028130600</v>
       </c>
       <c r="E205">
         <v>1236281200</v>
       </c>
       <c r="F205">
-        <v>4222856200</v>
+        <v>4264411800</v>
       </c>
       <c r="G205">
-        <v>127316480</v>
+        <v>85760880</v>
       </c>
       <c r="H205" t="s">
         <v>9</v>
@@ -6774,16 +6774,16 @@
         <v>113750000</v>
       </c>
       <c r="D212">
-        <v>3400000</v>
+        <v>18540090</v>
       </c>
       <c r="E212">
         <v>74218210</v>
       </c>
       <c r="F212">
-        <v>77618210</v>
+        <v>92758300</v>
       </c>
       <c r="G212">
-        <v>36131790</v>
+        <v>20991700</v>
       </c>
       <c r="H212" t="s">
         <v>9</v>
@@ -6800,16 +6800,16 @@
         <v>385534500</v>
       </c>
       <c r="D213">
-        <v>27485000</v>
+        <v>25480000</v>
       </c>
       <c r="E213">
         <v>274473000</v>
       </c>
       <c r="F213">
-        <v>301958000</v>
+        <v>299953000</v>
       </c>
       <c r="G213">
-        <v>83576500</v>
+        <v>85581500</v>
       </c>
       <c r="H213">
         <v>128511500</v>
@@ -6907,13 +6907,13 @@
         <v>0</v>
       </c>
       <c r="E217">
-        <v>170638000</v>
+        <v>174619250</v>
       </c>
       <c r="F217">
-        <v>170638000</v>
+        <v>174619250</v>
       </c>
       <c r="G217">
-        <v>49862000</v>
+        <v>45880750</v>
       </c>
       <c r="H217" t="s">
         <v>9</v>
@@ -6985,13 +6985,13 @@
         <v>0</v>
       </c>
       <c r="E220">
-        <v>7090340530</v>
+        <v>7090468030</v>
       </c>
       <c r="F220">
-        <v>7090340530</v>
+        <v>7090468030</v>
       </c>
       <c r="G220">
-        <v>2732821596</v>
+        <v>2732694096</v>
       </c>
       <c r="H220" t="s">
         <v>9</v>
@@ -7190,16 +7190,16 @@
         <v>47546983545</v>
       </c>
       <c r="D228">
-        <v>11236071245</v>
+        <v>11351831360</v>
       </c>
       <c r="E228">
-        <v>28927242406</v>
+        <v>28931351156</v>
       </c>
       <c r="F228">
-        <v>40163313651</v>
+        <v>40283182516</v>
       </c>
       <c r="G228">
-        <v>7383669894</v>
+        <v>7263801029</v>
       </c>
       <c r="H228">
         <v>319761500</v>
@@ -7739,13 +7739,13 @@
         <v>0</v>
       </c>
       <c r="E249">
-        <v>157565250</v>
+        <v>157677750</v>
       </c>
       <c r="F249">
-        <v>157565250</v>
+        <v>157677750</v>
       </c>
       <c r="G249">
-        <v>44718750</v>
+        <v>44606250</v>
       </c>
       <c r="H249">
         <v>67428000</v>
@@ -7791,13 +7791,13 @@
         <v>0</v>
       </c>
       <c r="E251">
-        <v>6996336726</v>
+        <v>6996342351</v>
       </c>
       <c r="F251">
-        <v>6996336726</v>
+        <v>6996342351</v>
       </c>
       <c r="G251">
-        <v>2829619444</v>
+        <v>2829613819</v>
       </c>
       <c r="H251" t="s">
         <v>9</v>
@@ -8025,13 +8025,13 @@
         <v>11062192178</v>
       </c>
       <c r="E260">
-        <v>30130712064</v>
+        <v>30130830189</v>
       </c>
       <c r="F260">
-        <v>41192904242</v>
+        <v>41193022367</v>
       </c>
       <c r="G260">
-        <v>7721868313</v>
+        <v>7721750188</v>
       </c>
       <c r="H260">
         <v>525212165</v>
@@ -8230,10 +8230,10 @@
         <v>3609800000</v>
       </c>
       <c r="D268">
-        <v>1660603451</v>
+        <v>1602606751</v>
       </c>
       <c r="E268">
-        <v>764581755</v>
+        <v>822578455</v>
       </c>
       <c r="F268">
         <v>2425185206</v>
@@ -8753,13 +8753,13 @@
         <v>0</v>
       </c>
       <c r="E288">
-        <v>212835250</v>
+        <v>232898250</v>
       </c>
       <c r="F288">
-        <v>212835250</v>
+        <v>232898250</v>
       </c>
       <c r="G288">
-        <v>135639000</v>
+        <v>115576000</v>
       </c>
       <c r="H288">
         <v>67824750</v>
@@ -8857,13 +8857,13 @@
         <v>0</v>
       </c>
       <c r="E292">
-        <v>8983839723</v>
+        <v>8985177173</v>
       </c>
       <c r="F292">
-        <v>8983839723</v>
+        <v>8985177173</v>
       </c>
       <c r="G292">
-        <v>3638779204</v>
+        <v>3637441754</v>
       </c>
       <c r="H292" t="s">
         <v>9</v>
@@ -9062,16 +9062,16 @@
         <v>63706784713</v>
       </c>
       <c r="D300">
-        <v>14537066030</v>
+        <v>14479069330</v>
       </c>
       <c r="E300">
-        <v>37241558210</v>
+        <v>37320955360</v>
       </c>
       <c r="F300">
-        <v>51778624240</v>
+        <v>51800024690</v>
       </c>
       <c r="G300">
-        <v>11928160473</v>
+        <v>11906760023</v>
       </c>
       <c r="H300">
         <v>531045413</v>
@@ -9270,16 +9270,16 @@
         <v>534300000</v>
       </c>
       <c r="D308">
-        <v>140921415</v>
+        <v>179430588</v>
       </c>
       <c r="E308">
         <v>298405428</v>
       </c>
       <c r="F308">
-        <v>439326843</v>
+        <v>477836016</v>
       </c>
       <c r="G308">
-        <v>94973157</v>
+        <v>56463984</v>
       </c>
       <c r="H308" t="s">
         <v>9</v>
@@ -9296,10 +9296,10 @@
         <v>145000000</v>
       </c>
       <c r="D309">
-        <v>114740165</v>
+        <v>79616553</v>
       </c>
       <c r="E309">
-        <v>30259835</v>
+        <v>65383447</v>
       </c>
       <c r="F309">
         <v>145000000</v>
@@ -9556,16 +9556,16 @@
         <v>64614000</v>
       </c>
       <c r="D319">
-        <v>22603358</v>
+        <v>19039408</v>
       </c>
       <c r="E319">
-        <v>26763571</v>
+        <v>27827521</v>
       </c>
       <c r="F319">
-        <v>49366929</v>
+        <v>46866929</v>
       </c>
       <c r="G319">
-        <v>15247071</v>
+        <v>17747071</v>
       </c>
       <c r="H319">
         <v>21538000</v>
@@ -9582,16 +9582,16 @@
         <v>82504500</v>
       </c>
       <c r="D320">
-        <v>12818500</v>
+        <v>15318500</v>
       </c>
       <c r="E320">
         <v>58799000</v>
       </c>
       <c r="F320">
-        <v>71617500</v>
+        <v>74117500</v>
       </c>
       <c r="G320">
-        <v>10887000</v>
+        <v>8387000</v>
       </c>
       <c r="H320">
         <v>27501500</v>
@@ -9634,10 +9634,10 @@
         <v>385800000</v>
       </c>
       <c r="D322">
-        <v>133230640</v>
+        <v>131687640</v>
       </c>
       <c r="E322">
-        <v>87546635</v>
+        <v>89089635</v>
       </c>
       <c r="F322">
         <v>220777275</v>
@@ -9663,13 +9663,13 @@
         <v>0</v>
       </c>
       <c r="E323">
-        <v>127458000</v>
+        <v>127839250</v>
       </c>
       <c r="F323">
-        <v>127458000</v>
+        <v>127839250</v>
       </c>
       <c r="G323">
-        <v>45042000</v>
+        <v>44660750</v>
       </c>
       <c r="H323">
         <v>57500000</v>
@@ -9715,13 +9715,13 @@
         <v>0</v>
       </c>
       <c r="E325">
-        <v>4997633746</v>
+        <v>4997639371</v>
       </c>
       <c r="F325">
-        <v>4997633746</v>
+        <v>4997639371</v>
       </c>
       <c r="G325">
-        <v>2056158519</v>
+        <v>2056152894</v>
       </c>
       <c r="H325" t="s">
         <v>9</v>
@@ -9920,16 +9920,16 @@
         <v>30454436960</v>
       </c>
       <c r="D333">
-        <v>2299418022</v>
+        <v>2300196633</v>
       </c>
       <c r="E333">
-        <v>22502679493</v>
+        <v>22540796930</v>
       </c>
       <c r="F333">
-        <v>24802097515</v>
+        <v>24840993563</v>
       </c>
       <c r="G333">
-        <v>5652339445</v>
+        <v>5613443397</v>
       </c>
       <c r="H333">
         <v>260139500</v>
@@ -9946,10 +9946,10 @@
         <v>13755471000</v>
       </c>
       <c r="D334">
-        <v>2663944960</v>
+        <v>1137360000</v>
       </c>
       <c r="E334">
-        <v>11043387055</v>
+        <v>12569972015</v>
       </c>
       <c r="F334">
         <v>13707332015</v>
@@ -9998,10 +9998,10 @@
         <v>447807006</v>
       </c>
       <c r="D336">
+        <v>0</v>
+      </c>
+      <c r="E336">
         <v>439914019</v>
-      </c>
-      <c r="E336">
-        <v>0</v>
       </c>
       <c r="F336">
         <v>439914019</v>
@@ -10469,13 +10469,13 @@
         <v>0</v>
       </c>
       <c r="E354">
-        <v>169130250</v>
+        <v>186368250</v>
       </c>
       <c r="F354">
-        <v>169130250</v>
+        <v>186368250</v>
       </c>
       <c r="G354">
-        <v>91419750</v>
+        <v>74181750</v>
       </c>
       <c r="H354">
         <v>86850000</v>
@@ -10547,13 +10547,13 @@
         <v>0</v>
       </c>
       <c r="E357">
-        <v>7461330543</v>
+        <v>7462375181</v>
       </c>
       <c r="F357">
-        <v>7461330543</v>
+        <v>7462375181</v>
       </c>
       <c r="G357">
-        <v>3253585470</v>
+        <v>3252540832</v>
       </c>
       <c r="H357" t="s">
         <v>9</v>
@@ -10752,16 +10752,16 @@
         <v>57427089299</v>
       </c>
       <c r="D365">
-        <v>8359429365</v>
+        <v>6392930386</v>
       </c>
       <c r="E365">
-        <v>41510677482</v>
+        <v>43495459099</v>
       </c>
       <c r="F365">
-        <v>49870106847</v>
+        <v>49888389485</v>
       </c>
       <c r="G365">
-        <v>7556982452</v>
+        <v>7538699814</v>
       </c>
       <c r="H365">
         <v>526334925</v>
@@ -10856,16 +10856,16 @@
         <v>2467762918</v>
       </c>
       <c r="D369">
-        <v>1755568584</v>
+        <v>1776751650</v>
       </c>
       <c r="E369">
         <v>558800786</v>
       </c>
       <c r="F369">
-        <v>2314369370</v>
+        <v>2335552436</v>
       </c>
       <c r="G369">
-        <v>153393548</v>
+        <v>132210482</v>
       </c>
       <c r="H369" t="s">
         <v>9</v>
@@ -11168,10 +11168,10 @@
         <v>120000000</v>
       </c>
       <c r="D381">
-        <v>29057875</v>
+        <v>27345375</v>
       </c>
       <c r="E381">
-        <v>36260105</v>
+        <v>37972605</v>
       </c>
       <c r="F381">
         <v>65317980</v>
@@ -11584,16 +11584,16 @@
         <v>24628424376</v>
       </c>
       <c r="D397">
-        <v>4960466126</v>
+        <v>4979936692</v>
       </c>
       <c r="E397">
-        <v>15553603990</v>
+        <v>15555316490</v>
       </c>
       <c r="F397">
-        <v>20514070116</v>
+        <v>20535253182</v>
       </c>
       <c r="G397">
-        <v>4114354260</v>
+        <v>4093171194</v>
       </c>
       <c r="H397">
         <v>232675000</v>
@@ -12026,16 +12026,16 @@
         <v>2230000000</v>
       </c>
       <c r="D414">
-        <v>9815000</v>
+        <v>19315000</v>
       </c>
       <c r="E414">
         <v>1025934097</v>
       </c>
       <c r="F414">
-        <v>1035749097</v>
+        <v>1045249097</v>
       </c>
       <c r="G414">
-        <v>1194250903</v>
+        <v>1184750903</v>
       </c>
       <c r="H414" t="s">
         <v>9</v>
@@ -12052,16 +12052,16 @@
         <v>145200000</v>
       </c>
       <c r="D415">
-        <v>22211800</v>
+        <v>29100807</v>
       </c>
       <c r="E415">
         <v>75745500</v>
       </c>
       <c r="F415">
-        <v>97957300</v>
+        <v>104846307</v>
       </c>
       <c r="G415">
-        <v>47242700</v>
+        <v>40353693</v>
       </c>
       <c r="H415">
         <v>48400000</v>
@@ -12078,10 +12078,10 @@
         <v>445223250</v>
       </c>
       <c r="D416">
-        <v>57149700</v>
+        <v>17923100</v>
       </c>
       <c r="E416">
-        <v>381835216</v>
+        <v>421061816</v>
       </c>
       <c r="F416">
         <v>438984916</v>
@@ -12156,16 +12156,16 @@
         <v>370995500</v>
       </c>
       <c r="D419">
-        <v>29995500</v>
+        <v>43450952</v>
       </c>
       <c r="E419">
         <v>318684088</v>
       </c>
       <c r="F419">
-        <v>348679588</v>
+        <v>362135040</v>
       </c>
       <c r="G419">
-        <v>22315912</v>
+        <v>8860460</v>
       </c>
       <c r="H419">
         <v>117000000</v>
@@ -12468,16 +12468,16 @@
         <v>35458361640</v>
       </c>
       <c r="D431">
-        <v>5486225856</v>
+        <v>5476843715</v>
       </c>
       <c r="E431">
-        <v>21363370034</v>
+        <v>21402596634</v>
       </c>
       <c r="F431">
-        <v>26849595890</v>
+        <v>26879440349</v>
       </c>
       <c r="G431">
-        <v>8608765750</v>
+        <v>8578921291</v>
       </c>
       <c r="H431">
         <v>472807750</v>
@@ -13570,16 +13570,16 @@
         <v>6189486656</v>
       </c>
       <c r="D496">
-        <v>3109048832</v>
+        <v>3174815466</v>
       </c>
       <c r="E496">
-        <v>1331606604</v>
+        <v>1340866604</v>
       </c>
       <c r="F496">
-        <v>4440655436</v>
+        <v>4515682070</v>
       </c>
       <c r="G496">
-        <v>1748831220</v>
+        <v>1673804586</v>
       </c>
       <c r="H496" t="s">
         <v>9</v>
@@ -13778,10 +13778,10 @@
         <v>7401091133</v>
       </c>
       <c r="D504">
-        <v>4572970263</v>
+        <v>4553860263</v>
       </c>
       <c r="E504">
-        <v>2607739789</v>
+        <v>2626849789</v>
       </c>
       <c r="F504">
         <v>7180710052</v>
@@ -13804,16 +13804,16 @@
         <v>297500000</v>
       </c>
       <c r="D505">
-        <v>0</v>
+        <v>25024608</v>
       </c>
       <c r="E505">
         <v>100610066</v>
       </c>
       <c r="F505">
-        <v>100610066</v>
+        <v>125634674</v>
       </c>
       <c r="G505">
-        <v>196889934</v>
+        <v>171865326</v>
       </c>
       <c r="H505" t="s">
         <v>9</v>
@@ -13830,16 +13830,16 @@
         <v>266250000</v>
       </c>
       <c r="D506">
-        <v>0</v>
+        <v>47324000</v>
       </c>
       <c r="E506">
         <v>197077000</v>
       </c>
       <c r="F506">
-        <v>197077000</v>
+        <v>244401000</v>
       </c>
       <c r="G506">
-        <v>69173000</v>
+        <v>21849000</v>
       </c>
       <c r="H506" t="s">
         <v>9</v>
@@ -13882,10 +13882,10 @@
         <v>75000000</v>
       </c>
       <c r="D508">
-        <v>29699686</v>
+        <v>0</v>
       </c>
       <c r="E508">
-        <v>12720000</v>
+        <v>42419686</v>
       </c>
       <c r="F508">
         <v>42419686</v>
@@ -14038,16 +14038,16 @@
         <v>422192250</v>
       </c>
       <c r="D514">
-        <v>232599600</v>
+        <v>293939800</v>
       </c>
       <c r="E514">
         <v>60100427</v>
       </c>
       <c r="F514">
-        <v>292700027</v>
+        <v>354040227</v>
       </c>
       <c r="G514">
-        <v>129492223</v>
+        <v>68152023</v>
       </c>
       <c r="H514">
         <v>140730750</v>
@@ -14067,13 +14067,13 @@
         <v>7568076</v>
       </c>
       <c r="E515">
-        <v>374270219</v>
+        <v>375520219</v>
       </c>
       <c r="F515">
-        <v>381838295</v>
+        <v>383088295</v>
       </c>
       <c r="G515">
-        <v>134595205</v>
+        <v>133345205</v>
       </c>
       <c r="H515">
         <v>172144500</v>
@@ -14249,13 +14249,13 @@
         <v>1068968</v>
       </c>
       <c r="E522">
-        <v>8956957415</v>
+        <v>8957002415</v>
       </c>
       <c r="F522">
-        <v>8958026383</v>
+        <v>8958071383</v>
       </c>
       <c r="G522">
-        <v>3206255514</v>
+        <v>3206210514</v>
       </c>
       <c r="H522" t="s">
         <v>9</v>
@@ -14480,16 +14480,16 @@
         <v>64019485320</v>
       </c>
       <c r="D531">
-        <v>14396453605</v>
+        <v>14547099361</v>
       </c>
       <c r="E531">
-        <v>40686772553</v>
+        <v>40746137239</v>
       </c>
       <c r="F531">
-        <v>55083226158</v>
+        <v>55293236600</v>
       </c>
       <c r="G531">
-        <v>8936259162</v>
+        <v>8726248720</v>
       </c>
       <c r="H531">
         <v>850782250</v>
@@ -15029,13 +15029,13 @@
         <v>7225381</v>
       </c>
       <c r="E552">
-        <v>253789351</v>
+        <v>257889351</v>
       </c>
       <c r="F552">
-        <v>261014732</v>
+        <v>265114732</v>
       </c>
       <c r="G552">
-        <v>75787768</v>
+        <v>71687768</v>
       </c>
       <c r="H552">
         <v>112267500</v>
@@ -15107,13 +15107,13 @@
         <v>0</v>
       </c>
       <c r="E555">
-        <v>7784118830</v>
+        <v>7784233205</v>
       </c>
       <c r="F555">
-        <v>7784118830</v>
+        <v>7784233205</v>
       </c>
       <c r="G555">
-        <v>2904798036</v>
+        <v>2904683661</v>
       </c>
       <c r="H555" t="s">
         <v>9</v>
@@ -15315,13 +15315,13 @@
         <v>14075370387</v>
       </c>
       <c r="E563">
-        <v>37087452125</v>
+        <v>37091666500</v>
       </c>
       <c r="F563">
-        <v>51162822512</v>
+        <v>51167036887</v>
       </c>
       <c r="G563">
-        <v>6685859711</v>
+        <v>6681645336</v>
       </c>
       <c r="H563">
         <v>720558750</v>
@@ -15338,16 +15338,16 @@
         <v>1108157528231</v>
       </c>
       <c r="D564">
-        <v>387069966949</v>
+        <v>367038000664</v>
       </c>
       <c r="E564">
-        <v>585636774332</v>
+        <v>607166141137</v>
       </c>
       <c r="F564">
-        <v>972706741281</v>
+        <v>974204141801</v>
       </c>
       <c r="G564">
-        <v>135450786950</v>
+        <v>133953386430</v>
       </c>
       <c r="H564">
         <v>6496339824</v>

--- a/data/rka.xlsx
+++ b/data/rka.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\76193\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:40009_{6590ACE8-AF52-4EA6-B5EC-0C5CF4291360}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:40009_{F5D9173E-DFB2-4B3F-89F4-4E261BF9791D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456"/>
   </bookViews>
   <sheets>
-    <sheet name="20260914 SAP ZFM01" sheetId="1" r:id="rId1"/>
+    <sheet name="20260918 SAP ZFM01" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
   <extLst>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1094" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1093" uniqueCount="131">
   <si>
     <t>Funds Center/Commitment Item</t>
   </si>
@@ -1574,16 +1574,16 @@
         <v>17276995631</v>
       </c>
       <c r="D12">
-        <v>10467818831</v>
+        <v>10951110831</v>
       </c>
       <c r="E12">
         <v>6309951800</v>
       </c>
       <c r="F12">
-        <v>16777770631</v>
+        <v>17261062631</v>
       </c>
       <c r="G12">
-        <v>499225000</v>
+        <v>15933000</v>
       </c>
       <c r="H12" t="s">
         <v>9</v>
@@ -1704,10 +1704,10 @@
         <v>1200000000</v>
       </c>
       <c r="D17">
-        <v>92079500</v>
+        <v>53642000</v>
       </c>
       <c r="E17">
-        <v>92721500</v>
+        <v>131159000</v>
       </c>
       <c r="F17">
         <v>184801000</v>
@@ -1756,10 +1756,10 @@
         <v>3894602130</v>
       </c>
       <c r="D19">
-        <v>402739408</v>
+        <v>170226548</v>
       </c>
       <c r="E19">
-        <v>2563937629</v>
+        <v>2796450489</v>
       </c>
       <c r="F19">
         <v>2966677037</v>
@@ -1808,16 +1808,16 @@
         <v>406635000</v>
       </c>
       <c r="D21">
-        <v>78034042</v>
+        <v>76984318</v>
       </c>
       <c r="E21">
         <v>89696662</v>
       </c>
       <c r="F21">
-        <v>167730704</v>
+        <v>166680980</v>
       </c>
       <c r="G21">
-        <v>238904296</v>
+        <v>239954020</v>
       </c>
       <c r="H21" t="s">
         <v>9</v>
@@ -1886,16 +1886,16 @@
         <v>600000000</v>
       </c>
       <c r="D24">
-        <v>45991873</v>
+        <v>58975573</v>
       </c>
       <c r="E24">
         <v>200398159</v>
       </c>
       <c r="F24">
-        <v>246390032</v>
+        <v>259373732</v>
       </c>
       <c r="G24">
-        <v>353609968</v>
+        <v>340626268</v>
       </c>
       <c r="H24" t="s">
         <v>9</v>
@@ -1912,16 +1912,16 @@
         <v>1691277133</v>
       </c>
       <c r="D25">
-        <v>215556103</v>
+        <v>235047759</v>
       </c>
       <c r="E25">
-        <v>1100380691</v>
+        <v>1114855691</v>
       </c>
       <c r="F25">
-        <v>1315936794</v>
+        <v>1349903450</v>
       </c>
       <c r="G25">
-        <v>375340339</v>
+        <v>341373683</v>
       </c>
       <c r="H25" t="s">
         <v>9</v>
@@ -1993,13 +1993,13 @@
         <v>0</v>
       </c>
       <c r="E28">
-        <v>2835270464</v>
+        <v>2835880775</v>
       </c>
       <c r="F28">
-        <v>2835270464</v>
+        <v>2835880775</v>
       </c>
       <c r="G28">
-        <v>621343740</v>
+        <v>620733429</v>
       </c>
       <c r="H28" t="s">
         <v>9</v>
@@ -2354,16 +2354,16 @@
         <v>346934395851</v>
       </c>
       <c r="D42">
-        <v>199249929561</v>
+        <v>199493696833</v>
       </c>
       <c r="E42">
-        <v>133419449486</v>
+        <v>133705485157</v>
       </c>
       <c r="F42">
-        <v>332669379047</v>
+        <v>333199181990</v>
       </c>
       <c r="G42">
-        <v>14265016804</v>
+        <v>13735213861</v>
       </c>
       <c r="H42" t="s">
         <v>9</v>
@@ -2562,16 +2562,16 @@
         <v>2000000000</v>
       </c>
       <c r="D50">
-        <v>1391798724</v>
+        <v>1361195942</v>
       </c>
       <c r="E50">
         <v>491537500</v>
       </c>
       <c r="F50">
-        <v>1883336224</v>
+        <v>1852733442</v>
       </c>
       <c r="G50">
-        <v>116663776</v>
+        <v>147266558</v>
       </c>
       <c r="H50" t="s">
         <v>9</v>
@@ -2692,16 +2692,16 @@
         <v>4260000000</v>
       </c>
       <c r="D55">
-        <v>1178332074</v>
+        <v>1166697100</v>
       </c>
       <c r="E55">
-        <v>2608784178</v>
+        <v>2714774178</v>
       </c>
       <c r="F55">
-        <v>3787116252</v>
+        <v>3881471278</v>
       </c>
       <c r="G55">
-        <v>472883748</v>
+        <v>378528722</v>
       </c>
       <c r="H55" t="s">
         <v>9</v>
@@ -2744,16 +2744,16 @@
         <v>2500000000</v>
       </c>
       <c r="D57">
-        <v>972014241</v>
+        <v>971552802</v>
       </c>
       <c r="E57">
         <v>1063184691</v>
       </c>
       <c r="F57">
-        <v>2035198932</v>
+        <v>2034737493</v>
       </c>
       <c r="G57">
-        <v>464801068</v>
+        <v>465262507</v>
       </c>
       <c r="H57" t="s">
         <v>9</v>
@@ -2822,16 +2822,16 @@
         <v>2620000000</v>
       </c>
       <c r="D60">
-        <v>652442541</v>
+        <v>338042541</v>
       </c>
       <c r="E60">
         <v>815038867</v>
       </c>
       <c r="F60">
-        <v>1467481408</v>
+        <v>1153081408</v>
       </c>
       <c r="G60">
-        <v>1152518592</v>
+        <v>1466918592</v>
       </c>
       <c r="H60" t="s">
         <v>9</v>
@@ -2848,16 +2848,16 @@
         <v>750000000</v>
       </c>
       <c r="D61">
-        <v>0</v>
+        <v>481567894</v>
       </c>
       <c r="E61">
         <v>0</v>
       </c>
-      <c r="F61" t="s">
-        <v>9</v>
+      <c r="F61">
+        <v>481567894</v>
       </c>
       <c r="G61">
-        <v>750000000</v>
+        <v>268432106</v>
       </c>
       <c r="H61" t="s">
         <v>9</v>
@@ -3004,16 +3004,16 @@
         <v>400400000</v>
       </c>
       <c r="D67">
-        <v>25382510</v>
+        <v>30029168</v>
       </c>
       <c r="E67">
         <v>119056922</v>
       </c>
       <c r="F67">
-        <v>144439432</v>
+        <v>149086090</v>
       </c>
       <c r="G67">
-        <v>255960568</v>
+        <v>251313910</v>
       </c>
       <c r="H67">
         <v>139000000</v>
@@ -3024,22 +3024,22 @@
         <v>28</v>
       </c>
       <c r="B68">
-        <v>446900000</v>
+        <v>436900000</v>
       </c>
       <c r="C68">
-        <v>335175000</v>
+        <v>325175000</v>
       </c>
       <c r="D68">
-        <v>68211850</v>
+        <v>51612850</v>
       </c>
       <c r="E68">
         <v>184205025</v>
       </c>
       <c r="F68">
-        <v>252416875</v>
+        <v>235817875</v>
       </c>
       <c r="G68">
-        <v>82758125</v>
+        <v>89357125</v>
       </c>
       <c r="H68">
         <v>111725000</v>
@@ -3134,16 +3134,16 @@
         <v>354225000</v>
       </c>
       <c r="D72">
-        <v>46676000</v>
+        <v>0</v>
       </c>
       <c r="E72">
-        <v>258971750</v>
+        <v>259809250</v>
       </c>
       <c r="F72">
-        <v>305647750</v>
+        <v>259809250</v>
       </c>
       <c r="G72">
-        <v>48577250</v>
+        <v>94415750</v>
       </c>
       <c r="H72">
         <v>118075000</v>
@@ -3154,19 +3154,19 @@
         <v>33</v>
       </c>
       <c r="B73">
-        <v>80000000</v>
+        <v>70400000</v>
       </c>
       <c r="C73">
-        <v>80000000</v>
+        <v>70400000</v>
       </c>
       <c r="D73">
-        <v>9600000</v>
+        <v>0</v>
       </c>
       <c r="E73">
         <v>36832700</v>
       </c>
       <c r="F73">
-        <v>46432700</v>
+        <v>36832700</v>
       </c>
       <c r="G73">
         <v>33567300</v>
@@ -3215,13 +3215,13 @@
         <v>0</v>
       </c>
       <c r="E75">
-        <v>16581026155</v>
+        <v>16581052405</v>
       </c>
       <c r="F75">
-        <v>16581026155</v>
+        <v>16581052405</v>
       </c>
       <c r="G75">
-        <v>6350581074</v>
+        <v>6350554824</v>
       </c>
       <c r="H75" t="s">
         <v>9</v>
@@ -3440,22 +3440,22 @@
         <v>67</v>
       </c>
       <c r="B84">
-        <v>111552711691</v>
+        <v>111533111691</v>
       </c>
       <c r="C84">
-        <v>110881210191</v>
+        <v>110861610191</v>
       </c>
       <c r="D84">
-        <v>35231658637</v>
+        <v>35287898994</v>
       </c>
       <c r="E84">
-        <v>58922582079</v>
+        <v>59029435829</v>
       </c>
       <c r="F84">
-        <v>94154240716</v>
+        <v>94317334823</v>
       </c>
       <c r="G84">
-        <v>16726969475</v>
+        <v>16544275368</v>
       </c>
       <c r="H84">
         <v>671501500</v>
@@ -3576,10 +3576,10 @@
         <v>30639775739</v>
       </c>
       <c r="D89">
-        <v>16269963610</v>
+        <v>16237532610</v>
       </c>
       <c r="E89">
-        <v>12001011321</v>
+        <v>12033442321</v>
       </c>
       <c r="F89">
         <v>28270974931</v>
@@ -3628,10 +3628,10 @@
         <v>88512582</v>
       </c>
       <c r="D91">
-        <v>24168400</v>
+        <v>0</v>
       </c>
       <c r="E91">
-        <v>63569500</v>
+        <v>87737900</v>
       </c>
       <c r="F91">
         <v>87737900</v>
@@ -3706,10 +3706,10 @@
         <v>2796520000</v>
       </c>
       <c r="D94">
-        <v>768155804</v>
+        <v>763263804</v>
       </c>
       <c r="E94">
-        <v>2028357617</v>
+        <v>2033249617</v>
       </c>
       <c r="F94">
         <v>2796513421</v>
@@ -3810,16 +3810,16 @@
         <v>289155000</v>
       </c>
       <c r="D98">
-        <v>38159000</v>
+        <v>68174000</v>
       </c>
       <c r="E98">
         <v>57100000</v>
       </c>
       <c r="F98">
-        <v>95259000</v>
+        <v>125274000</v>
       </c>
       <c r="G98">
-        <v>193896000</v>
+        <v>163881000</v>
       </c>
       <c r="H98" t="s">
         <v>9</v>
@@ -3836,16 +3836,16 @@
         <v>360000000</v>
       </c>
       <c r="D99">
-        <v>108184576</v>
+        <v>93146576</v>
       </c>
       <c r="E99">
-        <v>237556000</v>
+        <v>247536000</v>
       </c>
       <c r="F99">
-        <v>345740576</v>
+        <v>340682576</v>
       </c>
       <c r="G99">
-        <v>14259424</v>
+        <v>19317424</v>
       </c>
       <c r="H99" t="s">
         <v>9</v>
@@ -3862,16 +3862,16 @@
         <v>1710494400</v>
       </c>
       <c r="D100">
-        <v>484281260</v>
+        <v>419021980</v>
       </c>
       <c r="E100">
         <v>1099212506</v>
       </c>
       <c r="F100">
-        <v>1583493766</v>
+        <v>1518234486</v>
       </c>
       <c r="G100">
-        <v>127000634</v>
+        <v>192259914</v>
       </c>
       <c r="H100" t="s">
         <v>9</v>
@@ -3888,16 +3888,16 @@
         <v>150000000</v>
       </c>
       <c r="D101">
-        <v>0</v>
+        <v>17891177</v>
       </c>
       <c r="E101">
         <v>92034500</v>
       </c>
       <c r="F101">
-        <v>92034500</v>
+        <v>109925677</v>
       </c>
       <c r="G101">
-        <v>57965500</v>
+        <v>40074323</v>
       </c>
       <c r="H101">
         <v>50000000</v>
@@ -3908,10 +3908,10 @@
         <v>27</v>
       </c>
       <c r="B102">
-        <v>534300000</v>
+        <v>462220000</v>
       </c>
       <c r="C102">
-        <v>394475000</v>
+        <v>322395000</v>
       </c>
       <c r="D102">
         <v>51550900</v>
@@ -3923,7 +3923,7 @@
         <v>96978750</v>
       </c>
       <c r="G102">
-        <v>297496250</v>
+        <v>225416250</v>
       </c>
       <c r="H102">
         <v>139825000</v>
@@ -3934,22 +3934,22 @@
         <v>28</v>
       </c>
       <c r="B103">
-        <v>341280000</v>
+        <v>413360000</v>
       </c>
       <c r="C103">
-        <v>255960000</v>
+        <v>328040000</v>
       </c>
       <c r="D103">
-        <v>43040230</v>
+        <v>59800230</v>
       </c>
       <c r="E103">
         <v>174999400</v>
       </c>
       <c r="F103">
-        <v>218039630</v>
+        <v>234799630</v>
       </c>
       <c r="G103">
-        <v>37920370</v>
+        <v>93240370</v>
       </c>
       <c r="H103">
         <v>85320000</v>
@@ -3986,10 +3986,10 @@
         <v>30</v>
       </c>
       <c r="B105">
-        <v>388800000</v>
+        <v>317761000</v>
       </c>
       <c r="C105">
-        <v>291600000</v>
+        <v>220561000</v>
       </c>
       <c r="D105">
         <v>192481700</v>
@@ -4001,7 +4001,7 @@
         <v>220560700</v>
       </c>
       <c r="G105">
-        <v>71039300</v>
+        <v>300</v>
       </c>
       <c r="H105">
         <v>97200000</v>
@@ -4012,10 +4012,10 @@
         <v>31</v>
       </c>
       <c r="B106">
-        <v>20000000</v>
+        <v>15000000</v>
       </c>
       <c r="C106">
-        <v>15000000</v>
+        <v>10000000</v>
       </c>
       <c r="D106">
         <v>0</v>
@@ -4027,7 +4027,7 @@
         <v>9</v>
       </c>
       <c r="G106">
-        <v>15000000</v>
+        <v>10000000</v>
       </c>
       <c r="H106">
         <v>5000000</v>
@@ -4038,10 +4038,10 @@
         <v>32</v>
       </c>
       <c r="B107">
-        <v>393410000</v>
+        <v>482449000</v>
       </c>
       <c r="C107">
-        <v>295057500</v>
+        <v>384096500</v>
       </c>
       <c r="D107">
         <v>0</v>
@@ -4053,7 +4053,7 @@
         <v>294691068</v>
       </c>
       <c r="G107">
-        <v>366432</v>
+        <v>89405432</v>
       </c>
       <c r="H107">
         <v>98352500</v>
@@ -4064,10 +4064,10 @@
         <v>33</v>
       </c>
       <c r="B108">
-        <v>91080000</v>
+        <v>78080000</v>
       </c>
       <c r="C108">
-        <v>91080000</v>
+        <v>78080000</v>
       </c>
       <c r="D108">
         <v>0</v>
@@ -4079,7 +4079,7 @@
         <v>38927400</v>
       </c>
       <c r="G108">
-        <v>52152600</v>
+        <v>39152600</v>
       </c>
       <c r="H108" t="s">
         <v>9</v>
@@ -4408,16 +4408,16 @@
         <v>81693644736</v>
       </c>
       <c r="D121">
-        <v>20708953028</v>
+        <v>20631830525</v>
       </c>
       <c r="E121">
-        <v>50362507523</v>
+        <v>50433978923</v>
       </c>
       <c r="F121">
-        <v>71071460551</v>
+        <v>71065809448</v>
       </c>
       <c r="G121">
-        <v>10622184185</v>
+        <v>10627835288</v>
       </c>
       <c r="H121">
         <v>475697500</v>
@@ -4434,16 +4434,16 @@
         <v>8995670000</v>
       </c>
       <c r="D122">
-        <v>5683860320</v>
+        <v>905660000</v>
       </c>
       <c r="E122">
-        <v>3020023792</v>
+        <v>7784736312</v>
       </c>
       <c r="F122">
-        <v>8703884112</v>
+        <v>8690396312</v>
       </c>
       <c r="G122">
-        <v>291785888</v>
+        <v>305273688</v>
       </c>
       <c r="H122" t="s">
         <v>9</v>
@@ -4460,16 +4460,16 @@
         <v>1494332364</v>
       </c>
       <c r="D123">
-        <v>985946819</v>
+        <v>1322137072</v>
       </c>
       <c r="E123">
         <v>127583711</v>
       </c>
       <c r="F123">
-        <v>1113530530</v>
+        <v>1449720783</v>
       </c>
       <c r="G123">
-        <v>380801834</v>
+        <v>44611581</v>
       </c>
       <c r="H123" t="s">
         <v>9</v>
@@ -4538,16 +4538,16 @@
         <v>1200699000</v>
       </c>
       <c r="D126">
-        <v>662998053</v>
+        <v>1114070165</v>
       </c>
       <c r="E126">
         <v>81220975</v>
       </c>
       <c r="F126">
-        <v>744219028</v>
+        <v>1195291140</v>
       </c>
       <c r="G126">
-        <v>456479972</v>
+        <v>5407860</v>
       </c>
       <c r="H126" t="s">
         <v>9</v>
@@ -4642,16 +4642,16 @@
         <v>530067000</v>
       </c>
       <c r="D130">
-        <v>0</v>
+        <v>217692589</v>
       </c>
       <c r="E130">
         <v>300000000</v>
       </c>
       <c r="F130">
-        <v>300000000</v>
+        <v>517692589</v>
       </c>
       <c r="G130">
-        <v>230067000</v>
+        <v>12374411</v>
       </c>
       <c r="H130" t="s">
         <v>9</v>
@@ -4902,16 +4902,16 @@
         <v>354600000</v>
       </c>
       <c r="D140">
-        <v>23757100</v>
+        <v>19400000</v>
       </c>
       <c r="E140">
-        <v>220966600</v>
+        <v>225268700</v>
       </c>
       <c r="F140">
-        <v>244723700</v>
+        <v>244668700</v>
       </c>
       <c r="G140">
-        <v>109876300</v>
+        <v>109931300</v>
       </c>
       <c r="H140" t="s">
         <v>9</v>
@@ -4983,13 +4983,13 @@
         <v>0</v>
       </c>
       <c r="E143">
-        <v>152660750</v>
+        <v>153135750</v>
       </c>
       <c r="F143">
-        <v>152660750</v>
+        <v>153135750</v>
       </c>
       <c r="G143">
-        <v>60659250</v>
+        <v>60184250</v>
       </c>
       <c r="H143" t="s">
         <v>9</v>
@@ -5061,13 +5061,13 @@
         <v>0</v>
       </c>
       <c r="E146">
-        <v>7120218600</v>
+        <v>7120231725</v>
       </c>
       <c r="F146">
-        <v>7120218600</v>
+        <v>7120231725</v>
       </c>
       <c r="G146">
-        <v>2828875483</v>
+        <v>2828862358</v>
       </c>
       <c r="H146" t="s">
         <v>9</v>
@@ -5292,16 +5292,16 @@
         <v>52473056175</v>
       </c>
       <c r="D155">
-        <v>10192080159</v>
+        <v>6414477693</v>
       </c>
       <c r="E155">
-        <v>32728688885</v>
+        <v>37498191630</v>
       </c>
       <c r="F155">
-        <v>42920769044</v>
+        <v>43912669323</v>
       </c>
       <c r="G155">
-        <v>9552287131</v>
+        <v>8560386852</v>
       </c>
       <c r="H155">
         <v>111080000</v>
@@ -5812,16 +5812,16 @@
         <v>595150000</v>
       </c>
       <c r="D175">
-        <v>70019500</v>
+        <v>74848100</v>
       </c>
       <c r="E175">
         <v>451500394</v>
       </c>
       <c r="F175">
-        <v>521519894</v>
+        <v>526348494</v>
       </c>
       <c r="G175">
-        <v>73630106</v>
+        <v>68801506</v>
       </c>
       <c r="H175">
         <v>136250000</v>
@@ -5919,13 +5919,13 @@
         <v>0</v>
       </c>
       <c r="E179">
-        <v>128090250</v>
+        <v>130265250</v>
       </c>
       <c r="F179">
-        <v>128090250</v>
+        <v>130265250</v>
       </c>
       <c r="G179">
-        <v>34211250</v>
+        <v>32036250</v>
       </c>
       <c r="H179">
         <v>54100500</v>
@@ -5971,13 +5971,13 @@
         <v>0</v>
       </c>
       <c r="E181">
-        <v>5305591988</v>
+        <v>5305635113</v>
       </c>
       <c r="F181">
-        <v>5305591988</v>
+        <v>5305635113</v>
       </c>
       <c r="G181">
-        <v>2199131390</v>
+        <v>2199088265</v>
       </c>
       <c r="H181" t="s">
         <v>9</v>
@@ -6176,16 +6176,16 @@
         <v>46375593027</v>
       </c>
       <c r="D189">
-        <v>8793083294</v>
+        <v>8797911894</v>
       </c>
       <c r="E189">
-        <v>30180942065</v>
+        <v>30183160190</v>
       </c>
       <c r="F189">
-        <v>38974025359</v>
+        <v>38981072084</v>
       </c>
       <c r="G189">
-        <v>7401567668</v>
+        <v>7394520943</v>
       </c>
       <c r="H189">
         <v>449400500</v>
@@ -6202,10 +6202,10 @@
         <v>7317456560</v>
       </c>
       <c r="D190">
-        <v>3256309220</v>
+        <v>729734800</v>
       </c>
       <c r="E190">
-        <v>4060495000</v>
+        <v>6587069420</v>
       </c>
       <c r="F190">
         <v>7316804220</v>
@@ -6306,10 +6306,10 @@
         <v>296447320</v>
       </c>
       <c r="D194">
-        <v>1100000</v>
+        <v>0</v>
       </c>
       <c r="E194">
-        <v>289464000</v>
+        <v>290564000</v>
       </c>
       <c r="F194">
         <v>290564000</v>
@@ -6410,10 +6410,10 @@
         <v>469000000</v>
       </c>
       <c r="D198">
-        <v>84376635</v>
+        <v>53374985</v>
       </c>
       <c r="E198">
-        <v>64102434</v>
+        <v>95104084</v>
       </c>
       <c r="F198">
         <v>148479069</v>
@@ -6488,10 +6488,10 @@
         <v>1862650000</v>
       </c>
       <c r="D201">
-        <v>310005157</v>
+        <v>188748057</v>
       </c>
       <c r="E201">
-        <v>1416159706</v>
+        <v>1537416806</v>
       </c>
       <c r="F201">
         <v>1726164863</v>
@@ -6800,16 +6800,16 @@
         <v>385534500</v>
       </c>
       <c r="D213">
-        <v>25480000</v>
+        <v>26010000</v>
       </c>
       <c r="E213">
-        <v>274473000</v>
+        <v>275948000</v>
       </c>
       <c r="F213">
-        <v>299953000</v>
+        <v>301958000</v>
       </c>
       <c r="G213">
-        <v>85581500</v>
+        <v>83576500</v>
       </c>
       <c r="H213">
         <v>128511500</v>
@@ -6907,13 +6907,13 @@
         <v>0</v>
       </c>
       <c r="E217">
-        <v>174619250</v>
+        <v>189485250</v>
       </c>
       <c r="F217">
-        <v>174619250</v>
+        <v>189485250</v>
       </c>
       <c r="G217">
-        <v>45880750</v>
+        <v>31014750</v>
       </c>
       <c r="H217" t="s">
         <v>9</v>
@@ -6985,13 +6985,13 @@
         <v>0</v>
       </c>
       <c r="E220">
-        <v>7090468030</v>
+        <v>7091438430</v>
       </c>
       <c r="F220">
-        <v>7090468030</v>
+        <v>7091438430</v>
       </c>
       <c r="G220">
-        <v>2732694096</v>
+        <v>2731723696</v>
       </c>
       <c r="H220" t="s">
         <v>9</v>
@@ -7190,16 +7190,16 @@
         <v>47546983545</v>
       </c>
       <c r="D228">
-        <v>11351831360</v>
+        <v>8672428190</v>
       </c>
       <c r="E228">
-        <v>28931351156</v>
+        <v>31628595726</v>
       </c>
       <c r="F228">
-        <v>40283182516</v>
+        <v>40301023916</v>
       </c>
       <c r="G228">
-        <v>7263801029</v>
+        <v>7245959629</v>
       </c>
       <c r="H228">
         <v>319761500</v>
@@ -7216,10 +7216,10 @@
         <v>12264606000</v>
       </c>
       <c r="D229">
-        <v>8042712730</v>
+        <v>7985422730</v>
       </c>
       <c r="E229">
-        <v>3888767000</v>
+        <v>3946057000</v>
       </c>
       <c r="F229">
         <v>11931479730</v>
@@ -7320,16 +7320,16 @@
         <v>200000000</v>
       </c>
       <c r="D233">
-        <v>111648138</v>
+        <v>116645170</v>
       </c>
       <c r="E233">
         <v>80120815</v>
       </c>
       <c r="F233">
-        <v>191768953</v>
+        <v>196765985</v>
       </c>
       <c r="G233">
-        <v>8231047</v>
+        <v>3234015</v>
       </c>
       <c r="H233" t="s">
         <v>9</v>
@@ -7554,16 +7554,16 @@
         <v>780000000</v>
       </c>
       <c r="D242">
-        <v>674650000</v>
+        <v>199650000</v>
       </c>
       <c r="E242">
-        <v>46200000</v>
+        <v>511700000</v>
       </c>
       <c r="F242">
-        <v>720850000</v>
+        <v>711350000</v>
       </c>
       <c r="G242">
-        <v>59150000</v>
+        <v>68650000</v>
       </c>
       <c r="H242">
         <v>260000000</v>
@@ -7658,16 +7658,16 @@
         <v>354238500</v>
       </c>
       <c r="D246">
-        <v>27176500</v>
+        <v>25842500</v>
       </c>
       <c r="E246">
-        <v>315684400</v>
+        <v>316957400</v>
       </c>
       <c r="F246">
-        <v>342860900</v>
+        <v>342799900</v>
       </c>
       <c r="G246">
-        <v>11377600</v>
+        <v>11438600</v>
       </c>
       <c r="H246">
         <v>118079500</v>
@@ -7739,13 +7739,13 @@
         <v>0</v>
       </c>
       <c r="E249">
-        <v>157677750</v>
+        <v>159184000</v>
       </c>
       <c r="F249">
-        <v>157677750</v>
+        <v>159184000</v>
       </c>
       <c r="G249">
-        <v>44606250</v>
+        <v>43100000</v>
       </c>
       <c r="H249">
         <v>67428000</v>
@@ -7791,13 +7791,13 @@
         <v>0</v>
       </c>
       <c r="E251">
-        <v>6996342351</v>
+        <v>6996377976</v>
       </c>
       <c r="F251">
-        <v>6996342351</v>
+        <v>6996377976</v>
       </c>
       <c r="G251">
-        <v>2829613819</v>
+        <v>2829578194</v>
       </c>
       <c r="H251" t="s">
         <v>9</v>
@@ -8022,16 +8022,16 @@
         <v>48914772555</v>
       </c>
       <c r="D260">
-        <v>11062192178</v>
+        <v>10533565210</v>
       </c>
       <c r="E260">
-        <v>30130830189</v>
+        <v>30656435064</v>
       </c>
       <c r="F260">
-        <v>41193022367</v>
+        <v>41190000274</v>
       </c>
       <c r="G260">
-        <v>7721750188</v>
+        <v>7724772281</v>
       </c>
       <c r="H260">
         <v>525212165</v>
@@ -8230,16 +8230,16 @@
         <v>3609800000</v>
       </c>
       <c r="D268">
-        <v>1602606751</v>
+        <v>1661715751</v>
       </c>
       <c r="E268">
         <v>822578455</v>
       </c>
       <c r="F268">
-        <v>2425185206</v>
+        <v>2484294206</v>
       </c>
       <c r="G268">
-        <v>1184614794</v>
+        <v>1125505794</v>
       </c>
       <c r="H268" t="s">
         <v>9</v>
@@ -8282,10 +8282,10 @@
         <v>1240000000</v>
       </c>
       <c r="D270">
-        <v>883234492</v>
+        <v>480457432</v>
       </c>
       <c r="E270">
-        <v>116883614</v>
+        <v>519660674</v>
       </c>
       <c r="F270">
         <v>1000118106</v>
@@ -8308,16 +8308,16 @@
         <v>150000000</v>
       </c>
       <c r="D271">
-        <v>0</v>
+        <v>29165900</v>
       </c>
       <c r="E271">
         <v>46982180</v>
       </c>
       <c r="F271">
-        <v>46982180</v>
+        <v>76148080</v>
       </c>
       <c r="G271">
-        <v>103017820</v>
+        <v>73851920</v>
       </c>
       <c r="H271" t="s">
         <v>9</v>
@@ -8334,16 +8334,16 @@
         <v>2668302662</v>
       </c>
       <c r="D272">
-        <v>0</v>
+        <v>27700000</v>
       </c>
       <c r="E272">
         <v>2612869000</v>
       </c>
       <c r="F272">
-        <v>2612869000</v>
+        <v>2640569000</v>
       </c>
       <c r="G272">
-        <v>55433662</v>
+        <v>27733662</v>
       </c>
       <c r="H272" t="s">
         <v>9</v>
@@ -8464,16 +8464,16 @@
         <v>3309100507</v>
       </c>
       <c r="D277">
-        <v>1991152004</v>
+        <v>2001151740</v>
       </c>
       <c r="E277">
         <v>569806840</v>
       </c>
       <c r="F277">
-        <v>2560958844</v>
+        <v>2570958580</v>
       </c>
       <c r="G277">
-        <v>748141663</v>
+        <v>738141927</v>
       </c>
       <c r="H277" t="s">
         <v>9</v>
@@ -8594,10 +8594,10 @@
         <v>346377600</v>
       </c>
       <c r="D282">
-        <v>39199980</v>
+        <v>0</v>
       </c>
       <c r="E282">
-        <v>219200000</v>
+        <v>258399980</v>
       </c>
       <c r="F282">
         <v>258399980</v>
@@ -8646,16 +8646,16 @@
         <v>235553350</v>
       </c>
       <c r="D284">
-        <v>107400000</v>
+        <v>118623893</v>
       </c>
       <c r="E284">
         <v>56925714</v>
       </c>
       <c r="F284">
-        <v>164325714</v>
+        <v>175549607</v>
       </c>
       <c r="G284">
-        <v>71227636</v>
+        <v>60003743</v>
       </c>
       <c r="H284">
         <v>20684450</v>
@@ -8672,16 +8672,16 @@
         <v>470406638</v>
       </c>
       <c r="D285">
-        <v>131370322</v>
+        <v>99647500</v>
       </c>
       <c r="E285">
-        <v>282876433</v>
+        <v>313781933</v>
       </c>
       <c r="F285">
-        <v>414246755</v>
+        <v>413429433</v>
       </c>
       <c r="G285">
-        <v>56159883</v>
+        <v>56977205</v>
       </c>
       <c r="H285">
         <v>156802213</v>
@@ -8724,16 +8724,16 @@
         <v>388702000</v>
       </c>
       <c r="D287">
-        <v>111568199</v>
+        <v>148761000</v>
       </c>
       <c r="E287">
-        <v>116129811</v>
+        <v>123730811</v>
       </c>
       <c r="F287">
-        <v>227698010</v>
+        <v>272491811</v>
       </c>
       <c r="G287">
-        <v>161003990</v>
+        <v>116210189</v>
       </c>
       <c r="H287">
         <v>235734000</v>
@@ -8753,13 +8753,13 @@
         <v>0</v>
       </c>
       <c r="E288">
-        <v>232898250</v>
+        <v>233660750</v>
       </c>
       <c r="F288">
-        <v>232898250</v>
+        <v>233660750</v>
       </c>
       <c r="G288">
-        <v>115576000</v>
+        <v>114813500</v>
       </c>
       <c r="H288">
         <v>67824750</v>
@@ -8857,13 +8857,13 @@
         <v>0</v>
       </c>
       <c r="E292">
-        <v>8985177173</v>
+        <v>8985188423</v>
       </c>
       <c r="F292">
-        <v>8985177173</v>
+        <v>8985188423</v>
       </c>
       <c r="G292">
-        <v>3637441754</v>
+        <v>3637430504</v>
       </c>
       <c r="H292" t="s">
         <v>9</v>
@@ -9062,16 +9062,16 @@
         <v>63706784713</v>
       </c>
       <c r="D300">
-        <v>14479069330</v>
+        <v>14179760798</v>
       </c>
       <c r="E300">
-        <v>37320955360</v>
+        <v>37802212650</v>
       </c>
       <c r="F300">
-        <v>51800024690</v>
+        <v>51981973448</v>
       </c>
       <c r="G300">
-        <v>11906760023</v>
+        <v>11724811265</v>
       </c>
       <c r="H300">
         <v>531045413</v>
@@ -9088,16 +9088,16 @@
         <v>3628073000</v>
       </c>
       <c r="D301">
-        <v>348213000</v>
+        <v>340158685</v>
       </c>
       <c r="E301">
         <v>3279858000</v>
       </c>
       <c r="F301">
-        <v>3628071000</v>
+        <v>3620016685</v>
       </c>
       <c r="G301">
-        <v>2000</v>
+        <v>8056315</v>
       </c>
       <c r="H301" t="s">
         <v>9</v>
@@ -9192,10 +9192,10 @@
         <v>298750000</v>
       </c>
       <c r="D305">
-        <v>232513230</v>
+        <v>202246293</v>
       </c>
       <c r="E305">
-        <v>65826870</v>
+        <v>96093807</v>
       </c>
       <c r="F305">
         <v>298340100</v>
@@ -9244,10 +9244,10 @@
         <v>1222108000</v>
       </c>
       <c r="D307">
-        <v>155107114</v>
+        <v>117131114</v>
       </c>
       <c r="E307">
-        <v>1066657271</v>
+        <v>1104633271</v>
       </c>
       <c r="F307">
         <v>1221764385</v>
@@ -9270,10 +9270,10 @@
         <v>534300000</v>
       </c>
       <c r="D308">
-        <v>179430588</v>
+        <v>169435823</v>
       </c>
       <c r="E308">
-        <v>298405428</v>
+        <v>308400193</v>
       </c>
       <c r="F308">
         <v>477836016</v>
@@ -9504,16 +9504,16 @@
         <v>111310000</v>
       </c>
       <c r="D317">
-        <v>59854600</v>
+        <v>0</v>
       </c>
       <c r="E317">
-        <v>21262500</v>
+        <v>79542700</v>
       </c>
       <c r="F317">
-        <v>81117100</v>
+        <v>79542700</v>
       </c>
       <c r="G317">
-        <v>30192900</v>
+        <v>31767300</v>
       </c>
       <c r="H317" t="s">
         <v>9</v>
@@ -9556,10 +9556,10 @@
         <v>64614000</v>
       </c>
       <c r="D319">
-        <v>19039408</v>
+        <v>17929258</v>
       </c>
       <c r="E319">
-        <v>27827521</v>
+        <v>28937671</v>
       </c>
       <c r="F319">
         <v>46866929</v>
@@ -9628,22 +9628,22 @@
         <v>30</v>
       </c>
       <c r="B322">
-        <v>514400000</v>
+        <v>474400000</v>
       </c>
       <c r="C322">
-        <v>385800000</v>
+        <v>345800000</v>
       </c>
       <c r="D322">
-        <v>131687640</v>
+        <v>146146460</v>
       </c>
       <c r="E322">
         <v>89089635</v>
       </c>
       <c r="F322">
-        <v>220777275</v>
+        <v>235236095</v>
       </c>
       <c r="G322">
-        <v>165022725</v>
+        <v>110563905</v>
       </c>
       <c r="H322">
         <v>128600000</v>
@@ -9663,13 +9663,13 @@
         <v>0</v>
       </c>
       <c r="E323">
-        <v>127839250</v>
+        <v>139796500</v>
       </c>
       <c r="F323">
-        <v>127839250</v>
+        <v>139796500</v>
       </c>
       <c r="G323">
-        <v>44660750</v>
+        <v>32703500</v>
       </c>
       <c r="H323">
         <v>57500000</v>
@@ -9715,13 +9715,13 @@
         <v>0</v>
       </c>
       <c r="E325">
-        <v>4997639371</v>
+        <v>4998418396</v>
       </c>
       <c r="F325">
-        <v>4997639371</v>
+        <v>4998418396</v>
       </c>
       <c r="G325">
-        <v>2056152894</v>
+        <v>2055373869</v>
       </c>
       <c r="H325" t="s">
         <v>9</v>
@@ -9914,22 +9914,22 @@
         <v>88</v>
       </c>
       <c r="B333">
-        <v>30714576460</v>
+        <v>30674576460</v>
       </c>
       <c r="C333">
-        <v>30454436960</v>
+        <v>30414436960</v>
       </c>
       <c r="D333">
-        <v>2300196633</v>
+        <v>2167398686</v>
       </c>
       <c r="E333">
-        <v>22540796930</v>
+        <v>22691161257</v>
       </c>
       <c r="F333">
-        <v>24840993563</v>
+        <v>24858559943</v>
       </c>
       <c r="G333">
-        <v>5613443397</v>
+        <v>5555877017</v>
       </c>
       <c r="H333">
         <v>260139500</v>
@@ -10024,16 +10024,16 @@
         <v>2593734264</v>
       </c>
       <c r="D337">
-        <v>723018000</v>
+        <v>720248400</v>
       </c>
       <c r="E337">
         <v>1870716210</v>
       </c>
       <c r="F337">
-        <v>2593734210</v>
+        <v>2590964610</v>
       </c>
       <c r="G337">
-        <v>54</v>
+        <v>2769654</v>
       </c>
       <c r="H337" t="s">
         <v>9</v>
@@ -10050,16 +10050,16 @@
         <v>213056448</v>
       </c>
       <c r="D338">
-        <v>177539800</v>
+        <v>175409320</v>
       </c>
       <c r="E338">
         <v>33060600</v>
       </c>
       <c r="F338">
-        <v>210600400</v>
+        <v>208469920</v>
       </c>
       <c r="G338">
-        <v>2456048</v>
+        <v>4586528</v>
       </c>
       <c r="H338" t="s">
         <v>9</v>
@@ -10128,16 +10128,16 @@
         <v>1748195004</v>
       </c>
       <c r="D341">
-        <v>250654563</v>
+        <v>227042154</v>
       </c>
       <c r="E341">
-        <v>1362186775</v>
+        <v>1395795386</v>
       </c>
       <c r="F341">
-        <v>1612841338</v>
+        <v>1622837540</v>
       </c>
       <c r="G341">
-        <v>135353666</v>
+        <v>125357464</v>
       </c>
       <c r="H341" t="s">
         <v>9</v>
@@ -10154,10 +10154,10 @@
         <v>327155000</v>
       </c>
       <c r="D342">
-        <v>40400000</v>
+        <v>0</v>
       </c>
       <c r="E342">
-        <v>260006680</v>
+        <v>300406680</v>
       </c>
       <c r="F342">
         <v>300406680</v>
@@ -10206,16 +10206,16 @@
         <v>1515585000</v>
       </c>
       <c r="D344">
-        <v>480700000</v>
+        <v>491190000</v>
       </c>
       <c r="E344">
         <v>1022239000</v>
       </c>
       <c r="F344">
-        <v>1502939000</v>
+        <v>1513429000</v>
       </c>
       <c r="G344">
-        <v>12646000</v>
+        <v>2156000</v>
       </c>
       <c r="H344" t="s">
         <v>9</v>
@@ -10232,16 +10232,16 @@
         <v>600000000</v>
       </c>
       <c r="D345">
-        <v>478435648</v>
+        <v>471000000</v>
       </c>
       <c r="E345">
         <v>0</v>
       </c>
       <c r="F345">
-        <v>478435648</v>
+        <v>471000000</v>
       </c>
       <c r="G345">
-        <v>121564352</v>
+        <v>129000000</v>
       </c>
       <c r="H345" t="s">
         <v>9</v>
@@ -10258,16 +10258,16 @@
         <v>1000000000</v>
       </c>
       <c r="D346">
-        <v>260000000</v>
+        <v>258700000</v>
       </c>
       <c r="E346">
         <v>737260500</v>
       </c>
       <c r="F346">
-        <v>997260500</v>
+        <v>995960500</v>
       </c>
       <c r="G346">
-        <v>2739500</v>
+        <v>4039500</v>
       </c>
       <c r="H346" t="s">
         <v>9</v>
@@ -10336,16 +10336,16 @@
         <v>2911760000</v>
       </c>
       <c r="D349">
-        <v>292257770</v>
+        <v>901040</v>
       </c>
       <c r="E349">
         <v>1650655501</v>
       </c>
       <c r="F349">
-        <v>1942913271</v>
+        <v>1651556541</v>
       </c>
       <c r="G349">
-        <v>968846729</v>
+        <v>1260203459</v>
       </c>
       <c r="H349" t="s">
         <v>9</v>
@@ -10362,10 +10362,10 @@
         <v>135000000</v>
       </c>
       <c r="D350">
-        <v>12000000</v>
+        <v>6000000</v>
       </c>
       <c r="E350">
-        <v>79286598</v>
+        <v>85286598</v>
       </c>
       <c r="F350">
         <v>91286598</v>
@@ -10469,13 +10469,13 @@
         <v>0</v>
       </c>
       <c r="E354">
-        <v>186368250</v>
+        <v>189093250</v>
       </c>
       <c r="F354">
-        <v>186368250</v>
+        <v>189093250</v>
       </c>
       <c r="G354">
-        <v>74181750</v>
+        <v>71456750</v>
       </c>
       <c r="H354">
         <v>86850000</v>
@@ -10547,13 +10547,13 @@
         <v>0</v>
       </c>
       <c r="E357">
-        <v>7462375181</v>
+        <v>7462468931</v>
       </c>
       <c r="F357">
-        <v>7462375181</v>
+        <v>7462468931</v>
       </c>
       <c r="G357">
-        <v>3252540832</v>
+        <v>3252447082</v>
       </c>
       <c r="H357" t="s">
         <v>9</v>
@@ -10596,10 +10596,10 @@
         <v>10532164202</v>
       </c>
       <c r="D359">
-        <v>32608180</v>
+        <v>0</v>
       </c>
       <c r="E359">
-        <v>8834277017</v>
+        <v>8866885197</v>
       </c>
       <c r="F359">
         <v>8866885197</v>
@@ -10700,10 +10700,10 @@
         <v>1523018104</v>
       </c>
       <c r="D363">
-        <v>811692</v>
+        <v>0</v>
       </c>
       <c r="E363">
-        <v>1236176601</v>
+        <v>1236988293</v>
       </c>
       <c r="F363">
         <v>1236988293</v>
@@ -10752,16 +10752,16 @@
         <v>57427089299</v>
       </c>
       <c r="D365">
-        <v>6392930386</v>
+        <v>5994995647</v>
       </c>
       <c r="E365">
-        <v>43495459099</v>
+        <v>43611706332</v>
       </c>
       <c r="F365">
-        <v>49888389485</v>
+        <v>49606701979</v>
       </c>
       <c r="G365">
-        <v>7538699814</v>
+        <v>7820387320</v>
       </c>
       <c r="H365">
         <v>526334925</v>
@@ -10856,10 +10856,10 @@
         <v>2467762918</v>
       </c>
       <c r="D369">
-        <v>1776751650</v>
+        <v>1757395220</v>
       </c>
       <c r="E369">
-        <v>558800786</v>
+        <v>578157216</v>
       </c>
       <c r="F369">
         <v>2335552436</v>
@@ -10934,16 +10934,16 @@
         <v>1714789867</v>
       </c>
       <c r="D372">
-        <v>951703341</v>
+        <v>981827471</v>
       </c>
       <c r="E372">
         <v>732962308</v>
       </c>
       <c r="F372">
-        <v>1684665649</v>
+        <v>1714789779</v>
       </c>
       <c r="G372">
-        <v>30124218</v>
+        <v>88</v>
       </c>
       <c r="H372" t="s">
         <v>9</v>
@@ -11194,10 +11194,10 @@
         <v>300000000</v>
       </c>
       <c r="D382">
-        <v>67912000</v>
+        <v>57624250</v>
       </c>
       <c r="E382">
-        <v>194814712</v>
+        <v>205102462</v>
       </c>
       <c r="F382">
         <v>262726712</v>
@@ -11584,16 +11584,16 @@
         <v>24628424376</v>
       </c>
       <c r="D397">
-        <v>4979936692</v>
+        <v>4980416642</v>
       </c>
       <c r="E397">
-        <v>15555316490</v>
+        <v>15584960670</v>
       </c>
       <c r="F397">
-        <v>20535253182</v>
+        <v>20565377312</v>
       </c>
       <c r="G397">
-        <v>4093171194</v>
+        <v>4063047064</v>
       </c>
       <c r="H397">
         <v>232675000</v>
@@ -12000,16 +12000,16 @@
         <v>316800000</v>
       </c>
       <c r="D413">
-        <v>0</v>
+        <v>62315000</v>
       </c>
       <c r="E413">
         <v>179720150</v>
       </c>
       <c r="F413">
-        <v>179720150</v>
+        <v>242035150</v>
       </c>
       <c r="G413">
-        <v>137079850</v>
+        <v>74764850</v>
       </c>
       <c r="H413" t="s">
         <v>9</v>
@@ -12052,16 +12052,16 @@
         <v>145200000</v>
       </c>
       <c r="D415">
-        <v>29100807</v>
+        <v>37536807</v>
       </c>
       <c r="E415">
         <v>75745500</v>
       </c>
       <c r="F415">
-        <v>104846307</v>
+        <v>113282307</v>
       </c>
       <c r="G415">
-        <v>40353693</v>
+        <v>31917693</v>
       </c>
       <c r="H415">
         <v>48400000</v>
@@ -12156,10 +12156,10 @@
         <v>370995500</v>
       </c>
       <c r="D419">
-        <v>43450952</v>
+        <v>13455452</v>
       </c>
       <c r="E419">
-        <v>318684088</v>
+        <v>348679588</v>
       </c>
       <c r="F419">
         <v>362135040</v>
@@ -12312,10 +12312,10 @@
         <v>9379568492</v>
       </c>
       <c r="D425">
-        <v>26591563</v>
+        <v>0</v>
       </c>
       <c r="E425">
-        <v>7295042089</v>
+        <v>7321633652</v>
       </c>
       <c r="F425">
         <v>7321633652</v>
@@ -12468,16 +12468,16 @@
         <v>35458361640</v>
       </c>
       <c r="D431">
-        <v>5476843715</v>
+        <v>5491007652</v>
       </c>
       <c r="E431">
-        <v>21402596634</v>
+        <v>21459183697</v>
       </c>
       <c r="F431">
-        <v>26879440349</v>
+        <v>26950191349</v>
       </c>
       <c r="G431">
-        <v>8578921291</v>
+        <v>8508170291</v>
       </c>
       <c r="H431">
         <v>472807750</v>
@@ -13362,10 +13362,10 @@
         <v>10505111000</v>
       </c>
       <c r="D488">
-        <v>2311037927</v>
+        <v>1603170600</v>
       </c>
       <c r="E488">
-        <v>8168949047</v>
+        <v>8876816374</v>
       </c>
       <c r="F488">
         <v>10479986974</v>
@@ -13544,16 +13544,16 @@
         <v>2312795000</v>
       </c>
       <c r="D495">
-        <v>1255550010</v>
+        <v>1462735010</v>
       </c>
       <c r="E495">
         <v>654993954</v>
       </c>
       <c r="F495">
-        <v>1910543964</v>
+        <v>2117728964</v>
       </c>
       <c r="G495">
-        <v>402251036</v>
+        <v>195066036</v>
       </c>
       <c r="H495" t="s">
         <v>9</v>
@@ -13570,16 +13570,16 @@
         <v>6189486656</v>
       </c>
       <c r="D496">
-        <v>3174815466</v>
+        <v>4346193186</v>
       </c>
       <c r="E496">
-        <v>1340866604</v>
+        <v>1385897604</v>
       </c>
       <c r="F496">
-        <v>4515682070</v>
+        <v>5732090790</v>
       </c>
       <c r="G496">
-        <v>1673804586</v>
+        <v>457395866</v>
       </c>
       <c r="H496" t="s">
         <v>9</v>
@@ -13752,10 +13752,10 @@
         <v>745000000</v>
       </c>
       <c r="D503">
-        <v>673853563</v>
+        <v>668065563</v>
       </c>
       <c r="E503">
-        <v>51881480</v>
+        <v>57669480</v>
       </c>
       <c r="F503">
         <v>725735043</v>
@@ -13778,10 +13778,10 @@
         <v>7401091133</v>
       </c>
       <c r="D504">
-        <v>4553860263</v>
+        <v>4042531251</v>
       </c>
       <c r="E504">
-        <v>2626849789</v>
+        <v>3138178801</v>
       </c>
       <c r="F504">
         <v>7180710052</v>
@@ -13804,16 +13804,16 @@
         <v>297500000</v>
       </c>
       <c r="D505">
-        <v>25024608</v>
+        <v>195485808</v>
       </c>
       <c r="E505">
         <v>100610066</v>
       </c>
       <c r="F505">
-        <v>125634674</v>
+        <v>296095874</v>
       </c>
       <c r="G505">
-        <v>171865326</v>
+        <v>1404126</v>
       </c>
       <c r="H505" t="s">
         <v>9</v>
@@ -13934,10 +13934,10 @@
         <v>2560000000</v>
       </c>
       <c r="D510">
-        <v>23732367</v>
+        <v>8404406</v>
       </c>
       <c r="E510">
-        <v>1687140714</v>
+        <v>1702468675</v>
       </c>
       <c r="F510">
         <v>1710873081</v>
@@ -14067,13 +14067,13 @@
         <v>7568076</v>
       </c>
       <c r="E515">
-        <v>375520219</v>
+        <v>376720219</v>
       </c>
       <c r="F515">
-        <v>383088295</v>
+        <v>384288295</v>
       </c>
       <c r="G515">
-        <v>133345205</v>
+        <v>132145205</v>
       </c>
       <c r="H515">
         <v>172144500</v>
@@ -14249,13 +14249,13 @@
         <v>1068968</v>
       </c>
       <c r="E522">
-        <v>8957002415</v>
+        <v>8957039915</v>
       </c>
       <c r="F522">
-        <v>8958071383</v>
+        <v>8958108883</v>
       </c>
       <c r="G522">
-        <v>3206210514</v>
+        <v>3206173014</v>
       </c>
       <c r="H522" t="s">
         <v>9</v>
@@ -14480,16 +14480,16 @@
         <v>64019485320</v>
       </c>
       <c r="D531">
-        <v>14547099361</v>
+        <v>14855810981</v>
       </c>
       <c r="E531">
-        <v>40746137239</v>
+        <v>42032718039</v>
       </c>
       <c r="F531">
-        <v>55293236600</v>
+        <v>56888529020</v>
       </c>
       <c r="G531">
-        <v>8726248720</v>
+        <v>7130956300</v>
       </c>
       <c r="H531">
         <v>850782250</v>
@@ -14662,10 +14662,10 @@
         <v>11576266001</v>
       </c>
       <c r="D538">
-        <v>7366219160</v>
+        <v>7360714296</v>
       </c>
       <c r="E538">
-        <v>4140429499</v>
+        <v>4145934363</v>
       </c>
       <c r="F538">
         <v>11506648659</v>
@@ -14688,16 +14688,16 @@
         <v>2103744312</v>
       </c>
       <c r="D539">
-        <v>1036023487</v>
+        <v>1129375087</v>
       </c>
       <c r="E539">
-        <v>699348736</v>
+        <v>727358736</v>
       </c>
       <c r="F539">
-        <v>1735372223</v>
+        <v>1856733823</v>
       </c>
       <c r="G539">
-        <v>368372089</v>
+        <v>247010489</v>
       </c>
       <c r="H539" t="s">
         <v>9</v>
@@ -14870,10 +14870,10 @@
         <v>579713600</v>
       </c>
       <c r="D546">
-        <v>83158950</v>
+        <v>79128950</v>
       </c>
       <c r="E546">
-        <v>199030350</v>
+        <v>203060350</v>
       </c>
       <c r="F546">
         <v>282189300</v>
@@ -14896,10 +14896,10 @@
         <v>1539315000</v>
       </c>
       <c r="D547">
-        <v>6712544</v>
+        <v>6368850</v>
       </c>
       <c r="E547">
-        <v>933071899</v>
+        <v>933415593</v>
       </c>
       <c r="F547">
         <v>939784443</v>
@@ -14948,10 +14948,10 @@
         <v>532875000</v>
       </c>
       <c r="D549">
-        <v>52322721</v>
+        <v>51322721</v>
       </c>
       <c r="E549">
-        <v>167536270</v>
+        <v>168536270</v>
       </c>
       <c r="F549">
         <v>219858991</v>
@@ -15000,16 +15000,16 @@
         <v>395748750</v>
       </c>
       <c r="D551">
-        <v>2492800</v>
+        <v>12560735</v>
       </c>
       <c r="E551">
         <v>353426819</v>
       </c>
       <c r="F551">
-        <v>355919619</v>
+        <v>365987554</v>
       </c>
       <c r="G551">
-        <v>39829131</v>
+        <v>29761196</v>
       </c>
       <c r="H551">
         <v>131916250</v>
@@ -15026,16 +15026,16 @@
         <v>336802500</v>
       </c>
       <c r="D552">
-        <v>7225381</v>
+        <v>7700381</v>
       </c>
       <c r="E552">
-        <v>257889351</v>
+        <v>264108101</v>
       </c>
       <c r="F552">
-        <v>265114732</v>
+        <v>271808482</v>
       </c>
       <c r="G552">
-        <v>71687768</v>
+        <v>64994018</v>
       </c>
       <c r="H552">
         <v>112267500</v>
@@ -15107,13 +15107,13 @@
         <v>0</v>
       </c>
       <c r="E555">
-        <v>7784233205</v>
+        <v>7784363518</v>
       </c>
       <c r="F555">
-        <v>7784233205</v>
+        <v>7784363518</v>
       </c>
       <c r="G555">
-        <v>2904683661</v>
+        <v>2904553348</v>
       </c>
       <c r="H555" t="s">
         <v>9</v>
@@ -15312,16 +15312,16 @@
         <v>57848682223</v>
       </c>
       <c r="D563">
-        <v>14075370387</v>
+        <v>14168386364</v>
       </c>
       <c r="E563">
-        <v>37091666500</v>
+        <v>37136904121</v>
       </c>
       <c r="F563">
-        <v>51167036887</v>
+        <v>51305290485</v>
       </c>
       <c r="G563">
-        <v>6681645336</v>
+        <v>6543391738</v>
       </c>
       <c r="H563">
         <v>720558750</v>
@@ -15332,22 +15332,22 @@
         <v>130</v>
       </c>
       <c r="B564">
-        <v>1114653868055</v>
+        <v>1114880734005</v>
       </c>
       <c r="C564">
-        <v>1108157528231</v>
+        <v>1108384394181</v>
       </c>
       <c r="D564">
-        <v>367038000664</v>
+        <v>359484790449</v>
       </c>
       <c r="E564">
-        <v>607166141137</v>
+        <v>618173866765</v>
       </c>
       <c r="F564">
-        <v>974204141801</v>
+        <v>977658657214</v>
       </c>
       <c r="G564">
-        <v>133953386430</v>
+        <v>130725736967</v>
       </c>
       <c r="H564">
         <v>6496339824</v>

--- a/data/rka.xlsx
+++ b/data/rka.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x15 xr xr6 xr10">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\76193\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:40009_{F5D9173E-DFB2-4B3F-89F4-4E261BF9791D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCE886E9-7F45-4A70-80A6-484C5BF94DB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456"/>
+    <workbookView xWindow="768" yWindow="768" windowWidth="17280" windowHeight="9180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="20260918 SAP ZFM01" sheetId="1" r:id="rId1"/>
+    <sheet name="20260921 SAP ZFM01" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
   <extLst>
@@ -423,7 +423,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -1264,7 +1264,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H564"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -2692,10 +2692,10 @@
         <v>4260000000</v>
       </c>
       <c r="D55">
-        <v>1166697100</v>
+        <v>1087153100</v>
       </c>
       <c r="E55">
-        <v>2714774178</v>
+        <v>2794318178</v>
       </c>
       <c r="F55">
         <v>3881471278</v>
@@ -3446,10 +3446,10 @@
         <v>110861610191</v>
       </c>
       <c r="D84">
-        <v>35287898994</v>
+        <v>35208354994</v>
       </c>
       <c r="E84">
-        <v>59029435829</v>
+        <v>59108979829</v>
       </c>
       <c r="F84">
         <v>94317334823</v>
@@ -3576,10 +3576,10 @@
         <v>30639775739</v>
       </c>
       <c r="D89">
-        <v>16237532610</v>
+        <v>16201948810</v>
       </c>
       <c r="E89">
-        <v>12033442321</v>
+        <v>12069026121</v>
       </c>
       <c r="F89">
         <v>28270974931</v>
@@ -4408,10 +4408,10 @@
         <v>81693644736</v>
       </c>
       <c r="D121">
-        <v>20631830525</v>
+        <v>20596246725</v>
       </c>
       <c r="E121">
-        <v>50433978923</v>
+        <v>50469562723</v>
       </c>
       <c r="F121">
         <v>71065809448</v>
@@ -5318,10 +5318,10 @@
         <v>11383511000</v>
       </c>
       <c r="D156">
-        <v>2695026692</v>
+        <v>978809000</v>
       </c>
       <c r="E156">
-        <v>8674074198</v>
+        <v>10390291890</v>
       </c>
       <c r="F156">
         <v>11369100890</v>
@@ -6176,10 +6176,10 @@
         <v>46375593027</v>
       </c>
       <c r="D189">
-        <v>8797911894</v>
+        <v>7081694202</v>
       </c>
       <c r="E189">
-        <v>30183160190</v>
+        <v>31899377882</v>
       </c>
       <c r="F189">
         <v>38981072084</v>
@@ -6436,10 +6436,10 @@
         <v>400000000</v>
       </c>
       <c r="D199">
-        <v>21270500</v>
+        <v>0</v>
       </c>
       <c r="E199">
-        <v>160884799</v>
+        <v>182155299</v>
       </c>
       <c r="F199">
         <v>182155299</v>
@@ -7190,10 +7190,10 @@
         <v>47546983545</v>
       </c>
       <c r="D228">
-        <v>8672428190</v>
+        <v>8651157690</v>
       </c>
       <c r="E228">
-        <v>31628595726</v>
+        <v>31649866226</v>
       </c>
       <c r="F228">
         <v>40301023916</v>
@@ -7216,10 +7216,10 @@
         <v>12264606000</v>
       </c>
       <c r="D229">
-        <v>7985422730</v>
+        <v>6253487000</v>
       </c>
       <c r="E229">
-        <v>3946057000</v>
+        <v>5677992730</v>
       </c>
       <c r="F229">
         <v>11931479730</v>
@@ -8022,10 +8022,10 @@
         <v>48914772555</v>
       </c>
       <c r="D260">
-        <v>10533565210</v>
+        <v>8801629480</v>
       </c>
       <c r="E260">
-        <v>30656435064</v>
+        <v>32388370794</v>
       </c>
       <c r="F260">
         <v>41190000274</v>
@@ -8230,10 +8230,10 @@
         <v>3609800000</v>
       </c>
       <c r="D268">
-        <v>1661715751</v>
+        <v>1651738751</v>
       </c>
       <c r="E268">
-        <v>822578455</v>
+        <v>832555455</v>
       </c>
       <c r="F268">
         <v>2484294206</v>
@@ -9062,10 +9062,10 @@
         <v>63706784713</v>
       </c>
       <c r="D300">
-        <v>14179760798</v>
+        <v>14169783798</v>
       </c>
       <c r="E300">
-        <v>37802212650</v>
+        <v>37812189650</v>
       </c>
       <c r="F300">
         <v>51981973448</v>
@@ -9192,10 +9192,10 @@
         <v>298750000</v>
       </c>
       <c r="D305">
-        <v>202246293</v>
+        <v>168298148</v>
       </c>
       <c r="E305">
-        <v>96093807</v>
+        <v>130041952</v>
       </c>
       <c r="F305">
         <v>298340100</v>
@@ -9920,10 +9920,10 @@
         <v>30414436960</v>
       </c>
       <c r="D333">
-        <v>2167398686</v>
+        <v>2133450541</v>
       </c>
       <c r="E333">
-        <v>22691161257</v>
+        <v>22725109402</v>
       </c>
       <c r="F333">
         <v>24858559943</v>
@@ -10128,10 +10128,10 @@
         <v>1748195004</v>
       </c>
       <c r="D341">
-        <v>227042154</v>
+        <v>201602154</v>
       </c>
       <c r="E341">
-        <v>1395795386</v>
+        <v>1421235386</v>
       </c>
       <c r="F341">
         <v>1622837540</v>
@@ -10752,10 +10752,10 @@
         <v>57427089299</v>
       </c>
       <c r="D365">
-        <v>5994995647</v>
+        <v>5969555647</v>
       </c>
       <c r="E365">
-        <v>43611706332</v>
+        <v>43637146332</v>
       </c>
       <c r="F365">
         <v>49606701979</v>
@@ -11142,16 +11142,16 @@
         <v>411080000</v>
       </c>
       <c r="D380">
-        <v>489790</v>
+        <v>1827440</v>
       </c>
       <c r="E380">
         <v>281295904</v>
       </c>
       <c r="F380">
-        <v>281785694</v>
+        <v>283123344</v>
       </c>
       <c r="G380">
-        <v>129294306</v>
+        <v>127956656</v>
       </c>
       <c r="H380" t="s">
         <v>9</v>
@@ -11584,16 +11584,16 @@
         <v>24628424376</v>
       </c>
       <c r="D397">
-        <v>4980416642</v>
+        <v>4981754292</v>
       </c>
       <c r="E397">
         <v>15584960670</v>
       </c>
       <c r="F397">
-        <v>20565377312</v>
+        <v>20566714962</v>
       </c>
       <c r="G397">
-        <v>4063047064</v>
+        <v>4061709414</v>
       </c>
       <c r="H397">
         <v>232675000</v>
@@ -14067,13 +14067,13 @@
         <v>7568076</v>
       </c>
       <c r="E515">
-        <v>376720219</v>
+        <v>377370219</v>
       </c>
       <c r="F515">
-        <v>384288295</v>
+        <v>384938295</v>
       </c>
       <c r="G515">
-        <v>132145205</v>
+        <v>131495205</v>
       </c>
       <c r="H515">
         <v>172144500</v>
@@ -14249,13 +14249,13 @@
         <v>1068968</v>
       </c>
       <c r="E522">
-        <v>8957039915</v>
+        <v>8957051165</v>
       </c>
       <c r="F522">
-        <v>8958108883</v>
+        <v>8958120133</v>
       </c>
       <c r="G522">
-        <v>3206173014</v>
+        <v>3206161764</v>
       </c>
       <c r="H522" t="s">
         <v>9</v>
@@ -14483,13 +14483,13 @@
         <v>14855810981</v>
       </c>
       <c r="E531">
-        <v>42032718039</v>
+        <v>42033379289</v>
       </c>
       <c r="F531">
-        <v>56888529020</v>
+        <v>56889190270</v>
       </c>
       <c r="G531">
-        <v>7130956300</v>
+        <v>7130295050</v>
       </c>
       <c r="H531">
         <v>850782250</v>
@@ -14662,10 +14662,10 @@
         <v>11576266001</v>
       </c>
       <c r="D538">
-        <v>7360714296</v>
+        <v>10041225391</v>
       </c>
       <c r="E538">
-        <v>4145934363</v>
+        <v>1465423268</v>
       </c>
       <c r="F538">
         <v>11506648659</v>
@@ -15026,10 +15026,10 @@
         <v>336802500</v>
       </c>
       <c r="D552">
-        <v>7700381</v>
+        <v>1951631</v>
       </c>
       <c r="E552">
-        <v>264108101</v>
+        <v>269856851</v>
       </c>
       <c r="F552">
         <v>271808482</v>
@@ -15312,10 +15312,10 @@
         <v>57848682223</v>
       </c>
       <c r="D563">
-        <v>14168386364</v>
+        <v>16843148709</v>
       </c>
       <c r="E563">
-        <v>37136904121</v>
+        <v>34462141776</v>
       </c>
       <c r="F563">
         <v>51305290485</v>
@@ -15338,16 +15338,16 @@
         <v>1108384394181</v>
       </c>
       <c r="D564">
-        <v>359484790449</v>
+        <v>358054677899</v>
       </c>
       <c r="E564">
-        <v>618173866765</v>
+        <v>619602592930</v>
       </c>
       <c r="F564">
-        <v>977658657214</v>
+        <v>977657270829</v>
       </c>
       <c r="G564">
-        <v>130725736967</v>
+        <v>130727123352</v>
       </c>
       <c r="H564">
         <v>6496339824</v>

--- a/data/rka.xlsx
+++ b/data/rka.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\76193\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCE886E9-7F45-4A70-80A6-484C5BF94DB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45AC4FB6-2597-403D-8174-AB7CF0164D3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="768" yWindow="768" windowWidth="17280" windowHeight="9180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="20260921 SAP ZFM01" sheetId="1" r:id="rId1"/>
+    <sheet name="20260902 SAP ZFM01" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
   <extLst>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1093" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1081" uniqueCount="131">
   <si>
     <t>Funds Center/Commitment Item</t>
   </si>
@@ -1308,22 +1308,22 @@
         <v>8</v>
       </c>
       <c r="B2">
-        <v>108940456175</v>
+        <v>109317656175</v>
       </c>
       <c r="C2">
-        <v>108940456175</v>
+        <v>109317656175</v>
       </c>
       <c r="D2">
-        <v>80755967435</v>
+        <v>99268647251</v>
       </c>
       <c r="E2">
-        <v>27616513732</v>
+        <v>8267348916</v>
       </c>
       <c r="F2">
-        <v>108372481167</v>
+        <v>107535996167</v>
       </c>
       <c r="G2">
-        <v>567975008</v>
+        <v>1781660008</v>
       </c>
       <c r="H2" t="s">
         <v>9</v>
@@ -1392,10 +1392,10 @@
         <v>31123480081</v>
       </c>
       <c r="D5">
-        <v>232170400</v>
+        <v>2894652600</v>
       </c>
       <c r="E5">
-        <v>30861866020</v>
+        <v>28199383820</v>
       </c>
       <c r="F5">
         <v>31094036420</v>
@@ -1470,10 +1470,10 @@
         <v>3726972261</v>
       </c>
       <c r="D8">
-        <v>3398631820</v>
+        <v>3622271715</v>
       </c>
       <c r="E8">
-        <v>300804735</v>
+        <v>77164840</v>
       </c>
       <c r="F8">
         <v>3699436555</v>
@@ -1496,10 +1496,10 @@
         <v>62772333130</v>
       </c>
       <c r="D9">
-        <v>37626079655</v>
+        <v>54589308663</v>
       </c>
       <c r="E9">
-        <v>25117300370</v>
+        <v>8154071362</v>
       </c>
       <c r="F9">
         <v>62743380025</v>
@@ -1516,22 +1516,22 @@
         <v>17</v>
       </c>
       <c r="B10">
-        <v>490324430</v>
+        <v>579317296</v>
       </c>
       <c r="C10">
-        <v>490324430</v>
+        <v>579317296</v>
       </c>
       <c r="D10">
-        <v>148038375</v>
+        <v>197598375</v>
       </c>
       <c r="E10">
-        <v>242278055</v>
+        <v>192718055</v>
       </c>
       <c r="F10">
         <v>390316430</v>
       </c>
       <c r="G10">
-        <v>100008000</v>
+        <v>189000866</v>
       </c>
       <c r="H10" t="s">
         <v>9</v>
@@ -1574,16 +1574,16 @@
         <v>17276995631</v>
       </c>
       <c r="D12">
-        <v>10951110831</v>
+        <v>10467818831</v>
       </c>
       <c r="E12">
         <v>6309951800</v>
       </c>
       <c r="F12">
-        <v>17261062631</v>
+        <v>16777770631</v>
       </c>
       <c r="G12">
-        <v>15933000</v>
+        <v>499225000</v>
       </c>
       <c r="H12" t="s">
         <v>9</v>
@@ -1600,16 +1600,16 @@
         <v>12489080231</v>
       </c>
       <c r="D13">
-        <v>7204626993</v>
+        <v>7204677393</v>
       </c>
       <c r="E13">
         <v>5284402838</v>
       </c>
       <c r="F13">
-        <v>12489029831</v>
-      </c>
-      <c r="G13">
-        <v>50400</v>
+        <v>12489080231</v>
+      </c>
+      <c r="G13" t="s">
+        <v>9</v>
       </c>
       <c r="H13" t="s">
         <v>9</v>
@@ -1698,25 +1698,25 @@
         <v>24</v>
       </c>
       <c r="B17">
-        <v>1200000000</v>
+        <v>1600000000</v>
       </c>
       <c r="C17">
         <v>1200000000</v>
       </c>
       <c r="D17">
-        <v>53642000</v>
+        <v>65779500</v>
       </c>
       <c r="E17">
-        <v>131159000</v>
+        <v>92721500</v>
       </c>
       <c r="F17">
-        <v>184801000</v>
+        <v>158501000</v>
       </c>
       <c r="G17">
-        <v>1015199000</v>
-      </c>
-      <c r="H17" t="s">
-        <v>9</v>
+        <v>1041499000</v>
+      </c>
+      <c r="H17">
+        <v>400000000</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.3">
@@ -1724,10 +1724,10 @@
         <v>25</v>
       </c>
       <c r="B18">
-        <v>391942400</v>
+        <v>454442400</v>
       </c>
       <c r="C18">
-        <v>391942400</v>
+        <v>329442400</v>
       </c>
       <c r="D18">
         <v>0</v>
@@ -1739,10 +1739,10 @@
         <v>20986164</v>
       </c>
       <c r="G18">
-        <v>370956236</v>
-      </c>
-      <c r="H18" t="s">
-        <v>9</v>
+        <v>308456236</v>
+      </c>
+      <c r="H18">
+        <v>125000000</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.3">
@@ -1750,22 +1750,22 @@
         <v>26</v>
       </c>
       <c r="B19">
-        <v>3894602130</v>
+        <v>4500000000</v>
       </c>
       <c r="C19">
-        <v>3894602130</v>
+        <v>4500000000</v>
       </c>
       <c r="D19">
-        <v>170226548</v>
+        <v>346244860</v>
       </c>
       <c r="E19">
-        <v>2796450489</v>
+        <v>2563937629</v>
       </c>
       <c r="F19">
-        <v>2966677037</v>
+        <v>2910182489</v>
       </c>
       <c r="G19">
-        <v>927925093</v>
+        <v>1589817511</v>
       </c>
       <c r="H19" t="s">
         <v>9</v>
@@ -1776,10 +1776,10 @@
         <v>27</v>
       </c>
       <c r="B20">
-        <v>1000698000</v>
+        <v>1483013800</v>
       </c>
       <c r="C20">
-        <v>1000698000</v>
+        <v>1108013800</v>
       </c>
       <c r="D20">
         <v>0</v>
@@ -1791,10 +1791,10 @@
         <v>406948000</v>
       </c>
       <c r="G20">
-        <v>593750000</v>
-      </c>
-      <c r="H20" t="s">
-        <v>9</v>
+        <v>701065800</v>
+      </c>
+      <c r="H20">
+        <v>375000000</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.3">
@@ -1802,25 +1802,25 @@
         <v>28</v>
       </c>
       <c r="B21">
-        <v>406635000</v>
+        <v>702885000</v>
       </c>
       <c r="C21">
-        <v>406635000</v>
+        <v>510385000</v>
       </c>
       <c r="D21">
-        <v>76984318</v>
+        <v>75773600</v>
       </c>
       <c r="E21">
-        <v>89696662</v>
+        <v>84557037</v>
       </c>
       <c r="F21">
-        <v>166680980</v>
+        <v>160330637</v>
       </c>
       <c r="G21">
-        <v>239954020</v>
-      </c>
-      <c r="H21" t="s">
-        <v>9</v>
+        <v>350054363</v>
+      </c>
+      <c r="H21">
+        <v>192500000</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.3">
@@ -1828,10 +1828,10 @@
         <v>29</v>
       </c>
       <c r="B22">
-        <v>146000000</v>
+        <v>156000000</v>
       </c>
       <c r="C22">
-        <v>146000000</v>
+        <v>156000000</v>
       </c>
       <c r="D22">
         <v>0</v>
@@ -1843,7 +1843,7 @@
         <v>103000000</v>
       </c>
       <c r="G22">
-        <v>43000000</v>
+        <v>53000000</v>
       </c>
       <c r="H22" t="s">
         <v>9</v>
@@ -1854,25 +1854,25 @@
         <v>30</v>
       </c>
       <c r="B23">
-        <v>685097314</v>
+        <v>747597314</v>
       </c>
       <c r="C23">
-        <v>685097314</v>
+        <v>622597314</v>
       </c>
       <c r="D23">
-        <v>551635520</v>
+        <v>507783920</v>
       </c>
       <c r="E23">
         <v>114645294</v>
       </c>
       <c r="F23">
-        <v>666280814</v>
+        <v>622429214</v>
       </c>
       <c r="G23">
-        <v>18816500</v>
-      </c>
-      <c r="H23" t="s">
-        <v>9</v>
+        <v>168100</v>
+      </c>
+      <c r="H23">
+        <v>125000000</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.3">
@@ -1880,25 +1880,25 @@
         <v>31</v>
       </c>
       <c r="B24">
-        <v>600000000</v>
+        <v>800000000</v>
       </c>
       <c r="C24">
         <v>600000000</v>
       </c>
       <c r="D24">
-        <v>58975573</v>
+        <v>45991873</v>
       </c>
       <c r="E24">
         <v>200398159</v>
       </c>
       <c r="F24">
-        <v>259373732</v>
+        <v>246390032</v>
       </c>
       <c r="G24">
-        <v>340626268</v>
-      </c>
-      <c r="H24" t="s">
-        <v>9</v>
+        <v>353609968</v>
+      </c>
+      <c r="H24">
+        <v>200000000</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.3">
@@ -1906,25 +1906,25 @@
         <v>32</v>
       </c>
       <c r="B25">
-        <v>1691277133</v>
+        <v>2312674754</v>
       </c>
       <c r="C25">
-        <v>1691277133</v>
+        <v>1687674754</v>
       </c>
       <c r="D25">
-        <v>235047759</v>
+        <v>4827692</v>
       </c>
       <c r="E25">
-        <v>1114855691</v>
+        <v>1049799441</v>
       </c>
       <c r="F25">
-        <v>1349903450</v>
+        <v>1054627133</v>
       </c>
       <c r="G25">
-        <v>341373683</v>
-      </c>
-      <c r="H25" t="s">
-        <v>9</v>
+        <v>633047621</v>
+      </c>
+      <c r="H25">
+        <v>625000000</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.3">
@@ -1932,10 +1932,10 @@
         <v>33</v>
       </c>
       <c r="B26">
-        <v>128132588</v>
+        <v>220000000</v>
       </c>
       <c r="C26">
-        <v>128132588</v>
+        <v>220000000</v>
       </c>
       <c r="D26">
         <v>0</v>
@@ -1947,7 +1947,7 @@
         <v>28132588</v>
       </c>
       <c r="G26">
-        <v>100000000</v>
+        <v>191867412</v>
       </c>
       <c r="H26" t="s">
         <v>9</v>
@@ -1993,13 +1993,13 @@
         <v>0</v>
       </c>
       <c r="E28">
-        <v>2835880775</v>
+        <v>2833183590</v>
       </c>
       <c r="F28">
-        <v>2835880775</v>
+        <v>2833183590</v>
       </c>
       <c r="G28">
-        <v>620733429</v>
+        <v>623430614</v>
       </c>
       <c r="H28" t="s">
         <v>9</v>
@@ -2045,13 +2045,13 @@
         <v>0</v>
       </c>
       <c r="E30">
-        <v>3669312187</v>
+        <v>3661908187</v>
       </c>
       <c r="F30">
-        <v>3669312187</v>
+        <v>3661908187</v>
       </c>
       <c r="G30">
-        <v>408957848</v>
+        <v>416361848</v>
       </c>
       <c r="H30" t="s">
         <v>9</v>
@@ -2149,13 +2149,13 @@
         <v>0</v>
       </c>
       <c r="E34">
-        <v>10062254960</v>
+        <v>10058200960</v>
       </c>
       <c r="F34">
-        <v>10062254960</v>
+        <v>10058200960</v>
       </c>
       <c r="G34">
-        <v>3907811086</v>
+        <v>3911865086</v>
       </c>
       <c r="H34" t="s">
         <v>9</v>
@@ -2270,10 +2270,10 @@
         <v>46</v>
       </c>
       <c r="B39">
-        <v>274300566</v>
+        <v>752402686</v>
       </c>
       <c r="C39">
-        <v>274300566</v>
+        <v>502402686</v>
       </c>
       <c r="D39">
         <v>0</v>
@@ -2285,10 +2285,10 @@
         <v>8807378</v>
       </c>
       <c r="G39">
-        <v>265493188</v>
-      </c>
-      <c r="H39" t="s">
-        <v>9</v>
+        <v>493595308</v>
+      </c>
+      <c r="H39">
+        <v>250000000</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.3">
@@ -2296,10 +2296,10 @@
         <v>47</v>
       </c>
       <c r="B40">
-        <v>437500000</v>
+        <v>500000000</v>
       </c>
       <c r="C40">
-        <v>437500000</v>
+        <v>375000000</v>
       </c>
       <c r="D40">
         <v>0</v>
@@ -2311,10 +2311,10 @@
         <v>15794000</v>
       </c>
       <c r="G40">
-        <v>421706000</v>
-      </c>
-      <c r="H40" t="s">
-        <v>9</v>
+        <v>359206000</v>
+      </c>
+      <c r="H40">
+        <v>125000000</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.3">
@@ -2331,13 +2331,13 @@
         <v>0</v>
       </c>
       <c r="E41">
-        <v>1643261221</v>
+        <v>1437853656</v>
       </c>
       <c r="F41">
-        <v>1643261221</v>
+        <v>1437853656</v>
       </c>
       <c r="G41">
-        <v>-1643261221</v>
+        <v>-1437853656</v>
       </c>
       <c r="H41" t="s">
         <v>9</v>
@@ -2348,25 +2348,25 @@
         <v>49</v>
       </c>
       <c r="B42">
-        <v>346934395851</v>
+        <v>350773419540</v>
       </c>
       <c r="C42">
-        <v>346934395851</v>
+        <v>348355919540</v>
       </c>
       <c r="D42">
-        <v>199493696833</v>
+        <v>237321935879</v>
       </c>
       <c r="E42">
-        <v>133705485157</v>
+        <v>93896700253</v>
       </c>
       <c r="F42">
-        <v>333199181990</v>
+        <v>331218636132</v>
       </c>
       <c r="G42">
-        <v>13735213861</v>
-      </c>
-      <c r="H42" t="s">
-        <v>9</v>
+        <v>17137283408</v>
+      </c>
+      <c r="H42">
+        <v>2417500000</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.3">
@@ -2380,16 +2380,16 @@
         <v>26681487101</v>
       </c>
       <c r="D43">
-        <v>16851399022</v>
+        <v>17366902401</v>
       </c>
       <c r="E43">
-        <v>9787332180</v>
+        <v>9295238000</v>
       </c>
       <c r="F43">
-        <v>26638731202</v>
+        <v>26662140401</v>
       </c>
       <c r="G43">
-        <v>42755899</v>
+        <v>19346700</v>
       </c>
       <c r="H43" t="s">
         <v>9</v>
@@ -2562,16 +2562,16 @@
         <v>2000000000</v>
       </c>
       <c r="D50">
-        <v>1361195942</v>
+        <v>1883336224</v>
       </c>
       <c r="E50">
-        <v>491537500</v>
+        <v>0</v>
       </c>
       <c r="F50">
-        <v>1852733442</v>
+        <v>1883336224</v>
       </c>
       <c r="G50">
-        <v>147266558</v>
+        <v>116663776</v>
       </c>
       <c r="H50" t="s">
         <v>9</v>
@@ -2614,16 +2614,16 @@
         <v>400000000</v>
       </c>
       <c r="D52">
-        <v>391600000</v>
+        <v>399980984</v>
       </c>
       <c r="E52">
         <v>0</v>
       </c>
       <c r="F52">
-        <v>391600000</v>
+        <v>399980984</v>
       </c>
       <c r="G52">
-        <v>8400000</v>
+        <v>19016</v>
       </c>
       <c r="H52" t="s">
         <v>9</v>
@@ -2666,16 +2666,16 @@
         <v>6000000000</v>
       </c>
       <c r="D54">
-        <v>5229810269</v>
+        <v>5252888358</v>
       </c>
       <c r="E54">
         <v>541614545</v>
       </c>
       <c r="F54">
-        <v>5771424814</v>
+        <v>5794502903</v>
       </c>
       <c r="G54">
-        <v>228575186</v>
+        <v>205497097</v>
       </c>
       <c r="H54" t="s">
         <v>9</v>
@@ -2692,16 +2692,16 @@
         <v>4260000000</v>
       </c>
       <c r="D55">
-        <v>1087153100</v>
+        <v>1583822785</v>
       </c>
       <c r="E55">
-        <v>2794318178</v>
+        <v>2040648478</v>
       </c>
       <c r="F55">
-        <v>3881471278</v>
+        <v>3624471263</v>
       </c>
       <c r="G55">
-        <v>378528722</v>
+        <v>635528737</v>
       </c>
       <c r="H55" t="s">
         <v>9</v>
@@ -2744,16 +2744,16 @@
         <v>2500000000</v>
       </c>
       <c r="D57">
-        <v>971552802</v>
+        <v>978650860</v>
       </c>
       <c r="E57">
         <v>1063184691</v>
       </c>
       <c r="F57">
-        <v>2034737493</v>
+        <v>2041835551</v>
       </c>
       <c r="G57">
-        <v>465262507</v>
+        <v>458164449</v>
       </c>
       <c r="H57" t="s">
         <v>9</v>
@@ -2770,10 +2770,10 @@
         <v>250000000</v>
       </c>
       <c r="D58">
-        <v>0</v>
+        <v>75748702</v>
       </c>
       <c r="E58">
-        <v>149553662</v>
+        <v>73804960</v>
       </c>
       <c r="F58">
         <v>149553662</v>
@@ -2822,16 +2822,16 @@
         <v>2620000000</v>
       </c>
       <c r="D60">
-        <v>338042541</v>
+        <v>635195738</v>
       </c>
       <c r="E60">
-        <v>815038867</v>
+        <v>738524117</v>
       </c>
       <c r="F60">
-        <v>1153081408</v>
+        <v>1373719855</v>
       </c>
       <c r="G60">
-        <v>1466918592</v>
+        <v>1246280145</v>
       </c>
       <c r="H60" t="s">
         <v>9</v>
@@ -2848,16 +2848,16 @@
         <v>750000000</v>
       </c>
       <c r="D61">
-        <v>481567894</v>
+        <v>0</v>
       </c>
       <c r="E61">
         <v>0</v>
       </c>
-      <c r="F61">
-        <v>481567894</v>
+      <c r="F61" t="s">
+        <v>9</v>
       </c>
       <c r="G61">
-        <v>268432106</v>
+        <v>750000000</v>
       </c>
       <c r="H61" t="s">
         <v>9</v>
@@ -2900,16 +2900,16 @@
         <v>2500000000</v>
       </c>
       <c r="D63">
-        <v>1948112000</v>
+        <v>2007946000</v>
       </c>
       <c r="E63">
-        <v>383110100</v>
+        <v>333260100</v>
       </c>
       <c r="F63">
-        <v>2331222100</v>
+        <v>2341206100</v>
       </c>
       <c r="G63">
-        <v>168777900</v>
+        <v>158793900</v>
       </c>
       <c r="H63" t="s">
         <v>9</v>
@@ -2952,16 +2952,16 @@
         <v>180000150</v>
       </c>
       <c r="D65">
-        <v>31856000</v>
+        <v>9176000</v>
       </c>
       <c r="E65">
         <v>139677600</v>
       </c>
       <c r="F65">
-        <v>171533600</v>
+        <v>148853600</v>
       </c>
       <c r="G65">
-        <v>8466550</v>
+        <v>31146550</v>
       </c>
       <c r="H65" t="s">
         <v>9</v>
@@ -3004,16 +3004,16 @@
         <v>400400000</v>
       </c>
       <c r="D67">
-        <v>30029168</v>
+        <v>23372510</v>
       </c>
       <c r="E67">
         <v>119056922</v>
       </c>
       <c r="F67">
-        <v>149086090</v>
+        <v>142429432</v>
       </c>
       <c r="G67">
-        <v>251313910</v>
+        <v>257970568</v>
       </c>
       <c r="H67">
         <v>139000000</v>
@@ -3024,22 +3024,22 @@
         <v>28</v>
       </c>
       <c r="B68">
-        <v>436900000</v>
+        <v>446900000</v>
       </c>
       <c r="C68">
-        <v>325175000</v>
+        <v>335175000</v>
       </c>
       <c r="D68">
-        <v>51612850</v>
+        <v>68211850</v>
       </c>
       <c r="E68">
         <v>184205025</v>
       </c>
       <c r="F68">
-        <v>235817875</v>
+        <v>252416875</v>
       </c>
       <c r="G68">
-        <v>89357125</v>
+        <v>82758125</v>
       </c>
       <c r="H68">
         <v>111725000</v>
@@ -3134,16 +3134,16 @@
         <v>354225000</v>
       </c>
       <c r="D72">
-        <v>0</v>
+        <v>46676000</v>
       </c>
       <c r="E72">
-        <v>259809250</v>
+        <v>253203000</v>
       </c>
       <c r="F72">
-        <v>259809250</v>
+        <v>299879000</v>
       </c>
       <c r="G72">
-        <v>94415750</v>
+        <v>54346000</v>
       </c>
       <c r="H72">
         <v>118075000</v>
@@ -3154,19 +3154,19 @@
         <v>33</v>
       </c>
       <c r="B73">
-        <v>70400000</v>
+        <v>80000000</v>
       </c>
       <c r="C73">
-        <v>70400000</v>
+        <v>80000000</v>
       </c>
       <c r="D73">
-        <v>0</v>
+        <v>9600000</v>
       </c>
       <c r="E73">
         <v>36832700</v>
       </c>
       <c r="F73">
-        <v>36832700</v>
+        <v>46432700</v>
       </c>
       <c r="G73">
         <v>33567300</v>
@@ -3189,13 +3189,13 @@
         <v>0</v>
       </c>
       <c r="E74">
-        <v>50547487</v>
+        <v>44229053</v>
       </c>
       <c r="F74">
-        <v>50547487</v>
+        <v>44229053</v>
       </c>
       <c r="G74">
-        <v>-50547487</v>
+        <v>-44229053</v>
       </c>
       <c r="H74" t="s">
         <v>9</v>
@@ -3215,13 +3215,13 @@
         <v>0</v>
       </c>
       <c r="E75">
-        <v>16581052405</v>
+        <v>16580866780</v>
       </c>
       <c r="F75">
-        <v>16581052405</v>
+        <v>16580866780</v>
       </c>
       <c r="G75">
-        <v>6350554824</v>
+        <v>6350740449</v>
       </c>
       <c r="H75" t="s">
         <v>9</v>
@@ -3267,13 +3267,13 @@
         <v>9566218</v>
       </c>
       <c r="E77">
-        <v>18047013147</v>
+        <v>17994131226</v>
       </c>
       <c r="F77">
-        <v>18056579365</v>
+        <v>18003697444</v>
       </c>
       <c r="G77">
-        <v>2910842165</v>
+        <v>2963724086</v>
       </c>
       <c r="H77" t="s">
         <v>9</v>
@@ -3371,13 +3371,13 @@
         <v>165657</v>
       </c>
       <c r="E81">
-        <v>1890200919</v>
+        <v>1889267075</v>
       </c>
       <c r="F81">
-        <v>1890366576</v>
+        <v>1889432732</v>
       </c>
       <c r="G81">
-        <v>46751952</v>
+        <v>47685796</v>
       </c>
       <c r="H81" t="s">
         <v>9</v>
@@ -3440,22 +3440,22 @@
         <v>67</v>
       </c>
       <c r="B84">
-        <v>111533111691</v>
+        <v>111552711691</v>
       </c>
       <c r="C84">
-        <v>110861610191</v>
+        <v>110881210191</v>
       </c>
       <c r="D84">
-        <v>35208354994</v>
+        <v>36775931818</v>
       </c>
       <c r="E84">
-        <v>59108979829</v>
+        <v>57102638923</v>
       </c>
       <c r="F84">
-        <v>94317334823</v>
+        <v>93878570741</v>
       </c>
       <c r="G84">
-        <v>16544275368</v>
+        <v>17002639450</v>
       </c>
       <c r="H84">
         <v>671501500</v>
@@ -3576,16 +3576,16 @@
         <v>30639775739</v>
       </c>
       <c r="D89">
-        <v>16201948810</v>
+        <v>14048463637</v>
       </c>
       <c r="E89">
-        <v>12069026121</v>
+        <v>11923554821</v>
       </c>
       <c r="F89">
-        <v>28270974931</v>
+        <v>25972018458</v>
       </c>
       <c r="G89">
-        <v>2368800808</v>
+        <v>4667757281</v>
       </c>
       <c r="H89" t="s">
         <v>9</v>
@@ -3628,10 +3628,10 @@
         <v>88512582</v>
       </c>
       <c r="D91">
-        <v>0</v>
+        <v>87737900</v>
       </c>
       <c r="E91">
-        <v>87737900</v>
+        <v>0</v>
       </c>
       <c r="F91">
         <v>87737900</v>
@@ -3654,10 +3654,10 @@
         <v>1210765056</v>
       </c>
       <c r="D92">
-        <v>460919940</v>
+        <v>548419940</v>
       </c>
       <c r="E92">
-        <v>247342440</v>
+        <v>159842440</v>
       </c>
       <c r="F92">
         <v>708262380</v>
@@ -3706,16 +3706,16 @@
         <v>2796520000</v>
       </c>
       <c r="D94">
-        <v>763263804</v>
+        <v>825818554</v>
       </c>
       <c r="E94">
-        <v>2033249617</v>
+        <v>1964437867</v>
       </c>
       <c r="F94">
-        <v>2796513421</v>
+        <v>2790256421</v>
       </c>
       <c r="G94">
-        <v>6579</v>
+        <v>6263579</v>
       </c>
       <c r="H94" t="s">
         <v>9</v>
@@ -3758,10 +3758,10 @@
         <v>180831882</v>
       </c>
       <c r="D96">
-        <v>0</v>
+        <v>49487057</v>
       </c>
       <c r="E96">
-        <v>49487057</v>
+        <v>0</v>
       </c>
       <c r="F96">
         <v>49487057</v>
@@ -3784,10 +3784,10 @@
         <v>400000000</v>
       </c>
       <c r="D97">
-        <v>0</v>
+        <v>36520000</v>
       </c>
       <c r="E97">
-        <v>399814227</v>
+        <v>363294227</v>
       </c>
       <c r="F97">
         <v>399814227</v>
@@ -3810,16 +3810,16 @@
         <v>289155000</v>
       </c>
       <c r="D98">
-        <v>68174000</v>
+        <v>20359000</v>
       </c>
       <c r="E98">
         <v>57100000</v>
       </c>
       <c r="F98">
-        <v>125274000</v>
+        <v>77459000</v>
       </c>
       <c r="G98">
-        <v>163881000</v>
+        <v>211696000</v>
       </c>
       <c r="H98" t="s">
         <v>9</v>
@@ -3836,16 +3836,16 @@
         <v>360000000</v>
       </c>
       <c r="D99">
-        <v>93146576</v>
+        <v>105051976</v>
       </c>
       <c r="E99">
-        <v>247536000</v>
+        <v>204218000</v>
       </c>
       <c r="F99">
-        <v>340682576</v>
+        <v>309269976</v>
       </c>
       <c r="G99">
-        <v>19317424</v>
+        <v>50730024</v>
       </c>
       <c r="H99" t="s">
         <v>9</v>
@@ -3862,16 +3862,16 @@
         <v>1710494400</v>
       </c>
       <c r="D100">
-        <v>419021980</v>
+        <v>629986580</v>
       </c>
       <c r="E100">
-        <v>1099212506</v>
+        <v>1067501506</v>
       </c>
       <c r="F100">
-        <v>1518234486</v>
+        <v>1697488086</v>
       </c>
       <c r="G100">
-        <v>192259914</v>
+        <v>13006314</v>
       </c>
       <c r="H100" t="s">
         <v>9</v>
@@ -3888,16 +3888,16 @@
         <v>150000000</v>
       </c>
       <c r="D101">
-        <v>17891177</v>
+        <v>0</v>
       </c>
       <c r="E101">
         <v>92034500</v>
       </c>
       <c r="F101">
-        <v>109925677</v>
+        <v>92034500</v>
       </c>
       <c r="G101">
-        <v>40074323</v>
+        <v>57965500</v>
       </c>
       <c r="H101">
         <v>50000000</v>
@@ -3908,22 +3908,22 @@
         <v>27</v>
       </c>
       <c r="B102">
-        <v>462220000</v>
+        <v>534300000</v>
       </c>
       <c r="C102">
-        <v>322395000</v>
+        <v>394475000</v>
       </c>
       <c r="D102">
-        <v>51550900</v>
+        <v>119148000</v>
       </c>
       <c r="E102">
         <v>45427850</v>
       </c>
       <c r="F102">
-        <v>96978750</v>
+        <v>164575850</v>
       </c>
       <c r="G102">
-        <v>225416250</v>
+        <v>229899150</v>
       </c>
       <c r="H102">
         <v>139825000</v>
@@ -3934,22 +3934,22 @@
         <v>28</v>
       </c>
       <c r="B103">
-        <v>413360000</v>
+        <v>341280000</v>
       </c>
       <c r="C103">
-        <v>328040000</v>
+        <v>255960000</v>
       </c>
       <c r="D103">
-        <v>59800230</v>
+        <v>65004150</v>
       </c>
       <c r="E103">
         <v>174999400</v>
       </c>
       <c r="F103">
-        <v>234799630</v>
+        <v>240003550</v>
       </c>
       <c r="G103">
-        <v>93240370</v>
+        <v>15956450</v>
       </c>
       <c r="H103">
         <v>85320000</v>
@@ -3986,22 +3986,22 @@
         <v>30</v>
       </c>
       <c r="B105">
-        <v>317761000</v>
+        <v>388800000</v>
       </c>
       <c r="C105">
-        <v>220561000</v>
+        <v>291600000</v>
       </c>
       <c r="D105">
-        <v>192481700</v>
+        <v>220821700</v>
       </c>
       <c r="E105">
         <v>28079000</v>
       </c>
       <c r="F105">
-        <v>220560700</v>
+        <v>248900700</v>
       </c>
       <c r="G105">
-        <v>300</v>
+        <v>42699300</v>
       </c>
       <c r="H105">
         <v>97200000</v>
@@ -4012,22 +4012,22 @@
         <v>31</v>
       </c>
       <c r="B106">
+        <v>20000000</v>
+      </c>
+      <c r="C106">
         <v>15000000</v>
       </c>
-      <c r="C106">
-        <v>10000000</v>
-      </c>
       <c r="D106">
-        <v>0</v>
+        <v>2400000</v>
       </c>
       <c r="E106">
         <v>0</v>
       </c>
-      <c r="F106" t="s">
-        <v>9</v>
+      <c r="F106">
+        <v>2400000</v>
       </c>
       <c r="G106">
-        <v>10000000</v>
+        <v>12600000</v>
       </c>
       <c r="H106">
         <v>5000000</v>
@@ -4038,22 +4038,22 @@
         <v>32</v>
       </c>
       <c r="B107">
-        <v>482449000</v>
+        <v>393410000</v>
       </c>
       <c r="C107">
-        <v>384096500</v>
+        <v>295057500</v>
       </c>
       <c r="D107">
         <v>0</v>
       </c>
       <c r="E107">
-        <v>294691068</v>
+        <v>291366068</v>
       </c>
       <c r="F107">
-        <v>294691068</v>
+        <v>291366068</v>
       </c>
       <c r="G107">
-        <v>89405432</v>
+        <v>3691432</v>
       </c>
       <c r="H107">
         <v>98352500</v>
@@ -4064,22 +4064,22 @@
         <v>33</v>
       </c>
       <c r="B108">
-        <v>78080000</v>
+        <v>91080000</v>
       </c>
       <c r="C108">
-        <v>78080000</v>
+        <v>91080000</v>
       </c>
       <c r="D108">
-        <v>0</v>
+        <v>11880000</v>
       </c>
       <c r="E108">
         <v>38927400</v>
       </c>
       <c r="F108">
-        <v>38927400</v>
+        <v>50807400</v>
       </c>
       <c r="G108">
-        <v>39152600</v>
+        <v>40272600</v>
       </c>
       <c r="H108" t="s">
         <v>9</v>
@@ -4099,13 +4099,13 @@
         <v>0</v>
       </c>
       <c r="E109">
-        <v>384361230</v>
+        <v>346913941</v>
       </c>
       <c r="F109">
-        <v>384361230</v>
+        <v>346913941</v>
       </c>
       <c r="G109">
-        <v>-384361230</v>
+        <v>-346913941</v>
       </c>
       <c r="H109" t="s">
         <v>9</v>
@@ -4125,13 +4125,13 @@
         <v>0</v>
       </c>
       <c r="E110">
-        <v>109638038</v>
+        <v>95933284</v>
       </c>
       <c r="F110">
-        <v>109638038</v>
+        <v>95933284</v>
       </c>
       <c r="G110">
-        <v>-109638038</v>
+        <v>-95933284</v>
       </c>
       <c r="H110" t="s">
         <v>9</v>
@@ -4177,13 +4177,13 @@
         <v>0</v>
       </c>
       <c r="E112">
-        <v>11992126324</v>
+        <v>11992041949</v>
       </c>
       <c r="F112">
-        <v>11992126324</v>
+        <v>11992041949</v>
       </c>
       <c r="G112">
-        <v>4231518529</v>
+        <v>4231602904</v>
       </c>
       <c r="H112" t="s">
         <v>9</v>
@@ -4229,13 +4229,13 @@
         <v>9868545</v>
       </c>
       <c r="E114">
-        <v>13081397723</v>
+        <v>13036981539</v>
       </c>
       <c r="F114">
-        <v>13091266268</v>
+        <v>13046850084</v>
       </c>
       <c r="G114">
-        <v>1406913680</v>
+        <v>1451329864</v>
       </c>
       <c r="H114" t="s">
         <v>9</v>
@@ -4333,13 +4333,13 @@
         <v>0</v>
       </c>
       <c r="E118">
-        <v>1493975146</v>
+        <v>1493780716</v>
       </c>
       <c r="F118">
-        <v>1493975146</v>
+        <v>1493780716</v>
       </c>
       <c r="G118">
-        <v>434685728</v>
+        <v>434880158</v>
       </c>
       <c r="H118" t="s">
         <v>9</v>
@@ -4408,16 +4408,16 @@
         <v>81693644736</v>
       </c>
       <c r="D121">
-        <v>20596246725</v>
+        <v>19039146102</v>
       </c>
       <c r="E121">
-        <v>50469562723</v>
+        <v>49819833684</v>
       </c>
       <c r="F121">
-        <v>71065809448</v>
+        <v>68858979786</v>
       </c>
       <c r="G121">
-        <v>10627835288</v>
+        <v>12834664950</v>
       </c>
       <c r="H121">
         <v>475697500</v>
@@ -4434,16 +4434,16 @@
         <v>8995670000</v>
       </c>
       <c r="D122">
-        <v>905660000</v>
+        <v>5683860320</v>
       </c>
       <c r="E122">
-        <v>7784736312</v>
+        <v>3020023792</v>
       </c>
       <c r="F122">
-        <v>8690396312</v>
+        <v>8703884112</v>
       </c>
       <c r="G122">
-        <v>305273688</v>
+        <v>291785888</v>
       </c>
       <c r="H122" t="s">
         <v>9</v>
@@ -4460,16 +4460,16 @@
         <v>1494332364</v>
       </c>
       <c r="D123">
-        <v>1322137072</v>
+        <v>491000000</v>
       </c>
       <c r="E123">
         <v>127583711</v>
       </c>
       <c r="F123">
-        <v>1449720783</v>
+        <v>618583711</v>
       </c>
       <c r="G123">
-        <v>44611581</v>
+        <v>875748653</v>
       </c>
       <c r="H123" t="s">
         <v>9</v>
@@ -4538,16 +4538,16 @@
         <v>1200699000</v>
       </c>
       <c r="D126">
-        <v>1114070165</v>
+        <v>668247328</v>
       </c>
       <c r="E126">
         <v>81220975</v>
       </c>
       <c r="F126">
-        <v>1195291140</v>
+        <v>749468303</v>
       </c>
       <c r="G126">
-        <v>5407860</v>
+        <v>451230697</v>
       </c>
       <c r="H126" t="s">
         <v>9</v>
@@ -4564,10 +4564,10 @@
         <v>818532000</v>
       </c>
       <c r="D127">
-        <v>333965683</v>
+        <v>494768983</v>
       </c>
       <c r="E127">
-        <v>447877800</v>
+        <v>287074500</v>
       </c>
       <c r="F127">
         <v>781843483</v>
@@ -4590,16 +4590,16 @@
         <v>4824864000</v>
       </c>
       <c r="D128">
-        <v>11569210</v>
+        <v>0</v>
       </c>
       <c r="E128">
         <v>4612652831</v>
       </c>
       <c r="F128">
-        <v>4624222041</v>
+        <v>4612652831</v>
       </c>
       <c r="G128">
-        <v>200641959</v>
+        <v>212211169</v>
       </c>
       <c r="H128" t="s">
         <v>9</v>
@@ -4616,16 +4616,16 @@
         <v>1665000000</v>
       </c>
       <c r="D129">
-        <v>212643952</v>
+        <v>144401157</v>
       </c>
       <c r="E129">
         <v>713065052</v>
       </c>
       <c r="F129">
-        <v>925709004</v>
+        <v>857466209</v>
       </c>
       <c r="G129">
-        <v>739290996</v>
+        <v>807533791</v>
       </c>
       <c r="H129" t="s">
         <v>9</v>
@@ -4642,16 +4642,16 @@
         <v>530067000</v>
       </c>
       <c r="D130">
-        <v>217692589</v>
+        <v>0</v>
       </c>
       <c r="E130">
         <v>300000000</v>
       </c>
       <c r="F130">
-        <v>517692589</v>
+        <v>300000000</v>
       </c>
       <c r="G130">
-        <v>12374411</v>
+        <v>230067000</v>
       </c>
       <c r="H130" t="s">
         <v>9</v>
@@ -4694,16 +4694,16 @@
         <v>2233168000</v>
       </c>
       <c r="D132">
-        <v>1462560620</v>
+        <v>1437810620</v>
       </c>
       <c r="E132">
         <v>766560444</v>
       </c>
       <c r="F132">
-        <v>2229121064</v>
+        <v>2204371064</v>
       </c>
       <c r="G132">
-        <v>4046936</v>
+        <v>28796936</v>
       </c>
       <c r="H132" t="s">
         <v>9</v>
@@ -4795,7 +4795,7 @@
         <v>705000000</v>
       </c>
       <c r="C136">
-        <v>593920000</v>
+        <v>528750000</v>
       </c>
       <c r="D136">
         <v>0</v>
@@ -4807,10 +4807,10 @@
         <v>491500000</v>
       </c>
       <c r="G136">
-        <v>102420000</v>
+        <v>37250000</v>
       </c>
       <c r="H136">
-        <v>111080000</v>
+        <v>176250000</v>
       </c>
     </row>
     <row r="137" spans="1:8" x14ac:dyDescent="0.3">
@@ -4824,16 +4824,16 @@
         <v>118875000</v>
       </c>
       <c r="D137">
-        <v>18462500</v>
+        <v>3172500</v>
       </c>
       <c r="E137">
         <v>62015400</v>
       </c>
       <c r="F137">
-        <v>80477900</v>
+        <v>65187900</v>
       </c>
       <c r="G137">
-        <v>38397100</v>
+        <v>53687100</v>
       </c>
       <c r="H137" t="s">
         <v>9</v>
@@ -4873,22 +4873,22 @@
         <v>100000000</v>
       </c>
       <c r="C139">
-        <v>100000000</v>
+        <v>75000000</v>
       </c>
       <c r="D139">
-        <v>7999750</v>
+        <v>0</v>
       </c>
       <c r="E139">
         <v>74403889</v>
       </c>
       <c r="F139">
-        <v>82403639</v>
+        <v>74403889</v>
       </c>
       <c r="G139">
-        <v>17596361</v>
-      </c>
-      <c r="H139" t="s">
-        <v>9</v>
+        <v>596111</v>
+      </c>
+      <c r="H139">
+        <v>25000000</v>
       </c>
     </row>
     <row r="140" spans="1:8" x14ac:dyDescent="0.3">
@@ -4899,22 +4899,22 @@
         <v>354600000</v>
       </c>
       <c r="C140">
-        <v>354600000</v>
+        <v>265950000</v>
       </c>
       <c r="D140">
-        <v>19400000</v>
+        <v>14000000</v>
       </c>
       <c r="E140">
-        <v>225268700</v>
+        <v>206966600</v>
       </c>
       <c r="F140">
-        <v>244668700</v>
+        <v>220966600</v>
       </c>
       <c r="G140">
-        <v>109931300</v>
-      </c>
-      <c r="H140" t="s">
-        <v>9</v>
+        <v>44983400</v>
+      </c>
+      <c r="H140">
+        <v>88650000</v>
       </c>
     </row>
     <row r="141" spans="1:8" x14ac:dyDescent="0.3">
@@ -4951,7 +4951,7 @@
         <v>271400000</v>
       </c>
       <c r="C142">
-        <v>271400000</v>
+        <v>203550000</v>
       </c>
       <c r="D142">
         <v>2380000</v>
@@ -4963,10 +4963,10 @@
         <v>179583982</v>
       </c>
       <c r="G142">
-        <v>91816018</v>
-      </c>
-      <c r="H142" t="s">
-        <v>9</v>
+        <v>23966018</v>
+      </c>
+      <c r="H142">
+        <v>67850000</v>
       </c>
     </row>
     <row r="143" spans="1:8" x14ac:dyDescent="0.3">
@@ -4977,22 +4977,22 @@
         <v>213320000</v>
       </c>
       <c r="C143">
-        <v>213320000</v>
+        <v>159990000</v>
       </c>
       <c r="D143">
         <v>0</v>
       </c>
       <c r="E143">
-        <v>153135750</v>
+        <v>151710750</v>
       </c>
       <c r="F143">
-        <v>153135750</v>
+        <v>151710750</v>
       </c>
       <c r="G143">
-        <v>60184250</v>
-      </c>
-      <c r="H143" t="s">
-        <v>9</v>
+        <v>8279250</v>
+      </c>
+      <c r="H143">
+        <v>53330000</v>
       </c>
     </row>
     <row r="144" spans="1:8" x14ac:dyDescent="0.3">
@@ -5035,13 +5035,13 @@
         <v>0</v>
       </c>
       <c r="E145">
-        <v>309067829</v>
+        <v>270434351</v>
       </c>
       <c r="F145">
-        <v>309067829</v>
+        <v>270434351</v>
       </c>
       <c r="G145">
-        <v>-309067829</v>
+        <v>-270434351</v>
       </c>
       <c r="H145" t="s">
         <v>9</v>
@@ -5061,13 +5061,13 @@
         <v>0</v>
       </c>
       <c r="E146">
-        <v>7120231725</v>
+        <v>7120186725</v>
       </c>
       <c r="F146">
-        <v>7120231725</v>
+        <v>7120186725</v>
       </c>
       <c r="G146">
-        <v>2828862358</v>
+        <v>2828907358</v>
       </c>
       <c r="H146" t="s">
         <v>9</v>
@@ -5113,13 +5113,13 @@
         <v>0</v>
       </c>
       <c r="E148">
-        <v>8399118521</v>
+        <v>8371186419</v>
       </c>
       <c r="F148">
-        <v>8399118521</v>
+        <v>8371186419</v>
       </c>
       <c r="G148">
-        <v>1370731370</v>
+        <v>1398663472</v>
       </c>
       <c r="H148" t="s">
         <v>9</v>
@@ -5217,13 +5217,13 @@
         <v>0</v>
       </c>
       <c r="E152">
-        <v>1073128014</v>
+        <v>1071715901</v>
       </c>
       <c r="F152">
-        <v>1073128014</v>
+        <v>1071715901</v>
       </c>
       <c r="G152">
-        <v>257189525</v>
+        <v>258601638</v>
       </c>
       <c r="H152" t="s">
         <v>9</v>
@@ -5269,13 +5269,13 @@
         <v>0</v>
       </c>
       <c r="E154">
-        <v>146200000</v>
+        <v>127925000</v>
       </c>
       <c r="F154">
-        <v>146200000</v>
+        <v>127925000</v>
       </c>
       <c r="G154">
-        <v>-146200000</v>
+        <v>-127925000</v>
       </c>
       <c r="H154" t="s">
         <v>9</v>
@@ -5289,22 +5289,22 @@
         <v>52584136175</v>
       </c>
       <c r="C155">
-        <v>52473056175</v>
+        <v>52173056175</v>
       </c>
       <c r="D155">
-        <v>6414477693</v>
+        <v>9725577060</v>
       </c>
       <c r="E155">
-        <v>37498191630</v>
+        <v>32466651017</v>
       </c>
       <c r="F155">
-        <v>43912669323</v>
+        <v>42192228077</v>
       </c>
       <c r="G155">
-        <v>8560386852</v>
+        <v>9980828098</v>
       </c>
       <c r="H155">
-        <v>111080000</v>
+        <v>411080000</v>
       </c>
     </row>
     <row r="156" spans="1:8" x14ac:dyDescent="0.3">
@@ -5318,10 +5318,10 @@
         <v>11383511000</v>
       </c>
       <c r="D156">
-        <v>978809000</v>
+        <v>2949251692</v>
       </c>
       <c r="E156">
-        <v>10390291890</v>
+        <v>8419849198</v>
       </c>
       <c r="F156">
         <v>11369100890</v>
@@ -5344,16 +5344,16 @@
         <v>4687847624</v>
       </c>
       <c r="D157">
-        <v>2997007956</v>
+        <v>3660627472</v>
       </c>
       <c r="E157">
-        <v>1666441536</v>
+        <v>1000139013</v>
       </c>
       <c r="F157">
-        <v>4663449492</v>
+        <v>4660766485</v>
       </c>
       <c r="G157">
-        <v>24398132</v>
+        <v>27081139</v>
       </c>
       <c r="H157" t="s">
         <v>9</v>
@@ -5474,16 +5474,16 @@
         <v>1702406000</v>
       </c>
       <c r="D162">
-        <v>504786557</v>
+        <v>310951584</v>
       </c>
       <c r="E162">
         <v>807533375</v>
       </c>
       <c r="F162">
-        <v>1312319932</v>
+        <v>1118484959</v>
       </c>
       <c r="G162">
-        <v>390086068</v>
+        <v>583921041</v>
       </c>
       <c r="H162" t="s">
         <v>9</v>
@@ -5500,10 +5500,10 @@
         <v>463360000</v>
       </c>
       <c r="D163">
-        <v>0</v>
+        <v>429930120</v>
       </c>
       <c r="E163">
-        <v>449888120</v>
+        <v>19958000</v>
       </c>
       <c r="F163">
         <v>449888120</v>
@@ -5526,10 +5526,10 @@
         <v>996956000</v>
       </c>
       <c r="D164">
-        <v>0</v>
+        <v>481950000</v>
       </c>
       <c r="E164">
-        <v>540022672</v>
+        <v>58072672</v>
       </c>
       <c r="F164">
         <v>540022672</v>
@@ -5578,16 +5578,16 @@
         <v>2427860000</v>
       </c>
       <c r="D166">
-        <v>1728354135</v>
+        <v>2301645594</v>
       </c>
       <c r="E166">
-        <v>627340260</v>
+        <v>43500000</v>
       </c>
       <c r="F166">
-        <v>2355694395</v>
+        <v>2345145594</v>
       </c>
       <c r="G166">
-        <v>72165605</v>
+        <v>82714406</v>
       </c>
       <c r="H166" t="s">
         <v>9</v>
@@ -5604,16 +5604,16 @@
         <v>500000000</v>
       </c>
       <c r="D167">
-        <v>55354016</v>
+        <v>54664725</v>
       </c>
       <c r="E167">
         <v>185788488</v>
       </c>
       <c r="F167">
-        <v>241142504</v>
+        <v>240453213</v>
       </c>
       <c r="G167">
-        <v>258857496</v>
+        <v>259546787</v>
       </c>
       <c r="H167" t="s">
         <v>9</v>
@@ -5656,10 +5656,10 @@
         <v>867942000</v>
       </c>
       <c r="D169">
-        <v>0</v>
+        <v>642565410</v>
       </c>
       <c r="E169">
-        <v>642565410</v>
+        <v>0</v>
       </c>
       <c r="F169">
         <v>642565410</v>
@@ -5682,10 +5682,10 @@
         <v>187500000</v>
       </c>
       <c r="D170">
-        <v>0</v>
+        <v>142100000</v>
       </c>
       <c r="E170">
-        <v>142100000</v>
+        <v>0</v>
       </c>
       <c r="F170">
         <v>142100000</v>
@@ -5812,16 +5812,16 @@
         <v>595150000</v>
       </c>
       <c r="D175">
-        <v>74848100</v>
+        <v>73181400</v>
       </c>
       <c r="E175">
         <v>451500394</v>
       </c>
       <c r="F175">
-        <v>526348494</v>
+        <v>524681794</v>
       </c>
       <c r="G175">
-        <v>68801506</v>
+        <v>70468206</v>
       </c>
       <c r="H175">
         <v>136250000</v>
@@ -5864,16 +5864,16 @@
         <v>253250000</v>
       </c>
       <c r="D177">
-        <v>104564725</v>
+        <v>49900000</v>
       </c>
       <c r="E177">
         <v>104678200</v>
       </c>
       <c r="F177">
-        <v>209242925</v>
+        <v>154578200</v>
       </c>
       <c r="G177">
-        <v>44007075</v>
+        <v>98671800</v>
       </c>
       <c r="H177">
         <v>146550000</v>
@@ -5919,13 +5919,13 @@
         <v>0</v>
       </c>
       <c r="E179">
-        <v>130265250</v>
+        <v>115634250</v>
       </c>
       <c r="F179">
-        <v>130265250</v>
+        <v>115634250</v>
       </c>
       <c r="G179">
-        <v>32036250</v>
+        <v>46667250</v>
       </c>
       <c r="H179">
         <v>54100500</v>
@@ -5971,13 +5971,13 @@
         <v>0</v>
       </c>
       <c r="E181">
-        <v>5305635113</v>
+        <v>5304783338</v>
       </c>
       <c r="F181">
-        <v>5305635113</v>
+        <v>5304783338</v>
       </c>
       <c r="G181">
-        <v>2199088265</v>
+        <v>2199940040</v>
       </c>
       <c r="H181" t="s">
         <v>9</v>
@@ -6176,16 +6176,16 @@
         <v>46375593027</v>
       </c>
       <c r="D189">
-        <v>7081694202</v>
+        <v>11734737710</v>
       </c>
       <c r="E189">
-        <v>31899377882</v>
+        <v>26966764102</v>
       </c>
       <c r="F189">
-        <v>38981072084</v>
+        <v>38701501812</v>
       </c>
       <c r="G189">
-        <v>7394520943</v>
+        <v>7674091215</v>
       </c>
       <c r="H189">
         <v>449400500</v>
@@ -6202,10 +6202,10 @@
         <v>7317456560</v>
       </c>
       <c r="D190">
-        <v>729734800</v>
+        <v>3256309220</v>
       </c>
       <c r="E190">
-        <v>6587069420</v>
+        <v>4060495000</v>
       </c>
       <c r="F190">
         <v>7316804220</v>
@@ -6306,10 +6306,10 @@
         <v>296447320</v>
       </c>
       <c r="D194">
-        <v>0</v>
+        <v>1100000</v>
       </c>
       <c r="E194">
-        <v>290564000</v>
+        <v>289464000</v>
       </c>
       <c r="F194">
         <v>290564000</v>
@@ -6332,16 +6332,16 @@
         <v>3919663677</v>
       </c>
       <c r="D195">
-        <v>2893777960</v>
+        <v>3265311235</v>
       </c>
       <c r="E195">
         <v>530323683</v>
       </c>
       <c r="F195">
-        <v>3424101643</v>
+        <v>3795634918</v>
       </c>
       <c r="G195">
-        <v>495562034</v>
+        <v>124028759</v>
       </c>
       <c r="H195" t="s">
         <v>9</v>
@@ -6410,16 +6410,16 @@
         <v>469000000</v>
       </c>
       <c r="D198">
-        <v>53374985</v>
+        <v>77690468</v>
       </c>
       <c r="E198">
-        <v>95104084</v>
+        <v>64102434</v>
       </c>
       <c r="F198">
-        <v>148479069</v>
+        <v>141792902</v>
       </c>
       <c r="G198">
-        <v>320520931</v>
+        <v>327207098</v>
       </c>
       <c r="H198" t="s">
         <v>9</v>
@@ -6436,10 +6436,10 @@
         <v>400000000</v>
       </c>
       <c r="D199">
-        <v>0</v>
+        <v>21270500</v>
       </c>
       <c r="E199">
-        <v>182155299</v>
+        <v>160884799</v>
       </c>
       <c r="F199">
         <v>182155299</v>
@@ -6462,10 +6462,10 @@
         <v>609000000</v>
       </c>
       <c r="D200">
-        <v>0</v>
+        <v>295740587</v>
       </c>
       <c r="E200">
-        <v>570913762</v>
+        <v>275173175</v>
       </c>
       <c r="F200">
         <v>570913762</v>
@@ -6488,16 +6488,16 @@
         <v>1862650000</v>
       </c>
       <c r="D201">
-        <v>188748057</v>
+        <v>405032067</v>
       </c>
       <c r="E201">
-        <v>1537416806</v>
+        <v>1311136706</v>
       </c>
       <c r="F201">
-        <v>1726164863</v>
+        <v>1716168773</v>
       </c>
       <c r="G201">
-        <v>136485137</v>
+        <v>146481227</v>
       </c>
       <c r="H201" t="s">
         <v>9</v>
@@ -6514,16 +6514,16 @@
         <v>281000000</v>
       </c>
       <c r="D202">
-        <v>35987168</v>
+        <v>0</v>
       </c>
       <c r="E202">
         <v>54403548</v>
       </c>
       <c r="F202">
-        <v>90390716</v>
+        <v>54403548</v>
       </c>
       <c r="G202">
-        <v>190609284</v>
+        <v>226596452</v>
       </c>
       <c r="H202" t="s">
         <v>9</v>
@@ -6592,16 +6592,16 @@
         <v>4350172680</v>
       </c>
       <c r="D205">
-        <v>3028130600</v>
+        <v>3109885000</v>
       </c>
       <c r="E205">
         <v>1236281200</v>
       </c>
       <c r="F205">
-        <v>4264411800</v>
+        <v>4346166200</v>
       </c>
       <c r="G205">
-        <v>85760880</v>
+        <v>4006480</v>
       </c>
       <c r="H205" t="s">
         <v>9</v>
@@ -6618,16 +6618,16 @@
         <v>40000000</v>
       </c>
       <c r="D206">
-        <v>7640000</v>
+        <v>0</v>
       </c>
       <c r="E206">
         <v>13010000</v>
       </c>
       <c r="F206">
-        <v>20650000</v>
+        <v>13010000</v>
       </c>
       <c r="G206">
-        <v>19350000</v>
+        <v>26990000</v>
       </c>
       <c r="H206" t="s">
         <v>9</v>
@@ -6768,25 +6768,25 @@
         <v>27</v>
       </c>
       <c r="B212">
-        <v>113750000</v>
+        <v>130000000</v>
       </c>
       <c r="C212">
-        <v>113750000</v>
+        <v>97500000</v>
       </c>
       <c r="D212">
-        <v>18540090</v>
+        <v>6800000</v>
       </c>
       <c r="E212">
-        <v>74218210</v>
+        <v>71071407</v>
       </c>
       <c r="F212">
-        <v>92758300</v>
+        <v>77871407</v>
       </c>
       <c r="G212">
-        <v>20991700</v>
-      </c>
-      <c r="H212" t="s">
-        <v>9</v>
+        <v>19628593</v>
+      </c>
+      <c r="H212">
+        <v>32500000</v>
       </c>
     </row>
     <row r="213" spans="1:8" x14ac:dyDescent="0.3">
@@ -6800,10 +6800,10 @@
         <v>385534500</v>
       </c>
       <c r="D213">
-        <v>26010000</v>
+        <v>49485000</v>
       </c>
       <c r="E213">
-        <v>275948000</v>
+        <v>252473000</v>
       </c>
       <c r="F213">
         <v>301958000</v>
@@ -6852,16 +6852,16 @@
         <v>337500000</v>
       </c>
       <c r="D215">
-        <v>92956149</v>
+        <v>110694039</v>
       </c>
       <c r="E215">
-        <v>132840958</v>
+        <v>118245454</v>
       </c>
       <c r="F215">
-        <v>225797107</v>
+        <v>228939493</v>
       </c>
       <c r="G215">
-        <v>111702893</v>
+        <v>108560507</v>
       </c>
       <c r="H215">
         <v>112500000</v>
@@ -6878,10 +6878,10 @@
         <v>123750000</v>
       </c>
       <c r="D216">
-        <v>0</v>
+        <v>10000000</v>
       </c>
       <c r="E216">
-        <v>20900000</v>
+        <v>10900000</v>
       </c>
       <c r="F216">
         <v>20900000</v>
@@ -6898,25 +6898,25 @@
         <v>32</v>
       </c>
       <c r="B217">
-        <v>220500000</v>
+        <v>252000000</v>
       </c>
       <c r="C217">
-        <v>220500000</v>
+        <v>189000000</v>
       </c>
       <c r="D217">
         <v>0</v>
       </c>
       <c r="E217">
-        <v>189485250</v>
+        <v>169013000</v>
       </c>
       <c r="F217">
-        <v>189485250</v>
+        <v>169013000</v>
       </c>
       <c r="G217">
-        <v>31014750</v>
-      </c>
-      <c r="H217" t="s">
-        <v>9</v>
+        <v>19987000</v>
+      </c>
+      <c r="H217">
+        <v>63000000</v>
       </c>
     </row>
     <row r="218" spans="1:8" x14ac:dyDescent="0.3">
@@ -6930,16 +6930,16 @@
         <v>18000000</v>
       </c>
       <c r="D218">
-        <v>1795000</v>
+        <v>3590000</v>
       </c>
       <c r="E218">
-        <v>8983057</v>
+        <v>7935118</v>
       </c>
       <c r="F218">
-        <v>10778057</v>
+        <v>11525118</v>
       </c>
       <c r="G218">
-        <v>7221943</v>
+        <v>6474882</v>
       </c>
       <c r="H218" t="s">
         <v>9</v>
@@ -6985,13 +6985,13 @@
         <v>0</v>
       </c>
       <c r="E220">
-        <v>7091438430</v>
+        <v>7090319905</v>
       </c>
       <c r="F220">
-        <v>7091438430</v>
+        <v>7090319905</v>
       </c>
       <c r="G220">
-        <v>2731723696</v>
+        <v>2732842221</v>
       </c>
       <c r="H220" t="s">
         <v>9</v>
@@ -7037,13 +7037,13 @@
         <v>0</v>
       </c>
       <c r="E222">
-        <v>8270300754</v>
+        <v>8241279986</v>
       </c>
       <c r="F222">
-        <v>8270300754</v>
+        <v>8241279986</v>
       </c>
       <c r="G222">
-        <v>975374618</v>
+        <v>1004395386</v>
       </c>
       <c r="H222" t="s">
         <v>9</v>
@@ -7141,13 +7141,13 @@
         <v>0</v>
       </c>
       <c r="E226">
-        <v>1030179546</v>
+        <v>1029675511</v>
       </c>
       <c r="F226">
-        <v>1030179546</v>
+        <v>1029675511</v>
       </c>
       <c r="G226">
-        <v>-205013613</v>
+        <v>-204509578</v>
       </c>
       <c r="H226" t="s">
         <v>9</v>
@@ -7184,25 +7184,25 @@
         <v>85</v>
       </c>
       <c r="B228">
-        <v>47866745045</v>
+        <v>47914495045</v>
       </c>
       <c r="C228">
-        <v>47546983545</v>
+        <v>47499233545</v>
       </c>
       <c r="D228">
-        <v>8651157690</v>
+        <v>12187370997</v>
       </c>
       <c r="E228">
-        <v>31649866226</v>
+        <v>28444518145</v>
       </c>
       <c r="F228">
-        <v>40301023916</v>
+        <v>40631889142</v>
       </c>
       <c r="G228">
-        <v>7245959629</v>
+        <v>6867344403</v>
       </c>
       <c r="H228">
-        <v>319761500</v>
+        <v>415261500</v>
       </c>
     </row>
     <row r="229" spans="1:8" x14ac:dyDescent="0.3">
@@ -7216,16 +7216,16 @@
         <v>12264606000</v>
       </c>
       <c r="D229">
-        <v>6253487000</v>
+        <v>8206842730</v>
       </c>
       <c r="E229">
-        <v>5677992730</v>
+        <v>3238064000</v>
       </c>
       <c r="F229">
-        <v>11931479730</v>
+        <v>11444906730</v>
       </c>
       <c r="G229">
-        <v>333126270</v>
+        <v>819699270</v>
       </c>
       <c r="H229" t="s">
         <v>9</v>
@@ -7242,10 +7242,10 @@
         <v>1126306000</v>
       </c>
       <c r="D230">
-        <v>499624121</v>
+        <v>1108174121</v>
       </c>
       <c r="E230">
-        <v>620986007</v>
+        <v>12436007</v>
       </c>
       <c r="F230">
         <v>1120610128</v>
@@ -7294,16 +7294,16 @@
         <v>495000000</v>
       </c>
       <c r="D232">
-        <v>13642600</v>
+        <v>0</v>
       </c>
       <c r="E232">
         <v>456679595</v>
       </c>
       <c r="F232">
-        <v>470322195</v>
+        <v>456679595</v>
       </c>
       <c r="G232">
-        <v>24677805</v>
+        <v>38320405</v>
       </c>
       <c r="H232" t="s">
         <v>9</v>
@@ -7320,16 +7320,16 @@
         <v>200000000</v>
       </c>
       <c r="D233">
-        <v>116645170</v>
+        <v>111648138</v>
       </c>
       <c r="E233">
         <v>80120815</v>
       </c>
       <c r="F233">
-        <v>196765985</v>
+        <v>191768953</v>
       </c>
       <c r="G233">
-        <v>3234015</v>
+        <v>8231047</v>
       </c>
       <c r="H233" t="s">
         <v>9</v>
@@ -7372,16 +7372,16 @@
         <v>1380000000</v>
       </c>
       <c r="D235">
-        <v>188118460</v>
+        <v>195458460</v>
       </c>
       <c r="E235">
         <v>1036121967</v>
       </c>
       <c r="F235">
-        <v>1224240427</v>
+        <v>1231580427</v>
       </c>
       <c r="G235">
-        <v>155759573</v>
+        <v>148419573</v>
       </c>
       <c r="H235" t="s">
         <v>9</v>
@@ -7554,16 +7554,16 @@
         <v>780000000</v>
       </c>
       <c r="D242">
-        <v>199650000</v>
+        <v>674650000</v>
       </c>
       <c r="E242">
-        <v>511700000</v>
+        <v>46200000</v>
       </c>
       <c r="F242">
-        <v>711350000</v>
+        <v>720850000</v>
       </c>
       <c r="G242">
-        <v>68650000</v>
+        <v>59150000</v>
       </c>
       <c r="H242">
         <v>260000000</v>
@@ -7658,16 +7658,16 @@
         <v>354238500</v>
       </c>
       <c r="D246">
-        <v>25842500</v>
+        <v>38424000</v>
       </c>
       <c r="E246">
-        <v>316957400</v>
+        <v>304436900</v>
       </c>
       <c r="F246">
-        <v>342799900</v>
+        <v>342860900</v>
       </c>
       <c r="G246">
-        <v>11438600</v>
+        <v>11377600</v>
       </c>
       <c r="H246">
         <v>118079500</v>
@@ -7739,13 +7739,13 @@
         <v>0</v>
       </c>
       <c r="E249">
-        <v>159184000</v>
+        <v>142794250</v>
       </c>
       <c r="F249">
-        <v>159184000</v>
+        <v>142794250</v>
       </c>
       <c r="G249">
-        <v>43100000</v>
+        <v>59489750</v>
       </c>
       <c r="H249">
         <v>67428000</v>
@@ -7791,13 +7791,13 @@
         <v>0</v>
       </c>
       <c r="E251">
-        <v>6996377976</v>
+        <v>6995428577</v>
       </c>
       <c r="F251">
-        <v>6996377976</v>
+        <v>6995428577</v>
       </c>
       <c r="G251">
-        <v>2829578194</v>
+        <v>2830527593</v>
       </c>
       <c r="H251" t="s">
         <v>9</v>
@@ -7840,10 +7840,10 @@
         <v>9512105917</v>
       </c>
       <c r="D253">
-        <v>0</v>
+        <v>27847073</v>
       </c>
       <c r="E253">
-        <v>8046195218</v>
+        <v>8018348145</v>
       </c>
       <c r="F253">
         <v>8046195218</v>
@@ -8022,16 +8022,16 @@
         <v>48914772555</v>
       </c>
       <c r="D260">
-        <v>8801629480</v>
+        <v>11867664151</v>
       </c>
       <c r="E260">
-        <v>32388370794</v>
+        <v>28816685342</v>
       </c>
       <c r="F260">
-        <v>41190000274</v>
+        <v>40684349493</v>
       </c>
       <c r="G260">
-        <v>7724772281</v>
+        <v>8230423062</v>
       </c>
       <c r="H260">
         <v>525212165</v>
@@ -8048,10 +8048,10 @@
         <v>5695069150</v>
       </c>
       <c r="D261">
-        <v>3485289600</v>
+        <v>4255699600</v>
       </c>
       <c r="E261">
-        <v>2116532000</v>
+        <v>1346122000</v>
       </c>
       <c r="F261">
         <v>5601821600</v>
@@ -8074,16 +8074,16 @@
         <v>1540000000</v>
       </c>
       <c r="D262">
-        <v>743352000</v>
+        <v>0</v>
       </c>
       <c r="E262">
         <v>784443706</v>
       </c>
       <c r="F262">
-        <v>1527795706</v>
+        <v>784443706</v>
       </c>
       <c r="G262">
-        <v>12204294</v>
+        <v>755556294</v>
       </c>
       <c r="H262" t="s">
         <v>9</v>
@@ -8126,16 +8126,16 @@
         <v>150000000</v>
       </c>
       <c r="D264">
-        <v>137837144</v>
+        <v>0</v>
       </c>
       <c r="E264">
         <v>0</v>
       </c>
-      <c r="F264">
-        <v>137837144</v>
+      <c r="F264" t="s">
+        <v>9</v>
       </c>
       <c r="G264">
-        <v>12162856</v>
+        <v>150000000</v>
       </c>
       <c r="H264" t="s">
         <v>9</v>
@@ -8204,16 +8204,16 @@
         <v>491133000</v>
       </c>
       <c r="D267">
-        <v>388850000</v>
+        <v>0</v>
       </c>
       <c r="E267">
         <v>98325000</v>
       </c>
       <c r="F267">
-        <v>487175000</v>
+        <v>98325000</v>
       </c>
       <c r="G267">
-        <v>3958000</v>
+        <v>392808000</v>
       </c>
       <c r="H267" t="s">
         <v>9</v>
@@ -8230,16 +8230,16 @@
         <v>3609800000</v>
       </c>
       <c r="D268">
-        <v>1651738751</v>
+        <v>1123878540</v>
       </c>
       <c r="E268">
-        <v>832555455</v>
+        <v>764581755</v>
       </c>
       <c r="F268">
-        <v>2484294206</v>
+        <v>1888460295</v>
       </c>
       <c r="G268">
-        <v>1125505794</v>
+        <v>1721339705</v>
       </c>
       <c r="H268" t="s">
         <v>9</v>
@@ -8282,10 +8282,10 @@
         <v>1240000000</v>
       </c>
       <c r="D270">
-        <v>480457432</v>
+        <v>883234492</v>
       </c>
       <c r="E270">
-        <v>519660674</v>
+        <v>116883614</v>
       </c>
       <c r="F270">
         <v>1000118106</v>
@@ -8308,16 +8308,16 @@
         <v>150000000</v>
       </c>
       <c r="D271">
-        <v>29165900</v>
+        <v>0</v>
       </c>
       <c r="E271">
         <v>46982180</v>
       </c>
       <c r="F271">
-        <v>76148080</v>
+        <v>46982180</v>
       </c>
       <c r="G271">
-        <v>73851920</v>
+        <v>103017820</v>
       </c>
       <c r="H271" t="s">
         <v>9</v>
@@ -8334,16 +8334,16 @@
         <v>2668302662</v>
       </c>
       <c r="D272">
-        <v>27700000</v>
+        <v>0</v>
       </c>
       <c r="E272">
         <v>2612869000</v>
       </c>
       <c r="F272">
-        <v>2640569000</v>
+        <v>2612869000</v>
       </c>
       <c r="G272">
-        <v>27733662</v>
+        <v>55433662</v>
       </c>
       <c r="H272" t="s">
         <v>9</v>
@@ -8415,13 +8415,13 @@
         <v>0</v>
       </c>
       <c r="E275">
-        <v>493284281</v>
+        <v>495864281</v>
       </c>
       <c r="F275">
-        <v>493284281</v>
-      </c>
-      <c r="G275">
-        <v>2580000</v>
+        <v>495864281</v>
+      </c>
+      <c r="G275" t="s">
+        <v>9</v>
       </c>
       <c r="H275" t="s">
         <v>9</v>
@@ -8464,16 +8464,16 @@
         <v>3309100507</v>
       </c>
       <c r="D277">
-        <v>2001151740</v>
+        <v>1991152004</v>
       </c>
       <c r="E277">
         <v>569806840</v>
       </c>
       <c r="F277">
-        <v>2570958580</v>
+        <v>2560958844</v>
       </c>
       <c r="G277">
-        <v>738141927</v>
+        <v>748141663</v>
       </c>
       <c r="H277" t="s">
         <v>9</v>
@@ -8542,16 +8542,16 @@
         <v>1242000000</v>
       </c>
       <c r="D280">
-        <v>878639865</v>
+        <v>922639865</v>
       </c>
       <c r="E280">
-        <v>90954943</v>
+        <v>47046943</v>
       </c>
       <c r="F280">
-        <v>969594808</v>
+        <v>969686808</v>
       </c>
       <c r="G280">
-        <v>272405192</v>
+        <v>272313192</v>
       </c>
       <c r="H280" t="s">
         <v>9</v>
@@ -8568,16 +8568,16 @@
         <v>150000000</v>
       </c>
       <c r="D281">
-        <v>0</v>
+        <v>121000000</v>
       </c>
       <c r="E281">
-        <v>120747000</v>
+        <v>0</v>
       </c>
       <c r="F281">
-        <v>120747000</v>
+        <v>121000000</v>
       </c>
       <c r="G281">
-        <v>29253000</v>
+        <v>29000000</v>
       </c>
       <c r="H281">
         <v>50000000</v>
@@ -8594,10 +8594,10 @@
         <v>346377600</v>
       </c>
       <c r="D282">
-        <v>0</v>
+        <v>39199980</v>
       </c>
       <c r="E282">
-        <v>258399980</v>
+        <v>219200000</v>
       </c>
       <c r="F282">
         <v>258399980</v>
@@ -8646,16 +8646,16 @@
         <v>235553350</v>
       </c>
       <c r="D284">
-        <v>118623893</v>
+        <v>0</v>
       </c>
       <c r="E284">
         <v>56925714</v>
       </c>
       <c r="F284">
-        <v>175549607</v>
+        <v>56925714</v>
       </c>
       <c r="G284">
-        <v>60003743</v>
+        <v>178627636</v>
       </c>
       <c r="H284">
         <v>20684450</v>
@@ -8672,16 +8672,16 @@
         <v>470406638</v>
       </c>
       <c r="D285">
-        <v>99647500</v>
+        <v>52841500</v>
       </c>
       <c r="E285">
-        <v>313781933</v>
+        <v>282876433</v>
       </c>
       <c r="F285">
-        <v>413429433</v>
+        <v>335717933</v>
       </c>
       <c r="G285">
-        <v>56977205</v>
+        <v>134688705</v>
       </c>
       <c r="H285">
         <v>156802213</v>
@@ -8724,16 +8724,16 @@
         <v>388702000</v>
       </c>
       <c r="D287">
-        <v>148761000</v>
+        <v>107601000</v>
       </c>
       <c r="E287">
-        <v>123730811</v>
+        <v>116129811</v>
       </c>
       <c r="F287">
-        <v>272491811</v>
+        <v>223730811</v>
       </c>
       <c r="G287">
-        <v>116210189</v>
+        <v>164971189</v>
       </c>
       <c r="H287">
         <v>235734000</v>
@@ -8753,13 +8753,13 @@
         <v>0</v>
       </c>
       <c r="E288">
-        <v>233660750</v>
+        <v>211597750</v>
       </c>
       <c r="F288">
-        <v>233660750</v>
+        <v>211597750</v>
       </c>
       <c r="G288">
-        <v>114813500</v>
+        <v>136876500</v>
       </c>
       <c r="H288">
         <v>67824750</v>
@@ -8831,13 +8831,13 @@
         <v>0</v>
       </c>
       <c r="E291">
-        <v>72943583</v>
+        <v>63825635</v>
       </c>
       <c r="F291">
-        <v>72943583</v>
+        <v>63825635</v>
       </c>
       <c r="G291">
-        <v>-72943583</v>
+        <v>-63825635</v>
       </c>
       <c r="H291" t="s">
         <v>9</v>
@@ -8857,13 +8857,13 @@
         <v>0</v>
       </c>
       <c r="E292">
-        <v>8985188423</v>
+        <v>8983822848</v>
       </c>
       <c r="F292">
-        <v>8985188423</v>
+        <v>8983822848</v>
       </c>
       <c r="G292">
-        <v>3637430504</v>
+        <v>3638796079</v>
       </c>
       <c r="H292" t="s">
         <v>9</v>
@@ -8909,13 +8909,13 @@
         <v>0</v>
       </c>
       <c r="E294">
-        <v>10841494695</v>
+        <v>10802659505</v>
       </c>
       <c r="F294">
-        <v>10841494695</v>
+        <v>10802659505</v>
       </c>
       <c r="G294">
-        <v>2070222720</v>
+        <v>2109057910</v>
       </c>
       <c r="H294" t="s">
         <v>9</v>
@@ -9013,13 +9013,13 @@
         <v>0</v>
       </c>
       <c r="E298">
-        <v>1283585105</v>
+        <v>1283180553</v>
       </c>
       <c r="F298">
-        <v>1283585105</v>
+        <v>1283180553</v>
       </c>
       <c r="G298">
-        <v>276743732</v>
+        <v>277148284</v>
       </c>
       <c r="H298" t="s">
         <v>9</v>
@@ -9062,16 +9062,16 @@
         <v>63706784713</v>
       </c>
       <c r="D300">
-        <v>14169783798</v>
+        <v>13475815954</v>
       </c>
       <c r="E300">
-        <v>37812189650</v>
+        <v>36259461145</v>
       </c>
       <c r="F300">
-        <v>51981973448</v>
+        <v>49735277099</v>
       </c>
       <c r="G300">
-        <v>11724811265</v>
+        <v>13971507614</v>
       </c>
       <c r="H300">
         <v>531045413</v>
@@ -9088,16 +9088,16 @@
         <v>3628073000</v>
       </c>
       <c r="D301">
-        <v>340158685</v>
+        <v>1305682100</v>
       </c>
       <c r="E301">
-        <v>3279858000</v>
+        <v>2322388900</v>
       </c>
       <c r="F301">
-        <v>3620016685</v>
+        <v>3628071000</v>
       </c>
       <c r="G301">
-        <v>8056315</v>
+        <v>2000</v>
       </c>
       <c r="H301" t="s">
         <v>9</v>
@@ -9192,16 +9192,16 @@
         <v>298750000</v>
       </c>
       <c r="D305">
-        <v>168298148</v>
+        <v>228565327</v>
       </c>
       <c r="E305">
-        <v>130041952</v>
+        <v>65826870</v>
       </c>
       <c r="F305">
-        <v>298340100</v>
+        <v>294392197</v>
       </c>
       <c r="G305">
-        <v>409900</v>
+        <v>4357803</v>
       </c>
       <c r="H305" t="s">
         <v>9</v>
@@ -9244,16 +9244,16 @@
         <v>1222108000</v>
       </c>
       <c r="D307">
-        <v>117131114</v>
+        <v>154177064</v>
       </c>
       <c r="E307">
-        <v>1104633271</v>
+        <v>1066657271</v>
       </c>
       <c r="F307">
-        <v>1221764385</v>
+        <v>1220834335</v>
       </c>
       <c r="G307">
-        <v>343615</v>
+        <v>1273665</v>
       </c>
       <c r="H307" t="s">
         <v>9</v>
@@ -9270,16 +9270,16 @@
         <v>534300000</v>
       </c>
       <c r="D308">
-        <v>169435823</v>
+        <v>130976265</v>
       </c>
       <c r="E308">
-        <v>308400193</v>
+        <v>298405428</v>
       </c>
       <c r="F308">
-        <v>477836016</v>
+        <v>429381693</v>
       </c>
       <c r="G308">
-        <v>56463984</v>
+        <v>104918307</v>
       </c>
       <c r="H308" t="s">
         <v>9</v>
@@ -9296,10 +9296,10 @@
         <v>145000000</v>
       </c>
       <c r="D309">
-        <v>79616553</v>
+        <v>114740165</v>
       </c>
       <c r="E309">
-        <v>65383447</v>
+        <v>30259835</v>
       </c>
       <c r="F309">
         <v>145000000</v>
@@ -9322,16 +9322,16 @@
         <v>174000000</v>
       </c>
       <c r="D310">
-        <v>126215000</v>
+        <v>129869969</v>
       </c>
       <c r="E310">
         <v>44129340</v>
       </c>
       <c r="F310">
-        <v>170344340</v>
+        <v>173999309</v>
       </c>
       <c r="G310">
-        <v>3655660</v>
+        <v>691</v>
       </c>
       <c r="H310" t="s">
         <v>9</v>
@@ -9374,10 +9374,10 @@
         <v>1882400000</v>
       </c>
       <c r="D312">
-        <v>159330000</v>
+        <v>169090000</v>
       </c>
       <c r="E312">
-        <v>1723065000</v>
+        <v>1713305000</v>
       </c>
       <c r="F312">
         <v>1882395000</v>
@@ -9452,10 +9452,10 @@
         <v>463000000</v>
       </c>
       <c r="D315">
-        <v>353636000</v>
+        <v>388736000</v>
       </c>
       <c r="E315">
-        <v>80700000</v>
+        <v>45600000</v>
       </c>
       <c r="F315">
         <v>434336000</v>
@@ -9504,16 +9504,16 @@
         <v>111310000</v>
       </c>
       <c r="D317">
-        <v>0</v>
+        <v>59854600</v>
       </c>
       <c r="E317">
-        <v>79542700</v>
+        <v>21262500</v>
       </c>
       <c r="F317">
-        <v>79542700</v>
+        <v>81117100</v>
       </c>
       <c r="G317">
-        <v>31767300</v>
+        <v>30192900</v>
       </c>
       <c r="H317" t="s">
         <v>9</v>
@@ -9556,16 +9556,16 @@
         <v>64614000</v>
       </c>
       <c r="D319">
-        <v>17929258</v>
+        <v>20700400</v>
       </c>
       <c r="E319">
-        <v>28937671</v>
+        <v>24737271</v>
       </c>
       <c r="F319">
-        <v>46866929</v>
+        <v>45437671</v>
       </c>
       <c r="G319">
-        <v>17747071</v>
+        <v>19176329</v>
       </c>
       <c r="H319">
         <v>21538000</v>
@@ -9582,16 +9582,16 @@
         <v>82504500</v>
       </c>
       <c r="D320">
-        <v>15318500</v>
+        <v>14641500</v>
       </c>
       <c r="E320">
-        <v>58799000</v>
+        <v>52449000</v>
       </c>
       <c r="F320">
-        <v>74117500</v>
+        <v>67090500</v>
       </c>
       <c r="G320">
-        <v>8387000</v>
+        <v>15414000</v>
       </c>
       <c r="H320">
         <v>27501500</v>
@@ -9628,22 +9628,22 @@
         <v>30</v>
       </c>
       <c r="B322">
-        <v>474400000</v>
+        <v>514400000</v>
       </c>
       <c r="C322">
-        <v>345800000</v>
+        <v>385800000</v>
       </c>
       <c r="D322">
-        <v>146146460</v>
+        <v>133230640</v>
       </c>
       <c r="E322">
-        <v>89089635</v>
+        <v>87546635</v>
       </c>
       <c r="F322">
-        <v>235236095</v>
+        <v>220777275</v>
       </c>
       <c r="G322">
-        <v>110563905</v>
+        <v>165022725</v>
       </c>
       <c r="H322">
         <v>128600000</v>
@@ -9663,13 +9663,13 @@
         <v>0</v>
       </c>
       <c r="E323">
-        <v>139796500</v>
+        <v>126133000</v>
       </c>
       <c r="F323">
-        <v>139796500</v>
+        <v>126133000</v>
       </c>
       <c r="G323">
-        <v>32703500</v>
+        <v>46367000</v>
       </c>
       <c r="H323">
         <v>57500000</v>
@@ -9715,13 +9715,13 @@
         <v>0</v>
       </c>
       <c r="E325">
-        <v>4998418396</v>
+        <v>4997577496</v>
       </c>
       <c r="F325">
-        <v>4998418396</v>
+        <v>4997577496</v>
       </c>
       <c r="G325">
-        <v>2055373869</v>
+        <v>2056214769</v>
       </c>
       <c r="H325" t="s">
         <v>9</v>
@@ -9767,13 +9767,13 @@
         <v>0</v>
       </c>
       <c r="E327">
-        <v>5995210864</v>
+        <v>5976157047</v>
       </c>
       <c r="F327">
-        <v>5995210864</v>
+        <v>5976157047</v>
       </c>
       <c r="G327">
-        <v>1019831557</v>
+        <v>1038885374</v>
       </c>
       <c r="H327" t="s">
         <v>9</v>
@@ -9871,13 +9871,13 @@
         <v>0</v>
       </c>
       <c r="E331">
-        <v>1144803958</v>
+        <v>1144195047</v>
       </c>
       <c r="F331">
-        <v>1144803958</v>
+        <v>1144195047</v>
       </c>
       <c r="G331">
-        <v>304908421</v>
+        <v>305517332</v>
       </c>
       <c r="H331" t="s">
         <v>9</v>
@@ -9914,22 +9914,22 @@
         <v>88</v>
       </c>
       <c r="B333">
-        <v>30674576460</v>
+        <v>30714576460</v>
       </c>
       <c r="C333">
-        <v>30414436960</v>
+        <v>30454436960</v>
       </c>
       <c r="D333">
-        <v>2133450541</v>
+        <v>3290499030</v>
       </c>
       <c r="E333">
-        <v>22725109402</v>
+        <v>21470930115</v>
       </c>
       <c r="F333">
-        <v>24858559943</v>
+        <v>24761429145</v>
       </c>
       <c r="G333">
-        <v>5555877017</v>
+        <v>5693007815</v>
       </c>
       <c r="H333">
         <v>260139500</v>
@@ -9946,10 +9946,10 @@
         <v>13755471000</v>
       </c>
       <c r="D334">
-        <v>1137360000</v>
+        <v>2663944960</v>
       </c>
       <c r="E334">
-        <v>12569972015</v>
+        <v>11043387055</v>
       </c>
       <c r="F334">
         <v>13707332015</v>
@@ -9972,10 +9972,10 @@
         <v>2948978291</v>
       </c>
       <c r="D335">
-        <v>1200345631</v>
+        <v>2688818731</v>
       </c>
       <c r="E335">
-        <v>1696560040</v>
+        <v>208086940</v>
       </c>
       <c r="F335">
         <v>2896905671</v>
@@ -9998,10 +9998,10 @@
         <v>447807006</v>
       </c>
       <c r="D336">
-        <v>0</v>
+        <v>439914019</v>
       </c>
       <c r="E336">
-        <v>439914019</v>
+        <v>0</v>
       </c>
       <c r="F336">
         <v>439914019</v>
@@ -10024,16 +10024,16 @@
         <v>2593734264</v>
       </c>
       <c r="D337">
-        <v>720248400</v>
+        <v>1120961396</v>
       </c>
       <c r="E337">
-        <v>1870716210</v>
+        <v>1472772814</v>
       </c>
       <c r="F337">
-        <v>2590964610</v>
+        <v>2593734210</v>
       </c>
       <c r="G337">
-        <v>2769654</v>
+        <v>54</v>
       </c>
       <c r="H337" t="s">
         <v>9</v>
@@ -10050,16 +10050,16 @@
         <v>213056448</v>
       </c>
       <c r="D338">
-        <v>175409320</v>
+        <v>177539800</v>
       </c>
       <c r="E338">
         <v>33060600</v>
       </c>
       <c r="F338">
-        <v>208469920</v>
+        <v>210600400</v>
       </c>
       <c r="G338">
-        <v>4586528</v>
+        <v>2456048</v>
       </c>
       <c r="H338" t="s">
         <v>9</v>
@@ -10076,10 +10076,10 @@
         <v>512000000</v>
       </c>
       <c r="D339">
-        <v>0</v>
+        <v>32075000</v>
       </c>
       <c r="E339">
-        <v>508277100</v>
+        <v>476202100</v>
       </c>
       <c r="F339">
         <v>508277100</v>
@@ -10128,16 +10128,16 @@
         <v>1748195004</v>
       </c>
       <c r="D341">
-        <v>201602154</v>
+        <v>460240553</v>
       </c>
       <c r="E341">
-        <v>1421235386</v>
+        <v>1152600785</v>
       </c>
       <c r="F341">
-        <v>1622837540</v>
+        <v>1612841338</v>
       </c>
       <c r="G341">
-        <v>125357464</v>
+        <v>135353666</v>
       </c>
       <c r="H341" t="s">
         <v>9</v>
@@ -10154,10 +10154,10 @@
         <v>327155000</v>
       </c>
       <c r="D342">
-        <v>0</v>
+        <v>40400000</v>
       </c>
       <c r="E342">
-        <v>300406680</v>
+        <v>260006680</v>
       </c>
       <c r="F342">
         <v>300406680</v>
@@ -10206,16 +10206,16 @@
         <v>1515585000</v>
       </c>
       <c r="D344">
-        <v>491190000</v>
+        <v>469000000</v>
       </c>
       <c r="E344">
         <v>1022239000</v>
       </c>
       <c r="F344">
-        <v>1513429000</v>
+        <v>1491239000</v>
       </c>
       <c r="G344">
-        <v>2156000</v>
+        <v>24346000</v>
       </c>
       <c r="H344" t="s">
         <v>9</v>
@@ -10232,16 +10232,16 @@
         <v>600000000</v>
       </c>
       <c r="D345">
-        <v>471000000</v>
+        <v>478435648</v>
       </c>
       <c r="E345">
         <v>0</v>
       </c>
       <c r="F345">
-        <v>471000000</v>
+        <v>478435648</v>
       </c>
       <c r="G345">
-        <v>129000000</v>
+        <v>121564352</v>
       </c>
       <c r="H345" t="s">
         <v>9</v>
@@ -10258,16 +10258,16 @@
         <v>1000000000</v>
       </c>
       <c r="D346">
-        <v>258700000</v>
+        <v>464560500</v>
       </c>
       <c r="E346">
-        <v>737260500</v>
+        <v>532700000</v>
       </c>
       <c r="F346">
-        <v>995960500</v>
+        <v>997260500</v>
       </c>
       <c r="G346">
-        <v>4039500</v>
+        <v>2739500</v>
       </c>
       <c r="H346" t="s">
         <v>9</v>
@@ -10284,16 +10284,16 @@
         <v>150000000</v>
       </c>
       <c r="D347">
-        <v>100602000</v>
+        <v>101481590</v>
       </c>
       <c r="E347">
-        <v>42679590</v>
+        <v>0</v>
       </c>
       <c r="F347">
-        <v>143281590</v>
+        <v>101481590</v>
       </c>
       <c r="G347">
-        <v>6718410</v>
+        <v>48518410</v>
       </c>
       <c r="H347">
         <v>50000000</v>
@@ -10310,16 +10310,16 @@
         <v>141550000</v>
       </c>
       <c r="D348">
-        <v>37331800</v>
+        <v>0</v>
       </c>
       <c r="E348">
         <v>80399800</v>
       </c>
       <c r="F348">
-        <v>117731600</v>
+        <v>80399800</v>
       </c>
       <c r="G348">
-        <v>23818400</v>
+        <v>61150200</v>
       </c>
       <c r="H348" t="s">
         <v>9</v>
@@ -10336,16 +10336,16 @@
         <v>2911760000</v>
       </c>
       <c r="D349">
-        <v>901040</v>
+        <v>292257770</v>
       </c>
       <c r="E349">
         <v>1650655501</v>
       </c>
       <c r="F349">
-        <v>1651556541</v>
+        <v>1942913271</v>
       </c>
       <c r="G349">
-        <v>1260203459</v>
+        <v>968846729</v>
       </c>
       <c r="H349" t="s">
         <v>9</v>
@@ -10365,13 +10365,13 @@
         <v>6000000</v>
       </c>
       <c r="E350">
+        <v>79286598</v>
+      </c>
+      <c r="F350">
         <v>85286598</v>
       </c>
-      <c r="F350">
-        <v>91286598</v>
-      </c>
       <c r="G350">
-        <v>43713402</v>
+        <v>49713402</v>
       </c>
       <c r="H350">
         <v>45000000</v>
@@ -10388,16 +10388,16 @@
         <v>571079775</v>
       </c>
       <c r="D351">
-        <v>262833670</v>
+        <v>233791670</v>
       </c>
       <c r="E351">
         <v>274818994</v>
       </c>
       <c r="F351">
-        <v>537652664</v>
+        <v>508610664</v>
       </c>
       <c r="G351">
-        <v>33427111</v>
+        <v>62469111</v>
       </c>
       <c r="H351">
         <v>190359925</v>
@@ -10440,16 +10440,16 @@
         <v>462375000</v>
       </c>
       <c r="D353">
-        <v>21419612</v>
+        <v>238973912</v>
       </c>
       <c r="E353">
-        <v>331134371</v>
+        <v>99414371</v>
       </c>
       <c r="F353">
-        <v>352553983</v>
+        <v>338388283</v>
       </c>
       <c r="G353">
-        <v>109821017</v>
+        <v>123986717</v>
       </c>
       <c r="H353">
         <v>154125000</v>
@@ -10469,13 +10469,13 @@
         <v>0</v>
       </c>
       <c r="E354">
-        <v>189093250</v>
+        <v>167211500</v>
       </c>
       <c r="F354">
-        <v>189093250</v>
+        <v>167211500</v>
       </c>
       <c r="G354">
-        <v>71456750</v>
+        <v>93338500</v>
       </c>
       <c r="H354">
         <v>86850000</v>
@@ -10492,16 +10492,16 @@
         <v>6000000</v>
       </c>
       <c r="D355">
-        <v>838020</v>
+        <v>467190</v>
       </c>
       <c r="E355">
         <v>1500170</v>
       </c>
       <c r="F355">
-        <v>2338190</v>
+        <v>1967360</v>
       </c>
       <c r="G355">
-        <v>3661810</v>
+        <v>4032640</v>
       </c>
       <c r="H355" t="s">
         <v>9</v>
@@ -10547,13 +10547,13 @@
         <v>0</v>
       </c>
       <c r="E357">
-        <v>7462468931</v>
+        <v>7461283668</v>
       </c>
       <c r="F357">
-        <v>7462468931</v>
+        <v>7461283668</v>
       </c>
       <c r="G357">
-        <v>3252447082</v>
+        <v>3253632345</v>
       </c>
       <c r="H357" t="s">
         <v>9</v>
@@ -10599,13 +10599,13 @@
         <v>0</v>
       </c>
       <c r="E359">
-        <v>8866885197</v>
+        <v>8834277017</v>
       </c>
       <c r="F359">
-        <v>8866885197</v>
+        <v>8834277017</v>
       </c>
       <c r="G359">
-        <v>1665279005</v>
+        <v>1697887185</v>
       </c>
       <c r="H359" t="s">
         <v>9</v>
@@ -10703,13 +10703,13 @@
         <v>0</v>
       </c>
       <c r="E363">
-        <v>1236988293</v>
+        <v>1236176601</v>
       </c>
       <c r="F363">
-        <v>1236988293</v>
+        <v>1236176601</v>
       </c>
       <c r="G363">
-        <v>286029811</v>
+        <v>286841503</v>
       </c>
       <c r="H363" t="s">
         <v>9</v>
@@ -10752,16 +10752,16 @@
         <v>57427089299</v>
       </c>
       <c r="D365">
-        <v>5969555647</v>
+        <v>10792636739</v>
       </c>
       <c r="E365">
-        <v>43637146332</v>
+        <v>38901674281</v>
       </c>
       <c r="F365">
-        <v>49606701979</v>
+        <v>49694311020</v>
       </c>
       <c r="G365">
-        <v>7820387320</v>
+        <v>7732778279</v>
       </c>
       <c r="H365">
         <v>526334925</v>
@@ -10856,16 +10856,16 @@
         <v>2467762918</v>
       </c>
       <c r="D369">
-        <v>1757395220</v>
+        <v>1121519360</v>
       </c>
       <c r="E369">
-        <v>578157216</v>
+        <v>558800786</v>
       </c>
       <c r="F369">
-        <v>2335552436</v>
+        <v>1680320146</v>
       </c>
       <c r="G369">
-        <v>132210482</v>
+        <v>787442772</v>
       </c>
       <c r="H369" t="s">
         <v>9</v>
@@ -10934,16 +10934,16 @@
         <v>1714789867</v>
       </c>
       <c r="D372">
-        <v>981827471</v>
+        <v>920522269</v>
       </c>
       <c r="E372">
         <v>732962308</v>
       </c>
       <c r="F372">
-        <v>1714789779</v>
+        <v>1653484577</v>
       </c>
       <c r="G372">
-        <v>88</v>
+        <v>61305290</v>
       </c>
       <c r="H372" t="s">
         <v>9</v>
@@ -10960,10 +10960,10 @@
         <v>1400000000</v>
       </c>
       <c r="D373">
-        <v>182392970</v>
+        <v>227292970</v>
       </c>
       <c r="E373">
-        <v>630681594</v>
+        <v>585781594</v>
       </c>
       <c r="F373">
         <v>813074564</v>
@@ -10986,16 +10986,16 @@
         <v>290550000</v>
       </c>
       <c r="D374">
-        <v>290264873</v>
+        <v>290377764</v>
       </c>
       <c r="E374">
         <v>0</v>
       </c>
       <c r="F374">
-        <v>290264873</v>
+        <v>290377764</v>
       </c>
       <c r="G374">
-        <v>285127</v>
+        <v>172236</v>
       </c>
       <c r="H374" t="s">
         <v>9</v>
@@ -11038,16 +11038,16 @@
         <v>470200000</v>
       </c>
       <c r="D376">
-        <v>0</v>
+        <v>45290400</v>
       </c>
       <c r="E376">
         <v>424909600</v>
       </c>
       <c r="F376">
-        <v>424909600</v>
-      </c>
-      <c r="G376">
-        <v>45290400</v>
+        <v>470200000</v>
+      </c>
+      <c r="G376" t="s">
+        <v>9</v>
       </c>
       <c r="H376" t="s">
         <v>9</v>
@@ -11064,16 +11064,16 @@
         <v>200000000</v>
       </c>
       <c r="D377">
-        <v>147528500</v>
+        <v>150079500</v>
       </c>
       <c r="E377">
         <v>49920000</v>
       </c>
       <c r="F377">
-        <v>197448500</v>
+        <v>199999500</v>
       </c>
       <c r="G377">
-        <v>2551500</v>
+        <v>500</v>
       </c>
       <c r="H377" t="s">
         <v>9</v>
@@ -11090,16 +11090,16 @@
         <v>82500000</v>
       </c>
       <c r="D378">
-        <v>0</v>
+        <v>77719680</v>
       </c>
       <c r="E378">
-        <v>76086680</v>
+        <v>0</v>
       </c>
       <c r="F378">
-        <v>76086680</v>
+        <v>77719680</v>
       </c>
       <c r="G378">
-        <v>6413320</v>
+        <v>4780320</v>
       </c>
       <c r="H378">
         <v>27500000</v>
@@ -11142,16 +11142,16 @@
         <v>411080000</v>
       </c>
       <c r="D380">
-        <v>1827440</v>
+        <v>1337650</v>
       </c>
       <c r="E380">
+        <v>279958254</v>
+      </c>
+      <c r="F380">
         <v>281295904</v>
       </c>
-      <c r="F380">
-        <v>283123344</v>
-      </c>
       <c r="G380">
-        <v>127956656</v>
+        <v>129784096</v>
       </c>
       <c r="H380" t="s">
         <v>9</v>
@@ -11168,10 +11168,10 @@
         <v>120000000</v>
       </c>
       <c r="D381">
-        <v>27345375</v>
+        <v>29057875</v>
       </c>
       <c r="E381">
-        <v>37972605</v>
+        <v>36260105</v>
       </c>
       <c r="F381">
         <v>65317980</v>
@@ -11194,10 +11194,10 @@
         <v>300000000</v>
       </c>
       <c r="D382">
-        <v>57624250</v>
+        <v>79412000</v>
       </c>
       <c r="E382">
-        <v>205102462</v>
+        <v>183314712</v>
       </c>
       <c r="F382">
         <v>262726712</v>
@@ -11275,13 +11275,13 @@
         <v>0</v>
       </c>
       <c r="E385">
-        <v>124406000</v>
+        <v>110610500</v>
       </c>
       <c r="F385">
-        <v>124406000</v>
+        <v>110610500</v>
       </c>
       <c r="G385">
-        <v>3619000</v>
+        <v>17414500</v>
       </c>
       <c r="H385">
         <v>42675000</v>
@@ -11327,13 +11327,13 @@
         <v>0</v>
       </c>
       <c r="E387">
-        <v>93657349</v>
+        <v>81950180</v>
       </c>
       <c r="F387">
-        <v>93657349</v>
+        <v>81950180</v>
       </c>
       <c r="G387">
-        <v>-93657349</v>
+        <v>-81950180</v>
       </c>
       <c r="H387" t="s">
         <v>9</v>
@@ -11379,13 +11379,13 @@
         <v>0</v>
       </c>
       <c r="E389">
-        <v>3205993500</v>
+        <v>3205079550</v>
       </c>
       <c r="F389">
-        <v>3205993500</v>
+        <v>3205079550</v>
       </c>
       <c r="G389">
-        <v>1333813418</v>
+        <v>1334727368</v>
       </c>
       <c r="H389" t="s">
         <v>9</v>
@@ -11584,16 +11584,16 @@
         <v>24628424376</v>
       </c>
       <c r="D397">
-        <v>4981754292</v>
+        <v>4478157661</v>
       </c>
       <c r="E397">
-        <v>15584960670</v>
+        <v>15393363041</v>
       </c>
       <c r="F397">
-        <v>20566714962</v>
+        <v>19871520702</v>
       </c>
       <c r="G397">
-        <v>4061709414</v>
+        <v>4756903674</v>
       </c>
       <c r="H397">
         <v>232675000</v>
@@ -11870,10 +11870,10 @@
         <v>50000000</v>
       </c>
       <c r="D408">
-        <v>0</v>
+        <v>11200000</v>
       </c>
       <c r="E408">
-        <v>16100000</v>
+        <v>4900000</v>
       </c>
       <c r="F408">
         <v>16100000</v>
@@ -12000,16 +12000,16 @@
         <v>316800000</v>
       </c>
       <c r="D413">
-        <v>62315000</v>
+        <v>0</v>
       </c>
       <c r="E413">
         <v>179720150</v>
       </c>
       <c r="F413">
-        <v>242035150</v>
+        <v>179720150</v>
       </c>
       <c r="G413">
-        <v>74764850</v>
+        <v>137079850</v>
       </c>
       <c r="H413" t="s">
         <v>9</v>
@@ -12026,16 +12026,16 @@
         <v>2230000000</v>
       </c>
       <c r="D414">
-        <v>19315000</v>
+        <v>19000000</v>
       </c>
       <c r="E414">
-        <v>1025934097</v>
+        <v>1017375537</v>
       </c>
       <c r="F414">
-        <v>1045249097</v>
+        <v>1036375537</v>
       </c>
       <c r="G414">
-        <v>1184750903</v>
+        <v>1193624463</v>
       </c>
       <c r="H414" t="s">
         <v>9</v>
@@ -12052,16 +12052,16 @@
         <v>145200000</v>
       </c>
       <c r="D415">
-        <v>37536807</v>
+        <v>21012000</v>
       </c>
       <c r="E415">
-        <v>75745500</v>
+        <v>67309500</v>
       </c>
       <c r="F415">
-        <v>113282307</v>
+        <v>88321500</v>
       </c>
       <c r="G415">
-        <v>31917693</v>
+        <v>56878500</v>
       </c>
       <c r="H415">
         <v>48400000</v>
@@ -12078,10 +12078,10 @@
         <v>445223250</v>
       </c>
       <c r="D416">
-        <v>17923100</v>
+        <v>57149700</v>
       </c>
       <c r="E416">
-        <v>421061816</v>
+        <v>381835216</v>
       </c>
       <c r="F416">
         <v>438984916</v>
@@ -12156,16 +12156,16 @@
         <v>370995500</v>
       </c>
       <c r="D419">
-        <v>13455452</v>
+        <v>43405272</v>
       </c>
       <c r="E419">
+        <v>305274316</v>
+      </c>
+      <c r="F419">
         <v>348679588</v>
       </c>
-      <c r="F419">
-        <v>362135040</v>
-      </c>
       <c r="G419">
-        <v>8860460</v>
+        <v>22315912</v>
       </c>
       <c r="H419">
         <v>117000000</v>
@@ -12208,10 +12208,10 @@
         <v>20004500</v>
       </c>
       <c r="D421">
-        <v>0</v>
+        <v>20000000</v>
       </c>
       <c r="E421">
-        <v>20000000</v>
+        <v>0</v>
       </c>
       <c r="F421">
         <v>20000000</v>
@@ -12237,13 +12237,13 @@
         <v>0</v>
       </c>
       <c r="E422">
-        <v>400564719</v>
+        <v>350494131</v>
       </c>
       <c r="F422">
-        <v>400564719</v>
+        <v>350494131</v>
       </c>
       <c r="G422">
-        <v>-400564719</v>
+        <v>-350494131</v>
       </c>
       <c r="H422" t="s">
         <v>9</v>
@@ -12315,13 +12315,13 @@
         <v>0</v>
       </c>
       <c r="E425">
-        <v>7321633652</v>
+        <v>7295042089</v>
       </c>
       <c r="F425">
-        <v>7321633652</v>
+        <v>7295042089</v>
       </c>
       <c r="G425">
-        <v>2057934840</v>
+        <v>2084526403</v>
       </c>
       <c r="H425" t="s">
         <v>9</v>
@@ -12468,16 +12468,16 @@
         <v>35458361640</v>
       </c>
       <c r="D431">
-        <v>5491007652</v>
+        <v>5512229265</v>
       </c>
       <c r="E431">
-        <v>21459183697</v>
+        <v>21251695114</v>
       </c>
       <c r="F431">
-        <v>26950191349</v>
+        <v>26763924379</v>
       </c>
       <c r="G431">
-        <v>8508170291</v>
+        <v>8694437261</v>
       </c>
       <c r="H431">
         <v>472807750</v>
@@ -13362,10 +13362,10 @@
         <v>10505111000</v>
       </c>
       <c r="D488">
-        <v>1603170600</v>
+        <v>2311037927</v>
       </c>
       <c r="E488">
-        <v>8876816374</v>
+        <v>8168949047</v>
       </c>
       <c r="F488">
         <v>10479986974</v>
@@ -13544,16 +13544,16 @@
         <v>2312795000</v>
       </c>
       <c r="D495">
-        <v>1462735010</v>
+        <v>1294531850</v>
       </c>
       <c r="E495">
-        <v>654993954</v>
+        <v>605293954</v>
       </c>
       <c r="F495">
-        <v>2117728964</v>
+        <v>1899825804</v>
       </c>
       <c r="G495">
-        <v>195066036</v>
+        <v>412969196</v>
       </c>
       <c r="H495" t="s">
         <v>9</v>
@@ -13570,16 +13570,16 @@
         <v>6189486656</v>
       </c>
       <c r="D496">
-        <v>4346193186</v>
+        <v>3039997152</v>
       </c>
       <c r="E496">
-        <v>1385897604</v>
+        <v>1331606604</v>
       </c>
       <c r="F496">
-        <v>5732090790</v>
+        <v>4371603756</v>
       </c>
       <c r="G496">
-        <v>457395866</v>
+        <v>1817882900</v>
       </c>
       <c r="H496" t="s">
         <v>9</v>
@@ -13752,10 +13752,10 @@
         <v>745000000</v>
       </c>
       <c r="D503">
-        <v>668065563</v>
+        <v>673853563</v>
       </c>
       <c r="E503">
-        <v>57669480</v>
+        <v>51881480</v>
       </c>
       <c r="F503">
         <v>725735043</v>
@@ -13778,16 +13778,16 @@
         <v>7401091133</v>
       </c>
       <c r="D504">
-        <v>4042531251</v>
+        <v>4673665116</v>
       </c>
       <c r="E504">
-        <v>3138178801</v>
+        <v>2607739789</v>
       </c>
       <c r="F504">
-        <v>7180710052</v>
+        <v>7281404905</v>
       </c>
       <c r="G504">
-        <v>220381081</v>
+        <v>119686228</v>
       </c>
       <c r="H504" t="s">
         <v>9</v>
@@ -13804,16 +13804,16 @@
         <v>297500000</v>
       </c>
       <c r="D505">
-        <v>195485808</v>
+        <v>0</v>
       </c>
       <c r="E505">
         <v>100610066</v>
       </c>
       <c r="F505">
-        <v>296095874</v>
+        <v>100610066</v>
       </c>
       <c r="G505">
-        <v>1404126</v>
+        <v>196889934</v>
       </c>
       <c r="H505" t="s">
         <v>9</v>
@@ -13830,16 +13830,16 @@
         <v>266250000</v>
       </c>
       <c r="D506">
-        <v>47324000</v>
+        <v>6838800</v>
       </c>
       <c r="E506">
+        <v>190238200</v>
+      </c>
+      <c r="F506">
         <v>197077000</v>
       </c>
-      <c r="F506">
-        <v>244401000</v>
-      </c>
       <c r="G506">
-        <v>21849000</v>
+        <v>69173000</v>
       </c>
       <c r="H506" t="s">
         <v>9</v>
@@ -13882,10 +13882,10 @@
         <v>75000000</v>
       </c>
       <c r="D508">
-        <v>0</v>
+        <v>29699686</v>
       </c>
       <c r="E508">
-        <v>42419686</v>
+        <v>12720000</v>
       </c>
       <c r="F508">
         <v>42419686</v>
@@ -13934,10 +13934,10 @@
         <v>2560000000</v>
       </c>
       <c r="D510">
-        <v>8404406</v>
+        <v>23732367</v>
       </c>
       <c r="E510">
-        <v>1702468675</v>
+        <v>1687140714</v>
       </c>
       <c r="F510">
         <v>1710873081</v>
@@ -13960,16 +13960,16 @@
         <v>668379750</v>
       </c>
       <c r="D511">
-        <v>22370000</v>
+        <v>11185000</v>
       </c>
       <c r="E511">
         <v>168235828</v>
       </c>
       <c r="F511">
-        <v>190605828</v>
+        <v>179420828</v>
       </c>
       <c r="G511">
-        <v>477773922</v>
+        <v>488958922</v>
       </c>
       <c r="H511">
         <v>222793250</v>
@@ -13986,16 +13986,16 @@
         <v>870341250</v>
       </c>
       <c r="D512">
-        <v>192603060</v>
+        <v>96717780</v>
       </c>
       <c r="E512">
         <v>654475790</v>
       </c>
       <c r="F512">
-        <v>847078850</v>
+        <v>751193570</v>
       </c>
       <c r="G512">
-        <v>23262400</v>
+        <v>119147680</v>
       </c>
       <c r="H512">
         <v>290113750</v>
@@ -14038,16 +14038,16 @@
         <v>422192250</v>
       </c>
       <c r="D514">
-        <v>293939800</v>
+        <v>57403000</v>
       </c>
       <c r="E514">
         <v>60100427</v>
       </c>
       <c r="F514">
-        <v>354040227</v>
+        <v>117503427</v>
       </c>
       <c r="G514">
-        <v>68152023</v>
+        <v>304688823</v>
       </c>
       <c r="H514">
         <v>140730750</v>
@@ -14064,16 +14064,16 @@
         <v>516433500</v>
       </c>
       <c r="D515">
-        <v>7568076</v>
+        <v>21491715</v>
       </c>
       <c r="E515">
-        <v>377370219</v>
+        <v>342954080</v>
       </c>
       <c r="F515">
-        <v>384938295</v>
+        <v>364445795</v>
       </c>
       <c r="G515">
-        <v>131495205</v>
+        <v>151987705</v>
       </c>
       <c r="H515">
         <v>172144500</v>
@@ -14090,16 +14090,16 @@
         <v>36180000</v>
       </c>
       <c r="D516">
-        <v>3015406</v>
+        <v>2747000</v>
       </c>
       <c r="E516">
         <v>10574568</v>
       </c>
       <c r="F516">
-        <v>13589974</v>
+        <v>13321568</v>
       </c>
       <c r="G516">
-        <v>22590026</v>
+        <v>22858432</v>
       </c>
       <c r="H516" t="s">
         <v>9</v>
@@ -14116,16 +14116,16 @@
         <v>61741000</v>
       </c>
       <c r="D517">
-        <v>20788000</v>
+        <v>0</v>
       </c>
       <c r="E517">
         <v>40855444</v>
       </c>
       <c r="F517">
-        <v>61643444</v>
+        <v>40855444</v>
       </c>
       <c r="G517">
-        <v>97556</v>
+        <v>20885556</v>
       </c>
       <c r="H517" t="s">
         <v>9</v>
@@ -14145,13 +14145,13 @@
         <v>0</v>
       </c>
       <c r="E518">
-        <v>339277236</v>
+        <v>296867581</v>
       </c>
       <c r="F518">
-        <v>339277236</v>
+        <v>296867581</v>
       </c>
       <c r="G518">
-        <v>-339277236</v>
+        <v>-296867581</v>
       </c>
       <c r="H518" t="s">
         <v>9</v>
@@ -14171,13 +14171,13 @@
         <v>0</v>
       </c>
       <c r="E519">
-        <v>243559448</v>
+        <v>213114517</v>
       </c>
       <c r="F519">
-        <v>243559448</v>
+        <v>213114517</v>
       </c>
       <c r="G519">
-        <v>-243559448</v>
+        <v>-213114517</v>
       </c>
       <c r="H519" t="s">
         <v>9</v>
@@ -14194,16 +14194,16 @@
         <v>0</v>
       </c>
       <c r="D520">
-        <v>25388</v>
+        <v>0</v>
       </c>
       <c r="E520">
         <v>748141</v>
       </c>
       <c r="F520">
-        <v>773529</v>
+        <v>748141</v>
       </c>
       <c r="G520">
-        <v>-773529</v>
+        <v>-748141</v>
       </c>
       <c r="H520" t="s">
         <v>9</v>
@@ -14220,16 +14220,16 @@
         <v>0</v>
       </c>
       <c r="D521">
-        <v>1800000</v>
+        <v>0</v>
       </c>
       <c r="E521">
         <v>115182625</v>
       </c>
       <c r="F521">
-        <v>116982625</v>
+        <v>115182625</v>
       </c>
       <c r="G521">
-        <v>-116982625</v>
+        <v>-115182625</v>
       </c>
       <c r="H521" t="s">
         <v>9</v>
@@ -14246,16 +14246,16 @@
         <v>12164281897</v>
       </c>
       <c r="D522">
-        <v>1068968</v>
+        <v>0</v>
       </c>
       <c r="E522">
-        <v>8957051165</v>
+        <v>8955872915</v>
       </c>
       <c r="F522">
-        <v>8958120133</v>
+        <v>8955872915</v>
       </c>
       <c r="G522">
-        <v>3206161764</v>
+        <v>3208408982</v>
       </c>
       <c r="H522" t="s">
         <v>9</v>
@@ -14298,16 +14298,16 @@
         <v>10801404197</v>
       </c>
       <c r="D524">
-        <v>79545016</v>
+        <v>0</v>
       </c>
       <c r="E524">
         <v>9796841081</v>
       </c>
       <c r="F524">
-        <v>9876386097</v>
+        <v>9796841081</v>
       </c>
       <c r="G524">
-        <v>925018100</v>
+        <v>1004563116</v>
       </c>
       <c r="H524" t="s">
         <v>9</v>
@@ -14457,13 +14457,13 @@
         <v>0</v>
       </c>
       <c r="E530">
-        <v>551908302</v>
+        <v>482919765</v>
       </c>
       <c r="F530">
-        <v>551908302</v>
+        <v>482919765</v>
       </c>
       <c r="G530">
-        <v>-551908302</v>
+        <v>-482919765</v>
       </c>
       <c r="H530" t="s">
         <v>9</v>
@@ -14480,16 +14480,16 @@
         <v>64019485320</v>
       </c>
       <c r="D531">
-        <v>14855810981</v>
+        <v>14102078399</v>
       </c>
       <c r="E531">
-        <v>42033379289</v>
+        <v>40455989991</v>
       </c>
       <c r="F531">
-        <v>56889190270</v>
+        <v>54558068390</v>
       </c>
       <c r="G531">
-        <v>7130295050</v>
+        <v>9461416930</v>
       </c>
       <c r="H531">
         <v>850782250</v>
@@ -14506,10 +14506,10 @@
         <v>5572131338</v>
       </c>
       <c r="D532">
-        <v>1641723068</v>
+        <v>1782973068</v>
       </c>
       <c r="E532">
-        <v>3922283270</v>
+        <v>3781033270</v>
       </c>
       <c r="F532">
         <v>5564006338</v>
@@ -14584,10 +14584,10 @@
         <v>2166235262</v>
       </c>
       <c r="D535">
-        <v>1284417699</v>
+        <v>1729853601</v>
       </c>
       <c r="E535">
-        <v>881817563</v>
+        <v>436381661</v>
       </c>
       <c r="F535">
         <v>2166235262</v>
@@ -14662,16 +14662,16 @@
         <v>11576266001</v>
       </c>
       <c r="D538">
-        <v>10041225391</v>
+        <v>11196770846</v>
       </c>
       <c r="E538">
-        <v>1465423268</v>
+        <v>259825808</v>
       </c>
       <c r="F538">
-        <v>11506648659</v>
+        <v>11456596654</v>
       </c>
       <c r="G538">
-        <v>69617342</v>
+        <v>119669347</v>
       </c>
       <c r="H538" t="s">
         <v>9</v>
@@ -14688,16 +14688,16 @@
         <v>2103744312</v>
       </c>
       <c r="D539">
-        <v>1129375087</v>
+        <v>1288384905</v>
       </c>
       <c r="E539">
-        <v>727358736</v>
+        <v>330635136</v>
       </c>
       <c r="F539">
-        <v>1856733823</v>
+        <v>1619020041</v>
       </c>
       <c r="G539">
-        <v>247010489</v>
+        <v>484724271</v>
       </c>
       <c r="H539" t="s">
         <v>9</v>
@@ -14792,10 +14792,10 @@
         <v>1710735389</v>
       </c>
       <c r="D543">
-        <v>0</v>
+        <v>384000000</v>
       </c>
       <c r="E543">
-        <v>1710735389</v>
+        <v>1326735389</v>
       </c>
       <c r="F543">
         <v>1710735389</v>
@@ -14870,16 +14870,16 @@
         <v>579713600</v>
       </c>
       <c r="D546">
-        <v>79128950</v>
+        <v>62278650</v>
       </c>
       <c r="E546">
-        <v>203060350</v>
+        <v>199030350</v>
       </c>
       <c r="F546">
-        <v>282189300</v>
+        <v>261309000</v>
       </c>
       <c r="G546">
-        <v>297524300</v>
+        <v>318404600</v>
       </c>
       <c r="H546" t="s">
         <v>9</v>
@@ -14896,16 +14896,16 @@
         <v>1539315000</v>
       </c>
       <c r="D547">
-        <v>6368850</v>
+        <v>6343694</v>
       </c>
       <c r="E547">
-        <v>933415593</v>
+        <v>930071899</v>
       </c>
       <c r="F547">
-        <v>939784443</v>
+        <v>936415593</v>
       </c>
       <c r="G547">
-        <v>599530557</v>
+        <v>602899407</v>
       </c>
       <c r="H547" t="s">
         <v>9</v>
@@ -14922,16 +14922,16 @@
         <v>412500000</v>
       </c>
       <c r="D548">
-        <v>76012800</v>
+        <v>69956400</v>
       </c>
       <c r="E548">
         <v>74129175</v>
       </c>
       <c r="F548">
-        <v>150141975</v>
+        <v>144085575</v>
       </c>
       <c r="G548">
-        <v>262358025</v>
+        <v>268414425</v>
       </c>
       <c r="H548">
         <v>137500000</v>
@@ -14948,16 +14948,16 @@
         <v>532875000</v>
       </c>
       <c r="D549">
-        <v>51322721</v>
+        <v>33049570</v>
       </c>
       <c r="E549">
-        <v>168536270</v>
+        <v>167536270</v>
       </c>
       <c r="F549">
-        <v>219858991</v>
+        <v>200585840</v>
       </c>
       <c r="G549">
-        <v>313016009</v>
+        <v>332289160</v>
       </c>
       <c r="H549">
         <v>177625000</v>
@@ -15000,16 +15000,16 @@
         <v>395748750</v>
       </c>
       <c r="D551">
-        <v>12560735</v>
+        <v>2492800</v>
       </c>
       <c r="E551">
         <v>353426819</v>
       </c>
       <c r="F551">
-        <v>365987554</v>
+        <v>355919619</v>
       </c>
       <c r="G551">
-        <v>29761196</v>
+        <v>39829131</v>
       </c>
       <c r="H551">
         <v>131916250</v>
@@ -15026,16 +15026,16 @@
         <v>336802500</v>
       </c>
       <c r="D552">
-        <v>1951631</v>
+        <v>1037234</v>
       </c>
       <c r="E552">
-        <v>269856851</v>
+        <v>237070601</v>
       </c>
       <c r="F552">
-        <v>271808482</v>
+        <v>238107835</v>
       </c>
       <c r="G552">
-        <v>64994018</v>
+        <v>98694665</v>
       </c>
       <c r="H552">
         <v>112267500</v>
@@ -15081,13 +15081,13 @@
         <v>0</v>
       </c>
       <c r="E554">
-        <v>22371486</v>
+        <v>19575050</v>
       </c>
       <c r="F554">
-        <v>22371486</v>
+        <v>19575050</v>
       </c>
       <c r="G554">
-        <v>-22371486</v>
+        <v>-19575050</v>
       </c>
       <c r="H554" t="s">
         <v>9</v>
@@ -15107,13 +15107,13 @@
         <v>0</v>
       </c>
       <c r="E555">
-        <v>7784363518</v>
+        <v>7783248643</v>
       </c>
       <c r="F555">
-        <v>7784363518</v>
+        <v>7783248643</v>
       </c>
       <c r="G555">
-        <v>2904553348</v>
+        <v>2905668223</v>
       </c>
       <c r="H555" t="s">
         <v>9</v>
@@ -15312,16 +15312,16 @@
         <v>57848682223</v>
       </c>
       <c r="D563">
-        <v>16843148709</v>
+        <v>19076202545</v>
       </c>
       <c r="E563">
-        <v>34462141776</v>
+        <v>31844063559</v>
       </c>
       <c r="F563">
-        <v>51305290485</v>
+        <v>50920266104</v>
       </c>
       <c r="G563">
-        <v>6543391738</v>
+        <v>6928416119</v>
       </c>
       <c r="H563">
         <v>720558750</v>
@@ -15332,25 +15332,25 @@
         <v>130</v>
       </c>
       <c r="B564">
-        <v>1114880734005</v>
+        <v>1118540641744</v>
       </c>
       <c r="C564">
-        <v>1108384394181</v>
+        <v>1109231301920</v>
       </c>
       <c r="D564">
-        <v>358054677899</v>
+        <v>418022337705</v>
       </c>
       <c r="E564">
-        <v>619602592930</v>
+        <v>546756699571</v>
       </c>
       <c r="F564">
-        <v>977657270829</v>
+        <v>964779037276</v>
       </c>
       <c r="G564">
-        <v>130727123352</v>
+        <v>144452264644</v>
       </c>
       <c r="H564">
-        <v>6496339824</v>
+        <v>9309339824</v>
       </c>
     </row>
   </sheetData>

--- a/data/rka.xlsx
+++ b/data/rka.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x15 xr xr6 xr10">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
@@ -8,15 +8,24 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\76193\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:40009_{00183B8A-CE41-4C1C-8764-E43B408EA746}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{286AA0C3-8334-4BC1-94CB-9CCB22785514}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5760" yWindow="3060" windowWidth="17280" windowHeight="9180"/>
+    <workbookView xWindow="3180" yWindow="2292" windowWidth="17280" windowHeight="9180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="20261001 SAP ZFM01" sheetId="1" r:id="rId1"/>
+    <sheet name="20261001 AR12 SAP ZFM01" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
   <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="1"/>
     </ext>
@@ -420,7 +429,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -1261,7 +1270,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H564"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -1305,10 +1314,10 @@
         <v>8</v>
       </c>
       <c r="B2">
-        <v>108940456175</v>
+        <v>108372481167</v>
       </c>
       <c r="C2">
-        <v>108940456175</v>
+        <v>108372481167</v>
       </c>
       <c r="D2">
         <v>80755967435</v>
@@ -1320,7 +1329,7 @@
         <v>108372481167</v>
       </c>
       <c r="G2">
-        <v>567975008</v>
+        <v>0</v>
       </c>
       <c r="H2">
         <v>0</v>
@@ -1357,10 +1366,10 @@
         <v>10</v>
       </c>
       <c r="B4">
-        <v>36416664685</v>
+        <v>36000000000</v>
       </c>
       <c r="C4">
-        <v>36416664685</v>
+        <v>36000000000</v>
       </c>
       <c r="D4">
         <v>30600000000</v>
@@ -1372,7 +1381,7 @@
         <v>36000000000</v>
       </c>
       <c r="G4">
-        <v>416664685</v>
+        <v>0</v>
       </c>
       <c r="H4">
         <v>0</v>
@@ -1643,10 +1652,10 @@
         <v>21</v>
       </c>
       <c r="B15">
-        <v>10800965806</v>
+        <v>10398657485</v>
       </c>
       <c r="C15">
-        <v>10800965806</v>
+        <v>10398657485</v>
       </c>
       <c r="D15">
         <v>8162494976</v>
@@ -1658,7 +1667,7 @@
         <v>8162494976</v>
       </c>
       <c r="G15">
-        <v>2638470830</v>
+        <v>2236162509</v>
       </c>
       <c r="H15">
         <v>0</v>
@@ -2345,10 +2354,10 @@
         <v>48</v>
       </c>
       <c r="B42">
-        <v>346492886853</v>
+        <v>345105938839</v>
       </c>
       <c r="C42">
-        <v>346492886853</v>
+        <v>345105938839</v>
       </c>
       <c r="D42">
         <v>196055556745</v>
@@ -2360,7 +2369,7 @@
         <v>331986032545</v>
       </c>
       <c r="G42">
-        <v>14506854308</v>
+        <v>13119906294</v>
       </c>
       <c r="H42">
         <v>0</v>
@@ -6407,16 +6416,16 @@
         <v>469000000</v>
       </c>
       <c r="D198">
-        <v>53374985</v>
+        <v>63374985</v>
       </c>
       <c r="E198">
         <v>95104084</v>
       </c>
       <c r="F198">
-        <v>148479069</v>
+        <v>158479069</v>
       </c>
       <c r="G198">
-        <v>320520931</v>
+        <v>310520931</v>
       </c>
       <c r="H198">
         <v>0</v>
@@ -7187,16 +7196,16 @@
         <v>47690614295</v>
       </c>
       <c r="D228">
-        <v>8614285889</v>
+        <v>8624285889</v>
       </c>
       <c r="E228">
         <v>33943340518</v>
       </c>
       <c r="F228">
-        <v>42557626407</v>
+        <v>42567626407</v>
       </c>
       <c r="G228">
-        <v>5132987888</v>
+        <v>5122987888</v>
       </c>
       <c r="H228">
         <v>0</v>
@@ -12491,16 +12500,16 @@
         <v>873740000</v>
       </c>
       <c r="D432" s="1">
-        <v>255557500</v>
+        <v>85500000</v>
       </c>
       <c r="E432" s="1">
-        <v>589750552</v>
+        <v>752481052</v>
       </c>
       <c r="F432" s="1">
-        <v>845308052</v>
+        <v>837981052</v>
       </c>
       <c r="G432" s="1">
-        <v>28431948</v>
+        <v>35758948</v>
       </c>
       <c r="H432" s="1">
         <v>0</v>
@@ -12783,10 +12792,10 @@
         <v>220000000</v>
       </c>
       <c r="D452" s="1">
-        <v>48700000</v>
+        <v>0</v>
       </c>
       <c r="E452" s="1">
-        <v>89688678</v>
+        <v>138388678</v>
       </c>
       <c r="F452" s="1">
         <v>138388678</v>
@@ -12809,9 +12818,11 @@
         <v>75000000</v>
       </c>
       <c r="D453" s="1">
+        <v>0</v>
+      </c>
+      <c r="E453" s="1">
         <v>38500000</v>
       </c>
-      <c r="E453" s="1"/>
       <c r="F453" s="1">
         <v>38500000</v>
       </c>
@@ -12857,16 +12868,16 @@
         <v>45000000</v>
       </c>
       <c r="D456" s="1">
-        <v>7388000</v>
+        <v>2226250</v>
       </c>
       <c r="E456" s="1">
-        <v>10120000</v>
+        <v>17508000</v>
       </c>
       <c r="F456" s="1">
-        <v>17508000</v>
+        <v>19734250</v>
       </c>
       <c r="G456" s="1">
-        <v>27492000</v>
+        <v>25265750</v>
       </c>
       <c r="H456" s="1">
         <v>15000000</v>
@@ -13039,10 +13050,10 @@
         <v>30750000</v>
       </c>
       <c r="D468" s="1">
-        <v>6869550</v>
+        <v>1778550</v>
       </c>
       <c r="E468" s="1">
-        <v>4982700</v>
+        <v>10073700</v>
       </c>
       <c r="F468" s="1">
         <v>11852250</v>
@@ -13087,10 +13098,10 @@
         <v>128250000</v>
       </c>
       <c r="D470" s="1">
-        <v>17585000</v>
+        <v>0</v>
       </c>
       <c r="E470" s="1">
-        <v>20876000</v>
+        <v>38461000</v>
       </c>
       <c r="F470" s="1">
         <v>38461000</v>
@@ -13113,16 +13124,16 @@
         <v>97500000</v>
       </c>
       <c r="D471" s="1">
-        <v>23953308</v>
+        <v>42616710</v>
       </c>
       <c r="E471" s="1">
         <v>59537750</v>
       </c>
       <c r="F471" s="1">
-        <v>83491058</v>
+        <v>102154460</v>
       </c>
       <c r="G471" s="1">
-        <v>14008942</v>
+        <v>-4654460</v>
       </c>
       <c r="H471" s="1">
         <v>32500000</v>
@@ -15329,22 +15340,22 @@
         <v>129</v>
       </c>
       <c r="B564">
-        <v>1111839324220</v>
+        <v>1110452376206</v>
       </c>
       <c r="C564">
-        <v>1111839324219</v>
+        <v>1110452376205</v>
       </c>
       <c r="D564">
-        <v>347371006564</v>
+        <v>347381006564</v>
       </c>
       <c r="E564">
         <v>655283339661</v>
       </c>
       <c r="F564">
-        <v>1002654346225</v>
+        <v>1002664346225</v>
       </c>
       <c r="G564">
-        <v>109184977994</v>
+        <v>107788029980</v>
       </c>
       <c r="H564">
         <v>1</v>

--- a/data/rka.xlsx
+++ b/data/rka.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x15 xr xr6 xr10">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\76193\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9B365E2-51CF-4C06-BAF4-DCD3BE18EB74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:40009_{1E91865F-5577-45CA-9857-A782281A48D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4812" yWindow="2364" windowWidth="17280" windowHeight="9180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456"/>
   </bookViews>
   <sheets>
-    <sheet name="20261009AR12 SAP ZFM01" sheetId="1" r:id="rId1"/>
+    <sheet name="20261019 AR12 SAP ZFM01" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
   <extLst>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="573" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="574" uniqueCount="131">
   <si>
     <t>Funds Center/Commitment Item</t>
   </si>
@@ -423,7 +423,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -1264,8 +1264,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H566"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:H567"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="62.77734375" bestFit="1" customWidth="1"/>
@@ -1314,10 +1314,10 @@
         <v>108372481167</v>
       </c>
       <c r="D2">
-        <v>78752549040</v>
+        <v>78262705040</v>
       </c>
       <c r="E2">
-        <v>29602491620</v>
+        <v>30092335620</v>
       </c>
       <c r="F2">
         <v>108355040660</v>
@@ -1444,16 +1444,16 @@
         <v>17448622000</v>
       </c>
       <c r="D7">
-        <v>14831327892</v>
+        <v>0</v>
       </c>
       <c r="E7">
-        <v>2617293158</v>
+        <v>17448621051</v>
       </c>
       <c r="F7">
-        <v>17448621050</v>
+        <v>17448621051</v>
       </c>
       <c r="G7">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="H7">
         <v>0</v>
@@ -1470,10 +1470,10 @@
         <v>4372400589</v>
       </c>
       <c r="D8">
-        <v>4044060148</v>
+        <v>3549459748</v>
       </c>
       <c r="E8">
-        <v>300804735</v>
+        <v>795405135</v>
       </c>
       <c r="F8">
         <v>4344864883</v>
@@ -1600,10 +1600,10 @@
         <v>12489080231</v>
       </c>
       <c r="D13">
-        <v>7204626993</v>
+        <v>2758176993</v>
       </c>
       <c r="E13">
-        <v>5284402838</v>
+        <v>9730852838</v>
       </c>
       <c r="F13">
         <v>12489029831</v>
@@ -1704,16 +1704,16 @@
         <v>1200000000</v>
       </c>
       <c r="D17">
-        <v>26300000</v>
+        <v>20500000</v>
       </c>
       <c r="E17">
-        <v>158501000</v>
+        <v>184801000</v>
       </c>
       <c r="F17">
-        <v>184801000</v>
+        <v>205301000</v>
       </c>
       <c r="G17">
-        <v>1015199000</v>
+        <v>994699000</v>
       </c>
       <c r="H17">
         <v>0</v>
@@ -1756,16 +1756,16 @@
         <v>3894602130</v>
       </c>
       <c r="D19">
-        <v>107410093</v>
+        <v>162497520</v>
       </c>
       <c r="E19">
-        <v>2966677037</v>
+        <v>2990766130</v>
       </c>
       <c r="F19">
-        <v>3074087130</v>
+        <v>3153263650</v>
       </c>
       <c r="G19">
-        <v>820515000</v>
+        <v>741338480</v>
       </c>
       <c r="H19">
         <v>0</v>
@@ -1776,10 +1776,10 @@
         <v>26</v>
       </c>
       <c r="B20">
-        <v>1000698000</v>
+        <v>993359900</v>
       </c>
       <c r="C20">
-        <v>1000698000</v>
+        <v>993359900</v>
       </c>
       <c r="D20">
         <v>0</v>
@@ -1791,7 +1791,7 @@
         <v>406948000</v>
       </c>
       <c r="G20">
-        <v>593750000</v>
+        <v>586411900</v>
       </c>
       <c r="H20">
         <v>0</v>
@@ -1808,16 +1808,16 @@
         <v>384915000</v>
       </c>
       <c r="D21">
-        <v>69519493</v>
+        <v>37797318</v>
       </c>
       <c r="E21">
-        <v>97150587</v>
+        <v>129425587</v>
       </c>
       <c r="F21">
-        <v>166670080</v>
+        <v>167222905</v>
       </c>
       <c r="G21">
-        <v>218244920</v>
+        <v>217692095</v>
       </c>
       <c r="H21">
         <v>0</v>
@@ -1886,16 +1886,16 @@
         <v>600000000</v>
       </c>
       <c r="D24">
-        <v>12983700</v>
+        <v>55769220</v>
       </c>
       <c r="E24">
         <v>246346369</v>
       </c>
       <c r="F24">
-        <v>259330069</v>
+        <v>302115589</v>
       </c>
       <c r="G24">
-        <v>340669931</v>
+        <v>297884411</v>
       </c>
       <c r="H24">
         <v>0</v>
@@ -1915,13 +1915,13 @@
         <v>47659106</v>
       </c>
       <c r="E25">
-        <v>1388257008</v>
+        <v>1405257008</v>
       </c>
       <c r="F25">
-        <v>1435916114</v>
+        <v>1452916114</v>
       </c>
       <c r="G25">
-        <v>189160520</v>
+        <v>172160520</v>
       </c>
       <c r="H25">
         <v>0</v>
@@ -1993,13 +1993,13 @@
         <v>0</v>
       </c>
       <c r="E28">
-        <v>3145268832</v>
+        <v>3146039457</v>
       </c>
       <c r="F28">
-        <v>3145268832</v>
+        <v>3146039457</v>
       </c>
       <c r="G28">
-        <v>311345372</v>
+        <v>310574747</v>
       </c>
       <c r="H28">
         <v>0</v>
@@ -2045,13 +2045,13 @@
         <v>0</v>
       </c>
       <c r="E30">
-        <v>3880100020</v>
+        <v>3887696020</v>
       </c>
       <c r="F30">
-        <v>3880100020</v>
+        <v>3887696020</v>
       </c>
       <c r="G30">
-        <v>198170015</v>
+        <v>190574015</v>
       </c>
       <c r="H30">
         <v>0</v>
@@ -2149,13 +2149,13 @@
         <v>0</v>
       </c>
       <c r="E34">
-        <v>10649747460</v>
+        <v>10653747460</v>
       </c>
       <c r="F34">
-        <v>10649747460</v>
+        <v>10653747460</v>
       </c>
       <c r="G34">
-        <v>3320318586</v>
+        <v>3316318586</v>
       </c>
       <c r="H34">
         <v>0</v>
@@ -2348,22 +2348,22 @@
         <v>48</v>
       </c>
       <c r="B42">
-        <v>344713719782</v>
+        <v>344706381682</v>
       </c>
       <c r="C42">
-        <v>344713719782</v>
+        <v>344706381682</v>
       </c>
       <c r="D42">
-        <v>195281938885</v>
+        <v>175080067365</v>
       </c>
       <c r="E42">
-        <v>138186195516</v>
+        <v>158560448527</v>
       </c>
       <c r="F42">
-        <v>333468134401</v>
+        <v>333640515892</v>
       </c>
       <c r="G42">
-        <v>11245585381</v>
+        <v>11065865790</v>
       </c>
       <c r="H42">
         <v>0</v>
@@ -2380,16 +2380,16 @@
         <v>26681487101</v>
       </c>
       <c r="D43">
-        <v>11872191242</v>
+        <v>7880527850</v>
       </c>
       <c r="E43">
-        <v>14683664960</v>
+        <v>18716564352</v>
       </c>
       <c r="F43">
-        <v>26555856202</v>
+        <v>26597092202</v>
       </c>
       <c r="G43">
-        <v>125630899</v>
+        <v>84394899</v>
       </c>
       <c r="H43">
         <v>0</v>
@@ -2556,22 +2556,22 @@
         <v>11</v>
       </c>
       <c r="B50">
-        <v>2000000000</v>
+        <v>2125253740</v>
       </c>
       <c r="C50">
-        <v>2000000000</v>
+        <v>2125253740</v>
       </c>
       <c r="D50">
-        <v>1361195942</v>
+        <v>1632716240</v>
       </c>
       <c r="E50">
         <v>491537500</v>
       </c>
       <c r="F50">
-        <v>1852733442</v>
+        <v>2124253740</v>
       </c>
       <c r="G50">
-        <v>147266558</v>
+        <v>1000000</v>
       </c>
       <c r="H50">
         <v>0</v>
@@ -2634,22 +2634,22 @@
         <v>13</v>
       </c>
       <c r="B53">
-        <v>1300000000</v>
+        <v>1174746260</v>
       </c>
       <c r="C53">
-        <v>1300000000</v>
+        <v>1174746260</v>
       </c>
       <c r="D53">
-        <v>529845714</v>
+        <v>529845914</v>
       </c>
       <c r="E53">
         <v>470019137</v>
       </c>
       <c r="F53">
-        <v>999864851</v>
+        <v>999865051</v>
       </c>
       <c r="G53">
-        <v>300135149</v>
+        <v>174881209</v>
       </c>
       <c r="H53">
         <v>0</v>
@@ -2692,10 +2692,10 @@
         <v>4260000000</v>
       </c>
       <c r="D55">
-        <v>1007319920</v>
+        <v>924653290</v>
       </c>
       <c r="E55">
-        <v>3000513563</v>
+        <v>3083180193</v>
       </c>
       <c r="F55">
         <v>4007833483</v>
@@ -2718,16 +2718,16 @@
         <v>1000000000</v>
       </c>
       <c r="D56">
-        <v>624313139</v>
+        <v>594025575</v>
       </c>
       <c r="E56">
         <v>0</v>
       </c>
       <c r="F56">
-        <v>624313139</v>
+        <v>594025575</v>
       </c>
       <c r="G56">
-        <v>375686861</v>
+        <v>405974425</v>
       </c>
       <c r="H56">
         <v>0</v>
@@ -2822,16 +2822,16 @@
         <v>2420000000</v>
       </c>
       <c r="D60">
-        <v>422016508</v>
+        <v>1387993036</v>
       </c>
       <c r="E60">
         <v>911688617</v>
       </c>
       <c r="F60">
-        <v>1333705125</v>
+        <v>2299681653</v>
       </c>
       <c r="G60">
-        <v>1086294875</v>
+        <v>120318347</v>
       </c>
       <c r="H60">
         <v>0</v>
@@ -2848,16 +2848,16 @@
         <v>750000000</v>
       </c>
       <c r="D61">
-        <v>481567894</v>
+        <v>559730392</v>
       </c>
       <c r="E61">
         <v>0</v>
       </c>
       <c r="F61">
-        <v>481567894</v>
+        <v>559730392</v>
       </c>
       <c r="G61">
-        <v>268432106</v>
+        <v>190269608</v>
       </c>
       <c r="H61">
         <v>0</v>
@@ -2900,10 +2900,10 @@
         <v>2500000000</v>
       </c>
       <c r="D63">
-        <v>2041251000</v>
+        <v>1995051000</v>
       </c>
       <c r="E63">
-        <v>383110100</v>
+        <v>429310100</v>
       </c>
       <c r="F63">
         <v>2424361100</v>
@@ -2978,16 +2978,16 @@
         <v>3500000000</v>
       </c>
       <c r="D66">
-        <v>0</v>
+        <v>589335084</v>
       </c>
       <c r="E66">
         <v>2248583818</v>
       </c>
       <c r="F66">
-        <v>2248583818</v>
+        <v>2837918902</v>
       </c>
       <c r="G66">
-        <v>1251416182</v>
+        <v>662081098</v>
       </c>
       <c r="H66">
         <v>0</v>
@@ -3137,13 +3137,13 @@
         <v>0</v>
       </c>
       <c r="E72">
-        <v>286984250</v>
+        <v>312565500</v>
       </c>
       <c r="F72">
-        <v>286984250</v>
+        <v>312565500</v>
       </c>
       <c r="G72">
-        <v>185315750</v>
+        <v>159734500</v>
       </c>
       <c r="H72">
         <v>0</v>
@@ -3215,13 +3215,13 @@
         <v>0</v>
       </c>
       <c r="E75">
-        <v>18168210445</v>
+        <v>18170230070</v>
       </c>
       <c r="F75">
-        <v>18168210445</v>
+        <v>18170230070</v>
       </c>
       <c r="G75">
-        <v>4763396784</v>
+        <v>4761377159</v>
       </c>
       <c r="H75">
         <v>0</v>
@@ -3446,16 +3446,16 @@
         <v>111056398441</v>
       </c>
       <c r="D84">
-        <v>31380140681</v>
+        <v>29134317703</v>
       </c>
       <c r="E84">
-        <v>67733598794</v>
+        <v>71922965691</v>
       </c>
       <c r="F84">
-        <v>99113739475</v>
+        <v>101057283394</v>
       </c>
       <c r="G84">
-        <v>11942658966</v>
+        <v>9999115047</v>
       </c>
       <c r="H84">
         <v>0</v>
@@ -3576,10 +3576,10 @@
         <v>30639775739</v>
       </c>
       <c r="D89">
-        <v>15158286544</v>
+        <v>14268196083</v>
       </c>
       <c r="E89">
-        <v>14477662921</v>
+        <v>15367753382</v>
       </c>
       <c r="F89">
         <v>29635949465</v>
@@ -3654,10 +3654,10 @@
         <v>1210765056</v>
       </c>
       <c r="D92">
-        <v>377379987</v>
+        <v>348519987</v>
       </c>
       <c r="E92">
-        <v>320408440</v>
+        <v>349268440</v>
       </c>
       <c r="F92">
         <v>697788427</v>
@@ -3706,10 +3706,10 @@
         <v>2796520000</v>
       </c>
       <c r="D94">
-        <v>497966519</v>
+        <v>286834350</v>
       </c>
       <c r="E94">
-        <v>2297326902</v>
+        <v>2508459071</v>
       </c>
       <c r="F94">
         <v>2795293421</v>
@@ -3836,10 +3836,10 @@
         <v>360000000</v>
       </c>
       <c r="D99">
-        <v>92906576</v>
+        <v>22982600</v>
       </c>
       <c r="E99">
-        <v>247536000</v>
+        <v>317459976</v>
       </c>
       <c r="F99">
         <v>340442576</v>
@@ -3862,10 +3862,10 @@
         <v>1645235120</v>
       </c>
       <c r="D100">
-        <v>371949680</v>
+        <v>173005680</v>
       </c>
       <c r="E100">
-        <v>1143628806</v>
+        <v>1342572806</v>
       </c>
       <c r="F100">
         <v>1515578486</v>
@@ -3914,16 +3914,16 @@
         <v>392307500</v>
       </c>
       <c r="D102">
-        <v>61597900</v>
+        <v>53050900</v>
       </c>
       <c r="E102">
-        <v>45427850</v>
+        <v>55474850</v>
       </c>
       <c r="F102">
-        <v>107025750</v>
+        <v>108525750</v>
       </c>
       <c r="G102">
-        <v>285281750</v>
+        <v>283781750</v>
       </c>
       <c r="H102">
         <v>0</v>
@@ -3940,16 +3940,16 @@
         <v>370700000</v>
       </c>
       <c r="D103">
-        <v>79911380</v>
+        <v>72930730</v>
       </c>
       <c r="E103">
-        <v>174999400</v>
+        <v>183626550</v>
       </c>
       <c r="F103">
-        <v>254910780</v>
+        <v>256557280</v>
       </c>
       <c r="G103">
-        <v>115789220</v>
+        <v>114142720</v>
       </c>
       <c r="H103">
         <v>0</v>
@@ -4047,13 +4047,13 @@
         <v>0</v>
       </c>
       <c r="E107">
-        <v>298547318</v>
+        <v>300066068</v>
       </c>
       <c r="F107">
-        <v>298547318</v>
+        <v>300066068</v>
       </c>
       <c r="G107">
-        <v>183901682</v>
+        <v>182382932</v>
       </c>
       <c r="H107">
         <v>0</v>
@@ -4177,13 +4177,13 @@
         <v>0</v>
       </c>
       <c r="E112">
-        <v>13168307073</v>
+        <v>13168342698</v>
       </c>
       <c r="F112">
-        <v>13168307073</v>
+        <v>13168342698</v>
       </c>
       <c r="G112">
-        <v>3055337780</v>
+        <v>3055302155</v>
       </c>
       <c r="H112">
         <v>0</v>
@@ -4408,16 +4408,16 @@
         <v>81915410456</v>
       </c>
       <c r="D121">
-        <v>19196035482</v>
+        <v>17781557226</v>
       </c>
       <c r="E121">
-        <v>55431637352</v>
+        <v>56850816483</v>
       </c>
       <c r="F121">
-        <v>74627672834</v>
+        <v>74632373709</v>
       </c>
       <c r="G121">
-        <v>7287737622</v>
+        <v>7283036747</v>
       </c>
       <c r="H121">
         <v>0</v>
@@ -4428,10 +4428,10 @@
         <v>8</v>
       </c>
       <c r="B122">
-        <v>8995670000</v>
+        <v>8694808538</v>
       </c>
       <c r="C122">
-        <v>8995670000</v>
+        <v>8694808538</v>
       </c>
       <c r="D122">
         <v>905660000</v>
@@ -4443,7 +4443,7 @@
         <v>8690396312</v>
       </c>
       <c r="G122">
-        <v>305273688</v>
+        <v>4412226</v>
       </c>
       <c r="H122">
         <v>0</v>
@@ -4454,22 +4454,22 @@
         <v>11</v>
       </c>
       <c r="B123">
-        <v>1494332364</v>
+        <v>1721821664</v>
       </c>
       <c r="C123">
-        <v>1494332364</v>
+        <v>1721821664</v>
       </c>
       <c r="D123">
-        <v>1353756781</v>
+        <v>1449749391</v>
       </c>
       <c r="E123">
         <v>127583711</v>
       </c>
       <c r="F123">
-        <v>1481340492</v>
+        <v>1577333102</v>
       </c>
       <c r="G123">
-        <v>12991872</v>
+        <v>144488562</v>
       </c>
       <c r="H123">
         <v>0</v>
@@ -4506,10 +4506,10 @@
         <v>54</v>
       </c>
       <c r="B125">
-        <v>929147000</v>
+        <v>1002519162</v>
       </c>
       <c r="C125">
-        <v>929147000</v>
+        <v>1002519162</v>
       </c>
       <c r="D125">
         <v>0</v>
@@ -4521,7 +4521,7 @@
         <v>513025460</v>
       </c>
       <c r="G125">
-        <v>416121540</v>
+        <v>489493702</v>
       </c>
       <c r="H125">
         <v>0</v>
@@ -4564,16 +4564,16 @@
         <v>818532000</v>
       </c>
       <c r="D127">
-        <v>0</v>
+        <v>9900000</v>
       </c>
       <c r="E127">
         <v>781843483</v>
       </c>
       <c r="F127">
-        <v>781843483</v>
+        <v>791743483</v>
       </c>
       <c r="G127">
-        <v>36688517</v>
+        <v>26788517</v>
       </c>
       <c r="H127">
         <v>0</v>
@@ -4590,16 +4590,16 @@
         <v>4824864000</v>
       </c>
       <c r="D128">
-        <v>90911582</v>
+        <v>140761582</v>
       </c>
       <c r="E128">
         <v>4624222041</v>
       </c>
       <c r="F128">
-        <v>4715133623</v>
+        <v>4764983623</v>
       </c>
       <c r="G128">
-        <v>109730377</v>
+        <v>59880377</v>
       </c>
       <c r="H128">
         <v>0</v>
@@ -4616,10 +4616,10 @@
         <v>1665000000</v>
       </c>
       <c r="D129">
-        <v>620655219</v>
+        <v>585205524</v>
       </c>
       <c r="E129">
-        <v>810329827</v>
+        <v>845779522</v>
       </c>
       <c r="F129">
         <v>1430985046</v>
@@ -4694,10 +4694,10 @@
         <v>2233168000</v>
       </c>
       <c r="D132">
-        <v>1462560620</v>
+        <v>1437810620</v>
       </c>
       <c r="E132">
-        <v>766560444</v>
+        <v>791310444</v>
       </c>
       <c r="F132">
         <v>2229121064</v>
@@ -4720,16 +4720,16 @@
         <v>354000000</v>
       </c>
       <c r="D133">
-        <v>50978800</v>
+        <v>12639400</v>
       </c>
       <c r="E133">
-        <v>279645718</v>
+        <v>314185718</v>
       </c>
       <c r="F133">
-        <v>330624518</v>
+        <v>326825118</v>
       </c>
       <c r="G133">
-        <v>23375482</v>
+        <v>27174882</v>
       </c>
       <c r="H133">
         <v>0</v>
@@ -4746,16 +4746,16 @@
         <v>339375606</v>
       </c>
       <c r="D134">
-        <v>0</v>
+        <v>254714775</v>
       </c>
       <c r="E134">
         <v>59473907</v>
       </c>
       <c r="F134">
-        <v>59473907</v>
+        <v>314188682</v>
       </c>
       <c r="G134">
-        <v>279901699</v>
+        <v>25186924</v>
       </c>
       <c r="H134">
         <v>0</v>
@@ -4824,10 +4824,10 @@
         <v>118875000</v>
       </c>
       <c r="D137">
-        <v>2616400</v>
+        <v>0</v>
       </c>
       <c r="E137">
-        <v>86395900</v>
+        <v>89012300</v>
       </c>
       <c r="F137">
         <v>89012300</v>
@@ -4876,16 +4876,16 @@
         <v>87500000</v>
       </c>
       <c r="D139">
-        <v>0</v>
+        <v>3500000</v>
       </c>
       <c r="E139">
         <v>82403639</v>
       </c>
       <c r="F139">
-        <v>82403639</v>
+        <v>85903639</v>
       </c>
       <c r="G139">
-        <v>5096361</v>
+        <v>1596361</v>
       </c>
       <c r="H139">
         <v>0</v>
@@ -4902,10 +4902,10 @@
         <v>310275000</v>
       </c>
       <c r="D140">
-        <v>22955000</v>
+        <v>19955000</v>
       </c>
       <c r="E140">
-        <v>241668700</v>
+        <v>244668700</v>
       </c>
       <c r="F140">
         <v>264623700</v>
@@ -4983,13 +4983,13 @@
         <v>0</v>
       </c>
       <c r="E143">
-        <v>169399250</v>
+        <v>172924250</v>
       </c>
       <c r="F143">
-        <v>169399250</v>
+        <v>172924250</v>
       </c>
       <c r="G143">
-        <v>43920750</v>
+        <v>40395750</v>
       </c>
       <c r="H143">
         <v>0</v>
@@ -5058,10 +5058,10 @@
         <v>0</v>
       </c>
       <c r="D146">
+        <v>0</v>
+      </c>
+      <c r="E146">
         <v>1013187</v>
-      </c>
-      <c r="E146">
-        <v>0</v>
       </c>
       <c r="F146">
         <v>1013187</v>
@@ -5087,13 +5087,13 @@
         <v>0</v>
       </c>
       <c r="E147">
-        <v>7839091424</v>
+        <v>7839192674</v>
       </c>
       <c r="F147">
-        <v>7839091424</v>
+        <v>7839192674</v>
       </c>
       <c r="G147">
-        <v>2110002659</v>
+        <v>2109901409</v>
       </c>
       <c r="H147">
         <v>0</v>
@@ -5136,10 +5136,10 @@
         <v>9769849891</v>
       </c>
       <c r="D149">
-        <v>23970868</v>
+        <v>0</v>
       </c>
       <c r="E149">
-        <v>8744138521</v>
+        <v>8768109389</v>
       </c>
       <c r="F149">
         <v>8768109389</v>
@@ -5240,10 +5240,10 @@
         <v>1330317539</v>
       </c>
       <c r="D153">
-        <v>606069</v>
+        <v>0</v>
       </c>
       <c r="E153">
-        <v>1133100014</v>
+        <v>1133706083</v>
       </c>
       <c r="F153">
         <v>1133706083</v>
@@ -5318,16 +5318,16 @@
         <v>52405261175</v>
       </c>
       <c r="D156">
-        <v>5920912334</v>
+        <v>6205124100</v>
       </c>
       <c r="E156">
-        <v>40168271075</v>
+        <v>40297843544</v>
       </c>
       <c r="F156">
-        <v>46089183409</v>
+        <v>46502967644</v>
       </c>
       <c r="G156">
-        <v>6316077766</v>
+        <v>5902293531</v>
       </c>
       <c r="H156">
         <v>0</v>
@@ -5448,16 +5448,16 @@
         <v>870437000</v>
       </c>
       <c r="D161">
-        <v>169972300</v>
+        <v>164311300</v>
       </c>
       <c r="E161">
-        <v>690639000</v>
+        <v>695739000</v>
       </c>
       <c r="F161">
-        <v>860611300</v>
+        <v>860050300</v>
       </c>
       <c r="G161">
-        <v>9825700</v>
+        <v>10386700</v>
       </c>
       <c r="H161">
         <v>0</v>
@@ -5500,16 +5500,16 @@
         <v>1702406000</v>
       </c>
       <c r="D163">
-        <v>384514507</v>
+        <v>256546671</v>
       </c>
       <c r="E163">
-        <v>1024235322</v>
+        <v>1140577734</v>
       </c>
       <c r="F163">
-        <v>1408749829</v>
+        <v>1397124405</v>
       </c>
       <c r="G163">
-        <v>293656171</v>
+        <v>305281595</v>
       </c>
       <c r="H163">
         <v>0</v>
@@ -5604,16 +5604,16 @@
         <v>2427860000</v>
       </c>
       <c r="D167">
-        <v>1782208152</v>
+        <v>1739739552</v>
       </c>
       <c r="E167">
-        <v>636843684</v>
+        <v>675103684</v>
       </c>
       <c r="F167">
-        <v>2419051836</v>
+        <v>2414843236</v>
       </c>
       <c r="G167">
-        <v>8808164</v>
+        <v>13016764</v>
       </c>
       <c r="H167">
         <v>0</v>
@@ -5812,16 +5812,16 @@
         <v>157500000</v>
       </c>
       <c r="D175">
-        <v>16615067</v>
+        <v>11000317</v>
       </c>
       <c r="E175">
-        <v>50070391</v>
+        <v>55070391</v>
       </c>
       <c r="F175">
-        <v>66685458</v>
+        <v>66070708</v>
       </c>
       <c r="G175">
-        <v>90814542</v>
+        <v>91429292</v>
       </c>
       <c r="H175">
         <v>0</v>
@@ -5838,16 +5838,16 @@
         <v>663275000</v>
       </c>
       <c r="D176">
-        <v>73323100</v>
+        <v>37630650</v>
       </c>
       <c r="E176">
-        <v>485651644</v>
+        <v>519501594</v>
       </c>
       <c r="F176">
-        <v>558974744</v>
+        <v>557132244</v>
       </c>
       <c r="G176">
-        <v>104300256</v>
+        <v>106142756</v>
       </c>
       <c r="H176">
         <v>0</v>
@@ -5890,10 +5890,10 @@
         <v>326525000</v>
       </c>
       <c r="D178">
-        <v>104564725</v>
+        <v>54664725</v>
       </c>
       <c r="E178">
-        <v>104678200</v>
+        <v>154578200</v>
       </c>
       <c r="F178">
         <v>209242925</v>
@@ -5945,13 +5945,13 @@
         <v>0</v>
       </c>
       <c r="E180">
-        <v>147483750</v>
+        <v>148396250</v>
       </c>
       <c r="F180">
-        <v>147483750</v>
+        <v>148396250</v>
       </c>
       <c r="G180">
-        <v>68918250</v>
+        <v>68005750</v>
       </c>
       <c r="H180">
         <v>0</v>
@@ -5997,13 +5997,13 @@
         <v>0</v>
       </c>
       <c r="E182">
-        <v>5826504961</v>
+        <v>5826538711</v>
       </c>
       <c r="F182">
-        <v>5826504961</v>
+        <v>5826538711</v>
       </c>
       <c r="G182">
-        <v>1678218417</v>
+        <v>1678184667</v>
       </c>
       <c r="H182">
         <v>0</v>
@@ -6202,16 +6202,16 @@
         <v>46627343527</v>
       </c>
       <c r="D190">
-        <v>7389615939</v>
+        <v>7122311303</v>
       </c>
       <c r="E190">
-        <v>33455784248</v>
+        <v>33705182860</v>
       </c>
       <c r="F190">
-        <v>40845400187</v>
+        <v>40827494163</v>
       </c>
       <c r="G190">
-        <v>5781943340</v>
+        <v>5799849364</v>
       </c>
       <c r="H190">
         <v>0</v>
@@ -6332,16 +6332,16 @@
         <v>770509354</v>
       </c>
       <c r="D195">
-        <v>210156640</v>
+        <v>479666384</v>
       </c>
       <c r="E195">
         <v>290564000</v>
       </c>
       <c r="F195">
-        <v>500720640</v>
+        <v>770230384</v>
       </c>
       <c r="G195">
-        <v>269788714</v>
+        <v>278970</v>
       </c>
       <c r="H195">
         <v>0</v>
@@ -6358,10 +6358,10 @@
         <v>3445601643</v>
       </c>
       <c r="D196">
-        <v>2870558165</v>
+        <v>2820653966</v>
       </c>
       <c r="E196">
-        <v>570614678</v>
+        <v>620518877</v>
       </c>
       <c r="F196">
         <v>3441172843</v>
@@ -6436,16 +6436,16 @@
         <v>469000000</v>
       </c>
       <c r="D199">
-        <v>16686167</v>
+        <v>321859617</v>
       </c>
       <c r="E199">
         <v>141792902</v>
       </c>
       <c r="F199">
-        <v>158479069</v>
+        <v>463652519</v>
       </c>
       <c r="G199">
-        <v>310520931</v>
+        <v>5347481</v>
       </c>
       <c r="H199">
         <v>0</v>
@@ -6566,10 +6566,10 @@
         <v>950000000</v>
       </c>
       <c r="D204">
-        <v>447164894</v>
+        <v>0</v>
       </c>
       <c r="E204">
-        <v>494525000</v>
+        <v>941689894</v>
       </c>
       <c r="F204">
         <v>941689894</v>
@@ -6878,16 +6878,16 @@
         <v>393750000</v>
       </c>
       <c r="D216">
-        <v>177524649</v>
+        <v>169959000</v>
       </c>
       <c r="E216">
-        <v>155942458</v>
+        <v>170815935</v>
       </c>
       <c r="F216">
-        <v>333467107</v>
+        <v>340774935</v>
       </c>
       <c r="G216">
-        <v>60282893</v>
+        <v>52975065</v>
       </c>
       <c r="H216">
         <v>0</v>
@@ -6933,13 +6933,13 @@
         <v>0</v>
       </c>
       <c r="E218">
-        <v>207401250</v>
+        <v>209607500</v>
       </c>
       <c r="F218">
-        <v>207401250</v>
+        <v>209607500</v>
       </c>
       <c r="G218">
-        <v>13098750</v>
+        <v>10892500</v>
       </c>
       <c r="H218">
         <v>0</v>
@@ -7011,13 +7011,13 @@
         <v>0</v>
       </c>
       <c r="E221">
-        <v>7817909960</v>
+        <v>7817964335</v>
       </c>
       <c r="F221">
-        <v>7817909960</v>
+        <v>7817964335</v>
       </c>
       <c r="G221">
-        <v>2005252166</v>
+        <v>2005197791</v>
       </c>
       <c r="H221">
         <v>0</v>
@@ -7060,10 +7060,10 @@
         <v>9245675372</v>
       </c>
       <c r="D223">
-        <v>24345225</v>
+        <v>0</v>
       </c>
       <c r="E223">
-        <v>8604648254</v>
+        <v>8628993479</v>
       </c>
       <c r="F223">
         <v>8628993479</v>
@@ -7164,10 +7164,10 @@
         <v>825165933</v>
       </c>
       <c r="D227">
-        <v>479914</v>
+        <v>0</v>
       </c>
       <c r="E227">
-        <v>1086574546</v>
+        <v>1087054460</v>
       </c>
       <c r="F227">
         <v>1087054460</v>
@@ -7216,16 +7216,16 @@
         <v>47690614295</v>
       </c>
       <c r="D229">
-        <v>8863165337</v>
+        <v>8908388650</v>
       </c>
       <c r="E229">
-        <v>34130750981</v>
+        <v>34669779315</v>
       </c>
       <c r="F229">
-        <v>42993916318</v>
+        <v>43578167965</v>
       </c>
       <c r="G229">
-        <v>4696697977</v>
+        <v>4112446330</v>
       </c>
       <c r="H229">
         <v>0</v>
@@ -7268,16 +7268,16 @@
         <v>379765000</v>
       </c>
       <c r="D231">
-        <v>0</v>
+        <v>379765000</v>
       </c>
       <c r="E231">
         <v>0</v>
       </c>
       <c r="F231">
-        <v>0</v>
+        <v>379765000</v>
       </c>
       <c r="G231">
-        <v>379765000</v>
+        <v>0</v>
       </c>
       <c r="H231">
         <v>0</v>
@@ -7346,10 +7346,10 @@
         <v>495000000</v>
       </c>
       <c r="D234">
-        <v>13642600</v>
+        <v>0</v>
       </c>
       <c r="E234">
-        <v>456679595</v>
+        <v>470322195</v>
       </c>
       <c r="F234">
         <v>470322195</v>
@@ -7398,10 +7398,10 @@
         <v>1310391000</v>
       </c>
       <c r="D236">
-        <v>783697966</v>
+        <v>404624466</v>
       </c>
       <c r="E236">
-        <v>518257125</v>
+        <v>897330625</v>
       </c>
       <c r="F236">
         <v>1301955091</v>
@@ -7424,16 +7424,16 @@
         <v>1380000000</v>
       </c>
       <c r="D237">
-        <v>40494000</v>
+        <v>28983000</v>
       </c>
       <c r="E237">
-        <v>1205729427</v>
+        <v>1224240427</v>
       </c>
       <c r="F237">
-        <v>1246223427</v>
+        <v>1253223427</v>
       </c>
       <c r="G237">
-        <v>133776573</v>
+        <v>126776573</v>
       </c>
       <c r="H237">
         <v>0</v>
@@ -7450,16 +7450,16 @@
         <v>350000000</v>
       </c>
       <c r="D238">
-        <v>317168720</v>
+        <v>317569770</v>
       </c>
       <c r="E238">
         <v>11786500</v>
       </c>
       <c r="F238">
-        <v>328955220</v>
+        <v>329356270</v>
       </c>
       <c r="G238">
-        <v>21044780</v>
+        <v>20643730</v>
       </c>
       <c r="H238">
         <v>0</v>
@@ -7528,10 +7528,10 @@
         <v>2264065000</v>
       </c>
       <c r="D241">
-        <v>198350000</v>
+        <v>16500000</v>
       </c>
       <c r="E241">
-        <v>2032762000</v>
+        <v>2214612000</v>
       </c>
       <c r="F241">
         <v>2231112000</v>
@@ -7606,16 +7606,16 @@
         <v>910000000</v>
       </c>
       <c r="D244">
-        <v>194658750</v>
+        <v>197880000</v>
       </c>
       <c r="E244">
-        <v>511700000</v>
+        <v>706358750</v>
       </c>
       <c r="F244">
-        <v>706358750</v>
+        <v>904238750</v>
       </c>
       <c r="G244">
-        <v>203641250</v>
+        <v>5761250</v>
       </c>
       <c r="H244">
         <v>0</v>
@@ -7710,16 +7710,16 @@
         <v>413278250</v>
       </c>
       <c r="D248">
-        <v>25842500</v>
+        <v>26800500</v>
       </c>
       <c r="E248">
         <v>341347900</v>
       </c>
       <c r="F248">
-        <v>367190400</v>
+        <v>368148400</v>
       </c>
       <c r="G248">
-        <v>46087850</v>
+        <v>45129850</v>
       </c>
       <c r="H248">
         <v>0</v>
@@ -7762,10 +7762,10 @@
         <v>728771820</v>
       </c>
       <c r="D250">
-        <v>6245000</v>
+        <v>5000000</v>
       </c>
       <c r="E250">
-        <v>722526820</v>
+        <v>723771820</v>
       </c>
       <c r="F250">
         <v>728771820</v>
@@ -7814,16 +7814,16 @@
         <v>60000000</v>
       </c>
       <c r="D252">
-        <v>6000000</v>
+        <v>23142840</v>
       </c>
       <c r="E252">
         <v>36856200</v>
       </c>
       <c r="F252">
-        <v>42856200</v>
+        <v>59999040</v>
       </c>
       <c r="G252">
-        <v>17143800</v>
+        <v>960</v>
       </c>
       <c r="H252">
         <v>0</v>
@@ -8074,16 +8074,16 @@
         <v>49566121365</v>
       </c>
       <c r="D262">
-        <v>3101832337</v>
+        <v>2915998377</v>
       </c>
       <c r="E262">
-        <v>39964869294</v>
+        <v>40753850144</v>
       </c>
       <c r="F262">
-        <v>43066701631</v>
+        <v>43669848521</v>
       </c>
       <c r="G262">
-        <v>6499419734</v>
+        <v>5896272844</v>
       </c>
       <c r="H262">
         <v>0</v>
@@ -8282,16 +8282,16 @@
         <v>3609800000</v>
       </c>
       <c r="D270">
-        <v>1721825151</v>
+        <v>1778552571</v>
       </c>
       <c r="E270">
-        <v>890865055</v>
+        <v>910848335</v>
       </c>
       <c r="F270">
-        <v>2612690206</v>
+        <v>2689400906</v>
       </c>
       <c r="G270">
-        <v>997109794</v>
+        <v>920399094</v>
       </c>
       <c r="H270">
         <v>0</v>
@@ -8308,16 +8308,16 @@
         <v>400000000</v>
       </c>
       <c r="D271">
-        <v>0</v>
+        <v>42078280</v>
       </c>
       <c r="E271">
         <v>0</v>
       </c>
       <c r="F271">
-        <v>0</v>
+        <v>42078280</v>
       </c>
       <c r="G271">
-        <v>400000000</v>
+        <v>357921720</v>
       </c>
       <c r="H271">
         <v>0</v>
@@ -8360,10 +8360,10 @@
         <v>150000000</v>
       </c>
       <c r="D273">
-        <v>44565900</v>
+        <v>15400000</v>
       </c>
       <c r="E273">
-        <v>46982180</v>
+        <v>76148080</v>
       </c>
       <c r="F273">
         <v>91548080</v>
@@ -8516,16 +8516,16 @@
         <v>3309100507</v>
       </c>
       <c r="D279">
-        <v>2372091726</v>
+        <v>2368201990</v>
       </c>
       <c r="E279">
-        <v>569806840</v>
+        <v>579806576</v>
       </c>
       <c r="F279">
-        <v>2941898566</v>
+        <v>2948008566</v>
       </c>
       <c r="G279">
-        <v>367201941</v>
+        <v>361091941</v>
       </c>
       <c r="H279">
         <v>0</v>
@@ -8672,10 +8672,10 @@
         <v>1952349292</v>
       </c>
       <c r="D285">
-        <v>4772277</v>
+        <v>0</v>
       </c>
       <c r="E285">
-        <v>1413784332</v>
+        <v>1418556609</v>
       </c>
       <c r="F285">
         <v>1418556609</v>
@@ -8698,16 +8698,16 @@
         <v>245895575</v>
       </c>
       <c r="D286">
-        <v>106173893</v>
+        <v>59818393</v>
       </c>
       <c r="E286">
-        <v>106875714</v>
+        <v>156825714</v>
       </c>
       <c r="F286">
-        <v>213049607</v>
+        <v>216644107</v>
       </c>
       <c r="G286">
-        <v>32845968</v>
+        <v>29251468</v>
       </c>
       <c r="H286">
         <v>0</v>
@@ -8724,10 +8724,10 @@
         <v>548807745</v>
       </c>
       <c r="D287">
-        <v>116036610</v>
+        <v>102536610</v>
       </c>
       <c r="E287">
-        <v>362215933</v>
+        <v>375715933</v>
       </c>
       <c r="F287">
         <v>478252543</v>
@@ -8805,13 +8805,13 @@
         <v>0</v>
       </c>
       <c r="E290">
-        <v>256048750</v>
+        <v>256992500</v>
       </c>
       <c r="F290">
-        <v>256048750</v>
+        <v>256992500</v>
       </c>
       <c r="G290">
-        <v>160250250</v>
+        <v>159306500</v>
       </c>
       <c r="H290">
         <v>0</v>
@@ -8828,10 +8828,10 @@
         <v>181144082</v>
       </c>
       <c r="D291">
-        <v>1656600</v>
+        <v>828300</v>
       </c>
       <c r="E291">
-        <v>77235144</v>
+        <v>78063444</v>
       </c>
       <c r="F291">
         <v>78891744</v>
@@ -8909,13 +8909,13 @@
         <v>0</v>
       </c>
       <c r="E294">
-        <v>9850849747</v>
+        <v>9850891935</v>
       </c>
       <c r="F294">
-        <v>9850849747</v>
+        <v>9850891935</v>
       </c>
       <c r="G294">
-        <v>2771769180</v>
+        <v>2771726992</v>
       </c>
       <c r="H294">
         <v>0</v>
@@ -8958,10 +8958,10 @@
         <v>12911717415</v>
       </c>
       <c r="D296">
-        <v>31127774</v>
+        <v>0</v>
       </c>
       <c r="E296">
-        <v>11294818195</v>
+        <v>11325945969</v>
       </c>
       <c r="F296">
         <v>11325945969</v>
@@ -9062,10 +9062,10 @@
         <v>1560328837</v>
       </c>
       <c r="D300">
-        <v>590411</v>
+        <v>0</v>
       </c>
       <c r="E300">
-        <v>1357575105</v>
+        <v>1358165516</v>
       </c>
       <c r="F300">
         <v>1358165516</v>
@@ -9114,16 +9114,16 @@
         <v>64006219795</v>
       </c>
       <c r="D302">
-        <v>13790822896</v>
+        <v>13759398698</v>
       </c>
       <c r="E302">
-        <v>40902854933</v>
+        <v>41063758549</v>
       </c>
       <c r="F302">
-        <v>54693677829</v>
+        <v>54823157247</v>
       </c>
       <c r="G302">
-        <v>9312541966</v>
+        <v>9183062548</v>
       </c>
       <c r="H302">
         <v>0</v>
@@ -9244,10 +9244,10 @@
         <v>298750000</v>
       </c>
       <c r="D307">
-        <v>129447903</v>
+        <v>87500000</v>
       </c>
       <c r="E307">
-        <v>168892197</v>
+        <v>210840100</v>
       </c>
       <c r="F307">
         <v>298340100</v>
@@ -9374,16 +9374,16 @@
         <v>174000000</v>
       </c>
       <c r="D312">
-        <v>129833754</v>
+        <v>129862100</v>
       </c>
       <c r="E312">
         <v>44129340</v>
       </c>
       <c r="F312">
-        <v>173963094</v>
+        <v>173991440</v>
       </c>
       <c r="G312">
-        <v>36906</v>
+        <v>8560</v>
       </c>
       <c r="H312">
         <v>0</v>
@@ -9426,16 +9426,16 @@
         <v>1882400000</v>
       </c>
       <c r="D314">
-        <v>109760000</v>
+        <v>152143000</v>
       </c>
       <c r="E314">
         <v>1723065000</v>
       </c>
       <c r="F314">
-        <v>1832825000</v>
+        <v>1875208000</v>
       </c>
       <c r="G314">
-        <v>49575000</v>
+        <v>7192000</v>
       </c>
       <c r="H314">
         <v>0</v>
@@ -9608,16 +9608,16 @@
         <v>150383000</v>
       </c>
       <c r="D321">
-        <v>99792998</v>
+        <v>103486498</v>
       </c>
       <c r="E321">
         <v>46866929</v>
       </c>
       <c r="F321">
-        <v>146659927</v>
+        <v>150353427</v>
       </c>
       <c r="G321">
-        <v>3723073</v>
+        <v>29573</v>
       </c>
       <c r="H321">
         <v>0</v>
@@ -9634,16 +9634,16 @@
         <v>91255250</v>
       </c>
       <c r="D322">
-        <v>6441500</v>
+        <v>12473500</v>
       </c>
       <c r="E322">
         <v>67676000</v>
       </c>
       <c r="F322">
-        <v>74117500</v>
+        <v>80149500</v>
       </c>
       <c r="G322">
-        <v>17137750</v>
+        <v>11105750</v>
       </c>
       <c r="H322">
         <v>0</v>
@@ -9715,13 +9715,13 @@
         <v>0</v>
       </c>
       <c r="E325">
-        <v>143477750</v>
+        <v>146515250</v>
       </c>
       <c r="F325">
-        <v>143477750</v>
+        <v>146515250</v>
       </c>
       <c r="G325">
-        <v>86522250</v>
+        <v>83484750</v>
       </c>
       <c r="H325">
         <v>0</v>
@@ -9767,13 +9767,13 @@
         <v>0</v>
       </c>
       <c r="E327">
-        <v>5496987309</v>
+        <v>5497066997</v>
       </c>
       <c r="F327">
-        <v>5496987309</v>
+        <v>5497066997</v>
       </c>
       <c r="G327">
-        <v>1556804956</v>
+        <v>1556725268</v>
       </c>
       <c r="H327">
         <v>0</v>
@@ -9972,16 +9972,16 @@
         <v>30557896710</v>
       </c>
       <c r="D335">
-        <v>1997601591</v>
+        <v>2007790534</v>
       </c>
       <c r="E335">
-        <v>24031650805</v>
+        <v>24076715896</v>
       </c>
       <c r="F335">
-        <v>26029252396</v>
+        <v>26084506430</v>
       </c>
       <c r="G335">
-        <v>4528644314</v>
+        <v>4473390280</v>
       </c>
       <c r="H335">
         <v>0</v>
@@ -10076,16 +10076,16 @@
         <v>2593734264</v>
       </c>
       <c r="D339">
-        <v>720248400</v>
+        <v>721299430</v>
       </c>
       <c r="E339">
         <v>1870716210</v>
       </c>
       <c r="F339">
-        <v>2590964610</v>
+        <v>2592015640</v>
       </c>
       <c r="G339">
-        <v>2769654</v>
+        <v>1718624</v>
       </c>
       <c r="H339">
         <v>0</v>
@@ -10154,16 +10154,16 @@
         <v>1777927034</v>
       </c>
       <c r="D342">
-        <v>487618000</v>
+        <v>503693200</v>
       </c>
       <c r="E342">
         <v>1273883607</v>
       </c>
       <c r="F342">
-        <v>1761501607</v>
+        <v>1777576807</v>
       </c>
       <c r="G342">
-        <v>16425427</v>
+        <v>350227</v>
       </c>
       <c r="H342">
         <v>0</v>
@@ -10180,16 +10180,16 @@
         <v>1748195004</v>
       </c>
       <c r="D343">
-        <v>171426102</v>
+        <v>239803663</v>
       </c>
       <c r="E343">
         <v>1477787338</v>
       </c>
       <c r="F343">
-        <v>1649213440</v>
+        <v>1717591001</v>
       </c>
       <c r="G343">
-        <v>98981564</v>
+        <v>30604003</v>
       </c>
       <c r="H343">
         <v>0</v>
@@ -10258,10 +10258,10 @@
         <v>1515585000</v>
       </c>
       <c r="D346">
-        <v>479490000</v>
+        <v>307490000</v>
       </c>
       <c r="E346">
-        <v>1033939000</v>
+        <v>1205939000</v>
       </c>
       <c r="F346">
         <v>1513429000</v>
@@ -10284,16 +10284,16 @@
         <v>600000000</v>
       </c>
       <c r="D347">
-        <v>471000000</v>
+        <v>486559811</v>
       </c>
       <c r="E347">
         <v>0</v>
       </c>
       <c r="F347">
-        <v>471000000</v>
+        <v>486559811</v>
       </c>
       <c r="G347">
-        <v>129000000</v>
+        <v>113440189</v>
       </c>
       <c r="H347">
         <v>0</v>
@@ -10362,10 +10362,10 @@
         <v>141550000</v>
       </c>
       <c r="D350">
-        <v>37331800</v>
+        <v>0</v>
       </c>
       <c r="E350">
-        <v>80399800</v>
+        <v>117731600</v>
       </c>
       <c r="F350">
         <v>117731600</v>
@@ -10388,10 +10388,10 @@
         <v>2911760000</v>
       </c>
       <c r="D351">
-        <v>419270</v>
+        <v>0</v>
       </c>
       <c r="E351">
-        <v>1852494126</v>
+        <v>1852913396</v>
       </c>
       <c r="F351">
         <v>1852913396</v>
@@ -10414,16 +10414,16 @@
         <v>157500000</v>
       </c>
       <c r="D352">
-        <v>69043020</v>
+        <v>55910000</v>
       </c>
       <c r="E352">
-        <v>85286598</v>
+        <v>91286598</v>
       </c>
       <c r="F352">
-        <v>154329618</v>
+        <v>147196598</v>
       </c>
       <c r="G352">
-        <v>3170382</v>
+        <v>10303402</v>
       </c>
       <c r="H352">
         <v>0</v>
@@ -10440,16 +10440,16 @@
         <v>666259738</v>
       </c>
       <c r="D353">
-        <v>310633670</v>
+        <v>290474690</v>
       </c>
       <c r="E353">
-        <v>304220994</v>
+        <v>331512994</v>
       </c>
       <c r="F353">
-        <v>614854664</v>
+        <v>621987684</v>
       </c>
       <c r="G353">
-        <v>51405074</v>
+        <v>44272054</v>
       </c>
       <c r="H353">
         <v>0</v>
@@ -10521,13 +10521,13 @@
         <v>0</v>
       </c>
       <c r="E356">
-        <v>209356250</v>
+        <v>209831250</v>
       </c>
       <c r="F356">
-        <v>209356250</v>
+        <v>209831250</v>
       </c>
       <c r="G356">
-        <v>138043750</v>
+        <v>137568750</v>
       </c>
       <c r="H356">
         <v>0</v>
@@ -10599,13 +10599,13 @@
         <v>0</v>
       </c>
       <c r="E359">
-        <v>8198770641</v>
+        <v>8198778141</v>
       </c>
       <c r="F359">
-        <v>8198770641</v>
+        <v>8198778141</v>
       </c>
       <c r="G359">
-        <v>2516145372</v>
+        <v>2516137872</v>
       </c>
       <c r="H359">
         <v>0</v>
@@ -10648,10 +10648,10 @@
         <v>10532164202</v>
       </c>
       <c r="D361">
-        <v>25612237</v>
+        <v>0</v>
       </c>
       <c r="E361">
-        <v>9237257697</v>
+        <v>9262869934</v>
       </c>
       <c r="F361">
         <v>9262869934</v>
@@ -10752,10 +10752,10 @@
         <v>1523018104</v>
       </c>
       <c r="D365">
-        <v>811692</v>
+        <v>0</v>
       </c>
       <c r="E365">
-        <v>1305319126</v>
+        <v>1306130818</v>
       </c>
       <c r="F365">
         <v>1306130818</v>
@@ -10804,16 +10804,16 @@
         <v>57733681762</v>
       </c>
       <c r="D367">
-        <v>4418521812</v>
+        <v>4250118415</v>
       </c>
       <c r="E367">
-        <v>46941740179</v>
+        <v>47211689678</v>
       </c>
       <c r="F367">
-        <v>51360261991</v>
+        <v>51461808093</v>
       </c>
       <c r="G367">
-        <v>6373419771</v>
+        <v>6271873669</v>
       </c>
       <c r="H367">
         <v>0</v>
@@ -10830,16 +10830,16 @@
         <v>3072546373</v>
       </c>
       <c r="D368">
-        <v>48500000</v>
+        <v>55161500</v>
       </c>
       <c r="E368">
         <v>3017384626</v>
       </c>
       <c r="F368">
-        <v>3065884626</v>
+        <v>3072546126</v>
       </c>
       <c r="G368">
-        <v>6661747</v>
+        <v>247</v>
       </c>
       <c r="H368">
         <v>0</v>
@@ -10882,16 +10882,16 @@
         <v>1891862000</v>
       </c>
       <c r="D370">
-        <v>1516510290</v>
+        <v>1555098790</v>
       </c>
       <c r="E370">
         <v>336763000</v>
       </c>
       <c r="F370">
-        <v>1853273290</v>
+        <v>1891861790</v>
       </c>
       <c r="G370">
-        <v>38588710</v>
+        <v>210</v>
       </c>
       <c r="H370">
         <v>0</v>
@@ -10908,10 +10908,10 @@
         <v>2467762918</v>
       </c>
       <c r="D371">
-        <v>1704675436</v>
+        <v>1623934546</v>
       </c>
       <c r="E371">
-        <v>735371064</v>
+        <v>816111954</v>
       </c>
       <c r="F371">
         <v>2440046500</v>
@@ -11012,16 +11012,16 @@
         <v>1400000000</v>
       </c>
       <c r="D375">
-        <v>130786000</v>
+        <v>150151500</v>
       </c>
       <c r="E375">
-        <v>786074564</v>
+        <v>813074564</v>
       </c>
       <c r="F375">
-        <v>916860564</v>
+        <v>963226064</v>
       </c>
       <c r="G375">
-        <v>483139436</v>
+        <v>436773936</v>
       </c>
       <c r="H375">
         <v>0</v>
@@ -11116,16 +11116,16 @@
         <v>200000000</v>
       </c>
       <c r="D379">
-        <v>147528500</v>
+        <v>150080000</v>
       </c>
       <c r="E379">
         <v>49920000</v>
       </c>
       <c r="F379">
-        <v>197448500</v>
+        <v>200000000</v>
       </c>
       <c r="G379">
-        <v>2551500</v>
+        <v>0</v>
       </c>
       <c r="H379">
         <v>0</v>
@@ -11220,10 +11220,10 @@
         <v>140000000</v>
       </c>
       <c r="D383">
-        <v>12345375</v>
+        <v>1712500</v>
       </c>
       <c r="E383">
-        <v>52685105</v>
+        <v>63317980</v>
       </c>
       <c r="F383">
         <v>65030480</v>
@@ -11246,10 +11246,10 @@
         <v>350000000</v>
       </c>
       <c r="D384">
-        <v>44225500</v>
+        <v>21787750</v>
       </c>
       <c r="E384">
-        <v>239038962</v>
+        <v>261476712</v>
       </c>
       <c r="F384">
         <v>283264462</v>
@@ -11327,13 +11327,13 @@
         <v>0</v>
       </c>
       <c r="E387">
-        <v>132685000</v>
+        <v>134185000</v>
       </c>
       <c r="F387">
-        <v>132685000</v>
+        <v>134185000</v>
       </c>
       <c r="G387">
-        <v>38015000</v>
+        <v>36515000</v>
       </c>
       <c r="H387">
         <v>0</v>
@@ -11350,16 +11350,16 @@
         <v>24000000</v>
       </c>
       <c r="D388">
-        <v>0</v>
+        <v>7055400</v>
       </c>
       <c r="E388">
         <v>16944556</v>
       </c>
       <c r="F388">
-        <v>16944556</v>
+        <v>23999956</v>
       </c>
       <c r="G388">
-        <v>7055444</v>
+        <v>44</v>
       </c>
       <c r="H388">
         <v>0</v>
@@ -11431,13 +11431,13 @@
         <v>0</v>
       </c>
       <c r="E391">
-        <v>3515047926</v>
+        <v>3515085426</v>
       </c>
       <c r="F391">
-        <v>3515047926</v>
+        <v>3515085426</v>
       </c>
       <c r="G391">
-        <v>1024758992</v>
+        <v>1024721492</v>
       </c>
       <c r="H391">
         <v>0</v>
@@ -11636,16 +11636,16 @@
         <v>24766099376</v>
       </c>
       <c r="D399">
-        <v>5147498726</v>
+        <v>5107909611</v>
       </c>
       <c r="E399">
-        <v>16649309994</v>
+        <v>16791659009</v>
       </c>
       <c r="F399">
-        <v>21796808720</v>
+        <v>21899568620</v>
       </c>
       <c r="G399">
-        <v>2969290656</v>
+        <v>2866530756</v>
       </c>
       <c r="H399">
         <v>0</v>
@@ -11844,10 +11844,10 @@
         <v>690000000</v>
       </c>
       <c r="D407">
-        <v>250697176</v>
+        <v>240722176</v>
       </c>
       <c r="E407">
-        <v>438355433</v>
+        <v>448330433</v>
       </c>
       <c r="F407">
         <v>689052609</v>
@@ -12052,10 +12052,10 @@
         <v>316800000</v>
       </c>
       <c r="D415">
-        <v>18876000</v>
+        <v>0</v>
       </c>
       <c r="E415">
-        <v>223159150</v>
+        <v>242035150</v>
       </c>
       <c r="F415">
         <v>242035150</v>
@@ -12078,16 +12078,16 @@
         <v>2230000000</v>
       </c>
       <c r="D416">
-        <v>19315000</v>
+        <v>9815000</v>
       </c>
       <c r="E416">
-        <v>1167575903</v>
+        <v>1176134462</v>
       </c>
       <c r="F416">
-        <v>1186890903</v>
+        <v>1185949462</v>
       </c>
       <c r="G416">
-        <v>1043109097</v>
+        <v>1044050538</v>
       </c>
       <c r="H416">
         <v>0</v>
@@ -12104,10 +12104,10 @@
         <v>169400000</v>
       </c>
       <c r="D417">
-        <v>21012000</v>
+        <v>12576000</v>
       </c>
       <c r="E417">
-        <v>92270307</v>
+        <v>100706307</v>
       </c>
       <c r="F417">
         <v>113282307</v>
@@ -12182,16 +12182,16 @@
         <v>337750000</v>
       </c>
       <c r="D420">
-        <v>155899500</v>
+        <v>0</v>
       </c>
       <c r="E420">
-        <v>2609000</v>
+        <v>155386000</v>
       </c>
       <c r="F420">
-        <v>158508500</v>
+        <v>155386000</v>
       </c>
       <c r="G420">
-        <v>179241500</v>
+        <v>182364000</v>
       </c>
       <c r="H420">
         <v>0</v>
@@ -12211,13 +12211,13 @@
         <v>0</v>
       </c>
       <c r="E421">
-        <v>377611040</v>
+        <v>382836040</v>
       </c>
       <c r="F421">
-        <v>377611040</v>
+        <v>382836040</v>
       </c>
       <c r="G421">
-        <v>110384460</v>
+        <v>105159460</v>
       </c>
       <c r="H421">
         <v>0</v>
@@ -12315,13 +12315,13 @@
         <v>0</v>
       </c>
       <c r="E425">
-        <v>6570840938</v>
+        <v>6570957188</v>
       </c>
       <c r="F425">
-        <v>6570840938</v>
+        <v>6570957188</v>
       </c>
       <c r="G425">
-        <v>2070504773</v>
+        <v>2070388523</v>
       </c>
       <c r="H425">
         <v>0</v>
@@ -12367,13 +12367,13 @@
         <v>0</v>
       </c>
       <c r="E427">
-        <v>7627914985</v>
+        <v>7649854127</v>
       </c>
       <c r="F427">
-        <v>7627914985</v>
+        <v>7649854127</v>
       </c>
       <c r="G427">
-        <v>1751653507</v>
+        <v>1729714365</v>
       </c>
       <c r="H427">
         <v>0</v>
@@ -12520,16 +12520,16 @@
         <v>35753265515</v>
       </c>
       <c r="D433">
-        <v>5292331868</v>
+        <v>5089645368</v>
       </c>
       <c r="E433">
-        <v>22855480897</v>
+        <v>23081383848</v>
       </c>
       <c r="F433">
-        <v>28147812765</v>
+        <v>28171029216</v>
       </c>
       <c r="G433">
-        <v>7605452750</v>
+        <v>7582236299</v>
       </c>
       <c r="H433">
         <v>0</v>
@@ -13416,16 +13416,16 @@
         <v>10505111000</v>
       </c>
       <c r="D490">
-        <v>1110895000</v>
+        <v>1131934600</v>
       </c>
       <c r="E490">
         <v>9369091974</v>
       </c>
       <c r="F490">
-        <v>10479986974</v>
+        <v>10501026574</v>
       </c>
       <c r="G490">
-        <v>25124026</v>
+        <v>4084426</v>
       </c>
       <c r="H490">
         <v>0</v>
@@ -13598,10 +13598,10 @@
         <v>2312795000</v>
       </c>
       <c r="D497">
-        <v>1458809250</v>
+        <v>836393303</v>
       </c>
       <c r="E497">
-        <v>664649954</v>
+        <v>1287065901</v>
       </c>
       <c r="F497">
         <v>2123459204</v>
@@ -13624,16 +13624,16 @@
         <v>6189486656</v>
       </c>
       <c r="D498">
-        <v>4581223454</v>
+        <v>4554135205</v>
       </c>
       <c r="E498">
-        <v>1454949284</v>
+        <v>1502562998</v>
       </c>
       <c r="F498">
-        <v>6036172738</v>
+        <v>6056698203</v>
       </c>
       <c r="G498">
-        <v>153313918</v>
+        <v>132788453</v>
       </c>
       <c r="H498">
         <v>0</v>
@@ -13832,16 +13832,16 @@
         <v>7401091133</v>
       </c>
       <c r="D506">
-        <v>4074764751</v>
+        <v>4063997751</v>
       </c>
       <c r="E506">
-        <v>3138178801</v>
+        <v>3147878801</v>
       </c>
       <c r="F506">
-        <v>7212943552</v>
+        <v>7211876552</v>
       </c>
       <c r="G506">
-        <v>188147581</v>
+        <v>189214581</v>
       </c>
       <c r="H506">
         <v>0</v>
@@ -13858,10 +13858,10 @@
         <v>297500000</v>
       </c>
       <c r="D507">
-        <v>195485808</v>
+        <v>170461200</v>
       </c>
       <c r="E507">
-        <v>100610066</v>
+        <v>125634674</v>
       </c>
       <c r="F507">
         <v>296095874</v>
@@ -13884,10 +13884,10 @@
         <v>266250000</v>
       </c>
       <c r="D508">
-        <v>59208720</v>
+        <v>11884720</v>
       </c>
       <c r="E508">
-        <v>197077000</v>
+        <v>244401000</v>
       </c>
       <c r="F508">
         <v>256285720</v>
@@ -13910,16 +13910,16 @@
         <v>1350000000</v>
       </c>
       <c r="D509">
-        <v>491484000</v>
+        <v>530529000</v>
       </c>
       <c r="E509">
         <v>765693066</v>
       </c>
       <c r="F509">
-        <v>1257177066</v>
+        <v>1296222066</v>
       </c>
       <c r="G509">
-        <v>92822934</v>
+        <v>53777934</v>
       </c>
       <c r="H509">
         <v>0</v>
@@ -14014,10 +14014,10 @@
         <v>779776375</v>
       </c>
       <c r="D513">
-        <v>72370000</v>
+        <v>61185000</v>
       </c>
       <c r="E513">
-        <v>179420828</v>
+        <v>190605828</v>
       </c>
       <c r="F513">
         <v>251790828</v>
@@ -14040,10 +14040,10 @@
         <v>1015398125</v>
       </c>
       <c r="D514">
-        <v>191431060</v>
+        <v>96048560</v>
       </c>
       <c r="E514">
-        <v>751193570</v>
+        <v>846576070</v>
       </c>
       <c r="F514">
         <v>942624630</v>
@@ -14092,16 +14092,16 @@
         <v>492557625</v>
       </c>
       <c r="D516">
-        <v>243121800</v>
+        <v>247987800</v>
       </c>
       <c r="E516">
         <v>113864509</v>
       </c>
       <c r="F516">
-        <v>356986309</v>
+        <v>361852309</v>
       </c>
       <c r="G516">
-        <v>135571316</v>
+        <v>130705316</v>
       </c>
       <c r="H516">
         <v>0</v>
@@ -14118,16 +14118,16 @@
         <v>688578000</v>
       </c>
       <c r="D517">
-        <v>20742302</v>
+        <v>18257321</v>
       </c>
       <c r="E517">
-        <v>406718295</v>
+        <v>423816410</v>
       </c>
       <c r="F517">
-        <v>427460597</v>
+        <v>442073731</v>
       </c>
       <c r="G517">
-        <v>261117403</v>
+        <v>246504269</v>
       </c>
       <c r="H517">
         <v>0</v>
@@ -14144,10 +14144,10 @@
         <v>36180000</v>
       </c>
       <c r="D518">
-        <v>231574</v>
+        <v>0</v>
       </c>
       <c r="E518">
-        <v>13589974</v>
+        <v>13821548</v>
       </c>
       <c r="F518">
         <v>13821548</v>
@@ -14251,13 +14251,13 @@
         <v>12694</v>
       </c>
       <c r="E522">
-        <v>760835</v>
+        <v>773529</v>
       </c>
       <c r="F522">
-        <v>773529</v>
+        <v>786223</v>
       </c>
       <c r="G522">
-        <v>-773529</v>
+        <v>-786223</v>
       </c>
       <c r="H522">
         <v>0</v>
@@ -14277,13 +14277,13 @@
         <v>900000</v>
       </c>
       <c r="E523">
-        <v>116082625</v>
+        <v>116982625</v>
       </c>
       <c r="F523">
-        <v>116982625</v>
+        <v>117882625</v>
       </c>
       <c r="G523">
-        <v>-116982625</v>
+        <v>-117882625</v>
       </c>
       <c r="H523">
         <v>0</v>
@@ -14303,13 +14303,13 @@
         <v>534484</v>
       </c>
       <c r="E524">
-        <v>9851634000</v>
+        <v>9851687437</v>
       </c>
       <c r="F524">
-        <v>9852168484</v>
+        <v>9852221921</v>
       </c>
       <c r="G524">
-        <v>2312113413</v>
+        <v>2312059976</v>
       </c>
       <c r="H524">
         <v>0</v>
@@ -14407,13 +14407,13 @@
         <v>0</v>
       </c>
       <c r="E528">
-        <v>977286188</v>
+        <v>977738452</v>
       </c>
       <c r="F528">
-        <v>977286188</v>
+        <v>977738452</v>
       </c>
       <c r="G528">
-        <v>475399051</v>
+        <v>474946787</v>
       </c>
       <c r="H528">
         <v>0</v>
@@ -14459,13 +14459,13 @@
         <v>0</v>
       </c>
       <c r="E530">
-        <v>1447566245</v>
+        <v>1481500225</v>
       </c>
       <c r="F530">
-        <v>1447566245</v>
+        <v>1481500225</v>
       </c>
       <c r="G530">
-        <v>251182256</v>
+        <v>217248276</v>
       </c>
       <c r="H530">
         <v>0</v>
@@ -14534,16 +14534,16 @@
         <v>64530948695</v>
       </c>
       <c r="D533">
-        <v>14073538576</v>
+        <v>13296585317</v>
       </c>
       <c r="E533">
-        <v>45186661545</v>
+        <v>46097989378</v>
       </c>
       <c r="F533">
-        <v>59260200121</v>
+        <v>59394574695</v>
       </c>
       <c r="G533">
-        <v>5270748574</v>
+        <v>5136374000</v>
       </c>
       <c r="H533">
         <v>0</v>
@@ -14560,10 +14560,10 @@
         <v>5572131338</v>
       </c>
       <c r="D534">
-        <v>1641723068</v>
+        <v>0</v>
       </c>
       <c r="E534">
-        <v>3922283270</v>
+        <v>5564006338</v>
       </c>
       <c r="F534">
         <v>5564006338</v>
@@ -14612,10 +14612,10 @@
         <v>1674171093</v>
       </c>
       <c r="D536">
-        <v>887432993</v>
+        <v>0</v>
       </c>
       <c r="E536">
-        <v>786738100</v>
+        <v>1674171093</v>
       </c>
       <c r="F536">
         <v>1674171093</v>
@@ -14716,10 +14716,10 @@
         <v>11942308557</v>
       </c>
       <c r="D540">
-        <v>10157254386</v>
+        <v>10107202381</v>
       </c>
       <c r="E540">
-        <v>1465423268</v>
+        <v>1515475273</v>
       </c>
       <c r="F540">
         <v>11622677654</v>
@@ -14742,10 +14742,10 @@
         <v>2103744312</v>
       </c>
       <c r="D541">
-        <v>1078733574</v>
+        <v>978507947</v>
       </c>
       <c r="E541">
-        <v>836124871</v>
+        <v>936350498</v>
       </c>
       <c r="F541">
         <v>1914858445</v>
@@ -14924,10 +14924,10 @@
         <v>579713600</v>
       </c>
       <c r="D548">
-        <v>41760600</v>
+        <v>20880300</v>
       </c>
       <c r="E548">
-        <v>261309000</v>
+        <v>282189300</v>
       </c>
       <c r="F548">
         <v>303069600</v>
@@ -14941,25 +14941,25 @@
     </row>
     <row r="549" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A549" t="s">
-        <v>64</v>
+        <v>24</v>
       </c>
       <c r="B549">
-        <v>1539315000</v>
+        <v>0</v>
       </c>
       <c r="C549">
-        <v>1539315000</v>
+        <v>0</v>
       </c>
       <c r="D549">
-        <v>6368850</v>
+        <v>0</v>
       </c>
       <c r="E549">
-        <v>1061904767</v>
+        <v>0</v>
       </c>
       <c r="F549">
-        <v>1068273617</v>
+        <v>0</v>
       </c>
       <c r="G549">
-        <v>471041383</v>
+        <v>0</v>
       </c>
       <c r="H549">
         <v>0</v>
@@ -14967,25 +14967,25 @@
     </row>
     <row r="550" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A550" t="s">
-        <v>26</v>
+        <v>64</v>
       </c>
       <c r="B550">
-        <v>481250000</v>
+        <v>1539315000</v>
       </c>
       <c r="C550">
-        <v>481250000</v>
+        <v>1539315000</v>
       </c>
       <c r="D550">
-        <v>26512800</v>
+        <v>6356272</v>
       </c>
       <c r="E550">
-        <v>129685575</v>
+        <v>1062273617</v>
       </c>
       <c r="F550">
-        <v>156198375</v>
+        <v>1068629889</v>
       </c>
       <c r="G550">
-        <v>325051625</v>
+        <v>470685111</v>
       </c>
       <c r="H550">
         <v>0</v>
@@ -14993,25 +14993,25 @@
     </row>
     <row r="551" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A551" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B551">
-        <v>621687500</v>
+        <v>569621175</v>
       </c>
       <c r="C551">
-        <v>621687500</v>
+        <v>569621175</v>
       </c>
       <c r="D551">
-        <v>73450321</v>
+        <v>419319636</v>
       </c>
       <c r="E551">
-        <v>199481993</v>
+        <v>135741975</v>
       </c>
       <c r="F551">
-        <v>272932314</v>
+        <v>555061611</v>
       </c>
       <c r="G551">
-        <v>348755186</v>
+        <v>14559564</v>
       </c>
       <c r="H551">
         <v>0</v>
@@ -15019,25 +15019,25 @@
     </row>
     <row r="552" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A552" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B552">
-        <v>95700000</v>
+        <v>442974859</v>
       </c>
       <c r="C552">
-        <v>95700000</v>
+        <v>442974859</v>
       </c>
       <c r="D552">
-        <v>0</v>
+        <v>72953900</v>
       </c>
       <c r="E552">
-        <v>60750000</v>
+        <v>199978414</v>
       </c>
       <c r="F552">
-        <v>60750000</v>
+        <v>272932314</v>
       </c>
       <c r="G552">
-        <v>34950000</v>
+        <v>170042545</v>
       </c>
       <c r="H552">
         <v>0</v>
@@ -15045,25 +15045,25 @@
     </row>
     <row r="553" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A553" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B553">
-        <v>461706875</v>
+        <v>95700000</v>
       </c>
       <c r="C553">
-        <v>461706875</v>
+        <v>95700000</v>
       </c>
       <c r="D553">
-        <v>10067935</v>
+        <v>0</v>
       </c>
       <c r="E553">
-        <v>355919619</v>
+        <v>60750000</v>
       </c>
       <c r="F553">
-        <v>365987554</v>
+        <v>60750000</v>
       </c>
       <c r="G553">
-        <v>95719321</v>
+        <v>34950000</v>
       </c>
       <c r="H553">
         <v>0</v>
@@ -15071,25 +15071,25 @@
     </row>
     <row r="554" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A554" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B554">
-        <v>449070000</v>
+        <v>461706875</v>
       </c>
       <c r="C554">
-        <v>449070000</v>
+        <v>461706875</v>
       </c>
       <c r="D554">
-        <v>8679897</v>
+        <v>0</v>
       </c>
       <c r="E554">
-        <v>286519085</v>
+        <v>365987554</v>
       </c>
       <c r="F554">
-        <v>295198982</v>
+        <v>365987554</v>
       </c>
       <c r="G554">
-        <v>153871018</v>
+        <v>95719321</v>
       </c>
       <c r="H554">
         <v>0</v>
@@ -15097,25 +15097,25 @@
     </row>
     <row r="555" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A555" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B555">
-        <v>68288000</v>
+        <v>449070000</v>
       </c>
       <c r="C555">
-        <v>68288000</v>
+        <v>449070000</v>
       </c>
       <c r="D555">
-        <v>0</v>
+        <v>35545824</v>
       </c>
       <c r="E555">
-        <v>18485500</v>
+        <v>288969085</v>
       </c>
       <c r="F555">
-        <v>18485500</v>
+        <v>324514909</v>
       </c>
       <c r="G555">
-        <v>49802500</v>
+        <v>124555091</v>
       </c>
       <c r="H555">
         <v>0</v>
@@ -15123,25 +15123,25 @@
     </row>
     <row r="556" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A556" t="s">
-        <v>65</v>
+        <v>32</v>
       </c>
       <c r="B556">
-        <v>0</v>
+        <v>68288000</v>
       </c>
       <c r="C556">
-        <v>0</v>
+        <v>68288000</v>
       </c>
       <c r="D556">
         <v>0</v>
       </c>
       <c r="E556">
-        <v>25167921</v>
+        <v>18485500</v>
       </c>
       <c r="F556">
-        <v>25167921</v>
+        <v>18485500</v>
       </c>
       <c r="G556">
-        <v>-25167921</v>
+        <v>49802500</v>
       </c>
       <c r="H556">
         <v>0</v>
@@ -15149,25 +15149,25 @@
     </row>
     <row r="557" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A557" t="s">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="B557">
-        <v>10688916866</v>
+        <v>0</v>
       </c>
       <c r="C557">
-        <v>10688916866</v>
+        <v>0</v>
       </c>
       <c r="D557">
         <v>0</v>
       </c>
       <c r="E557">
-        <v>8586387573</v>
+        <v>25167921</v>
       </c>
       <c r="F557">
-        <v>8586387573</v>
+        <v>25167921</v>
       </c>
       <c r="G557">
-        <v>2102529293</v>
+        <v>-25167921</v>
       </c>
       <c r="H557">
         <v>0</v>
@@ -15175,25 +15175,25 @@
     </row>
     <row r="558" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A558" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B558">
-        <v>106116051</v>
+        <v>10688916866</v>
       </c>
       <c r="C558">
-        <v>106116051</v>
+        <v>10688916866</v>
       </c>
       <c r="D558">
         <v>0</v>
       </c>
       <c r="E558">
-        <v>74480389</v>
+        <v>8586435385</v>
       </c>
       <c r="F558">
-        <v>74480389</v>
+        <v>8586435385</v>
       </c>
       <c r="G558">
-        <v>31635662</v>
+        <v>2102481481</v>
       </c>
       <c r="H558">
         <v>0</v>
@@ -15201,25 +15201,25 @@
     </row>
     <row r="559" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A559" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B559">
-        <v>9218326343</v>
+        <v>106116051</v>
       </c>
       <c r="C559">
-        <v>9218326343</v>
+        <v>106116051</v>
       </c>
       <c r="D559">
         <v>0</v>
       </c>
       <c r="E559">
-        <v>8463642276</v>
+        <v>74480389</v>
       </c>
       <c r="F559">
-        <v>8463642276</v>
+        <v>74480389</v>
       </c>
       <c r="G559">
-        <v>754684067</v>
+        <v>31635662</v>
       </c>
       <c r="H559">
         <v>0</v>
@@ -15227,25 +15227,25 @@
     </row>
     <row r="560" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A560" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B560">
-        <v>58858990</v>
+        <v>9218326343</v>
       </c>
       <c r="C560">
-        <v>58858990</v>
+        <v>9218326343</v>
       </c>
       <c r="D560">
         <v>0</v>
       </c>
       <c r="E560">
-        <v>0</v>
+        <v>8463642276</v>
       </c>
       <c r="F560">
-        <v>0</v>
+        <v>8463642276</v>
       </c>
       <c r="G560">
-        <v>58858990</v>
+        <v>754684067</v>
       </c>
       <c r="H560">
         <v>0</v>
@@ -15253,25 +15253,25 @@
     </row>
     <row r="561" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A561" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B561">
-        <v>1422805953</v>
+        <v>58858990</v>
       </c>
       <c r="C561">
-        <v>1422805953</v>
+        <v>58858990</v>
       </c>
       <c r="D561">
         <v>0</v>
       </c>
       <c r="E561">
-        <v>1161324150</v>
+        <v>0</v>
       </c>
       <c r="F561">
-        <v>1161324150</v>
+        <v>0</v>
       </c>
       <c r="G561">
-        <v>261481803</v>
+        <v>58858990</v>
       </c>
       <c r="H561">
         <v>0</v>
@@ -15279,25 +15279,25 @@
     </row>
     <row r="562" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A562" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B562">
-        <v>13916758</v>
+        <v>1422805953</v>
       </c>
       <c r="C562">
-        <v>13916758</v>
+        <v>1422805953</v>
       </c>
       <c r="D562">
         <v>0</v>
       </c>
       <c r="E562">
-        <v>16639510</v>
+        <v>1161324150</v>
       </c>
       <c r="F562">
-        <v>16639510</v>
+        <v>1161324150</v>
       </c>
       <c r="G562">
-        <v>-2722752</v>
+        <v>261481803</v>
       </c>
       <c r="H562">
         <v>0</v>
@@ -15305,25 +15305,25 @@
     </row>
     <row r="563" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A563" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B563">
-        <v>1559682761</v>
+        <v>13916758</v>
       </c>
       <c r="C563">
-        <v>1559682761</v>
+        <v>13916758</v>
       </c>
       <c r="D563">
         <v>0</v>
       </c>
       <c r="E563">
-        <v>1497221547</v>
+        <v>16639510</v>
       </c>
       <c r="F563">
-        <v>1497221547</v>
+        <v>16639510</v>
       </c>
       <c r="G563">
-        <v>62461214</v>
+        <v>-2722752</v>
       </c>
       <c r="H563">
         <v>0</v>
@@ -15331,25 +15331,25 @@
     </row>
     <row r="564" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A564" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B564">
-        <v>3850588</v>
+        <v>1559682761</v>
       </c>
       <c r="C564">
-        <v>3850588</v>
+        <v>1559682761</v>
       </c>
       <c r="D564">
         <v>0</v>
       </c>
       <c r="E564">
-        <v>0</v>
+        <v>1497221547</v>
       </c>
       <c r="F564">
-        <v>0</v>
+        <v>1497221547</v>
       </c>
       <c r="G564">
-        <v>3850588</v>
+        <v>62461214</v>
       </c>
       <c r="H564">
         <v>0</v>
@@ -15357,25 +15357,25 @@
     </row>
     <row r="565" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A565" t="s">
-        <v>129</v>
+        <v>41</v>
       </c>
       <c r="B565">
-        <v>58631137904</v>
+        <v>3850588</v>
       </c>
       <c r="C565">
-        <v>58631137904</v>
+        <v>3850588</v>
       </c>
       <c r="D565">
-        <v>16788663430</v>
+        <v>0</v>
       </c>
       <c r="E565">
-        <v>36240333977</v>
+        <v>0</v>
       </c>
       <c r="F565">
-        <v>53028997407</v>
+        <v>0</v>
       </c>
       <c r="G565">
-        <v>5602140497</v>
+        <v>3850588</v>
       </c>
       <c r="H565">
         <v>0</v>
@@ -15383,27 +15383,53 @@
     </row>
     <row r="566" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A566" t="s">
+        <v>129</v>
+      </c>
+      <c r="B566">
+        <v>58540796438</v>
+      </c>
+      <c r="C566">
+        <v>58540796438</v>
+      </c>
+      <c r="D566">
+        <v>14497445266</v>
+      </c>
+      <c r="E566">
+        <v>38960135388</v>
+      </c>
+      <c r="F566">
+        <v>53457580654</v>
+      </c>
+      <c r="G566">
+        <v>5083215784</v>
+      </c>
+      <c r="H566">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="567" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A567" t="s">
         <v>130</v>
       </c>
-      <c r="B566">
-        <v>1110174662869</v>
-      </c>
-      <c r="C566">
-        <v>1110174662868</v>
-      </c>
-      <c r="D566">
-        <v>340147891521</v>
-      </c>
-      <c r="E566">
-        <v>669344219243</v>
-      </c>
-      <c r="F566">
-        <v>1009492110764</v>
-      </c>
-      <c r="G566">
-        <v>100682552104</v>
-      </c>
-      <c r="H566">
+      <c r="B567">
+        <v>1110076983303</v>
+      </c>
+      <c r="C567">
+        <v>1110076983302</v>
+      </c>
+      <c r="D567">
+        <v>312554209876</v>
+      </c>
+      <c r="E567">
+        <v>701637272085</v>
+      </c>
+      <c r="F567">
+        <v>1014191481961</v>
+      </c>
+      <c r="G567">
+        <v>95885501341</v>
+      </c>
+      <c r="H567">
         <v>1</v>
       </c>
     </row>
